--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -497,7 +497,7 @@
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -627,16 +627,16 @@
         <v>0.4881384780615803</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7453300462667705</v>
+        <v>0.7453299403682752</v>
       </c>
       <c r="N2" s="6" t="n">
         <v>0.944512198213405</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.15791772195673</v>
+        <v>2.157917375270766</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4671243893505963</v>
+        <v>0.4671243356621115</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.8744448065313644</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.378779795097108</v>
+        <v>2.378779440173198</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5005597607299823</v>
+        <v>0.5005597081878823</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.5637254242607663</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.9972191429973363</v>
+        <v>0.9972188943636113</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.259336835662711</v>
+        <v>0.2593367834044462</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.5590290012319978</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6237337059775929</v>
+        <v>0.6237339217573197</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1753618818292768</v>
+        <v>0.1753619338943113</v>
       </c>
     </row>
     <row r="6">
@@ -854,13 +854,13 @@
         <v>0.366891456181085</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5203395510118518</v>
+        <v>0.5203397099701246</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.451613969204115</v>
+        <v>1.451614175873486</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.348395710959795</v>
+        <v>0.3483957488494041</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.5517388278611113</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.435765431263782</v>
+        <v>2.435765759474704</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5089487926857919</v>
+        <v>0.5089488407346152</v>
       </c>
     </row>
     <row r="8">
@@ -966,7 +966,7 @@
         <v>0.1583917862990591</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3280487452047611</v>
+        <v>0.3280486318618989</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>0.4512040731422011</v>
@@ -1193,10 +1193,10 @@
         <v>0.08878792045808215</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.5812911115135011</v>
+        <v>0.5812909163307862</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1650304501888928</v>
+        <v>0.1650304022546838</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.2037243436122176</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1099146294422049</v>
+        <v>0.1099145489046669</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.03537226045148101</v>
+        <v>0.03537223540861345</v>
       </c>
     </row>
     <row r="14">
@@ -1361,10 +1361,10 @@
         <v>0.2885194493603942</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7936922544612015</v>
+        <v>0.7936920496356643</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2150178108135978</v>
+        <v>0.2150177645651059</v>
       </c>
     </row>
     <row r="16">
@@ -1473,10 +1473,10 @@
         <v>0.05427946128539696</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1410062744703764</v>
+        <v>0.1410061798194142</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.04495120441565881</v>
+        <v>0.04495117552138583</v>
       </c>
     </row>
     <row r="18">
@@ -1520,13 +1520,13 @@
         <v>0.007314092787185089</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.04026642984416395</v>
+        <v>0.04026654762137927</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1952767031705027</v>
+        <v>0.1952767809166733</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1755873764560663</v>
+        <v>0.1755874516619684</v>
       </c>
       <c r="O18" s="6" t="n">
         <v>0.7601331994161846</v>
@@ -1582,13 +1582,13 @@
         <v>0.1330625779350605</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1197624198477694</v>
+        <v>0.1197625212819105</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1651006665864259</v>
+        <v>0.1651005567720492</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05225536872158654</v>
+        <v>0.05225533566213381</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.2254968845405563</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4399273417975569</v>
+        <v>0.4399274748509472</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.129224241563815</v>
+        <v>0.1292242763449933</v>
       </c>
     </row>
     <row r="21">
@@ -1747,16 +1747,16 @@
         <v>0.007247417674119516</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1986825882951999</v>
+        <v>0.198682489784973</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0.08690246673796587</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.0547937359578432</v>
+        <v>0.05479381223738522</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.01794078211331973</v>
+        <v>0.01794080665146769</v>
       </c>
     </row>
     <row r="23">
@@ -1971,10 +1971,10 @@
         <v>0.1693260499886728</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6893424307734368</v>
+        <v>0.689342536654401</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1909839167976672</v>
+        <v>0.1909839416796411</v>
       </c>
     </row>
     <row r="27">
@@ -2021,7 +2021,7 @@
         <v>-0.06224587527861825</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1221689492968916</v>
+        <v>0.1221688618931907</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>0.1450423868300328</v>
@@ -2083,10 +2083,10 @@
         <v>0.09642996155702854</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3029702403603334</v>
+        <v>0.3029703963789445</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.09222345573826241</v>
+        <v>0.09222349933280616</v>
       </c>
     </row>
     <row r="29">
@@ -2133,16 +2133,16 @@
         <v>0.008719466889954175</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.03940837869111102</v>
+        <v>0.03940826053506052</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.01820616497162053</v>
+        <v>0.01820627835648403</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4198569938172687</v>
+        <v>0.4198571040581907</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1239531315064422</v>
+        <v>0.1239531605951993</v>
       </c>
     </row>
     <row r="30">
@@ -2307,10 +2307,10 @@
         <v>-0.006193290426003917</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4035103891183653</v>
+        <v>0.4035105067322227</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1196231696556525</v>
+        <v>0.1196232009303755</v>
       </c>
     </row>
     <row r="33">
@@ -2363,10 +2363,10 @@
         <v>0.04710404761015452</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5336082870885552</v>
+        <v>0.5336084269154799</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1532004828340117</v>
+        <v>0.1532005178817426</v>
       </c>
     </row>
     <row r="34">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5203395510118518</v>
+        <v>0.5203397099701246</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3280487452047611</v>
+        <v>0.3280486318618989</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.01820616497162053</v>
+        <v>0.01820627835648403</v>
       </c>
     </row>
     <row r="67">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.435765431263782</v>
+        <v>2.435765759474704</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.0547937359578432</v>
+        <v>0.05479381223738522</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.378779795097108</v>
+        <v>2.378779440173198</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1099146294422049</v>
+        <v>0.1099145489046669</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.15791772195673</v>
+        <v>2.157917375270766</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1410062744703764</v>
+        <v>0.1410061798194142</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.451613969204115</v>
+        <v>1.451614175873486</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1651006665864259</v>
+        <v>0.1651005567720492</v>
       </c>
     </row>
     <row r="77">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9972191429973363</v>
+        <v>0.9972188943636113</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7936922544612015</v>
+        <v>0.7936920496356643</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -497,7 +497,7 @@
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -633,10 +633,10 @@
         <v>0.944512198213405</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.157917375270766</v>
+        <v>2.15791772195673</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4671243356621115</v>
+        <v>0.4671243893505963</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.8744448065313644</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.378779440173198</v>
+        <v>2.378779795097108</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5005597081878823</v>
+        <v>0.5005597607299823</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.5637254242607663</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.9972188943636113</v>
+        <v>0.9972190186804661</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2593367834044462</v>
+        <v>0.2593368095335775</v>
       </c>
     </row>
     <row r="5">
@@ -795,16 +795,16 @@
         <v>0.1928076187977046</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4802257094488755</v>
+        <v>0.4802257991105585</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5590290012319978</v>
+        <v>0.5590289017695063</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6237339217573197</v>
+        <v>0.6237338138674491</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1753619338943113</v>
+        <v>0.175361907861793</v>
       </c>
     </row>
     <row r="6">
@@ -913,10 +913,10 @@
         <v>0.5517388278611113</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.435765759474704</v>
+        <v>2.435765431263782</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5089488407346152</v>
+        <v>0.5089487926857919</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.3280486318618989</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4512040731422011</v>
+        <v>0.4512039378031527</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1321644039101491</v>
+        <v>0.1321643687149938</v>
       </c>
     </row>
     <row r="9">
@@ -1019,7 +1019,7 @@
         <v>0.1182064142505757</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1902701886213711</v>
+        <v>0.1902702651932942</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>0.4483397004692005</v>
@@ -1078,7 +1078,7 @@
         <v>0.1673529052596574</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1623763819965536</v>
+        <v>0.1623764541829626</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>0.9591776451451504</v>
@@ -1137,10 +1137,10 @@
         <v>0.2168132542319201</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.16285366246064</v>
+        <v>1.162853893672241</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2932298254927455</v>
+        <v>0.2932298715753403</v>
       </c>
     </row>
     <row r="12">
@@ -1187,16 +1187,16 @@
         <v>0.1122617111097528</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1428870032344536</v>
+        <v>0.1428869012757517</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.08878792045808215</v>
+        <v>0.08878782792345064</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.5812909163307862</v>
+        <v>0.5812910139221377</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1650304022546838</v>
+        <v>0.1650304262217872</v>
       </c>
     </row>
     <row r="13">
@@ -1305,10 +1305,10 @@
         <v>0.01368141307688586</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2503372400309611</v>
+        <v>0.2503373718833106</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.07731421118809978</v>
+        <v>0.07731424905692452</v>
       </c>
     </row>
     <row r="15">
@@ -1361,10 +1361,10 @@
         <v>0.2885194493603942</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7936920496356643</v>
+        <v>0.7936922544612015</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2150177645651059</v>
+        <v>0.2150178108135978</v>
       </c>
     </row>
     <row r="16">
@@ -1473,10 +1473,10 @@
         <v>0.05427946128539696</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1410061798194142</v>
+        <v>0.1410062744703764</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.04495117552138583</v>
+        <v>0.04495120441565881</v>
       </c>
     </row>
     <row r="18">
@@ -1585,10 +1585,10 @@
         <v>0.1197625212819105</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1651005567720492</v>
+        <v>0.1651007764008232</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05225533566213381</v>
+        <v>0.05225540178104326</v>
       </c>
     </row>
     <row r="20">
@@ -1697,10 +1697,10 @@
         <v>0.1626148979427879</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2158053022501587</v>
+        <v>0.2158051927691715</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.06730369024238247</v>
+        <v>0.0673036582061497</v>
       </c>
     </row>
     <row r="22">
@@ -1747,16 +1747,16 @@
         <v>0.007247417674119516</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.198682489784973</v>
+        <v>0.1986825882951999</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0.08690246673796587</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.05479381223738522</v>
+        <v>0.0547937359578432</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.01794080665146769</v>
+        <v>0.01794078211331973</v>
       </c>
     </row>
     <row r="23">
@@ -1803,7 +1803,7 @@
         <v>0.1161354666506746</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>-0.01447869274886115</v>
+        <v>-0.01447861270925177</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>-0.04449221291586569</v>
@@ -2027,10 +2027,10 @@
         <v>0.1450423868300328</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.051395980825927</v>
+        <v>1.051395834782393</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2706223788952469</v>
+        <v>0.2706223487424162</v>
       </c>
     </row>
     <row r="28">
@@ -2083,10 +2083,10 @@
         <v>0.09642996155702854</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3029703963789445</v>
+        <v>0.3029702403603334</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.09222349933280616</v>
+        <v>0.09222345573826241</v>
       </c>
     </row>
     <row r="29">
@@ -2139,10 +2139,10 @@
         <v>0.01820627835648403</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4198571040581907</v>
+        <v>0.4198572142991297</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1239531605951993</v>
+        <v>0.1239531896839596</v>
       </c>
     </row>
     <row r="30">
@@ -2195,10 +2195,10 @@
         <v>-0.1012101463350646</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2704849791813029</v>
+        <v>0.270484884800172</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08306996293701974</v>
+        <v>0.08306993611750535</v>
       </c>
     </row>
     <row r="31">
@@ -2245,7 +2245,7 @@
         <v>-0.01299858296256096</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.01888197378021861</v>
+        <v>-0.01888190741478546</v>
       </c>
       <c r="N31" s="6" t="n">
         <v>-0.007482528813908207</v>
@@ -2304,13 +2304,13 @@
         <v>-0.02543494245029465</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.006193290426003917</v>
+        <v>-0.006193172486012921</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4035105067322227</v>
+        <v>0.4035103891183653</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1196232009303755</v>
+        <v>0.1196231696556525</v>
       </c>
     </row>
     <row r="33">
@@ -2360,13 +2360,13 @@
         <v>-0.02401358497993078</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.04710404761015452</v>
+        <v>0.04710398242607705</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5336084269154799</v>
+        <v>0.5336081472616561</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1532005178817426</v>
+        <v>0.1532004477862849</v>
       </c>
     </row>
     <row r="34">
@@ -2416,13 +2416,13 @@
         <v>-0.01276347617420259</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.05247213785370597</v>
+        <v>-0.05247207947855614</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2984601668750564</v>
+        <v>0.2984602764979605</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09096179924427661</v>
+        <v>0.09096182994587232</v>
       </c>
     </row>
   </sheetData>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.05247213785370597</v>
+        <v>-0.05247207947855614</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5590290012319978</v>
+        <v>0.5590289017695063</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.006193290426003917</v>
+        <v>-0.006193172486012921</v>
       </c>
     </row>
     <row r="65">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.04710404761015452</v>
+        <v>0.04710398242607705</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.435765759474704</v>
+        <v>2.435765431263782</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.05479381223738522</v>
+        <v>0.0547937359578432</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.378779440173198</v>
+        <v>2.378779795097108</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.157917375270766</v>
+        <v>2.15791772195673</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1410061798194142</v>
+        <v>0.1410062744703764</v>
       </c>
     </row>
     <row r="76">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1651005567720492</v>
+        <v>0.1651007764008232</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.16285366246064</v>
+        <v>1.162853893672241</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.051395980825927</v>
+        <v>1.051395834782393</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2158053022501587</v>
+        <v>0.2158051927691715</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9972188943636113</v>
+        <v>0.9972190186804661</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2503372400309611</v>
+        <v>0.2503373718833106</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7936920496356643</v>
+        <v>0.7936922544612015</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2704849791813029</v>
+        <v>0.270484884800172</v>
       </c>
     </row>
     <row r="82">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2984601668750564</v>
+        <v>0.2984602764979605</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,14 +490,14 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>219.46</v>
+        <v>221.75</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.02003259558285886</v>
+        <v>0.0104346724509059</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.03304464409614738</v>
+        <v>0.04717607552091985</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.01780916280325795</v>
+        <v>0.0437750208771408</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.008594192782064525</v>
+        <v>0.05902860999273973</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.04648938468019193</v>
+        <v>0.02174815116459095</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4881384780615803</v>
+        <v>0.5731436258361036</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7453299403682752</v>
+        <v>0.7444243205453247</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.944512198213405</v>
+        <v>0.9464236230117864</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.15791772195673</v>
+        <v>2.242750389735201</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4671243893505963</v>
+        <v>0.4801458326189951</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>61.35</v>
+        <v>93.75</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.02988079215067607</v>
+        <v>0.005685462050596612</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.03057281592717209</v>
+        <v>-0.003295742788007594</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.01237623793539</v>
+        <v>0.03878116343490312</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>-0.02881114053473155</v>
+        <v>0.1206071706456369</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.1528583260800356</v>
+        <v>0.1289739759922139</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4196277453949253</v>
+        <v>0.1979076390593539</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5354973879175204</v>
+        <v>0.5127211129727407</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8744448065313644</v>
+        <v>0.599344851705278</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.378779795097108</v>
+        <v>0.6105418140260654</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5005597607299823</v>
+        <v>0.1721701786943273</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>30.6</v>
+        <v>61.45</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.009388119582672827</v>
+        <v>0.001630029198135041</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.009901028117592858</v>
+        <v>0.04276260724102432</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.01576068731789237</v>
+        <v>0.02810775125161569</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.07670655521898428</v>
+        <v>-0.0384916146197154</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2171838156077872</v>
+        <v>-0.1043579621588262</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2271056958961459</v>
+        <v>0.4615434516770405</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.2596844761162502</v>
+        <v>0.4996813278805614</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5637254242607663</v>
+        <v>0.8113433306410325</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.9972190186804661</v>
+        <v>2.526315559045417</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2593368095335775</v>
+        <v>0.5220902047947917</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>93.22</v>
+        <v>30.08</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.007453119270541486</v>
+        <v>-0.01699347880003832</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.02642591426936192</v>
+        <v>-0.01570679157803201</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.008983676117955364</v>
+        <v>-0.04568529546778388</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.100460420590305</v>
+        <v>0.02278136959435928</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1102906412244469</v>
+        <v>0.2282564395602957</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.1928076187977046</v>
+        <v>0.2435746157401866</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4802257991105585</v>
+        <v>0.2292500020460762</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5590289017695063</v>
+        <v>0.524714544736294</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6237338138674491</v>
+        <v>0.9895518955489806</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.175361907861793</v>
+        <v>0.2577232538516481</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>55.47</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.006897822963563449</v>
+        <v>-0.004956214948297455</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.01481890551687148</v>
+        <v>0.04341186253094853</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.03180809063539325</v>
+        <v>-0.06531557884153549</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.01167243057223377</v>
+        <v>0.09954897105180693</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.04870519783401617</v>
+        <v>0.2678306452967101</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4008664274395921</v>
+        <v>-0.010796467515237</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.366891456181085</v>
+        <v>0.2967427273791896</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5203397099701246</v>
+        <v>0.4834908741925921</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.451614175873486</v>
+        <v>2.537353441782955</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3483957488494041</v>
+        <v>0.5236766722030373</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>68.59999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.01634642134453912</v>
+        <v>-0.003064755361482319</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.009529362427843746</v>
+        <v>0.02067181479468849</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.03529745626053449</v>
+        <v>0.03791292237319999</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.2724911643162278</v>
+        <v>0.0003618027895320175</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1633033246408868</v>
+        <v>-0.003244417928279675</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>-0.04606616324414392</v>
+        <v>0.4113898515118986</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2720522705606589</v>
+        <v>0.3495284420971356</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5517388278611113</v>
+        <v>0.5074531073530928</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.435765431263782</v>
+        <v>1.494206992214337</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5089487926857919</v>
+        <v>0.3561596880456934</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>29.68</v>
+        <v>29.43</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.006693402316203079</v>
+        <v>-0.008423180506383021</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.005420048947527345</v>
+        <v>0.0006800563708753149</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.02432609366411009</v>
+        <v>-0.03508195720735141</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.07536231503469604</v>
+        <v>0.03335676889778694</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2001617814220076</v>
+        <v>0.2136082600072486</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.193723085193934</v>
+        <v>0.2184819062520951</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1583917862990591</v>
+        <v>0.1527353434076113</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3280486318618989</v>
+        <v>0.2995161575452143</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4512039378031527</v>
+        <v>0.4582708346230018</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1321643687149938</v>
+        <v>0.1339991525424298</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>35.29</v>
+        <v>34.49</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.009542524344523629</v>
+        <v>-0.02266928921241695</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.004268683223799252</v>
+        <v>-0.0229461069716782</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.03394464563936128</v>
+        <v>-0.0630263408929832</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.05029769399269157</v>
+        <v>0.01143704462748518</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.05406216840020051</v>
+        <v>0.04105042458511865</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1182064142505757</v>
+        <v>0.1230603156882002</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1902702651932942</v>
+        <v>0.1606885349401852</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4483397004692005</v>
+        <v>0.4111126042120743</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6904249788721135</v>
+        <v>0.6399164021168819</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1912382607465002</v>
+        <v>0.1792536700955469</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.85</v>
+        <v>17.55</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.005016730764139776</v>
+        <v>-0.01680678644245936</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.004501965202319491</v>
+        <v>0.004004559305341049</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01305332186614905</v>
+        <v>-0.01071028954391251</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01305332186614905</v>
+        <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1464354997645521</v>
+        <v>0.1300708009544111</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.180951189962268</v>
+        <v>0.1937884494263038</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1673529052596574</v>
+        <v>0.1512541830499925</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1623764541829626</v>
+        <v>0.1569323968906651</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9591776451451504</v>
+        <v>0.9590839337089507</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2512898994340056</v>
+        <v>0.2512699485388745</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>38.59</v>
+        <v>38.09</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.002858643754161783</v>
+        <v>-0.01295672448880436</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01552631980494446</v>
+        <v>0.0220016014154194</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01525919117776198</v>
+        <v>0.003953651325999452</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.01981200915566128</v>
+        <v>-0.02006685877876491</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.09351088556103071</v>
+        <v>0.07842583470264253</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1498554118457829</v>
+        <v>0.1792833216527763</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1841654316169528</v>
+        <v>0.1668657395607682</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2168132542319201</v>
+        <v>0.2146520017298186</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.162853893672241</v>
+        <v>1.21221654013801</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2932298715753403</v>
+        <v>0.302994387475245</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>97.73999999999999</v>
+        <v>15.06</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.01491638116030158</v>
+        <v>0.005340512671900166</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.003771305109369183</v>
+        <v>0.01756758280615434</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.005038538444930962</v>
+        <v>0.009383400979011913</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.003284743387792721</v>
+        <v>0.01688048567972089</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1583313705288181</v>
+        <v>-0.04502219515139172</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1122617111097528</v>
+        <v>0.2037016851688676</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1428869012757517</v>
+        <v>0.2668181832038214</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.08878782792345064</v>
+        <v>0.3016940716764671</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.5812910139221377</v>
+        <v>0.8498631833467325</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1650304262217872</v>
+        <v>0.2275707630561989</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>116.7</v>
+        <v>116.29</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.007484307442663041</v>
+        <v>-0.00351324801573627</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.0139009426180039</v>
+        <v>-0.001288230184934847</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.0146943290202699</v>
+        <v>0.003538174592917276</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.002921934823884698</v>
+        <v>-0.007341020906103779</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.07736334266088796</v>
+        <v>0.05660551967227567</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1560178353256925</v>
+        <v>0.1848191452637473</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1422167624120596</v>
+        <v>0.153897073045729</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2037243436122176</v>
+        <v>0.1909607125154005</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1099145489046669</v>
+        <v>0.1033406421938192</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.03537223540861345</v>
+        <v>0.03332405286188345</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>45.23</v>
+        <v>70.5</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.01545492176092211</v>
+        <v>0.005706155985532257</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.02014732036936784</v>
+        <v>0.01526494126333278</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.002426127260285904</v>
+        <v>0.01511883510290613</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.0141255849701607</v>
+        <v>0.04212857959849203</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.1123954675842205</v>
+        <v>0.03754418270418358</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.231456447130798</v>
+        <v>0.06865791639961527</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.06393494770628649</v>
+        <v>0.2071311136351004</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.01368141307688586</v>
+        <v>0.192751466095765</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2503373718833106</v>
+        <v>0.832065027909989</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.07731424905692452</v>
+        <v>0.2236211119000799</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>14.98</v>
+        <v>95.61</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0</v>
+        <v>-0.02179248311818838</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.01079621124877539</v>
+        <v>-0.01361807170812246</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.006720391601231279</v>
+        <v>-0.02706824181928502</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.01697216617578001</v>
+        <v>-0.03091428074747959</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.09486403427188717</v>
+        <v>0.1148553897943507</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1751179743733882</v>
+        <v>0.09993724321283159</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2551433157371434</v>
+        <v>0.1307321854871586</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2885194493603942</v>
+        <v>0.07918025388020844</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7936922544612015</v>
+        <v>0.5566352450644616</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2150178108135978</v>
+        <v>0.1589435598331459</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>23.61</v>
+        <v>51.56</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01951824397191093</v>
+        <v>-0.01734324044675362</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.03828915095402396</v>
+        <v>-0.009794475216482468</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01330478040522554</v>
+        <v>-0.04376848805261113</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.02163565498895048</v>
+        <v>0.01556038818996175</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.08751734712130044</v>
+        <v>0.1833831015476446</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.2953580258851012</v>
+        <v>0.1121406008424071</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.02622849975170105</v>
+        <v>-0.01180007429698071</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.02987410656729828</v>
+        <v>0.02454640089488414</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3279046156830066</v>
+        <v>0.1654393010612316</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.09914661515915468</v>
+        <v>0.05235730424175644</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>52.47</v>
+        <v>44.4</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.009065147031542375</v>
+        <v>-0.01835060855091009</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01316526184593758</v>
+        <v>-0.01223580039433536</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.03156144471836231</v>
+        <v>-0.02802098885169768</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.07125360782123535</v>
+        <v>-0.0002251367162250384</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1772493062591676</v>
+        <v>0.1234818069734249</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.09952737264145961</v>
+        <v>0.1928026387769277</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>-0.01611525103707179</v>
+        <v>0.04792971830166737</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.05427946128539696</v>
+        <v>-0.003983145269362498</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1410062744703764</v>
+        <v>0.2378309020785621</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.04495120441565881</v>
+        <v>0.07371026926022806</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>70.09999999999999</v>
+        <v>23.3</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.01128354068463322</v>
+        <v>-0.0131300874746737</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.009213927412669687</v>
+        <v>-0.01977287385998405</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.01344513994209295</v>
+        <v>0.01040762257920358</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.03377084497825833</v>
+        <v>-0.002995361560078957</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.007314092787185089</v>
+        <v>0.1228915294968937</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.04026654762137927</v>
+        <v>0.2362540860897013</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1952767809166733</v>
+        <v>-0.008308481330474016</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1755874516619684</v>
+        <v>-0.003125456475774446</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7601331994161846</v>
+        <v>0.3055368915745547</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2073926049118651</v>
+        <v>0.0929401561551364</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>94.31</v>
+        <v>102.69</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.006112359940830148</v>
+        <v>-0.003106491488088947</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.00788975404231107</v>
+        <v>0.006962140234371583</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.0146275367179064</v>
+        <v>-0.02478632986428952</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.0007427811588600619</v>
+        <v>0.005089598529708139</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.06712509865041238</v>
+        <v>0.03372263163893297</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.02842610555348757</v>
+        <v>0.0419878288294635</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1330625779350605</v>
+        <v>0.2123954562364154</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1197625212819105</v>
+        <v>0.1469302592155111</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1651007764008232</v>
+        <v>0.2558126819896311</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05225540178104326</v>
+        <v>0.0788845026676257</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>118.89</v>
+        <v>117.16</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.008824785142069524</v>
+        <v>-0.01455123001447078</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.01865457786022151</v>
+        <v>0.004285959063126565</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.02485235256564056</v>
+        <v>-0.04398204206793876</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.04918427287947347</v>
+        <v>-0.05577045508403089</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.007844466552971774</v>
+        <v>-0.02407329709439876</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.04162412389746684</v>
+        <v>0.09332735089755406</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.152548021509092</v>
+        <v>0.1294364319319543</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2254968845405563</v>
+        <v>0.2045827874767097</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4399274748509472</v>
+        <v>0.4588693711927849</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1292242763449933</v>
+        <v>0.1341542785329011</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>103.01</v>
+        <v>93.45</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.005406947574044807</v>
+        <v>-0.009118870030902615</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01284136423080973</v>
+        <v>-0.01163412023279864</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.01548308477217875</v>
+        <v>-0.02959507801867722</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.03071842725463347</v>
+        <v>-0.01121579900570047</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.003675377267252533</v>
+        <v>0.03592177937965024</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.003271360890588992</v>
+        <v>0.03392204314916847</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1944321281314889</v>
+        <v>0.1324102407930428</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1626148979427879</v>
+        <v>0.1161078857933473</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2158051927691715</v>
+        <v>0.1678947412080691</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.0673036582061497</v>
+        <v>0.05309584914542542</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>13.91</v>
+        <v>13.74</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>-0.01222142905526868</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.008553092504847037</v>
+        <v>-0.008658000615553441</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.00713778585553293</v>
+        <v>-0.01927198096735661</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.0134752148168249</v>
+        <v>-0.03171246106921877</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.01237264040217023</v>
+        <v>0.01327428804803477</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.007247417674119516</v>
+        <v>0.03391137191464044</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1986825882951999</v>
+        <v>0.2144968470143387</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.08690246673796587</v>
+        <v>0.06154670808492257</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.0547937359578432</v>
+        <v>0.07214267737521896</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.01794078211331973</v>
+        <v>0.02349139240158005</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>185.16</v>
+        <v>51.65</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.008885577545388434</v>
+        <v>0.004668385123111074</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.008460971321501476</v>
+        <v>0.0213565718325528</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.0003778657185342649</v>
+        <v>0.0001936897046608266</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.03187695688184644</v>
+        <v>-0.03331459421916649</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1257296234906689</v>
+        <v>-0.02675707889788814</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1161354666506746</v>
+        <v>0.0860535195713199</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>-0.01447861270925177</v>
+        <v>0.1051131489625039</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>-0.04449221291586569</v>
+        <v>0.1734732029522175</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.6337350069137886</v>
+        <v>0.7237395483536759</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1777701369571916</v>
+        <v>0.1990129727113272</v>
       </c>
     </row>
     <row r="24">
@@ -1824,52 +1824,46 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>17.73</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.0144524865030432</v>
+        <v>-0.006876838623884662</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02044203488593266</v>
+        <v>0.01300598254682628</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.02044203488593266</v>
+        <v>-0.02722428267259203</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.01430205987110766</v>
+        <v>-0.07868153026351932</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1695250475390295</v>
+        <v>-0.003736736553439202</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.09647492013493686</v>
+        <v>0.03803535432700245</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>-0.06635072375293893</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>-0.1148278115608177</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>0.1891347903208516</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>0.05944161593507835</v>
-      </c>
+        <v>0.146043236247914</v>
+      </c>
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1880,46 +1874,52 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>69.8</v>
+        <v>181.44</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.00706976641789403</v>
+        <v>-0.02009073853493537</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.008522705413586351</v>
+        <v>-0.005154087159994547</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.03257101073349511</v>
+        <v>-0.02775690071435533</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.075986203259228</v>
+        <v>0.01898239317733474</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.01035014518890565</v>
+        <v>0.1221473170993184</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.001434807860750453</v>
+        <v>0.1209278543716448</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.14448049429888</v>
-      </c>
-      <c r="N25" s="6" t="inlineStr"/>
-      <c r="O25" s="6" t="inlineStr"/>
-      <c r="P25" s="6" t="inlineStr"/>
+        <v>-0.03286785537587311</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>-0.06278976854142315</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>0.5957773576357239</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>0.1685772653627926</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>51.41</v>
+        <v>41.48</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.001165754262055119</v>
+        <v>-0.000722688039264785</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.0001944442218833053</v>
+        <v>-0.02537598205371427</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.0121060925640234</v>
+        <v>-0.05340027770160571</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.03816652734160142</v>
+        <v>-0.04445980907532388</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.06048978982914732</v>
+        <v>-0.009787535292097083</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.0406418567450455</v>
+        <v>0.02547269189890633</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.09194054327125434</v>
+        <v>0.1031195595285788</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1693260499886728</v>
+        <v>0.09254299494347351</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.689342536654401</v>
+        <v>0.3201330946335528</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1909839416796411</v>
+        <v>0.09699817784937781</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>27.48</v>
+        <v>27.12</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.00109285167442974</v>
+        <v>-0.01310038970159433</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02760087333079153</v>
+        <v>-0.007683830408301673</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.04682623604031511</v>
+        <v>-0.04842102318479302</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.1034257786540864</v>
+        <v>-0.1122749094430804</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.01575933140599128</v>
+        <v>-0.01166179623163799</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.06224587527861825</v>
+        <v>-0.05029542739270942</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1221688618931907</v>
+        <v>0.1087970401907306</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1450423868300328</v>
+        <v>0.1332758672909025</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.051395834782393</v>
+        <v>1.113282362671004</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2706223487424162</v>
+        <v>0.2832733525844195</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>41.51</v>
+        <v>17.16</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.02695737294871714</v>
+        <v>-0.03214888378684766</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.03330229042639765</v>
+        <v>-0.01605508475178707</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.0450886322551205</v>
+        <v>-0.06331877001831143</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.04837232145847725</v>
+        <v>-0.02333522222728823</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.01546417263401134</v>
+        <v>0.1578947503895778</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.006398478637610339</v>
+        <v>0.07317073752604109</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.09531991582171817</v>
+        <v>-0.08771928045600341</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.09642996155702854</v>
+        <v>-0.1407110446950921</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3029702403603334</v>
+        <v>0.1729323112221912</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.09222345573826241</v>
+        <v>0.05460781038621199</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.44</v>
+        <v>17.16</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.003452323140870073</v>
+        <v>-0.01605508475178707</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.008527550723653965</v>
+        <v>-0.005793764782366151</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.013016386035272</v>
+        <v>-0.03323944521621924</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.05525452876500925</v>
+        <v>-0.07142855668407022</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.01218810199655018</v>
+        <v>0.002922222985211276</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.008719466889954175</v>
+        <v>0.01905071828562455</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.03940826053506052</v>
+        <v>0.02373572345061348</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.01820627835648403</v>
+        <v>-8.357845605255765e-05</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4198572142991297</v>
+        <v>0.4098849796206585</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1239531896839596</v>
+        <v>0.1213156784519334</v>
       </c>
     </row>
     <row r="30">
@@ -2154,51 +2154,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>16.31</v>
+        <v>129.48</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01091572514700989</v>
+        <v>0.008961224032384418</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.04842473472941466</v>
+        <v>0.02461021534670449</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.05885749926452066</v>
+        <v>0.008646885195705334</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.0354819862143021</v>
+        <v>-0.005606412323841625</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.0475272823135735</v>
+        <v>-0.01843295157301605</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.02868141840275684</v>
+        <v>-0.06680540240163191</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.004087442861224089</v>
+        <v>0.007660407937592817</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.1012101463350646</v>
+        <v>0.06986788981456415</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.270484884800172</v>
+        <v>0.5299655020369998</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08306993611750535</v>
+        <v>0.1522866919138737</v>
       </c>
     </row>
     <row r="31">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>55.33</v>
+        <v>15.95</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.001804049676538688</v>
+        <v>-0.0220723279255145</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.01374129671745949</v>
+        <v>-0.03157252736906435</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.009310593684391133</v>
+        <v>-0.08752859113493139</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.01040912211455169</v>
+        <v>-0.08333332419852169</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.01653033270928062</v>
+        <v>0.02903224575904106</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.01299858296256096</v>
+        <v>0.005976024804887681</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.01888190741478546</v>
+        <v>-0.02012509983426569</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.007482528813908207</v>
+        <v>-0.1119014683947063</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2224945164681267</v>
+        <v>0.2526502221993867</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.06925750347948578</v>
+        <v>0.07797810503918012</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>63.89</v>
+        <v>63.31</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.006067196593881219</v>
+        <v>-0.009078072028458894</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.009457373803900215</v>
+        <v>0.005080166475588621</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02428228292258927</v>
+        <v>-0.02359646901623169</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.04513531769795942</v>
+        <v>-0.05732582011442733</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.02562147800815673</v>
+        <v>-0.02057546455624515</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.01002273089448691</v>
+        <v>0.005752172328463034</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.02543494245029465</v>
+        <v>-0.02580215897017479</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.006193172486012921</v>
+        <v>-0.02009109023693756</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4035103891183653</v>
+        <v>0.4077769188820226</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1196231696556525</v>
+        <v>0.1207565357582043</v>
       </c>
     </row>
     <row r="33">
@@ -2322,51 +2322,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>128.33</v>
+        <v>54.32</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.003754425988755417</v>
+        <v>-0.0182541496982852</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.01366511356860123</v>
+        <v>0.001659600836208641</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.009518557727573596</v>
+        <v>-0.01254314938669776</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.02469980205786071</v>
+        <v>-0.014334982884739</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.04354794448729971</v>
+        <v>-0.02389940331692886</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.09326310074223132</v>
+        <v>-0.002293588105768074</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.02401358497993078</v>
+        <v>-0.03574380757106699</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.04710398242607705</v>
+        <v>-0.03228546299239932</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5336081472616561</v>
+        <v>0.2152013002279836</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1532004477862849</v>
+        <v>0.0671269184165213</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>117.34</v>
+        <v>116.29</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.01163892144999146</v>
+        <v>-0.008948316474629237</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.00390498049193666</v>
+        <v>0.0139506359757775</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.03128870636064018</v>
+        <v>-0.03075514534225099</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.07343653740192613</v>
+        <v>-0.08541093574537806</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.04841457577570973</v>
+        <v>-0.03987782134682116</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.07573626107622489</v>
+        <v>-0.04052365941679803</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.01276347617420259</v>
+        <v>-0.01394214562036611</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.05247207947855614</v>
+        <v>-0.07349030901966891</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2984602764979605</v>
+        <v>0.3202808921220555</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09096182994587232</v>
+        <v>0.09703911501598572</v>
       </c>
     </row>
   </sheetData>
@@ -2562,17 +2562,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.2724911643162278</v>
+        <v>0.1206071706456369</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1034257786540864</v>
+        <v>-0.1122749094430804</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.100460420590305</v>
+        <v>0.09954897105180693</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.075986203259228</v>
+        <v>-0.08541093574537806</v>
       </c>
     </row>
     <row r="19">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.07670655521898428</v>
+        <v>0.05902860999273973</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.07343653740192613</v>
+        <v>-0.08333332419852169</v>
       </c>
     </row>
     <row r="20">
@@ -3163,21 +3163,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.07536231503469604</v>
+        <v>0.04212857959849203</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.05525452876500925</v>
+        <v>-0.07868153026351932</v>
       </c>
     </row>
     <row r="21">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.07125360782123535</v>
+        <v>0.03335676889778694</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.04918427287947347</v>
+        <v>-0.07142855668407022</v>
       </c>
     </row>
     <row r="22">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.05029769399269157</v>
+        <v>0.02278136959435928</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.04837232145847725</v>
+        <v>-0.05732582011442733</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.03377084497825833</v>
+        <v>0.01898239317733474</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.04513531769795942</v>
+        <v>-0.05577045508403089</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.03187695688184644</v>
+        <v>0.01688048567972089</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.03816652734160142</v>
+        <v>-0.04445980907532388</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03071842725463347</v>
+        <v>0.01556038818996175</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.0354819862143021</v>
+        <v>-0.0384916146197154</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.02163565498895048</v>
+        <v>0.01143704462748518</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.02881114053473155</v>
+        <v>-0.03331459421916649</v>
       </c>
     </row>
     <row r="27"/>
@@ -3539,21 +3539,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2171838156077872</v>
+        <v>0.2678306452967101</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1528583260800356</v>
+        <v>-0.1043579621588262</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E32" s="11" t="n">
-        <v>0.2001617814220076</v>
+        <v>0.2282564395602957</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.09486403427188717</v>
+        <v>-0.04502219515139172</v>
       </c>
     </row>
     <row r="33">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1772493062591676</v>
+        <v>0.2136082600072486</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.06048978982914732</v>
+        <v>-0.03987782134682116</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1695250475390295</v>
+        <v>0.1833831015476446</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.04870519783401617</v>
+        <v>-0.02675707889788814</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1633033246408868</v>
+        <v>0.1578947503895778</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.04841457577570973</v>
+        <v>-0.02407329709439876</v>
       </c>
     </row>
     <row r="36">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1583313705288181</v>
+        <v>0.1300708009544111</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.04648938468019193</v>
+        <v>-0.02389940331692886</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1464354997645521</v>
+        <v>0.1289739759922139</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.04354794448729971</v>
+        <v>-0.02057546455624515</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1257296234906689</v>
+        <v>0.1234818069734249</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.02562147800815673</v>
+        <v>-0.01843295157301605</v>
       </c>
     </row>
     <row r="39">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1123954675842205</v>
+        <v>0.1228915294968937</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.01653033270928062</v>
+        <v>-0.01166179623163799</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1102906412244469</v>
+        <v>0.1221473170993184</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.01575933140599128</v>
+        <v>-0.009787535292097083</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4881384780615803</v>
+        <v>0.5731436258361036</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.09326310074223132</v>
+        <v>-0.06680540240163191</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4196277453949253</v>
+        <v>0.4615434516770405</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.07573626107622489</v>
+        <v>-0.05029542739270942</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4008664274395921</v>
+        <v>0.4113898515118986</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.06224587527861825</v>
+        <v>-0.04052365941679803</v>
       </c>
     </row>
     <row r="48">
@@ -4185,21 +4185,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.2953580258851012</v>
+        <v>0.2435746157401866</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.04606616324414392</v>
+        <v>-0.010796467515237</v>
       </c>
     </row>
     <row r="49">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.231456447130798</v>
+        <v>0.2362540860897013</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01299858296256096</v>
+        <v>-0.002293588105768074</v>
       </c>
     </row>
     <row r="50">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2271056958961459</v>
+        <v>0.2184819062520951</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01002273089448691</v>
+        <v>0.005752172328463034</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.193723085193934</v>
+        <v>0.2037016851688676</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.001434807860750453</v>
+        <v>0.005976024804887681</v>
       </c>
     </row>
     <row r="52">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1928076187977046</v>
+        <v>0.1979076390593539</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.003271360890588992</v>
+        <v>0.01905071828562455</v>
       </c>
     </row>
     <row r="53">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.180951189962268</v>
+        <v>0.1937884494263038</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.006398478637610339</v>
+        <v>0.02547269189890633</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1751179743733882</v>
+        <v>0.1928026387769277</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.007247417674119516</v>
+        <v>0.03391137191464044</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.944512198213405</v>
+        <v>0.9464236230117864</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1148278115608177</v>
+        <v>-0.1407110446950921</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8744448065313644</v>
+        <v>0.8113433306410325</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1012101463350646</v>
+        <v>-0.1119014683947063</v>
       </c>
     </row>
     <row r="61">
@@ -4651,21 +4651,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5637254242607663</v>
+        <v>0.599344851705278</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.05247207947855614</v>
+        <v>-0.07349030901966891</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5590289017695063</v>
+        <v>0.524714544736294</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.04449221291586569</v>
+        <v>-0.06278976854142315</v>
       </c>
     </row>
     <row r="63">
@@ -4741,21 +4741,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5517388278611113</v>
+        <v>0.5074531073530928</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.007482528813908207</v>
+        <v>-0.03228546299239932</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5203397099701246</v>
+        <v>0.4834908741925921</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.006193172486012921</v>
+        <v>-0.02009109023693756</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4483397004692005</v>
+        <v>0.4111126042120743</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.01368141307688586</v>
+        <v>-0.003983145269362498</v>
       </c>
     </row>
     <row r="66">
@@ -4876,21 +4876,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3280486318618989</v>
+        <v>0.3016940716764671</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4898,21 +4898,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.01820627835648403</v>
+        <v>-0.003125456475774446</v>
       </c>
     </row>
     <row r="67">
@@ -4921,21 +4921,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2885194493603942</v>
+        <v>0.2995161575452143</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.02987410656729828</v>
+        <v>-8.357845605255765e-05</v>
       </c>
     </row>
     <row r="68">
@@ -4966,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2254968845405563</v>
+        <v>0.2146520017298186</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.04710398242607705</v>
+        <v>0.02454640089488414</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.435765431263782</v>
+        <v>2.537353441782955</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.0547937359578432</v>
+        <v>0.07214267737521896</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.378779795097108</v>
+        <v>2.526315559045417</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1099145489046669</v>
+        <v>0.1033406421938192</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.15791772195673</v>
+        <v>2.242750389735201</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1410062744703764</v>
+        <v>0.1654393010612316</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.451614175873486</v>
+        <v>1.494206992214337</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1651007764008232</v>
+        <v>0.1678947412080691</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.162853893672241</v>
+        <v>1.21221654013801</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1891347903208516</v>
+        <v>0.1729323112221912</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.051395834782393</v>
+        <v>1.113282362671004</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5319,21 +5319,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2158051927691715</v>
+        <v>0.2152013002279836</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9972190186804661</v>
+        <v>0.9895518955489806</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2224945164681267</v>
+        <v>0.2378309020785621</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9591776451451504</v>
+        <v>0.9590839337089507</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5409,21 +5409,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2503373718833106</v>
+        <v>0.2526502221993867</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7936922544612015</v>
+        <v>0.8498631833467325</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.270484884800172</v>
+        <v>0.2558126819896311</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7601331994161846</v>
+        <v>0.832065027909989</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2984602764979605</v>
+        <v>0.3055368915745547</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -630,13 +630,13 @@
         <v>0.7444243205453247</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9464236230117864</v>
+        <v>0.9464234926647535</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.242750389735201</v>
+        <v>2.242750751522681</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4801458326189951</v>
+        <v>0.4801458876646763</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.599344851705278</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.6105418140260654</v>
+        <v>0.6105419195698931</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1721701786943273</v>
+        <v>0.1721702042996491</v>
       </c>
     </row>
     <row r="4">
@@ -742,13 +742,13 @@
         <v>0.4996813278805614</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8113433306410325</v>
+        <v>0.8113435343169997</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.526315559045417</v>
+        <v>2.526315173078137</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5220902047947917</v>
+        <v>0.5220901492621328</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.524714544736294</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.9895518955489806</v>
+        <v>0.989551519058524</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2577232538516481</v>
+        <v>0.2577231745170614</v>
       </c>
     </row>
     <row r="6">
@@ -913,10 +913,10 @@
         <v>0.5074531073530928</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.494206992214337</v>
+        <v>1.49420720678482</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3561596880456934</v>
+        <v>0.3561597269347179</v>
       </c>
     </row>
     <row r="8">
@@ -1025,10 +1025,10 @@
         <v>0.4111126042120743</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6399164021168819</v>
+        <v>0.6399166995644077</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1792536700955469</v>
+        <v>0.179253741393097</v>
       </c>
     </row>
     <row r="10">
@@ -1075,16 +1075,16 @@
         <v>0.1937884494263038</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1512541830499925</v>
+        <v>0.1512542550720384</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1569323968906651</v>
+        <v>0.156932469624917</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9590839337089507</v>
+        <v>0.959083725149908</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2512699485388745</v>
+        <v>0.2512699041365447</v>
       </c>
     </row>
     <row r="11">
@@ -1137,10 +1137,10 @@
         <v>0.2146520017298186</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.21221654013801</v>
+        <v>1.212216295076937</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.302994387475245</v>
+        <v>0.3029943393616286</v>
       </c>
     </row>
     <row r="12">
@@ -1305,10 +1305,10 @@
         <v>0.192751466095765</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.832065027909989</v>
+        <v>0.8320653911409102</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2236211119000799</v>
+        <v>0.223621192766386</v>
       </c>
     </row>
     <row r="15">
@@ -1361,10 +1361,10 @@
         <v>0.07918025388020844</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.5566352450644616</v>
+        <v>0.5566353417430951</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1589435598331459</v>
+        <v>0.1589435838261521</v>
       </c>
     </row>
     <row r="16">
@@ -1417,10 +1417,10 @@
         <v>0.02454640089488414</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1654393010612316</v>
+        <v>0.1654392005704004</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.05235730424175644</v>
+        <v>0.05235727399500356</v>
       </c>
     </row>
     <row r="17">
@@ -1585,10 +1585,10 @@
         <v>0.1469302592155111</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2558126819896311</v>
+        <v>0.2558125648209346</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.0788845026676257</v>
+        <v>0.07888446911392322</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.2045827874767097</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4588693711927849</v>
+        <v>0.4588690940054243</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1341542785329011</v>
+        <v>0.1341542067025605</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>0.1161078857933473</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1678947412080691</v>
+        <v>0.1678948525652504</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.05309584914542542</v>
+        <v>0.05309588261584519</v>
       </c>
     </row>
     <row r="22">
@@ -1753,10 +1753,10 @@
         <v>0.06154670808492257</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.07214267737521896</v>
+        <v>0.07214259759072483</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.02349139240158005</v>
+        <v>0.02349136701355814</v>
       </c>
     </row>
     <row r="23">
@@ -1909,16 +1909,16 @@
         <v>0.1209278543716448</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.03286785537587311</v>
+        <v>-0.03286793403672172</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.06278976854142315</v>
+        <v>-0.06278969467261308</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5957773576357239</v>
+        <v>0.5957774647140706</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1685772653627926</v>
+        <v>0.1685772915003816</v>
       </c>
     </row>
     <row r="26">
@@ -1965,16 +1965,16 @@
         <v>0.02547269189890633</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1031195595285788</v>
+        <v>0.1031196714379743</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.09254299494347351</v>
+        <v>0.09254288516975784</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.3201330946335528</v>
+        <v>0.3201327740902831</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.09699817784937781</v>
+        <v>0.0969980890615092</v>
       </c>
     </row>
     <row r="27">
@@ -2139,10 +2139,10 @@
         <v>-8.357845605255765e-05</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4098849796206585</v>
+        <v>0.4098852005636544</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1213156784519334</v>
+        <v>0.1213157370257025</v>
       </c>
     </row>
     <row r="30">
@@ -2195,10 +2195,10 @@
         <v>0.06986788981456415</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5299655020369998</v>
+        <v>0.5299656399644517</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1522866919138737</v>
+        <v>0.1522867265403542</v>
       </c>
     </row>
     <row r="31">
@@ -2304,7 +2304,7 @@
         <v>-0.02580215897017479</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.02009109023693756</v>
+        <v>-0.0200909745220561</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>0.4077769188820226</v>
@@ -2360,7 +2360,7 @@
         <v>-0.03574380757106699</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.03228546299239932</v>
+        <v>-0.03228552875739865</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>0.2152013002279836</v>
@@ -2413,16 +2413,16 @@
         <v>-0.04052365941679803</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.01394214562036611</v>
+        <v>-0.01394220941034607</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07349030901966891</v>
+        <v>-0.07349036533771847</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.3202808921220555</v>
+        <v>0.3202807777604251</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09703911501598572</v>
+        <v>0.09703908334111344</v>
       </c>
     </row>
   </sheetData>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9464236230117864</v>
+        <v>0.9464234926647535</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8113433306410325</v>
+        <v>0.8113435343169997</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.07349030901966891</v>
+        <v>-0.07349036533771847</v>
       </c>
     </row>
     <row r="62">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.06278976854142315</v>
+        <v>-0.06278969467261308</v>
       </c>
     </row>
     <row r="63">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.03228546299239932</v>
+        <v>-0.03228552875739865</v>
       </c>
     </row>
     <row r="64">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.02009109023693756</v>
+        <v>-0.0200909745220561</v>
       </c>
     </row>
     <row r="65">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.07214267737521896</v>
+        <v>0.07214259759072483</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.526315559045417</v>
+        <v>2.526315173078137</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.242750389735201</v>
+        <v>2.242750751522681</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1654393010612316</v>
+        <v>0.1654392005704004</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.494206992214337</v>
+        <v>1.49420720678482</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1678947412080691</v>
+        <v>0.1678948525652504</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.21221654013801</v>
+        <v>1.212216295076937</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9895518955489806</v>
+        <v>0.989551519058524</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9590839337089507</v>
+        <v>0.959083725149908</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2558126819896311</v>
+        <v>0.2558125648209346</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.832065027909989</v>
+        <v>0.8320653911409102</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,14 +489,14 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>221.75</v>
+        <v>220.22</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.0104346724509059</v>
+        <v>-0.006899656276423305</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.04717607552091985</v>
+        <v>0.03007628110060567</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.0437750208771408</v>
+        <v>0.02176032324024102</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.05902860999273973</v>
+        <v>0.05172167659689131</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.02174815116459095</v>
+        <v>0.0327815299593015</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5731436258361036</v>
+        <v>0.5216644966515624</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7444243205453247</v>
+        <v>0.737033156191875</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9464234926647535</v>
+        <v>0.9263144582651097</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.242750751522681</v>
+        <v>2.220376885947061</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4801458876646763</v>
+        <v>0.4767338623692459</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>93.75</v>
+        <v>94.59</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.005685462050596612</v>
+        <v>0.008959960937499956</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.003295742788007594</v>
+        <v>0.001800446645223719</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.03878116343490312</v>
+        <v>0.04369413223526619</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1206071706456369</v>
+        <v>0.1306477671209041</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1289739759922139</v>
+        <v>0.159049082593594</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.1979076390593539</v>
+        <v>0.2128139737581181</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5127211129727407</v>
+        <v>0.5172839929971509</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.599344851705278</v>
+        <v>0.6002990436296112</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.6105419195698931</v>
+        <v>0.6249720992784673</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1721702042996491</v>
+        <v>0.1756606152132174</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>61.45</v>
+        <v>61.58</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.001630029198135041</v>
+        <v>0.002115558445910271</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.04276260724102432</v>
+        <v>0.03687493625042815</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.02810775125161569</v>
+        <v>0.02993813159588843</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.0384916146197154</v>
+        <v>-0.03645748743421051</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.1043579621588262</v>
+        <v>-0.08594330828969865</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.4615434516770405</v>
+        <v>0.4118002853715799</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4996813278805614</v>
+        <v>0.5070258137050536</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8113435343169997</v>
+        <v>0.8142422285870663</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.526315173078137</v>
+        <v>2.533775298925485</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5220901492621328</v>
+        <v>0.5231627501243163</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>30.08</v>
+        <v>68.92</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.01699347880003832</v>
+        <v>0.009668854556987183</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01570679157803201</v>
+        <v>0.0255952574228222</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.04568529546778388</v>
+        <v>-0.02874860402829027</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.02278136959435928</v>
+        <v>0.1101803501311918</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2282564395602957</v>
+        <v>0.3040681203177928</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2435746157401866</v>
+        <v>-0.006569947028688627</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2292500020460762</v>
+        <v>0.2775335654634903</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.524714544736294</v>
+        <v>0.5100553824592513</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.989551519058524</v>
+        <v>2.571555597728212</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2577231745170614</v>
+        <v>0.5285716656562596</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>68.26000000000001</v>
+        <v>29.73</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.004956214948297455</v>
+        <v>-0.01163565100922392</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.04341186253094853</v>
+        <v>-0.037864080606406</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.06531557884153549</v>
+        <v>-0.05318471645166578</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.09954897105180693</v>
+        <v>0.01088064251902332</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2678306452967101</v>
+        <v>0.192060902390021</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>-0.010796467515237</v>
+        <v>0.2037968636109266</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.2967427273791896</v>
+        <v>0.2338859865898426</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4834908741925921</v>
+        <v>0.4991245935544233</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.537353441782955</v>
+        <v>0.9664021640276326</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5236766722030373</v>
+        <v>0.2528260675180238</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>55.3</v>
+        <v>55.25</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.003064755361482319</v>
+        <v>-0.0009041453481076767</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.02067181479468849</v>
+        <v>0.01880878602938685</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.03791292237319999</v>
+        <v>0.03174604644556056</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.0003618027895320175</v>
+        <v>-0.0005426696808847886</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.003244417928279675</v>
+        <v>0.01506521569404162</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.4113898515118986</v>
+        <v>0.3844939835244381</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3495284420971356</v>
+        <v>0.3540551567281418</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5074531073530928</v>
+        <v>0.4994307560286699</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.49420720678482</v>
+        <v>1.491951866565108</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3561597269347179</v>
+        <v>0.3557508429780571</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>29.43</v>
+        <v>29.18</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.008423180506383021</v>
+        <v>-0.008494733177288882</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.0006800563708753149</v>
+        <v>-0.02113381992798657</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.03508195720735141</v>
+        <v>-0.0366457767184335</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.03335676889778694</v>
+        <v>0.02457867886905474</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2136082600072486</v>
+        <v>0.170947039158893</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2184819062520951</v>
+        <v>0.1893293488772727</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1527353434076113</v>
+        <v>0.1610312365459976</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.2995161575452143</v>
+        <v>0.2823772999951131</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4582708346230018</v>
+        <v>0.4458830763321711</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1339991525424298</v>
+        <v>0.1307789748091848</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>34.49</v>
+        <v>34.22</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.02266928921241695</v>
+        <v>-0.007828368936619756</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.0229461069716782</v>
+        <v>-0.03714123975296557</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.0630263408929832</v>
+        <v>-0.0515521207305103</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.01143704462748518</v>
+        <v>0.00351914228597705</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.04105042458511865</v>
+        <v>0.02455088794498606</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1230603156882002</v>
+        <v>0.1142685851989163</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1606885349401852</v>
+        <v>0.1752344391846825</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4111126042120743</v>
+        <v>0.3968136913330629</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6399166995644077</v>
+        <v>0.6270785314958969</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.179253741393097</v>
+        <v>0.1761683942090591</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.55</v>
+        <v>15.01</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.01680678644245936</v>
+        <v>-0.003320065693340535</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.004004559305341049</v>
+        <v>0.01145553062978233</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.01071028954391251</v>
+        <v>0.003342258730439029</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>0.01350437566498819</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1300708009544111</v>
+        <v>-0.02595714617073452</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1937884494263038</v>
+        <v>0.1940684428877364</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1512542550720384</v>
+        <v>0.2726409453320229</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.156932469624917</v>
+        <v>0.3015880918089011</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.959083725149908</v>
+        <v>0.8437215160543292</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2512699041365447</v>
+        <v>0.2262107182723332</v>
       </c>
     </row>
     <row r="11">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>38.09</v>
+        <v>17.46</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01295672448880436</v>
+        <v>-0.00512821404560726</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0220016014154194</v>
+        <v>-0.0124435077435332</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.003953651325999452</v>
+        <v>-0.01578357893224813</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.02006685877876491</v>
+        <v>-0.00512821404560726</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.07842583470264253</v>
+        <v>0.107867946123211</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1792833216527763</v>
+        <v>0.1956803787486046</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1668657395607682</v>
+        <v>0.1432460841396141</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2146520017298186</v>
+        <v>0.1517094845100377</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.212216295076937</v>
+        <v>0.9490371244740736</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3029943393616286</v>
+        <v>0.2491273107603826</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>15.06</v>
+        <v>37.96</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.005340512671900166</v>
+        <v>-0.0034129973114847</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.01756758280615434</v>
+        <v>-0.002627490415398115</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.009383400979011913</v>
+        <v>-0.002627490415398115</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.01688048567972089</v>
+        <v>-0.02341136795518772</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.04502219515139172</v>
+        <v>0.05974314371525957</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2037016851688676</v>
+        <v>0.1816981992466382</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2668181832038214</v>
+        <v>0.1622345535353364</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.3016940716764671</v>
+        <v>0.2147401372874354</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8498631833467325</v>
+        <v>1.20466649525883</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2275707630561989</v>
+        <v>0.3015103737713016</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>116.29</v>
+        <v>115.61</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.00351324801573627</v>
+        <v>-0.005847452917897344</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.001288230184934847</v>
+        <v>-0.01263981359490518</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.003538174592917276</v>
+        <v>-0.01103508039939394</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.007341020906103779</v>
+        <v>-0.01314554754988329</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.05660551967227567</v>
+        <v>0.02600284253851926</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1848191452637473</v>
+        <v>0.1686040660438886</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.153897073045729</v>
+        <v>0.1463594665414287</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1909607125154005</v>
+        <v>0.1622589000060133</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1033406421938192</v>
+        <v>0.09688890973618824</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.03332405286188345</v>
+        <v>0.03130600968209163</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.005706155985532257</v>
+        <v>-0.01276597909048094</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.01526494126333278</v>
+        <v>-0.007840385456797327</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.01511883510290613</v>
+        <v>0.00129472500539185</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.04212857959849203</v>
+        <v>0.02882478794174514</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.03754418270418358</v>
+        <v>0.03347664563788655</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.06865791639961527</v>
+        <v>0.0713028669348228</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2071311136351004</v>
+        <v>0.2060643442867587</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.192751466095765</v>
+        <v>0.1782966913030686</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8320653911409102</v>
+        <v>0.8086771033682323</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.223621192766386</v>
+        <v>0.2183919294018835</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>95.61</v>
+        <v>23.21</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.02179248311818838</v>
+        <v>-0.003862667619522364</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01361807170812246</v>
+        <v>-0.001720469485047005</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.02706824181928502</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.03091428074747959</v>
+        <v>-0.006846459093494461</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1148553897943507</v>
+        <v>0.1433497515654822</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.09993724321283159</v>
+        <v>0.2326726750819328</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1307321854871586</v>
+        <v>-0.01487085723722847</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.07918025388020844</v>
+        <v>-0.009047764427338567</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.5566353417430951</v>
+        <v>0.3004941754835952</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1589435838261521</v>
+        <v>0.0915311577481801</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>51.56</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01734324044675362</v>
+        <v>-0.007425991841231938</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.009794475216482468</v>
+        <v>-0.02796267340306091</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.04376848805261113</v>
+        <v>-0.03742767977559569</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.01556038818996175</v>
+        <v>-0.03811070339210321</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1833831015476446</v>
+        <v>0.09432657045699999</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1121406008424071</v>
+        <v>0.110320408268195</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>-0.01180007429698071</v>
+        <v>0.1129092550156701</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.02454640089488414</v>
+        <v>0.07638685891994168</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1654392005704004</v>
+        <v>0.5450755884741521</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.05235727399500356</v>
+        <v>0.1560676368340097</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>44.4</v>
+        <v>44.38</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.01835060855091009</v>
+        <v>-0.0004504607449622444</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01223580039433536</v>
+        <v>-0.01530948816021893</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.02802098885169768</v>
+        <v>-0.02675432997433613</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.0002251367162250384</v>
+        <v>-0.0006754960459344206</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1234818069734249</v>
+        <v>0.1212733455028403</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1928026387769277</v>
+        <v>0.1989243848994251</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.04792971830166737</v>
+        <v>0.04704278466674361</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>-0.003983145269362498</v>
+        <v>-0.004994037550899777</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2378309020785621</v>
+        <v>0.2372733078482745</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.07371026926022806</v>
+        <v>0.07354902360360271</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>23.3</v>
+        <v>101.95</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.0131300874746737</v>
+        <v>-0.007206207766781381</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.01977287385998405</v>
+        <v>-0.0183901757258319</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.01040762257920358</v>
+        <v>-0.02978687503112964</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.002995361560078957</v>
+        <v>-0.002153285941527971</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1228915294968937</v>
+        <v>0.01402422936020775</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.2362540860897013</v>
+        <v>0.02870828683236559</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>-0.008308481330474016</v>
+        <v>0.2027127029446447</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>-0.003125456475774446</v>
+        <v>0.1523840832413315</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.3055368915745547</v>
+        <v>0.2467630348870549</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.0929401561551364</v>
+        <v>0.07628669723592041</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>102.69</v>
+        <v>51.39</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.003106491488088947</v>
+        <v>-0.003297167942486579</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.006962140234371583</v>
+        <v>-0.02578200209197279</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.02478632986428952</v>
+        <v>-0.04550521463588242</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.005089598529708139</v>
+        <v>0.0122119150343627</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.03372263163893297</v>
+        <v>0.1455639476248705</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0419878288294635</v>
+        <v>0.09529715699247321</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2123954562364154</v>
+        <v>-0.0009127931053714011</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1469302592155111</v>
+        <v>0.02437848923642871</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2558125648209346</v>
+        <v>0.1615965517993625</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.07888446911392322</v>
+        <v>0.05119940093778652</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>117.16</v>
+        <v>115.38</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.01455123001447078</v>
+        <v>-0.01519295282565003</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.004285959063126565</v>
+        <v>-0.01603278908888595</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.04398204206793876</v>
+        <v>-0.05858355457083908</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.05577045508403089</v>
+        <v>-0.07011609001652419</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.02407329709439876</v>
+        <v>-0.05099526636175022</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.09332735089755406</v>
+        <v>0.07112754525015075</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1294364319319543</v>
+        <v>0.1225223540100271</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2045827874767097</v>
+        <v>0.1931602794076064</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4588690940054243</v>
+        <v>0.4367047011694214</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1341542067025605</v>
+        <v>0.1283811892743656</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>93.45</v>
+        <v>51.15</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.009118870030902615</v>
+        <v>-0.009680541824369171</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01163412023279864</v>
+        <v>0.008875754559522386</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.02959507801867722</v>
+        <v>-0.01747982757217093</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.01121579900570047</v>
+        <v>-0.0426726327208351</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.03592177937965024</v>
+        <v>-0.03308128449001824</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.03392204314916847</v>
+        <v>0.06603169060666647</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1324102407930428</v>
+        <v>0.09602851625152664</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1161078857933473</v>
+        <v>0.1699513344312715</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1678948525652504</v>
+        <v>0.7070529242236894</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.05309588261584519</v>
+        <v>0.1951314139714617</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>13.74</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01222142905526868</v>
+        <v>-0.01444621207284569</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.008658000615553441</v>
+        <v>-0.03032222342622459</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.01927198096735661</v>
+        <v>-0.0406250158945719</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.03171246106921877</v>
+        <v>-0.02549998526754338</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.01327428804803477</v>
+        <v>0.007941641617161155</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.03391137191464044</v>
+        <v>0.01865052968560788</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2144968470143387</v>
+        <v>0.1119798416922515</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.06154670808492257</v>
+        <v>0.09934745280746471</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.07214259759072483</v>
+        <v>0.1510233055948207</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.02349136701355814</v>
+        <v>0.04800021657472886</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>51.65</v>
+        <v>13.58</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.004668385123111074</v>
+        <v>-0.01164482169413372</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.0213565718325528</v>
+        <v>-0.03000000544956749</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.0001936897046608266</v>
+        <v>-0.03276353556957279</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.03331459421916649</v>
+        <v>-0.04298799680871934</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.02675707889788814</v>
+        <v>-0.02020200143629136</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0860535195713199</v>
+        <v>0.01511914709147555</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1051131489625039</v>
+        <v>0.2013846962230066</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1734732029522175</v>
+        <v>0.06434459631979172</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.7237395483536759</v>
+        <v>0.05965776706651349</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1990129727113272</v>
+        <v>0.01950307945127538</v>
       </c>
     </row>
     <row r="24">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.006876838623884662</v>
+        <v>-0.01457014051755512</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.01300598254682628</v>
+        <v>-0.003501174069720281</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.02722428267259203</v>
+        <v>-0.05322250708349352</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.07868153026351932</v>
+        <v>-0.09210526982899869</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.003736736553439202</v>
+        <v>-0.02996308811723392</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.03803535432700245</v>
+        <v>0.01425388427947083</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.146043236247914</v>
+        <v>0.1384230204473664</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>181.44</v>
+        <v>178.99</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.02009073853493537</v>
+        <v>-0.01350306941840673</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.005154087159994547</v>
+        <v>-0.01420940533668502</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.02775690071435533</v>
+        <v>-0.03825691845595258</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.01898239317733474</v>
+        <v>0.005223003186127118</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1221473170993184</v>
+        <v>0.08735802703051698</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1209278543716448</v>
+        <v>0.1103859229630766</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.03286793403672172</v>
+        <v>-0.06317884417645825</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.06278969467261308</v>
+        <v>-0.0759588050054858</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5957774647140706</v>
+        <v>0.5742294651992472</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1685772915003816</v>
+        <v>0.1632936183862252</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>41.48</v>
+        <v>41.05</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.000722688039264785</v>
+        <v>-0.01036644913021134</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.02537598205371427</v>
+        <v>-0.0270206074130267</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.05340027770160571</v>
+        <v>-0.05762171848253173</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.04445980907532388</v>
+        <v>-0.05436536785641699</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.009787535292097083</v>
+        <v>-0.04245392442663642</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.02547269189890633</v>
+        <v>0.01235064644651729</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1031196714379743</v>
+        <v>0.09598567774998568</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.09254288516975784</v>
+        <v>0.08233916175879674</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.3201327740902831</v>
+        <v>0.3064480020629254</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.0969980890615092</v>
+        <v>0.09319434472891741</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>27.12</v>
+        <v>26.66</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01310038970159433</v>
+        <v>-0.01696168796410302</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.007683830408301673</v>
+        <v>-0.01659906871295413</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.04842102318479302</v>
+        <v>-0.07237299722584967</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.1122749094430804</v>
+        <v>-0.1273322254270119</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.01166179623163799</v>
+        <v>-0.04341589362702625</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.05029542739270942</v>
+        <v>-0.06575168042499135</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1087970401907306</v>
+        <v>0.1023361768088957</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1332758672909025</v>
+        <v>0.1209275357669852</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.113282362671004</v>
+        <v>1.077437681037072</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2832733525844195</v>
+        <v>0.2759764773421287</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>17.16</v>
+        <v>16.84</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.03214888378684766</v>
+        <v>-0.01864800102970154</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01605508475178707</v>
+        <v>-0.05233541256153806</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.06331877001831143</v>
+        <v>-0.07370737789296944</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.02333522222728823</v>
+        <v>-0.0415480680088669</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.1578947503895778</v>
+        <v>0.124916489793105</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.07317073752604109</v>
+        <v>0.04987526130912601</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.08771928045600341</v>
+        <v>-0.1037786411882528</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1407110446950921</v>
+        <v>-0.1563125789074752</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1729323112221912</v>
+        <v>0.1510594682747497</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05460781038621199</v>
+        <v>0.04801119176504409</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.16</v>
+        <v>16.86</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.01605508475178707</v>
+        <v>-0.01748247317763174</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.005793764782366151</v>
+        <v>-0.02317494862259262</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.03323944521621924</v>
+        <v>-0.04745763369381861</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.07142855668407022</v>
+        <v>-0.08766228203535575</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.002922222985211276</v>
+        <v>-0.02712056061301948</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.01905071828562455</v>
+        <v>0.001235191436549821</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.02373572345061348</v>
+        <v>0.004343008601483955</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-8.357845605255765e-05</v>
+        <v>-0.01613398525964471</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4098852005636544</v>
+        <v>0.3852367032808945</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1213157370257025</v>
+        <v>0.1147427676578674</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>129.48</v>
+        <v>127.93</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.008961224032384418</v>
+        <v>-0.01197092580714088</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.02461021534670449</v>
+        <v>0.009707998315391153</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.008646885195705334</v>
+        <v>-0.008678827741932182</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.005606412323841625</v>
+        <v>-0.01751022418500947</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.01843295157301605</v>
+        <v>-0.03802946830719878</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.06680540240163191</v>
+        <v>-0.08456481121160786</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.007660407937592817</v>
+        <v>-0.004254059964804546</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.06986788981456415</v>
+        <v>0.04913759823909492</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5299656399644517</v>
+        <v>0.5116505348009626</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1522867265403542</v>
+        <v>0.1476702765435471</v>
       </c>
     </row>
     <row r="31">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>15.95</v>
+        <v>53.71</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.0220723279255145</v>
+        <v>-0.01122976093112327</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.03157252736906435</v>
+        <v>-0.01359048058949652</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.08752859113493139</v>
+        <v>-0.01593995451438446</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.08333332419852169</v>
+        <v>-0.0254037653851148</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.02903224575904106</v>
+        <v>-0.03085527139968147</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.005976024804887681</v>
+        <v>-0.01893939921809218</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.02012509983426569</v>
+        <v>-0.0401593308811975</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1119014683947063</v>
+        <v>-0.04240616521652374</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2526502221993867</v>
+        <v>0.201554982682969</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.07797810503918012</v>
+        <v>0.06311737541665186</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>63.31</v>
+        <v>62.46</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.009078072028458894</v>
+        <v>-0.01342603491360772</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.005080166475588621</v>
+        <v>-0.01404892519471812</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02359646901623169</v>
+        <v>-0.03132760805360169</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.05732582011442733</v>
+        <v>-0.06998219656572757</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.02057546455624515</v>
+        <v>-0.04231833922987338</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.005752172328463034</v>
+        <v>-0.008350537110951239</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.02580215897017479</v>
+        <v>-0.04126702659353831</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.0200909745220561</v>
+        <v>-0.0294028415499048</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4077769188820226</v>
+        <v>0.3888760568185414</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1207565357582043</v>
+        <v>0.115718147375417</v>
       </c>
     </row>
     <row r="33">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>54.32</v>
+        <v>15.65</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.0182541496982852</v>
+        <v>-0.01880878961268684</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.001659600836208641</v>
+        <v>-0.05495168337919532</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.01254314938669776</v>
+        <v>-0.0995396792734955</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.014334982884739</v>
+        <v>-0.1005747148486327</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.02389940331692886</v>
+        <v>-0.006979734057996678</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.002293588105768074</v>
+        <v>-0.01471200125173777</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.03574380757106699</v>
+        <v>-0.03905676775704481</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.03228552875739865</v>
+        <v>-0.125710437581281</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2152013002279836</v>
+        <v>0.229089387711753</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.0671269184165213</v>
+        <v>0.07117679585362469</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>116.29</v>
+        <v>114.48</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.008948316474629237</v>
+        <v>-0.01556451581687168</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.0139506359757775</v>
+        <v>-0.004694777446469067</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.03075514534225099</v>
+        <v>-0.0471909953969003</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.08541093574537806</v>
+        <v>-0.09964607170190698</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.03987782134682116</v>
+        <v>-0.07907645720149559</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.04052365941679803</v>
+        <v>-0.05942799273549637</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.01394220941034607</v>
+        <v>-0.01989950214829994</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07349036533771847</v>
+        <v>-0.07444075368340874</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.3202807777604251</v>
+        <v>0.2997313592939082</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09703908334111344</v>
+        <v>0.09131770030397623</v>
       </c>
     </row>
   </sheetData>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1206071706456369</v>
+        <v>0.1306477671209041</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1122749094430804</v>
+        <v>-0.1273322254270119</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.09954897105180693</v>
+        <v>0.1101803501311918</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.08541093574537806</v>
+        <v>-0.1005747148486327</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05902860999273973</v>
+        <v>0.05172167659689131</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.08333332419852169</v>
+        <v>-0.09964607170190698</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04212857959849203</v>
+        <v>0.02882478794174514</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.07868153026351932</v>
+        <v>-0.09210526982899869</v>
       </c>
     </row>
     <row r="21">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.03335676889778694</v>
+        <v>0.02457867886905474</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.07142855668407022</v>
+        <v>-0.08766228203535575</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.02278136959435928</v>
+        <v>0.01350437566498819</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.05732582011442733</v>
+        <v>-0.07011609001652419</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.01898239317733474</v>
+        <v>0.0122119150343627</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.05577045508403089</v>
+        <v>-0.06998219656572757</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01688048567972089</v>
+        <v>0.01088064251902332</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.04445980907532388</v>
+        <v>-0.05436536785641699</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01556038818996175</v>
+        <v>0.005223003186127118</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.0384916146197154</v>
+        <v>-0.04298799680871934</v>
       </c>
     </row>
     <row r="26">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.01143704462748518</v>
+        <v>0.00351914228597705</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.03331459421916649</v>
+        <v>-0.0426726327208351</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2678306452967101</v>
+        <v>0.3040681203177928</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1043579621588262</v>
+        <v>-0.08594330828969865</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2282564395602957</v>
+        <v>0.192060902390021</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3606,21 +3606,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.04502219515139172</v>
+        <v>-0.07907645720149559</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2136082600072486</v>
+        <v>0.170947039158893</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.03987782134682116</v>
+        <v>-0.05099526636175022</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1833831015476446</v>
+        <v>0.159049082593594</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.02675707889788814</v>
+        <v>-0.04341589362702625</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1578947503895778</v>
+        <v>0.1455639476248705</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.02407329709439876</v>
+        <v>-0.04245392442663642</v>
       </c>
     </row>
     <row r="36">
@@ -3764,21 +3764,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1300708009544111</v>
+        <v>0.1433497515654822</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.02389940331692886</v>
+        <v>-0.04231833922987338</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1289739759922139</v>
+        <v>0.124916489793105</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.02057546455624515</v>
+        <v>-0.03802946830719878</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1234818069734249</v>
+        <v>0.1212733455028403</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.01843295157301605</v>
+        <v>-0.03308128449001824</v>
       </c>
     </row>
     <row r="39">
@@ -3899,21 +3899,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1228915294968937</v>
+        <v>0.107867946123211</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.01166179623163799</v>
+        <v>-0.03085527139968147</v>
       </c>
     </row>
     <row r="40">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1221473170993184</v>
+        <v>0.09432657045699999</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.009787535292097083</v>
+        <v>-0.02996308811723392</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5731436258361036</v>
+        <v>0.5216644966515624</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.06680540240163191</v>
+        <v>-0.08456481121160786</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4615434516770405</v>
+        <v>0.4118002853715799</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.05029542739270942</v>
+        <v>-0.06575168042499135</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4113898515118986</v>
+        <v>0.3844939835244381</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.04052365941679803</v>
+        <v>-0.05942799273549637</v>
       </c>
     </row>
     <row r="48">
@@ -4185,21 +4185,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.2435746157401866</v>
+        <v>0.2326726750819328</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.010796467515237</v>
+        <v>-0.01893939921809218</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2362540860897013</v>
+        <v>0.2128139737581181</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.002293588105768074</v>
+        <v>-0.01471200125173777</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E50" s="11" t="n">
-        <v>0.2184819062520951</v>
+        <v>0.2037968636109266</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.005752172328463034</v>
+        <v>-0.008350537110951239</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2037016851688676</v>
+        <v>0.1989243848994251</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.005976024804887681</v>
+        <v>-0.006569947028688627</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1979076390593539</v>
+        <v>0.1956803787486046</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.01905071828562455</v>
+        <v>0.001235191436549821</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1937884494263038</v>
+        <v>0.1940684428877364</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.02547269189890633</v>
+        <v>0.01235064644651729</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1928026387769277</v>
+        <v>0.1893293488772727</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.03391137191464044</v>
+        <v>0.01425388427947083</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9464234926647535</v>
+        <v>0.9263144582651097</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1407110446950921</v>
+        <v>-0.1563125789074752</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8113435343169997</v>
+        <v>0.8142422285870663</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1119014683947063</v>
+        <v>-0.125710437581281</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.599344851705278</v>
+        <v>0.6002990436296112</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4673,21 +4673,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.07349036533771847</v>
+        <v>-0.0759588050054858</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.524714544736294</v>
+        <v>0.5100553824592513</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4718,21 +4718,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.06278969467261308</v>
+        <v>-0.07444075368340874</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5074531073530928</v>
+        <v>0.4994307560286699</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.03228552875739865</v>
+        <v>-0.04240616521652374</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4834908741925921</v>
+        <v>0.4991245935544233</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.0200909745220561</v>
+        <v>-0.0294028415499048</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4111126042120743</v>
+        <v>0.3968136913330629</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4853,21 +4853,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.003983145269362498</v>
+        <v>-0.01613398525964471</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3016940716764671</v>
+        <v>0.3015880918089011</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.003125456475774446</v>
+        <v>-0.009047764427338567</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2995161575452143</v>
+        <v>0.2823772999951131</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-8.357845605255765e-05</v>
+        <v>-0.004994037550899777</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2146520017298186</v>
+        <v>0.2147401372874354</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.02454640089488414</v>
+        <v>0.02437848923642871</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.537353441782955</v>
+        <v>2.571555597728212</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.07214259759072483</v>
+        <v>0.05965776706651349</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.526315173078137</v>
+        <v>2.533775298925485</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1033406421938192</v>
+        <v>0.09688890973618824</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.242750751522681</v>
+        <v>2.220376885947061</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5184,21 +5184,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1654392005704004</v>
+        <v>0.1510233055948207</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.49420720678482</v>
+        <v>1.491951866565108</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1678948525652504</v>
+        <v>0.1510594682747497</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.212216295076937</v>
+        <v>1.20466649525883</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1729323112221912</v>
+        <v>0.1615965517993625</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.113282362671004</v>
+        <v>1.077437681037072</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2152013002279836</v>
+        <v>0.201554982682969</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.989551519058524</v>
+        <v>0.9664021640276326</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2378309020785621</v>
+        <v>0.229089387711753</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.959083725149908</v>
+        <v>0.9490371244740736</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5409,21 +5409,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2526502221993867</v>
+        <v>0.2372733078482745</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8498631833467325</v>
+        <v>0.8437215160543292</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2558125648209346</v>
+        <v>0.2467630348870549</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8320653911409102</v>
+        <v>0.8086771033682323</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3055368915745547</v>
+        <v>0.2997313592939082</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -495,7 +495,7 @@
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>220.22</v>
+        <v>216.83</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.006899656276423305</v>
+        <v>-0.01539369435499638</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.03007628110060567</v>
+        <v>0.007808542794468298</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.02176032324024102</v>
+        <v>0.000322971609120204</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.05172167659689131</v>
+        <v>0.03493870228696849</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.0327815299593015</v>
+        <v>0.04875454331828144</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5216644966515624</v>
+        <v>0.4821892746486622</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.737033156191875</v>
+        <v>0.6863427226642802</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9263144582651097</v>
+        <v>0.8772014578850098</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.220376885947061</v>
+        <v>2.170803034696446</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4767338623692459</v>
+        <v>0.4691171268057484</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>94.59</v>
+        <v>93.92</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.008959960937499956</v>
+        <v>-0.007083182100483087</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.001800446645223719</v>
+        <v>0</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.04369413223526619</v>
+        <v>0.03641575063280111</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1306477671209041</v>
+        <v>0.06836530834347299</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.159049082593594</v>
+        <v>0.1385622572575669</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2128139737581181</v>
+        <v>0.2166700335994858</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5172839929971509</v>
+        <v>0.496293143244847</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.6002990436296112</v>
+        <v>0.5584764045620914</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.6249720992784673</v>
+        <v>0.6134623374614829</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1756606152132174</v>
+        <v>0.1728782806203817</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>61.58</v>
+        <v>60.07</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.002115558445910271</v>
+        <v>-0.02452098232106548</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.03687493625042815</v>
+        <v>0.008393486697355845</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.02993813159588843</v>
+        <v>-0.02767884620039351</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.03645748743421051</v>
+        <v>-0.0345548293747624</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.08594330828969865</v>
+        <v>-0.07385138560672266</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.4118002853715799</v>
+        <v>0.3714289546311644</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5070258137050536</v>
+        <v>0.4520877590132177</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8142422285870663</v>
+        <v>0.7155114383298466</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.533775298925485</v>
+        <v>2.447124034593412</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5231627501243163</v>
+        <v>0.5106098197081832</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>68.92</v>
+        <v>29.35</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.009668854556987183</v>
+        <v>-0.01278167395282837</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.0255952574228222</v>
+        <v>-0.04985429066388325</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.02874860402829027</v>
+        <v>-0.05959624343367254</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.1101803501311918</v>
+        <v>-0.005758810083257848</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.3040681203177928</v>
+        <v>0.1974704246181354</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>-0.006569947028688627</v>
+        <v>0.1801574130898715</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2775335654634903</v>
+        <v>0.203574418652672</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5100553824592513</v>
+        <v>0.4891295312168098</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.571555597728212</v>
+        <v>0.9412680078045068</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5285716656562596</v>
+        <v>0.2474653723354814</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29.73</v>
+        <v>66.83</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.01163565100922392</v>
+        <v>-0.03032496217958924</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.037864080606406</v>
+        <v>-0.04172635678021164</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.05318471645166578</v>
+        <v>-0.066880769782656</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.01088064251902332</v>
+        <v>0.07030754806051287</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.192060902390021</v>
+        <v>0.3281002034252525</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2037968636109266</v>
+        <v>-0.04886918096839732</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.2338859865898426</v>
+        <v>0.2200064499375305</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4991245935544233</v>
+        <v>0.4351397597751889</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.9664021640276326</v>
+        <v>2.463247966989884</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2528260675180238</v>
+        <v>0.512961450821209</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>55.25</v>
+        <v>54.73</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.0009041453481076767</v>
+        <v>-0.009411772991197664</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.01880878602938685</v>
+        <v>-0.006534772360763053</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.03174604644556056</v>
+        <v>-0.01582451103141014</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.0005426696808847886</v>
+        <v>0.0003655722554991581</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.01506521569404162</v>
+        <v>0.03186271865644419</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3844939835244381</v>
+        <v>0.3714634404438271</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3540551567281418</v>
+        <v>0.3356183008536535</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4994307560286699</v>
+        <v>0.4722989475326125</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.491951866565108</v>
+        <v>1.468498181292006</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3557508429780571</v>
+        <v>0.3514840892206619</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>29.18</v>
+        <v>28.86</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.008494733177288882</v>
+        <v>-0.01096640477990185</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.02113381992798657</v>
+        <v>-0.03413649862997081</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.0366457767184335</v>
+        <v>-0.04310342319753335</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.02457867886905474</v>
+        <v>-0.0003463882435447152</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.170947039158893</v>
+        <v>0.1722176940124827</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1893293488772727</v>
+        <v>0.1848633017674182</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1610312365459976</v>
+        <v>0.1355692007078961</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.2823772999951131</v>
+        <v>0.2904003579804193</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4458830763321711</v>
+        <v>0.430027072404624</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1307789748091848</v>
+        <v>0.126630280939676</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>34.22</v>
+        <v>15.05</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.007828368936619756</v>
+        <v>0.00266488749121141</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.03714123975296557</v>
+        <v>0.004672940630015887</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.0515521207305103</v>
+        <v>0.005344016184305245</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.00351914228597705</v>
+        <v>0.03082190393887085</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.02455088794498606</v>
+        <v>-0.01311474159115655</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1142685851989163</v>
+        <v>0.1953783199421653</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1752344391846825</v>
+        <v>0.2649801620780308</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3968136913330629</v>
+        <v>0.3179039064268099</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6270785314958969</v>
+        <v>0.8486348264597399</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1761683942090591</v>
+        <v>0.2272989900050484</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>15.01</v>
+        <v>17.41</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.003320065693340535</v>
+        <v>-0.002863644884438243</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.01145553062978233</v>
+        <v>-0.02954295824235598</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.003342258730439029</v>
+        <v>-0.01471421775660608</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01350437566498819</v>
+        <v>-0.009670084017731173</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.02595714617073452</v>
+        <v>0.110331601311594</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1940684428877364</v>
+        <v>0.1954830762702375</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2726409453320229</v>
+        <v>0.1207554071204837</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3015880918089011</v>
+        <v>0.1541071947305719</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.8437215160543292</v>
+        <v>0.9434557742829932</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2262107182723332</v>
+        <v>0.2479338184438198</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>17.46</v>
+        <v>33.9</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.00512821404560726</v>
+        <v>-0.009351247323469369</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.0124435077435332</v>
+        <v>-0.0485545745263668</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.01578357893224813</v>
+        <v>-0.05042014561885233</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.00512821404560726</v>
+        <v>-0.01739126011945202</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.107867946123211</v>
+        <v>0.0244787358584424</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1956803787486046</v>
+        <v>0.08185426742076563</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1432460841396141</v>
+        <v>0.1485317117954628</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1517094845100377</v>
+        <v>0.3885900595457223</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.9490371244740736</v>
+        <v>0.6118634639127911</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2491273107603826</v>
+        <v>0.1724907281710009</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>37.96</v>
+        <v>38.05</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.0034129973114847</v>
+        <v>0.002370920831362922</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.002627490415398115</v>
+        <v>-0.01117464423833492</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.002627490415398115</v>
+        <v>0.003692940918278431</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.02341136795518772</v>
+        <v>-0.02159938713733889</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.05974314371525957</v>
+        <v>0.05900358791757032</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1816981992466382</v>
+        <v>0.183779179014786</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1622345535353364</v>
+        <v>0.1309299085251678</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2147401372874354</v>
+        <v>0.2190414116985373</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.20466649525883</v>
+        <v>1.209893340174876</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3015103737713016</v>
+        <v>0.3025381065254376</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>115.61</v>
+        <v>23.14</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.005847452917897344</v>
+        <v>-0.003015928375070365</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01263981359490518</v>
+        <v>-0.03903656715265247</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.01103508039939394</v>
+        <v>-0.0650505297111742</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.01314554754988329</v>
+        <v>-0.03462661441311077</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.02600284253851926</v>
+        <v>0.158158154144703</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1686040660438886</v>
+        <v>0.2569827314412803</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1463594665414287</v>
+        <v>-0.01716235923989506</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1622589000060133</v>
+        <v>-0.005117827126525643</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.09688890973618824</v>
+        <v>0.2965718396310955</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.03130600968209163</v>
+        <v>0.09043268730080145</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>69.59999999999999</v>
+        <v>44.23</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.01276597909048094</v>
+        <v>-0.003379935157024505</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.007840385456797327</v>
+        <v>-0.03722244526752083</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.00129472500539185</v>
+        <v>-0.04491474345440882</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.02882478794174514</v>
+        <v>-0.0111781803066614</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.03347664563788655</v>
+        <v>0.1341025523650341</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.0713028669348228</v>
+        <v>0.2071843458111289</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2060643442867587</v>
+        <v>0.03672641483706252</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1782966913030686</v>
+        <v>0.00661321331723741</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8086771033682323</v>
+        <v>0.23309140429623</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2183919294018835</v>
+        <v>0.07233814965617147</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>23.21</v>
+        <v>114.67</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.003862667619522364</v>
+        <v>-0.008130805608888458</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.001720469485047005</v>
+        <v>-0.0247491377512532</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0</v>
+        <v>-0.008645284134434106</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.006846459093494461</v>
+        <v>-0.0247491377512532</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1433497515654822</v>
+        <v>0.02192317177206959</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2326726750819328</v>
+        <v>0.1797325284897455</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>-0.01487085723722847</v>
+        <v>0.1284869943788229</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>-0.009047764427338567</v>
+        <v>0.1616176831447866</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3004941754835952</v>
+        <v>0.08797031923657772</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.0915311577481801</v>
+        <v>0.02850328353111542</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>94.90000000000001</v>
+        <v>69.87</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.007425991841231938</v>
+        <v>0.003879371815810106</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02796267340306091</v>
+        <v>-0.01452748599618747</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.03742767977559569</v>
+        <v>0.01143602916310571</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.03811070339210321</v>
+        <v>0.03007520065543279</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.09432657045699999</v>
+        <v>0.02827255170555354</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.110320408268195</v>
+        <v>0.0704364149384189</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1129092550156701</v>
+        <v>0.1925485905224431</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.07638685891994168</v>
+        <v>0.1938238200155009</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.5450755884741521</v>
+        <v>0.8156934543544372</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1560676368340097</v>
+        <v>0.2199653878817978</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>44.38</v>
+        <v>95.27</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.0004504607449622444</v>
+        <v>0.003898789370267775</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01530948816021893</v>
+        <v>-0.03981056771860347</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.02675432997433613</v>
+        <v>-0.02166770045043831</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.0006754960459344206</v>
+        <v>-0.02855106618202208</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1212733455028403</v>
+        <v>0.08433867495149783</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1989243848994251</v>
+        <v>0.1225108147668188</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.04704278466674361</v>
+        <v>0.117498613779444</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>-0.004994037550899777</v>
+        <v>0.08234184768062214</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2372733078482745</v>
+        <v>0.551099801759243</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.07354902360360271</v>
+        <v>0.1575681818089021</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>101.95</v>
+        <v>50.9</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.007206207766781381</v>
+        <v>-0.009534887518761748</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.0183901757258319</v>
+        <v>-0.03871575462743659</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.02978687503112964</v>
+        <v>-0.05372744637403781</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.002153285941527971</v>
+        <v>-0.01718477261856166</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.01402422936020775</v>
+        <v>0.1549807551248255</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.02870828683236559</v>
+        <v>0.1047573486181312</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2027127029446447</v>
+        <v>-0.02351753468937912</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1523840832413315</v>
+        <v>0.04007966357340242</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2467630348870549</v>
+        <v>0.1505208593357741</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.07628669723592041</v>
+        <v>0.04784770288738516</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>51.39</v>
+        <v>115.62</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.003297167942486579</v>
+        <v>0.002080130862171181</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.02578200209197279</v>
+        <v>-0.01892232292246276</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.04550521463588242</v>
+        <v>-0.04784647569786848</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.0122119150343627</v>
+        <v>-0.0626671732724895</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1455639476248705</v>
+        <v>-0.01440623005015074</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.09529715699247321</v>
+        <v>0.08632496234665288</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>-0.0009127931053714011</v>
+        <v>0.1090869331438717</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.02437848923642871</v>
+        <v>0.1992901856577523</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1615965517993625</v>
+        <v>0.4396932349581502</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05119940093778652</v>
+        <v>0.1291630409188225</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>115.38</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.01519295282565003</v>
+        <v>-0.01951935187187703</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.01603278908888595</v>
+        <v>-0.03485565917725852</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.05858355457083908</v>
+        <v>-0.04636520343923967</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.07011609001652419</v>
+        <v>-0.02828816549444546</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.05099526636175022</v>
+        <v>0.01979190479337234</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.07112754525015075</v>
+        <v>0.007740986795642391</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1225223540100271</v>
+        <v>0.1571510215984864</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1931602794076064</v>
+        <v>0.1256521256139795</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4367047011694214</v>
+        <v>0.2224269144544666</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1283811892743656</v>
+        <v>0.06923779369979077</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>51.15</v>
+        <v>50.56</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.009680541824369171</v>
+        <v>-0.01153470449633098</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.008875754559522386</v>
+        <v>-0.01768019867553594</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.01747982757217093</v>
+        <v>-0.03067481746168899</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.0426726327208351</v>
+        <v>-0.04855096059447828</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.03308128449001824</v>
+        <v>-0.01519280827772962</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.06603169060666647</v>
+        <v>0.0520050322252914</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.09602851625152664</v>
+        <v>0.06875486439054845</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1699513344312715</v>
+        <v>0.1456386299566759</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.7070529242236894</v>
+        <v>0.6873624657743871</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1951314139714617</v>
+        <v>0.190518444101202</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>92.06</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01444621207284569</v>
+        <v>-0.0004343204798052946</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.03032222342622459</v>
+        <v>-0.02982402623308911</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.0406250158945719</v>
+        <v>-0.02726121986151331</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.02549998526754338</v>
+        <v>-0.02167907490549403</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.007941641617161155</v>
+        <v>-0.004856837876985098</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.01865052968560788</v>
+        <v>0.02033492792622216</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1119798416922515</v>
+        <v>0.1056421939833359</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.09934745280746471</v>
+        <v>0.1105724039349083</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1510233055948207</v>
+        <v>0.150523282899621</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.04800021657472886</v>
+        <v>0.04784843864806421</v>
       </c>
     </row>
     <row r="23">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13.58</v>
+        <v>13.42</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01164482169413372</v>
+        <v>-0.01178202123056016</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.03000000544956749</v>
+        <v>-0.03522643971914396</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.03276353556957279</v>
+        <v>-0.03799281291883483</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.04298799680871934</v>
+        <v>-0.05225987140482968</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.02020200143629136</v>
+        <v>-0.01540719269139834</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.01511914709147555</v>
+        <v>0.01132684863074163</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2013846962230066</v>
+        <v>0.1662080777778689</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.06434459631979172</v>
+        <v>0.05824244349428498</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.05965776706651349</v>
+        <v>0.0471728567578078</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.01950307945127538</v>
+        <v>0.01548331524741675</v>
       </c>
     </row>
     <row r="24">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>68.31</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01457014051755512</v>
+        <v>-0.01039377997142577</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.003501174069720281</v>
+        <v>-0.02467175219602402</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.05322250708349352</v>
+        <v>-0.05215929944785302</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.09210526982899869</v>
+        <v>-0.09661904557021028</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.02996308811723392</v>
+        <v>-0.002655655184679029</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.01425388427947083</v>
+        <v>0.006851341803014277</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1384230204473664</v>
+        <v>0.1002396496157343</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>178.99</v>
+        <v>176.56</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01350306941840673</v>
+        <v>-0.01357622135311409</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.01420940533668502</v>
+        <v>-0.05491922365584301</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.03825691845595258</v>
+        <v>-0.05253559551526721</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.005223003186127118</v>
+        <v>-0.0117542038535231</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.08735802703051698</v>
+        <v>0.07836072904078573</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1103859229630766</v>
+        <v>0.1103022505644331</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.06317884417645825</v>
+        <v>-0.08744333506837643</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.0759588050054858</v>
+        <v>-0.09221892589380387</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5742294651992472</v>
+        <v>0.5528573775191077</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1632936183862252</v>
+        <v>0.1580052363881137</v>
       </c>
     </row>
     <row r="26">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>41.05</v>
+        <v>26.5</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.01036644913021134</v>
+        <v>-0.006001494685966446</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.0270206074130267</v>
+        <v>-0.03460840570256229</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.05762171848253173</v>
+        <v>-0.06821380090110818</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05436536785641699</v>
+        <v>-0.1317169199694774</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.04245392442663642</v>
+        <v>-0.02537699597296206</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.01235064644651729</v>
+        <v>-0.06580958780160029</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.09598567774998568</v>
+        <v>0.08649058546690025</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.08233916175879674</v>
+        <v>0.1006180386679365</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.3064480020629254</v>
+        <v>1.064969642923494</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.09319434472891741</v>
+        <v>0.2734187020279384</v>
       </c>
     </row>
     <row r="27">
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>26.66</v>
+        <v>40.66</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01696168796410302</v>
+        <v>-0.009500594321481537</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.01659906871295413</v>
+        <v>-0.04688232553102845</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.07237299722584967</v>
+        <v>-0.05748724101353164</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.1273322254270119</v>
+        <v>-0.05155118123478564</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.04341589362702625</v>
+        <v>-0.04977800940738741</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.06575168042499135</v>
+        <v>0.003718422553376399</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1023361768088957</v>
+        <v>0.08301271050303693</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1209275357669852</v>
+        <v>0.07456492761378652</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.077437681037072</v>
+        <v>0.2940358124899005</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2759764773421287</v>
+        <v>0.08972128005000202</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.84</v>
+        <v>16.69</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.01864800102970154</v>
+        <v>-0.008907340687121179</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.05233541256153806</v>
+        <v>-0.07226232649250031</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.07370737789296944</v>
+        <v>-0.08397359149050299</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.0415480680088669</v>
+        <v>-0.0538548122710425</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.124916489793105</v>
+        <v>0.1346023447162457</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.04987526130912601</v>
+        <v>0.04705150397853908</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1037786411882528</v>
+        <v>-0.128004124018722</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1563125789074752</v>
+        <v>-0.1502036123863457</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1510594682747497</v>
+        <v>0.1408065894396899</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.04801119176504409</v>
+        <v>0.04489024264544628</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16.86</v>
+        <v>16.76</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.01748247317763174</v>
+        <v>-0.005931220513024749</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02317494862259262</v>
+        <v>-0.03567312783790832</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.04745763369381861</v>
+        <v>-0.03511805301550486</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.08766228203535575</v>
+        <v>-0.09307355822295382</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.02712056061301948</v>
+        <v>-0.03009261788777262</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.001235191436549821</v>
+        <v>-0.007466591062862182</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.004343008601483955</v>
+        <v>-0.009467645054618612</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.01613398525964471</v>
+        <v>-0.009954350308763016</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3852367032808945</v>
+        <v>0.3770207747238143</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1147427676578674</v>
+        <v>0.112534525639465</v>
       </c>
     </row>
     <row r="30">
@@ -2154,51 +2154,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>127.93</v>
+        <v>53.83</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01197092580714088</v>
+        <v>0.002234271990831704</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.009707998315391153</v>
+        <v>-0.02886520774512236</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.008678827741932182</v>
+        <v>-0.01319885272366239</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.01751022418500947</v>
+        <v>-0.02162847358793629</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.03802946830719878</v>
+        <v>-0.0022242619126559</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.08456481121160786</v>
+        <v>-0.01521958717028571</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.004254059964804546</v>
+        <v>-0.05428703589151629</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.04913759823909492</v>
+        <v>-0.02721113806176578</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5116505348009626</v>
+        <v>0.2042395833262218</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1476702765435471</v>
+        <v>0.06390855093340386</v>
       </c>
     </row>
     <row r="31">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>53.71</v>
+        <v>62.1</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01122976093112327</v>
+        <v>-0.005763698617169188</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01359048058949652</v>
+        <v>-0.03391413109170605</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.01593995451438446</v>
+        <v>-0.02618789354954854</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.0254037653851148</v>
+        <v>-0.07216497548232015</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.03085527139968147</v>
+        <v>-0.02862508716281875</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.01893939921809218</v>
+        <v>-0.01257456728712769</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.0401593308811975</v>
+        <v>-0.06212753179860586</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.04240616521652374</v>
+        <v>-0.02432706184701983</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.201554982682969</v>
+        <v>0.3808709938104369</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.06311737541665186</v>
+        <v>0.1135704614894144</v>
       </c>
     </row>
     <row r="32">
@@ -2266,51 +2266,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
+          <t>Leisure</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="F32" s="5" t="n">
-        <v>62.46</v>
+        <v>15.61</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.01342603491360772</v>
+        <v>-0.002555908167925169</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01404892519471812</v>
+        <v>-0.05336568384811124</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03132760805360169</v>
+        <v>-0.08176472607780905</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.06998219656572757</v>
+        <v>-0.09191395161681359</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.04231833922987338</v>
+        <v>0.005798917284731919</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.008350537110951239</v>
+        <v>-0.005361044377918844</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.04126702659353831</v>
+        <v>-0.04944659985337752</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.0294028415499048</v>
+        <v>-0.1178974079072764</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3888760568185414</v>
+        <v>0.2259480399274361</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.115718147375417</v>
+        <v>0.07026343411159042</v>
       </c>
     </row>
     <row r="33">
@@ -2322,51 +2322,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>15.65</v>
+        <v>126.52</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01880878961268684</v>
+        <v>-0.01102168106578461</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.05495168337919532</v>
+        <v>-0.01040283024582045</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.0995396792734955</v>
+        <v>-0.01310452687338237</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.1005747148486327</v>
+        <v>-0.01945285716481926</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.006979734057996678</v>
+        <v>-0.04239089799429774</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.01471200125173777</v>
+        <v>-0.09108886959610107</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.03905676775704481</v>
+        <v>-0.01996836378877143</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.125710437581281</v>
+        <v>0.01421458718036517</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.229089387711753</v>
+        <v>0.4949894699491253</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.07117679585362469</v>
+        <v>0.1434382373693068</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>114.48</v>
+        <v>112.62</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01556451581687168</v>
+        <v>-0.01624738431001194</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.004694777446469067</v>
+        <v>-0.0290541872510901</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.0471909953969003</v>
+        <v>-0.05090174219719867</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.09964607170190698</v>
+        <v>-0.09976015891095913</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.07907645720149559</v>
+        <v>-0.06523904707294503</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.05942799273549637</v>
+        <v>-0.07412231750153953</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.01989950214829994</v>
+        <v>-0.05232480838429576</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07444075368340874</v>
+        <v>-0.09051718481263471</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2997313592939082</v>
+        <v>0.2786140136471962</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09131770030397623</v>
+        <v>0.08537501492171629</v>
       </c>
     </row>
   </sheetData>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1306477671209041</v>
+        <v>0.07030754806051287</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1273322254270119</v>
+        <v>-0.1317169199694774</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1101803501311918</v>
+        <v>0.06836530834347299</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1005747148486327</v>
+        <v>-0.09976015891095913</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05172167659689131</v>
+        <v>0.03493870228696849</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.09964607170190698</v>
+        <v>-0.09661904557021028</v>
       </c>
     </row>
     <row r="20">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.02882478794174514</v>
+        <v>0.03082190393887085</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09210526982899869</v>
+        <v>-0.09307355822295382</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.02457867886905474</v>
+        <v>0.03007520065543279</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08766228203535575</v>
+        <v>-0.09191395161681359</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01350437566498819</v>
+        <v>0.0003655722554991581</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.07011609001652419</v>
+        <v>-0.07216497548232015</v>
       </c>
     </row>
     <row r="23">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.0122119150343627</v>
+        <v>-0.0003463882435447152</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.06998219656572757</v>
+        <v>-0.0626671732724895</v>
       </c>
     </row>
     <row r="24">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01088064251902332</v>
+        <v>-0.005758810083257848</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.05436536785641699</v>
+        <v>-0.0538548122710425</v>
       </c>
     </row>
     <row r="25">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.005223003186127118</v>
+        <v>-0.009670084017731173</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.04298799680871934</v>
+        <v>-0.05225987140482968</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.00351914228597705</v>
+        <v>-0.0111781803066614</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.0426726327208351</v>
+        <v>-0.05155118123478564</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3040681203177928</v>
+        <v>0.3281002034252525</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.08594330828969865</v>
+        <v>-0.07385138560672266</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.192060902390021</v>
+        <v>0.1974704246181354</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.07907645720149559</v>
+        <v>-0.06523904707294503</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.170947039158893</v>
+        <v>0.1722176940124827</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.05099526636175022</v>
+        <v>-0.04977800940738741</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.159049082593594</v>
+        <v>0.158158154144703</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.04341589362702625</v>
+        <v>-0.04239089799429774</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1455639476248705</v>
+        <v>0.1549807551248255</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.04245392442663642</v>
+        <v>-0.03009261788777262</v>
       </c>
     </row>
     <row r="36">
@@ -3764,21 +3764,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1433497515654822</v>
+        <v>0.1385622572575669</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.04231833922987338</v>
+        <v>-0.02862508716281875</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.124916489793105</v>
+        <v>0.1346023447162457</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.03802946830719878</v>
+        <v>-0.02537699597296206</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1212733455028403</v>
+        <v>0.1341025523650341</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.03308128449001824</v>
+        <v>-0.01540719269139834</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.107867946123211</v>
+        <v>0.110331601311594</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03085527139968147</v>
+        <v>-0.01519280827772962</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.09432657045699999</v>
+        <v>0.08433867495149783</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
       <c r="K40" s="11" t="n">
-        <v>-0.02996308811723392</v>
+        <v>-0.01440623005015074</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5216644966515624</v>
+        <v>0.4821892746486622</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.08456481121160786</v>
+        <v>-0.09108886959610107</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4118002853715799</v>
+        <v>0.3714634404438271</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.06575168042499135</v>
+        <v>-0.07412231750153953</v>
       </c>
     </row>
     <row r="47">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3844939835244381</v>
+        <v>0.3714289546311644</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.05942799273549637</v>
+        <v>-0.06580958780160029</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.2326726750819328</v>
+        <v>0.2569827314412803</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.01893939921809218</v>
+        <v>-0.04886918096839732</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2128139737581181</v>
+        <v>0.2166700335994858</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01471200125173777</v>
+        <v>-0.01521958717028571</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2037968636109266</v>
+        <v>0.2071843458111289</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.008350537110951239</v>
+        <v>-0.01257456728712769</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.1989243848994251</v>
+        <v>0.1954830762702375</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.006569947028688627</v>
+        <v>-0.007466591062862182</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1956803787486046</v>
+        <v>0.1953783199421653</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.001235191436549821</v>
+        <v>-0.005361044377918844</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1940684428877364</v>
+        <v>0.1848633017674182</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.01235064644651729</v>
+        <v>0.003718422553376399</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1893293488772727</v>
+        <v>0.183779179014786</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.01425388427947083</v>
+        <v>0.006851341803014277</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9263144582651097</v>
+        <v>0.8772014578850098</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1563125789074752</v>
+        <v>-0.1502036123863457</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8142422285870663</v>
+        <v>0.7155114383298466</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.125710437581281</v>
+        <v>-0.1178974079072764</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.6002990436296112</v>
+        <v>0.5584764045620914</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.0759588050054858</v>
+        <v>-0.09221892589380387</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5100553824592513</v>
+        <v>0.4891295312168098</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.07444075368340874</v>
+        <v>-0.09051718481263471</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4994307560286699</v>
+        <v>0.4722989475326125</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.04240616521652374</v>
+        <v>-0.02721113806176578</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4991245935544233</v>
+        <v>0.4351397597751889</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.0294028415499048</v>
+        <v>-0.02432706184701983</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3968136913330629</v>
+        <v>0.3885900595457223</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.01613398525964471</v>
+        <v>-0.009954350308763016</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3015880918089011</v>
+        <v>0.3179039064268099</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.009047764427338567</v>
+        <v>-0.005117827126525643</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2823772999951131</v>
+        <v>0.2904003579804193</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.004994037550899777</v>
+        <v>0.00661321331723741</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2147401372874354</v>
+        <v>0.2190414116985373</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.02437848923642871</v>
+        <v>0.01421458718036517</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.571555597728212</v>
+        <v>2.463247966989884</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.05965776706651349</v>
+        <v>0.0471728567578078</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.533775298925485</v>
+        <v>2.447124034593412</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09688890973618824</v>
+        <v>0.08797031923657772</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.220376885947061</v>
+        <v>2.170803034696446</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5184,21 +5184,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1510233055948207</v>
+        <v>0.1408065894396899</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.491951866565108</v>
+        <v>1.468498181292006</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1510594682747497</v>
+        <v>0.1505208593357741</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.20466649525883</v>
+        <v>1.209893340174876</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1615965517993625</v>
+        <v>0.150523282899621</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.077437681037072</v>
+        <v>1.064969642923494</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.201554982682969</v>
+        <v>0.2042395833262218</v>
       </c>
     </row>
     <row r="79">
@@ -5342,21 +5342,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9664021640276326</v>
+        <v>0.9434557742829932</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.229089387711753</v>
+        <v>0.2224269144544666</v>
       </c>
     </row>
     <row r="80">
@@ -5387,21 +5387,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9490371244740736</v>
+        <v>0.9412680078045068</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5409,21 +5409,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2372733078482745</v>
+        <v>0.2259480399274361</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8437215160543292</v>
+        <v>0.8486348264597399</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2467630348870549</v>
+        <v>0.23309140429623</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8086771033682323</v>
+        <v>0.8156934543544372</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2997313592939082</v>
+        <v>0.2786140136471962</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,10 +489,10 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>216.83</v>
+        <v>221.02</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.01539369435499638</v>
+        <v>0.01932390539142692</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.007808542794468298</v>
+        <v>0.007108345533898053</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.000322971609120204</v>
+        <v>0.04038788237832547</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.03493870228696849</v>
+        <v>0.0501259228895754</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.04875454331828144</v>
+        <v>0.005458997853968306</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4821892746486622</v>
+        <v>0.4948164586635062</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.6863427226642802</v>
+        <v>0.7154974862849781</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8772014578850098</v>
+        <v>0.8864689486904751</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.170803034696446</v>
+        <v>2.211989506371251</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4691171268057484</v>
+        <v>0.4754507106976316</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>93.92</v>
+        <v>94.14</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.007083182100483087</v>
+        <v>0.002342432123001004</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0</v>
+        <v>0.009869107025295643</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.03641575063280111</v>
+        <v>0.03655582147082326</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.06836530834347299</v>
+        <v>0.06001578625805215</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1385622572575669</v>
+        <v>0.1535350898858778</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2166700335994858</v>
+        <v>0.1924058226806387</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.496293143244847</v>
+        <v>0.5074259472937388</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5584764045620914</v>
+        <v>0.5651810358294154</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.6134623374614829</v>
+        <v>0.636007085716392</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1728782806203817</v>
+        <v>0.1783158694835469</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>60.07</v>
+        <v>60.91</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.02452098232106548</v>
+        <v>0.01398368831122654</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.008393486697355845</v>
+        <v>-0.007171941934026038</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.02767884620039351</v>
+        <v>0.0231816075325566</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.0345548293747624</v>
+        <v>-0.02621901534215765</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.07385138560672266</v>
+        <v>-0.1182686995814436</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3714289546311644</v>
+        <v>0.3894458720846199</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4520877590132177</v>
+        <v>0.4827136892478403</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.7155114383298466</v>
+        <v>0.7300165274356081</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.447124034593412</v>
+        <v>2.502751086630683</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5106098197081832</v>
+        <v>0.5186921874370181</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>29.35</v>
+        <v>55.24</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.01278167395282837</v>
+        <v>0.00931851161147712</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.04985429066388325</v>
+        <v>-0.004146377089865427</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.05959624343367254</v>
+        <v>0.01061108365667418</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.005758810083257848</v>
+        <v>0.01098100833676119</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1974704246181354</v>
+        <v>0.004546281003259045</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.1801574130898715</v>
+        <v>0.3812320088927899</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.203574418652672</v>
+        <v>0.3544516143514955</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4891295312168098</v>
+        <v>0.4759561947599442</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.9412680078045068</v>
+        <v>1.476457904866404</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2474653723354814</v>
+        <v>0.3529351601574136</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>66.83</v>
+        <v>29.36</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.03032496217958924</v>
+        <v>0.0003407232964858231</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.04172635678021164</v>
+        <v>-0.04052286783202341</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.066880769782656</v>
+        <v>-0.03102305776824088</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.07030754806051287</v>
+        <v>-0.001360510499921919</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.3281002034252525</v>
+        <v>0.1650793540264506</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>-0.04886918096839732</v>
+        <v>0.1920569680882618</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.2200064499375305</v>
+        <v>0.1938707416704128</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4351397597751889</v>
+        <v>0.4624638519155564</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.463247966989884</v>
+        <v>0.9266944460403128</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.512961450821209</v>
+        <v>0.2443358545540013</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>54.73</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.009411772991197664</v>
+        <v>0.009426862728667773</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.006534772360763053</v>
+        <v>-0.01661806727413406</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.01582451103141014</v>
+        <v>-0.02598907011607232</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.0003655722554991581</v>
+        <v>0.08247752591172297</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.03186271865644419</v>
+        <v>0.274754372989751</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3714634404438271</v>
+        <v>-0.02086692991362549</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3356183008536535</v>
+        <v>0.1872218912119286</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4722989475326125</v>
+        <v>0.4333855756177889</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.468498181292006</v>
+        <v>2.461348218786648</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3514840892206619</v>
+        <v>0.5126847576190789</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>28.86</v>
+        <v>28.92</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.01096640477990185</v>
+        <v>0.002078983529919309</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.03413649862997081</v>
+        <v>-0.02560647645105663</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.04310342319753335</v>
+        <v>-0.02032521585926761</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.0003463882435447152</v>
+        <v>0.005563276986744636</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1722176940124827</v>
+        <v>0.1563374574821794</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1848633017674182</v>
+        <v>0.1951694920130669</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1355692007078961</v>
+        <v>0.1368180016370277</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.2904003579804193</v>
+        <v>0.2807453801241315</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.430027072404624</v>
+        <v>0.420646585700803</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.126630280939676</v>
+        <v>0.124161438825777</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>15.05</v>
+        <v>15.33</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.00266488749121141</v>
+        <v>0.01860463318422845</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.004672940630015887</v>
+        <v>0.02336451216055746</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.005344016184305245</v>
+        <v>0.03441297161834278</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.03082190393887085</v>
+        <v>0.0449897644157915</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.01311474159115655</v>
+        <v>-0.03402646287000921</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1953783199421653</v>
+        <v>0.2252819540275444</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2649801620780308</v>
+        <v>0.2844691270009263</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3179039064268099</v>
+        <v>0.3271805384029947</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.8486348264597399</v>
+        <v>0.8616504185354006</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2272989900050484</v>
+        <v>0.2301725843572566</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.41</v>
+        <v>17.48</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.002863644884438243</v>
+        <v>0.004020660277870292</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.02954295824235598</v>
+        <v>-0.02072833788942097</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.01471421775660608</v>
+        <v>-0.01631969094298158</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.009670084017731173</v>
+        <v>-0.01019254285000226</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.110331601311594</v>
+        <v>0.1042324463981414</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1954830762702375</v>
+        <v>0.2109407511963826</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1207554071204837</v>
+        <v>0.1105523543068292</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1541071947305719</v>
+        <v>0.1424568405485831</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9434557742829932</v>
+        <v>0.9457420463790664</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2479338184438198</v>
+        <v>0.2484229811401126</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>33.9</v>
+        <v>38.15</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.009351247323469369</v>
+        <v>0.002628181099172178</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.0485545745263668</v>
+        <v>-0.01140188196344116</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.05042014561885233</v>
+        <v>0.003947408575760702</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.01739126011945202</v>
+        <v>-0.02678569430165012</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.0244787358584424</v>
+        <v>0.04922994734542807</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.08185426742076563</v>
+        <v>0.1974549397560355</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1485317117954628</v>
+        <v>0.1271890104190208</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3885900595457223</v>
+        <v>0.2144489492875454</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6118634639127911</v>
+        <v>1.213561636710333</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1724907281710009</v>
+        <v>0.3032584210286067</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>38.05</v>
+        <v>33.91</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.002370920831362922</v>
+        <v>0.0002949357251671447</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.01117464423833492</v>
+        <v>-0.03910459145123013</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.003692940918278431</v>
+        <v>-0.03500283334093235</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.02159938713733889</v>
+        <v>-0.01021595129212571</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.05900358791757032</v>
+        <v>-0.001178230180513218</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.183779179014786</v>
+        <v>0.08657105558448408</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1309299085251678</v>
+        <v>0.1444574305701467</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2190414116985373</v>
+        <v>0.3836242622361901</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.209893340174876</v>
+        <v>0.6011830229949893</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3025381065254376</v>
+        <v>0.1698952892861243</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>23.14</v>
+        <v>23.22</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.003015928375070365</v>
+        <v>0.003457213734493036</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.03903656715265247</v>
+        <v>-0.01651847890364211</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.0650505297111742</v>
+        <v>-0.05417515132539363</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.03462661441311077</v>
+        <v>-0.02641513870183054</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.158158154144703</v>
+        <v>0.1662480909748785</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2569827314412803</v>
+        <v>0.2600788467442285</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>-0.01716235923989506</v>
+        <v>-0.01102787334591038</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>-0.005117827126525643</v>
+        <v>-0.006894166886446507</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2965718396310955</v>
+        <v>0.2889267194365044</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09043268730080145</v>
+        <v>0.08828524800218363</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>44.23</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.003379935157024505</v>
+        <v>0.01474164503803843</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.03722244526752083</v>
+        <v>0.01141231197106451</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.04491474345440882</v>
+        <v>0.02073139159784643</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.0111781803066614</v>
+        <v>0.04065763076662932</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.1341025523650341</v>
+        <v>0.01779714776001518</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2071843458111289</v>
+        <v>0.09996997070575464</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.03672641483706252</v>
+        <v>0.1953589535077265</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.00661321331723741</v>
+        <v>0.1979493201837852</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.23309140429623</v>
+        <v>0.8306239404429978</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.07233814965617147</v>
+        <v>0.2233001976005911</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>114.67</v>
+        <v>44.55</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.008130805608888458</v>
+        <v>0.007234901608322186</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.0247491377512532</v>
+        <v>-0.01503427618965125</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.008645284134434106</v>
+        <v>-0.03487869618010464</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.0247491377512532</v>
+        <v>-0.006245875140700408</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.02192317177206959</v>
+        <v>0.1390948233651814</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1797325284897455</v>
+        <v>0.221913728826842</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1284869943788229</v>
+        <v>0.02367694187414027</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1616176831447866</v>
+        <v>0.002781613103763236</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.08797031923657772</v>
+        <v>0.2364459347677013</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.02850328353111542</v>
+        <v>0.07330967373152286</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>69.87</v>
+        <v>51.32</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.003879371815810106</v>
+        <v>0.008251437256475702</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01452748599618747</v>
+        <v>-0.02191731463930569</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01143602916310571</v>
+        <v>-0.03479402929905706</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.03007520065543279</v>
+        <v>-0.01269718840370182</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.02827255170555354</v>
+        <v>0.1647752631695147</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.0704364149384189</v>
+        <v>0.1189526190346282</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1925485905224431</v>
+        <v>-0.0171816761905319</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1938238200155009</v>
+        <v>0.03653146581596478</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8156934543544372</v>
+        <v>0.1487354264102507</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2199653878817978</v>
+        <v>0.0473053889798023</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>95.27</v>
+        <v>95.45</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.003898789370267775</v>
+        <v>0.001889370331880746</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.03981056771860347</v>
+        <v>-0.02342951673396965</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.02166770045043831</v>
+        <v>-0.02711246198716988</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.02855106618202208</v>
+        <v>-0.02212891761707769</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.08433867495149783</v>
+        <v>0.08601658449304939</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1225108147668188</v>
+        <v>0.1369886829346849</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.117498613779444</v>
+        <v>0.09041984855577678</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.08234184768062214</v>
+        <v>0.06395723223971506</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.551099801759243</v>
+        <v>0.5479761263570349</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1575681818089021</v>
+        <v>0.1567906050991137</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>50.9</v>
+        <v>114.09</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.009534887518761748</v>
+        <v>-0.005058008549020498</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.03871575462743659</v>
+        <v>-0.0223650443753578</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.05372744637403781</v>
+        <v>-0.008774996955864922</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.01718477261856166</v>
+        <v>-0.01374484753708993</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1549807551248255</v>
+        <v>0.008129346857211228</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1047573486181312</v>
+        <v>0.1749742340963854</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>-0.02351753468937912</v>
+        <v>0.1010547710176308</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.04007966357340242</v>
+        <v>0.1349735470175606</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1505208593357741</v>
+        <v>0.07424122664321553</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.04784770288738516</v>
+        <v>0.02415873121844414</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>115.62</v>
+        <v>115.96</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.002080130862171181</v>
+        <v>0.002940635961026894</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01892232292246276</v>
+        <v>-0.02464463218283852</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.04784647569786848</v>
+        <v>-0.04283947483316874</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.0626671732724895</v>
+        <v>-0.06143264896647183</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.01440623005015074</v>
+        <v>-0.04880653267904078</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.08632496234665288</v>
+        <v>0.09190954637047755</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1090869331438717</v>
+        <v>0.1037835998352361</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1992901856577523</v>
+        <v>0.1898834096416895</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4396932349581502</v>
+        <v>0.4363728891404788</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1291630409188225</v>
+        <v>0.1282943147113387</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>99.95999999999999</v>
+        <v>51.55</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.01951935187187703</v>
+        <v>0.01958065341929571</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.03485565917725852</v>
+        <v>0.002723193737871332</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.04636520343923967</v>
+        <v>0.002528220006700499</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.02828816549444546</v>
+        <v>-0.03680869214972804</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.01979190479337234</v>
+        <v>-0.02422870622051965</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.007740986795642391</v>
+        <v>0.07414723140582247</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1571510215984864</v>
+        <v>0.08226141836510448</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1256521256139795</v>
+        <v>0.1514026025480177</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2224269144544666</v>
+        <v>0.7032202258050124</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.06923779369979077</v>
+        <v>0.1942363019681228</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>50.56</v>
+        <v>92.58</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.01153470449633098</v>
+        <v>0.005648536674465632</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01768019867553594</v>
+        <v>-0.0183437151131749</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.03067481746168899</v>
+        <v>-0.02608874175502085</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.04855096059447828</v>
+        <v>-0.01500155404576675</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.01519280827772962</v>
+        <v>0.001518787505434771</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0520050322252914</v>
+        <v>0.03727379228018401</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.06875486439054845</v>
+        <v>0.1050319075319479</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1456386299566759</v>
+        <v>0.1077706512822489</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6873624657743871</v>
+        <v>0.1484833000356527</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.190518444101202</v>
+        <v>0.04722876192672776</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>92.06</v>
+        <v>100.47</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.0004343204798052946</v>
+        <v>0.005102062233909077</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.02982402623308911</v>
+        <v>-0.0246578085899678</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.02726121986151331</v>
+        <v>-0.0371825329195401</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.02167907490549403</v>
+        <v>-0.02427891590135622</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.004856837876985098</v>
+        <v>-0.01034274484912523</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.02033492792622216</v>
+        <v>0.01130033010396914</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1056421939833359</v>
+        <v>0.1352887016014457</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1105724039349083</v>
+        <v>0.1091668372962205</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.150523282899621</v>
+        <v>0.2216429482211051</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.04784843864806421</v>
+        <v>0.06900917046562483</v>
       </c>
     </row>
     <row r="23">
@@ -1768,52 +1768,46 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13.42</v>
+        <v>68.56</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01178202123056016</v>
+        <v>0.01420117020919998</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.03522643971914396</v>
+        <v>-0.01776512090185123</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.03799281291883483</v>
+        <v>-0.02613641942335432</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.05225987140482968</v>
+        <v>-0.09119836506044854</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.01540719269139834</v>
+        <v>-0.02377909324384175</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.01132684863074163</v>
+        <v>0.02496633553869865</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1662080777778689</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0.05824244349428498</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>0.0471728567578078</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>0.01548331524741675</v>
-      </c>
+        <v>0.104189083633117</v>
+      </c>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1824,46 +1818,52 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>13.49</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01039377997142577</v>
+        <v>0.005216072610004785</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02467175219602402</v>
+        <v>-0.03019411077650613</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.05215929944785302</v>
+        <v>-0.03848895025878019</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.09661904557021028</v>
+        <v>-0.04933050246406201</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.002655655184679029</v>
+        <v>-0.03642858777727398</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.006851341803014277</v>
+        <v>0.01509930151548455</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1002396496157343</v>
-      </c>
-      <c r="N24" s="6" t="inlineStr"/>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr"/>
+        <v>0.1518950789640665</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0.03834005824274622</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0.04917461059879757</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0.01612996230756347</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>176.56</v>
+        <v>177.5</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01357622135311409</v>
+        <v>0.005323983090191664</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.05491922365584301</v>
+        <v>-0.04136964522904085</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.05253559551526721</v>
+        <v>-0.0494805891686787</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.0117542038535231</v>
+        <v>-0.02079772816022207</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.07836072904078573</v>
+        <v>0.07582274131965083</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1103022505644331</v>
+        <v>0.1341953666885296</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.08744333506837643</v>
+        <v>-0.08072478713098152</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.09221892589380387</v>
+        <v>-0.1073737598438051</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5528573775191077</v>
+        <v>0.5602029573956719</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1580052363881137</v>
+        <v>0.1598282934005526</v>
       </c>
     </row>
     <row r="26">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>26.5</v>
+        <v>41</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.006001494685966446</v>
+        <v>0.008362030345888671</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.03460840570256229</v>
+        <v>-0.01228615615887996</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.06821380090110818</v>
+        <v>-0.04517928944465055</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.1317169199694774</v>
+        <v>-0.03823600814625316</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.02537699597296206</v>
+        <v>-0.04160820079682415</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-0.06580958780160029</v>
+        <v>0.02063984281930065</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.08649058546690025</v>
+        <v>0.086092056723857</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1006180386679365</v>
+        <v>0.0655421336055837</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.064969642923494</v>
+        <v>0.3030211314259728</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2734187020279384</v>
+        <v>0.09223767547769701</v>
       </c>
     </row>
     <row r="27">
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>40.66</v>
+        <v>16.83</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.009500594321481537</v>
+        <v>0.008388219602674996</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.04688232553102845</v>
+        <v>-0.05076140111488991</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.05748724101353164</v>
+        <v>-0.07016576966837318</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.05155118123478564</v>
+        <v>-0.04591833866035788</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.04977800940738741</v>
+        <v>0.1249999920314646</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.003718422553376399</v>
+        <v>0.06317119424002393</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.08301271050303693</v>
+        <v>-0.1395705325549609</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.07456492761378652</v>
+        <v>-0.1551204889936314</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.2940358124899005</v>
+        <v>0.1472392526365811</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.08972128005000202</v>
+        <v>0.04685050279049818</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.69</v>
+        <v>26.62</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.008907340687121179</v>
+        <v>0.004528333555977371</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.07226232649250031</v>
+        <v>-0.03129544095083137</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.08397359149050299</v>
+        <v>-0.05803253278010778</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.0538548122710425</v>
+        <v>-0.1292116092581967</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.1346023447162457</v>
+        <v>-0.06792712405413104</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.04705150397853908</v>
+        <v>-0.05926454977131979</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.128004124018722</v>
+        <v>0.07121513065073382</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1502036123863457</v>
+        <v>0.1038079803707672</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1408065894396899</v>
+        <v>1.095942214572911</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.04489024264544628</v>
+        <v>0.2797538211809139</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16.76</v>
+        <v>16.96</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.005931220513024749</v>
+        <v>0.01193310577920936</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.03567312783790832</v>
+        <v>-0.0275230180553947</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.03511805301550486</v>
+        <v>-0.03581586484651322</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.09307355822295382</v>
+        <v>-0.07271742834772521</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.03009261788777262</v>
+        <v>-0.03800340942641378</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.007466591062862182</v>
+        <v>0.01508623740435255</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.009467645054618612</v>
+        <v>-0.007407557899208994</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.009954350308763016</v>
+        <v>-0.008855061759825644</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3770207747238143</v>
+        <v>0.3807782441403575</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.112534525639465</v>
+        <v>0.1135455290117995</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>53.83</v>
+        <v>54.31</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.002234271990831704</v>
+        <v>0.008916951995335376</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02886520774512236</v>
+        <v>-0.01843485313588378</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.01319885272366239</v>
+        <v>-0.004946875205307344</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.02162847358793629</v>
+        <v>-0.01505255759058355</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.0022242619126559</v>
+        <v>-0.01236588987852416</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.01521958717028571</v>
+        <v>-0.003686077971889468</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.05428703589151629</v>
+        <v>-0.05226657879671415</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.02721113806176578</v>
+        <v>-0.03920558990832024</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2042395833262218</v>
+        <v>0.1983626660727478</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.06390855093340386</v>
+        <v>0.06217503616215447</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>62.1</v>
+        <v>62.68</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.005763698617169188</v>
+        <v>0.009339804272239904</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.03391413109170605</v>
+        <v>-0.01893878691551065</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02618789354954854</v>
+        <v>-0.02821704953215842</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.07216497548232015</v>
+        <v>-0.06139560570630276</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.02862508716281875</v>
+        <v>-0.04756112094718112</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.01257456728712769</v>
+        <v>0.001496162620509889</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.06212753179860586</v>
+        <v>-0.05850679986353635</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.02432706184701983</v>
+        <v>-0.03326106750869062</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3808709938104369</v>
+        <v>0.3614780723392317</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1135704614894144</v>
+        <v>0.1083328793476499</v>
       </c>
     </row>
     <row r="32">
@@ -2266,51 +2266,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>15.61</v>
+        <v>126.41</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.002555908167925169</v>
+        <v>-0.000869372303789584</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.05336568384811124</v>
+        <v>-0.01496141308774368</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.08176472607780905</v>
+        <v>-0.001500748928133344</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.09191395161681359</v>
+        <v>-0.03104401995502371</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.005798917284731919</v>
+        <v>-0.04810423000645747</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.005361044377918844</v>
+        <v>-0.08200107752101027</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.04944659985337752</v>
+        <v>-0.03058197804008356</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1178974079072764</v>
+        <v>0.01009509108577467</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2259480399274361</v>
+        <v>0.4899193479494379</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07026343411159042</v>
+        <v>0.1421441507755314</v>
       </c>
     </row>
     <row r="33">
@@ -2322,51 +2322,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>126.52</v>
+        <v>15.67</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01102168106578461</v>
+        <v>0.003843716908157324</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01040283024582045</v>
+        <v>-0.03923969408980355</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.01310452687338237</v>
+        <v>-0.08576425704205604</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.01945285716481926</v>
+        <v>-0.09421960882372593</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.04239089799429774</v>
+        <v>-0.01817042363157151</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.09108886959610107</v>
+        <v>0.002700505335562209</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.01996836378877143</v>
+        <v>-0.05989700235781181</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.01421458718036517</v>
+        <v>-0.1245932023042156</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4949894699491253</v>
+        <v>0.2270597096581521</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1434382373693068</v>
+        <v>0.07058683553418899</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>112.62</v>
+        <v>114.55</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01624738431001194</v>
+        <v>0.01713727808654619</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.0290541872510901</v>
+        <v>-0.02377700164655527</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.05090174219719867</v>
+        <v>-0.0275891334109053</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.09976015891095913</v>
+        <v>-0.09331956330441082</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.06523904707294503</v>
+        <v>-0.08065807018810378</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.07412231750153953</v>
+        <v>-0.04897142543330835</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.05232480838429576</v>
+        <v>-0.04740575490263199</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09051718481263471</v>
+        <v>-0.09198525675551616</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2786140136471962</v>
+        <v>0.2928135236597658</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08537501492171629</v>
+        <v>0.08937807117222141</v>
       </c>
     </row>
   </sheetData>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.07030754806051287</v>
+        <v>0.08247752591172297</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1317169199694774</v>
+        <v>-0.1292116092581967</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.06836530834347299</v>
+        <v>0.06001578625805215</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.09976015891095913</v>
+        <v>-0.09421960882372593</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.03493870228696849</v>
+        <v>0.0501259228895754</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.09661904557021028</v>
+        <v>-0.09331956330441082</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.03082190393887085</v>
+        <v>0.0449897644157915</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09307355822295382</v>
+        <v>-0.09119836506044854</v>
       </c>
     </row>
     <row r="21">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.03007520065543279</v>
+        <v>0.04065763076662932</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.09191395161681359</v>
+        <v>-0.07271742834772521</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.0003655722554991581</v>
+        <v>0.01098100833676119</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.07216497548232015</v>
+        <v>-0.06143264896647183</v>
       </c>
     </row>
     <row r="23">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.0003463882435447152</v>
+        <v>0.005563276986744636</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.0626671732724895</v>
+        <v>-0.06139560570630276</v>
       </c>
     </row>
     <row r="24">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.005758810083257848</v>
+        <v>-0.001360510499921919</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.0538548122710425</v>
+        <v>-0.04933050246406201</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.009670084017731173</v>
+        <v>-0.006245875140700408</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.05225987140482968</v>
+        <v>-0.04591833866035788</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.0111781803066614</v>
+        <v>-0.01019254285000226</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.05155118123478564</v>
+        <v>-0.03823600814625316</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3281002034252525</v>
+        <v>0.274754372989751</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.07385138560672266</v>
+        <v>-0.1182686995814436</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.1974704246181354</v>
+        <v>0.1662480909748785</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.06523904707294503</v>
+        <v>-0.08065807018810378</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E33" s="11" t="n">
-        <v>0.1722176940124827</v>
+        <v>0.1650793540264506</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.04977800940738741</v>
+        <v>-0.06792712405413104</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.158158154144703</v>
+        <v>0.1647752631695147</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.04239089799429774</v>
+        <v>-0.04880653267904078</v>
       </c>
     </row>
     <row r="35">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1549807551248255</v>
+        <v>0.1563374574821794</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.03009261788777262</v>
+        <v>-0.04810423000645747</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1385622572575669</v>
+        <v>0.1535350898858778</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.02862508716281875</v>
+        <v>-0.04756112094718112</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1346023447162457</v>
+        <v>0.1390948233651814</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.02537699597296206</v>
+        <v>-0.04160820079682415</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1341025523650341</v>
+        <v>0.1249999920314646</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.01540719269139834</v>
+        <v>-0.03800340942641378</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.110331601311594</v>
+        <v>0.1042324463981414</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.01519280827772962</v>
+        <v>-0.03642858777727398</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.08433867495149783</v>
+        <v>0.08601658449304939</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.01440623005015074</v>
+        <v>-0.03402646287000921</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4821892746486622</v>
+        <v>0.4948164586635062</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.09108886959610107</v>
+        <v>-0.08200107752101027</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3714634404438271</v>
+        <v>0.3894458720846199</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.07412231750153953</v>
+        <v>-0.05926454977131979</v>
       </c>
     </row>
     <row r="47">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3714289546311644</v>
+        <v>0.3812320088927899</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.06580958780160029</v>
+        <v>-0.04897142543330835</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.2569827314412803</v>
+        <v>0.2600788467442285</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.04886918096839732</v>
+        <v>-0.02086692991362549</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2166700335994858</v>
+        <v>0.2252819540275444</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01521958717028571</v>
+        <v>-0.003686077971889468</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2071843458111289</v>
+        <v>0.221913728826842</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01257456728712769</v>
+        <v>0.001496162620509889</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.1954830762702375</v>
+        <v>0.2109407511963826</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.007466591062862182</v>
+        <v>0.002700505335562209</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1953783199421653</v>
+        <v>0.1974549397560355</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.005361044377918844</v>
+        <v>0.01130033010396914</v>
       </c>
     </row>
     <row r="53">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1848633017674182</v>
+        <v>0.1951694920130669</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.003718422553376399</v>
+        <v>0.01508623740435255</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.183779179014786</v>
+        <v>0.1924058226806387</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.006851341803014277</v>
+        <v>0.01509930151548455</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8772014578850098</v>
+        <v>0.8864689486904751</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1502036123863457</v>
+        <v>-0.1551204889936314</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7155114383298466</v>
+        <v>0.7300165274356081</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1178974079072764</v>
+        <v>-0.1245932023042156</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5584764045620914</v>
+        <v>0.5651810358294154</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.09221892589380387</v>
+        <v>-0.1073737598438051</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4891295312168098</v>
+        <v>0.4759561947599442</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09051718481263471</v>
+        <v>-0.09198525675551616</v>
       </c>
     </row>
     <row r="63">
@@ -4741,21 +4741,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4722989475326125</v>
+        <v>0.4624638519155564</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.02721113806176578</v>
+        <v>-0.03920558990832024</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4351397597751889</v>
+        <v>0.4333855756177889</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.02432706184701983</v>
+        <v>-0.03326106750869062</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3885900595457223</v>
+        <v>0.3836242622361901</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.009954350308763016</v>
+        <v>-0.008855061759825644</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3179039064268099</v>
+        <v>0.3271805384029947</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.005117827126525643</v>
+        <v>-0.006894166886446507</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2904003579804193</v>
+        <v>0.2807453801241315</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.00661321331723741</v>
+        <v>0.002781613103763236</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2190414116985373</v>
+        <v>0.2144489492875454</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01421458718036517</v>
+        <v>0.01009509108577467</v>
       </c>
     </row>
     <row r="69"/>
@@ -5072,21 +5072,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.463247966989884</v>
+        <v>2.502751086630683</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.0471728567578078</v>
+        <v>0.04917461059879757</v>
       </c>
     </row>
     <row r="74">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.447124034593412</v>
+        <v>2.461348218786648</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.08797031923657772</v>
+        <v>0.07424122664321553</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.170803034696446</v>
+        <v>2.211989506371251</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1408065894396899</v>
+        <v>0.1472392526365811</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.468498181292006</v>
+        <v>1.476457904866404</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1505208593357741</v>
+        <v>0.1484833000356527</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.209893340174876</v>
+        <v>1.213561636710333</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.150523282899621</v>
+        <v>0.1487354264102507</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.064969642923494</v>
+        <v>1.095942214572911</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2042395833262218</v>
+        <v>0.1983626660727478</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9434557742829932</v>
+        <v>0.9457420463790664</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2224269144544666</v>
+        <v>0.2216429482211051</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9412680078045068</v>
+        <v>0.9266944460403128</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2259480399274361</v>
+        <v>0.2270597096581521</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8486348264597399</v>
+        <v>0.8616504185354006</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.23309140429623</v>
+        <v>0.2364459347677013</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8156934543544372</v>
+        <v>0.8306239404429978</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2786140136471962</v>
+        <v>0.2889267194365044</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,14 +489,14 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>221.02</v>
+        <v>213.38</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.01932390539142692</v>
+        <v>-0.03456700408090785</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.007108345533898053</v>
+        <v>-0.02770437275608861</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.04038788237832547</v>
+        <v>-0.002710795535870059</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.0501259228895754</v>
+        <v>-0.0382656078839807</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.005458997853968306</v>
+        <v>-0.04668720396173598</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4948164586635062</v>
+        <v>0.4653745226082946</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7154974862849781</v>
+        <v>0.70507416680841</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8864689486904751</v>
+        <v>0.8372505760264604</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.211989506371251</v>
+        <v>2.114332425213759</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4754507106976316</v>
+        <v>0.4603433897383722</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>94.14</v>
+        <v>93.02</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.002342432123001004</v>
+        <v>-0.01189720367371472</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.009869107025295643</v>
+        <v>-0.002145511424776703</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.03655582147082326</v>
+        <v>0.002478669309944781</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.06001578625805215</v>
+        <v>0.02920999634737864</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1535350898858778</v>
+        <v>0.1308046952030995</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.1924058226806387</v>
+        <v>0.1711182957213895</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5074259472937388</v>
+        <v>0.4985419339931072</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5651810358294154</v>
+        <v>0.5516155178388513</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.636007085716392</v>
+        <v>0.571346484039333</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1783158694835469</v>
+        <v>0.1625830479018018</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>60.91</v>
+        <v>29.47</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01398368831122654</v>
+        <v>0.003746549751914685</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.007171941934026038</v>
+        <v>-0.0369281390205316</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.0231816075325566</v>
+        <v>-0.02963455716195573</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.02621901534215765</v>
+        <v>0.002722011751188802</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.1182686995814436</v>
+        <v>0.1611505235551927</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3894458720846199</v>
+        <v>0.2370015801610488</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4827136892478403</v>
+        <v>0.2035559144319676</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.7300165274356081</v>
+        <v>0.4895406658157264</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.502751086630683</v>
+        <v>0.9563452776739159</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5186921874370181</v>
+        <v>0.2506866153488698</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>55.24</v>
+        <v>54.43</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.00931851161147712</v>
+        <v>-0.01466331188774683</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.004146377089865427</v>
+        <v>-0.01874888935713925</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.01061108365667418</v>
+        <v>-0.00657055309976351</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.01098100833676119</v>
+        <v>-0.02332674049414463</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.004546281003259045</v>
+        <v>-0.01018369442076783</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3812320088927899</v>
+        <v>0.3950366858964738</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3544516143514955</v>
+        <v>0.3706345928104713</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4759561947599442</v>
+        <v>0.4511551984183082</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.476457904866404</v>
+        <v>1.464323436170802</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3529351601574136</v>
+        <v>0.3507217788546291</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29.36</v>
+        <v>57.38</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.0003407232964858231</v>
+        <v>-0.05795433899425395</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.04052286783202341</v>
+        <v>-0.06471063577418834</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.03102305776824088</v>
+        <v>-0.04318826246236196</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-0.001360510499921919</v>
+        <v>-0.1069260534145489</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1650793540264506</v>
+        <v>-0.1737940447876787</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1920569680882618</v>
+        <v>0.3506355658261655</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1938707416704128</v>
+        <v>0.4820959578268682</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4624638519155564</v>
+        <v>0.6253236881775166</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.9266944460403128</v>
+        <v>2.283015791705671</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2443358545540013</v>
+        <v>0.4862469985628759</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>67.45999999999999</v>
+        <v>29.27</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.009426862728667773</v>
+        <v>0.01210236447255841</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.01661806727413406</v>
+        <v>-0.01381401088936685</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.02598907011607232</v>
+        <v>-0.008468834557021521</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.08247752591172297</v>
+        <v>0.02378455059624152</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.274754372989751</v>
+        <v>0.168463127713784</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>-0.02086692991362549</v>
+        <v>0.2438688682502028</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1872218912119286</v>
+        <v>0.1535822713225479</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4333855756177889</v>
+        <v>0.3131111658743115</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.461348218786648</v>
+        <v>0.4556166634843244</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5126847576190789</v>
+        <v>0.1333107445908881</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>28.92</v>
+        <v>65.61</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.002078983529919309</v>
+        <v>-0.02742363621743527</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.02560647645105663</v>
+        <v>-0.04358597566000655</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.02032521585926761</v>
+        <v>-0.038117556209042</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.005563276986744636</v>
+        <v>0.05026411602834768</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1563374574821794</v>
+        <v>0.2007686922262557</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1951694920130669</v>
+        <v>0.02532187833132027</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1368180016370277</v>
+        <v>0.1630678328676129</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.2807453801241315</v>
+        <v>0.3974791652989205</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.420646585700803</v>
+        <v>2.338149206675457</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.124161438825777</v>
+        <v>0.4945206319333748</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>15.33</v>
+        <v>24.11</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.01860463318422845</v>
+        <v>0.03832908369145405</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02336451216055746</v>
+        <v>0.02117746662745867</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.03441297161834278</v>
+        <v>-0.01752242417007022</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.0449897644157915</v>
+        <v>0.01174992394217189</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.03402646287000921</v>
+        <v>0.2164480818154417</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2252819540275444</v>
+        <v>0.3361721451421815</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2844691270009263</v>
+        <v>0.04316102138241007</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3271805384029947</v>
+        <v>0.03658644891484508</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.8616504185354006</v>
+        <v>0.3585925287741762</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2301725843572566</v>
+        <v>0.1075493179767508</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.48</v>
+        <v>34.45</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.004020660277870292</v>
+        <v>0.01592453311581354</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.02072833788942097</v>
+        <v>-0.02380278069696218</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.01631969094298158</v>
+        <v>-0.01683790345811442</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.01019254285000226</v>
+        <v>0.01742469409192848</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1042324463981414</v>
+        <v>0.02164885871321176</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2109407511963826</v>
+        <v>0.1325508023821431</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1105523543068292</v>
+        <v>0.1634272665119099</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1424568405485831</v>
+        <v>0.4171750735609296</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9457420463790664</v>
+        <v>0.6508697636382796</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2484229811401126</v>
+        <v>0.181873344278805</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>38.15</v>
+        <v>15.08</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.002628181099172178</v>
+        <v>-0.01630789310138248</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.01140188196344116</v>
+        <v>0.006675593092494658</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.003947408575760702</v>
+        <v>0.01823089104924835</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.02678569430165012</v>
+        <v>0.009370839843033218</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.04922994734542807</v>
+        <v>-0.05216844322227077</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1974549397560355</v>
+        <v>0.2138958041918853</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1271890104190208</v>
+        <v>0.2765481001322279</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2144489492875454</v>
+        <v>0.3065968053399128</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.213561636710333</v>
+        <v>0.8175344399939908</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3032584210286067</v>
+        <v>0.2203775683459672</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>33.91</v>
+        <v>45.56</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.0002949357251671447</v>
+        <v>0.02267120434404535</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.03910459145123013</v>
+        <v>0.007296083006733678</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.03500283334093235</v>
+        <v>-0.008487472974385457</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.01021595129212571</v>
+        <v>0.007518800163858197</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.001178230180513218</v>
+        <v>0.1616522171152097</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.08657105558448408</v>
+        <v>0.2725189155278496</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1444574305701467</v>
+        <v>0.04688493100565649</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.3836242622361901</v>
+        <v>0.0394644277496965</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6011830229949893</v>
+        <v>0.2806344068334923</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1698952892861243</v>
+        <v>0.08594639670712589</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>23.22</v>
+        <v>17.38</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.003457213734493036</v>
+        <v>-0.005720845771654548</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01651847890364211</v>
+        <v>-0.02633060003690746</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.05417515132539363</v>
+        <v>-0.01473924251008818</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.02641513870183054</v>
+        <v>-0.03337043363434367</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1662480909748785</v>
+        <v>0.08354103296478543</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2600788467442285</v>
+        <v>0.226619733041562</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>-0.01102787334591038</v>
+        <v>0.1041989886635752</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>-0.006894166886446507</v>
+        <v>0.1415029599497304</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2889267194365044</v>
+        <v>0.8987513880469906</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08828524800218363</v>
+        <v>0.2382909572411127</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>70.90000000000001</v>
+        <v>52.11</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.01474164503803843</v>
+        <v>0.01539362666066069</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.01141231197106451</v>
+        <v>-0.006861074937606793</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.02073139159784643</v>
+        <v>-0.01734863643452478</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.04065763076662932</v>
+        <v>0.01204115190666322</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.01779714776001518</v>
+        <v>0.1886405207340194</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.09996997070575464</v>
+        <v>0.1782662473541392</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1953589535077265</v>
+        <v>0.006853220497689216</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1979493201837852</v>
+        <v>0.06625127043635581</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8306239404429978</v>
+        <v>0.1818045519851466</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2233001976005911</v>
+        <v>0.05726020587720959</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>44.55</v>
+        <v>37.95</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.007234901608322186</v>
+        <v>-0.005242483746790483</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01503427618965125</v>
+        <v>-0.01658459152935554</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.03487869618010464</v>
+        <v>0.009308571888885897</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.006245875140700408</v>
+        <v>-0.04720062720784091</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1390948233651814</v>
+        <v>0.02761983345071117</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.221913728826842</v>
+        <v>0.2150456657449937</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.02367694187414027</v>
+        <v>0.1236989211846975</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.002781613103763236</v>
+        <v>0.2108909240068455</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.2364459347677013</v>
+        <v>1.150048794677982</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.07330967373152286</v>
+        <v>0.2906726445505012</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>51.32</v>
+        <v>96.97</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.008251437256475702</v>
+        <v>0.01592461310695659</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02191731463930569</v>
+        <v>-0.007878009616284487</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.03479402929905706</v>
+        <v>0.0007223910600819838</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.01269718840370182</v>
+        <v>-0.00543588491586533</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1647752631695147</v>
+        <v>0.09632565931513315</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1189526190346282</v>
+        <v>0.1545550462069933</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>-0.0171816761905319</v>
+        <v>0.09665853566571769</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.03653146581596478</v>
+        <v>0.08587028815598874</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1487354264102507</v>
+        <v>0.5427828253166105</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.0473053889798023</v>
+        <v>0.155495517801677</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>95.45</v>
+        <v>116.12</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.001889370331880746</v>
+        <v>0.01779302720528886</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.02342951673396965</v>
+        <v>-0.004969959013087166</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.02711246198716988</v>
+        <v>0.01450291521393665</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.02212891761707769</v>
+        <v>-0.005906984217387778</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.08601658449304939</v>
+        <v>0.01868589282156208</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1369886829346849</v>
+        <v>0.2087020205625962</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.09041984855577678</v>
+        <v>0.1167948393493303</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.06395723223971506</v>
+        <v>0.1627452743479818</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5479761263570349</v>
+        <v>0.09423050267042576</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1567906050991137</v>
+        <v>0.03047218199378476</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>114.09</v>
+        <v>70.87</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.005058008549020498</v>
+        <v>-0.0004231139443053866</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.0223650443753578</v>
+        <v>0.01098436931842728</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.008774996955864922</v>
+        <v>0.01956553831901986</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.01374484753708993</v>
+        <v>0.01751616933202538</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.008129346857211228</v>
+        <v>0.01133472052802831</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1749742340963854</v>
+        <v>0.09549378088975713</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1010547710176308</v>
+        <v>0.1978165841167467</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1349735470175606</v>
+        <v>0.2039406096059813</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.07424122664321553</v>
+        <v>0.7873244882407229</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.02415873121844414</v>
+        <v>0.2135782990890678</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>115.96</v>
+        <v>116.65</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.002940635961026894</v>
+        <v>0.005950348800051408</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.02464463218283852</v>
+        <v>-0.01884092754032396</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.04283947483316874</v>
+        <v>-0.0245839526886934</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.06143264896647183</v>
+        <v>-0.05904654047548541</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.04880653267904078</v>
+        <v>-0.04822124796379323</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.09190954637047755</v>
+        <v>0.1366061767187048</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1037835998352361</v>
+        <v>0.1106429904592299</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1898834096416895</v>
+        <v>0.2032053422948674</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4363728891404788</v>
+        <v>0.4404276566499508</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1282943147113387</v>
+        <v>0.1293550125691092</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>51.55</v>
+        <v>93.7</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01958065341929571</v>
+        <v>0.01209759229894303</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.002723193737871332</v>
+        <v>-0.006468037600918963</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.002528220006700499</v>
+        <v>-0.008990016669278345</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.03680869214972804</v>
+        <v>-0.0187454283754519</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.02422870622051965</v>
+        <v>0.005942553027325825</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.07414723140582247</v>
+        <v>0.04830781385610994</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.08226141836510448</v>
+        <v>0.1118038849530716</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1514026025480177</v>
+        <v>0.1282440086089214</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7032202258050124</v>
+        <v>0.1586442514897863</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1942363019681228</v>
+        <v>0.0503080733172081</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>92.58</v>
+        <v>50.32</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.005648536674465632</v>
+        <v>-0.02386032125005444</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.0183437151131749</v>
+        <v>-0.02120210378959497</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.02608874175502085</v>
+        <v>-0.01967664329245</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.01500155404576675</v>
+        <v>-0.06084363614823518</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.001518787505434771</v>
+        <v>-0.05697153074877592</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.03727379228018401</v>
+        <v>0.07821578561047815</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1050319075319479</v>
+        <v>0.0672295198404611</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1077706512822489</v>
+        <v>0.1259072024986083</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1484833000356527</v>
+        <v>0.6625809488320764</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.04722876192672776</v>
+        <v>0.1846614779155331</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>100.47</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.005102062233909077</v>
+        <v>-0.0150293830783722</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.0246578085899678</v>
+        <v>-0.03931660001716819</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.0371825329195401</v>
+        <v>-0.04377233426229266</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.02427891590135622</v>
+        <v>-0.03065919645112447</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.01034274484912523</v>
+        <v>-0.04377233426229266</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.01130033010396914</v>
+        <v>0.01220872988801625</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1352887016014457</v>
+        <v>0.1181057150698988</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1091668372962205</v>
+        <v>0.1018737201255013</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2216429482211051</v>
+        <v>0.1917300313852894</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06900917046562483</v>
+        <v>0.0602117861463356</v>
       </c>
     </row>
     <row r="23">
@@ -1768,46 +1768,52 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>68.56</v>
+        <v>17.11</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.01420117020919998</v>
+        <v>0.01663699868774859</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01776512090185123</v>
+        <v>-0.03496891979087802</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02613641942335432</v>
+        <v>-0.04199327963994048</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.09119836506044854</v>
+        <v>-0.05521810967959917</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.02377909324384175</v>
+        <v>0.1391478088476084</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.02496633553869865</v>
+        <v>0.1175702247812171</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.104189083633117</v>
-      </c>
-      <c r="N23" s="6" t="inlineStr"/>
-      <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="6" t="inlineStr"/>
+        <v>-0.124808118768799</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>-0.1305894133623726</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>0.1695147284013139</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0.05358254072171498</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1818,52 +1824,46 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>13.49</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.005216072610004785</v>
+        <v>-0.02173275841347755</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.03019411077650613</v>
+        <v>-0.03911179423458266</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03848895025878019</v>
+        <v>-0.03426922041755698</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.04933050246406201</v>
+        <v>-0.1135342790313271</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.03642858777727398</v>
+        <v>-0.05026908685485187</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.01509930151548455</v>
+        <v>0.04016743491084385</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1518950789640665</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>0.03834005824274622</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>0.04917461059879757</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>0.01612996230756347</v>
-      </c>
+        <v>0.09248859634896767</v>
+      </c>
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>177.5</v>
+        <v>177.06</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.005323983090191664</v>
+        <v>-0.002478886993838025</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.04136964522904085</v>
+        <v>-0.04374598154738096</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.0494805891686787</v>
+        <v>-0.0502601270466323</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.02079772816022207</v>
+        <v>-0.04198684914026696</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.07582274131965083</v>
+        <v>0.05720087219634085</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1341953666885296</v>
+        <v>0.1488064052286029</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.08072478713098152</v>
+        <v>-0.07085305521871677</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.1073737598438051</v>
+        <v>-0.102519052843061</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5602029573956719</v>
+        <v>0.5325490575205594</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1598282934005526</v>
+        <v>0.1529349249360146</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>41</v>
+        <v>40.72</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.008362030345888671</v>
+        <v>-0.006829238519435954</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01228615615887996</v>
+        <v>-0.01903148958741996</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.04517928944465055</v>
+        <v>-0.04435577006749181</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.03823600814625316</v>
+        <v>-0.06946977187917691</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.04160820079682415</v>
+        <v>-0.05740739579717502</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.02063984281930065</v>
+        <v>0.01795848024086544</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.086092056723857</v>
+        <v>0.08121097204116801</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.0655421336055837</v>
+        <v>0.06425189734771108</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.3030211314259728</v>
+        <v>0.282931821114097</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.09223767547769701</v>
+        <v>0.08659539232173197</v>
       </c>
     </row>
     <row r="27">
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>16.83</v>
+        <v>13.33</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.008388219602674996</v>
+        <v>-0.0118606263993174</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.05076140111488991</v>
+        <v>-0.04169661610844377</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.07016576966837318</v>
+        <v>-0.0478571483067104</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.04591833866035788</v>
+        <v>-0.05326704574317853</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1249999920314646</v>
+        <v>-0.0612675983975316</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.06317119424002393</v>
+        <v>-0.004299653309375318</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.1395705325549609</v>
+        <v>0.1326026182027622</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1551204889936314</v>
+        <v>0.03686571198737609</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.1472392526365811</v>
+        <v>0.03063232188572851</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.04685050279049818</v>
+        <v>0.01010825290880701</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>26.62</v>
+        <v>17.04</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.004528333555977371</v>
+        <v>0.004717089349841386</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.03129544095083137</v>
+        <v>-0.0229357572408978</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.05803253278010778</v>
+        <v>-0.02012642244998775</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.1292116092581967</v>
+        <v>-0.05595558804564704</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.06792712405413104</v>
+        <v>-0.03126772213129458</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-0.05926454977131979</v>
+        <v>0.04149936155635459</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.07121513065073382</v>
+        <v>0.001663633825651489</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1038079803707672</v>
+        <v>0.005104123305394559</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.095942214572911</v>
+        <v>0.3791743449403977</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2797538211809139</v>
+        <v>0.1131142005739663</v>
       </c>
     </row>
     <row r="29">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16.96</v>
+        <v>26.28</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.01193310577920936</v>
+        <v>-0.01277235694473711</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.0275230180553947</v>
+        <v>-0.04366808135300149</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.03581586484651322</v>
+        <v>-0.04954788248773179</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.07271742834772521</v>
+        <v>-0.1445312085270407</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.03800340942641378</v>
+        <v>-0.0746478507169247</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.01508623740435255</v>
+        <v>-0.02705524795165459</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.007407557899208994</v>
+        <v>0.04968130826340422</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.008855061759825644</v>
+        <v>0.09414847723344577</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3807782441403575</v>
+        <v>1.07322398903673</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1135455290117995</v>
+        <v>0.2751132005680523</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>54.31</v>
+        <v>54.33</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.008916951995335376</v>
+        <v>0.0003682647257952087</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01843485313588378</v>
+        <v>-0.01807337731622372</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.004946875205307344</v>
+        <v>-0.009119095081204454</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.01505255759058355</v>
+        <v>-0.01771830623583326</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.01236588987852416</v>
+        <v>-0.01558247539506374</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.003686077971889468</v>
+        <v>0.03168966999482925</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.05226657879671415</v>
+        <v>-0.05177276076161863</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.03920558990832024</v>
+        <v>-0.03885169835472935</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1983626660727478</v>
+        <v>0.182409661660081</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.06217503616215447</v>
+        <v>0.0574406218406327</v>
       </c>
     </row>
     <row r="31">
@@ -2210,51 +2210,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
+          <t>Leisure</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="F31" s="5" t="n">
-        <v>62.68</v>
+        <v>15.83</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.009339804272239904</v>
+        <v>0.01021058370345274</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01893878691551065</v>
+        <v>-0.02942977056735263</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02821704953215842</v>
+        <v>-0.05209585625673141</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.06139560570630276</v>
+        <v>-0.09594519036068927</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.04756112094718112</v>
+        <v>-0.01615911910603796</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.001496162620509889</v>
+        <v>0.03234598996409632</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.05850679986353635</v>
+        <v>-0.05559277790358019</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.03326106750869062</v>
+        <v>-0.1024492021948765</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3614780723392317</v>
+        <v>0.2266687733192547</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1083328793476499</v>
+        <v>0.07047312855644439</v>
       </c>
     </row>
     <row r="32">
@@ -2266,51 +2266,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>126.41</v>
+        <v>62.6</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.000869372303789584</v>
+        <v>-0.001276353392871354</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01496141308774368</v>
+        <v>-0.02019096772344553</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.001500748928133344</v>
+        <v>-0.02370561770666735</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.03104401995502371</v>
+        <v>-0.05122771613889754</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.04810423000645747</v>
+        <v>-0.05180245899489133</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.08200107752101027</v>
+        <v>0.02723386179371468</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.03058197804008356</v>
+        <v>-0.05903635570049104</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01009509108577467</v>
+        <v>-0.03422267650895294</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4899193479494379</v>
+        <v>0.3497243053390235</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1421441507755314</v>
+        <v>0.1051342098171384</v>
       </c>
     </row>
     <row r="33">
@@ -2322,51 +2322,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>15.67</v>
+        <v>124.38</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.003843716908157324</v>
+        <v>-0.01605890633559004</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03923969408980355</v>
+        <v>-0.03078005549190954</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.08576425704205604</v>
+        <v>-0.008134005263552124</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.09421960882372593</v>
+        <v>-0.06142474159831091</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.01817042363157151</v>
+        <v>-0.07415632593271049</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.002700505335562209</v>
+        <v>-0.1086564030270418</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.05989700235781181</v>
+        <v>-0.03260528621594105</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.1245932023042156</v>
+        <v>-0.01154006174473565</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2270597096581521</v>
+        <v>0.4306034598122714</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.07058683553418899</v>
+        <v>0.1267816273239972</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>114.55</v>
+        <v>112.98</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.01713727808654619</v>
+        <v>-0.01370580229591822</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02377700164655527</v>
+        <v>-0.03715692105871604</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.0275891334109053</v>
+        <v>-0.030963145161227</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.09331956330441082</v>
+        <v>-0.09832401751606645</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.08065807018810378</v>
+        <v>-0.1000477733550843</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.04897142543330835</v>
+        <v>-0.03445672507691699</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.04740575490263199</v>
+        <v>-0.04846613873624017</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09198525675551616</v>
+        <v>-0.09285240582392029</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2928135236597658</v>
+        <v>0.2860823081421777</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08937807117222141</v>
+        <v>0.08748411357027774</v>
       </c>
     </row>
   </sheetData>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.08247752591172297</v>
+        <v>0.05026411602834768</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1292116092581967</v>
+        <v>-0.1445312085270407</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.06001578625805215</v>
+        <v>0.02920999634737864</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.09421960882372593</v>
+        <v>-0.1135342790313271</v>
       </c>
     </row>
     <row r="19">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0501259228895754</v>
+        <v>0.02378455059624152</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.09331956330441082</v>
+        <v>-0.1069260534145489</v>
       </c>
     </row>
     <row r="20">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.0449897644157915</v>
+        <v>0.01751616933202538</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09119836506044854</v>
+        <v>-0.09832401751606645</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.04065763076662932</v>
+        <v>0.01742469409192848</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.07271742834772521</v>
+        <v>-0.09594519036068927</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01098100833676119</v>
+        <v>0.01204115190666322</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.06143264896647183</v>
+        <v>-0.06946977187917691</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.005563276986744636</v>
+        <v>0.01174992394217189</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.06139560570630276</v>
+        <v>-0.06142474159831091</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.001360510499921919</v>
+        <v>0.009370839843033218</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.04933050246406201</v>
+        <v>-0.06084363614823518</v>
       </c>
     </row>
     <row r="25">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.006245875140700408</v>
+        <v>0.007518800163858197</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.04591833866035788</v>
+        <v>-0.05904654047548541</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.01019254285000226</v>
+        <v>0.002722011751188802</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.03823600814625316</v>
+        <v>-0.05595558804564704</v>
       </c>
     </row>
     <row r="27"/>
@@ -3539,21 +3539,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.274754372989751</v>
+        <v>0.2164480818154417</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1182686995814436</v>
+        <v>-0.1737940447876787</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.1662480909748785</v>
+        <v>0.2007686922262557</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.08065807018810378</v>
+        <v>-0.1000477733550843</v>
       </c>
     </row>
     <row r="33">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1650793540264506</v>
+        <v>0.1886405207340194</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.06792712405413104</v>
+        <v>-0.0746478507169247</v>
       </c>
     </row>
     <row r="34">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1647752631695147</v>
+        <v>0.168463127713784</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.04880653267904078</v>
+        <v>-0.07415632593271049</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1563374574821794</v>
+        <v>0.1616522171152097</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.04810423000645747</v>
+        <v>-0.0612675983975316</v>
       </c>
     </row>
     <row r="36">
@@ -3764,21 +3764,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1535350898858778</v>
+        <v>0.1611505235551927</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.04756112094718112</v>
+        <v>-0.05740739579717502</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1390948233651814</v>
+        <v>0.1391478088476084</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.04160820079682415</v>
+        <v>-0.05697153074877592</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1249999920314646</v>
+        <v>0.1308046952030995</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.03800340942641378</v>
+        <v>-0.05216844322227077</v>
       </c>
     </row>
     <row r="39">
@@ -3899,21 +3899,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="E39" s="11" t="n">
-        <v>0.1042324463981414</v>
+        <v>0.09632565931513315</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03642858777727398</v>
+        <v>-0.05180245899489133</v>
       </c>
     </row>
     <row r="40">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.08601658449304939</v>
+        <v>0.08354103296478543</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.03402646287000921</v>
+        <v>-0.05026908685485187</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4948164586635062</v>
+        <v>0.4653745226082946</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.08200107752101027</v>
+        <v>-0.1086564030270418</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3894458720846199</v>
+        <v>0.3950366858964738</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.05926454977131979</v>
+        <v>-0.03445672507691699</v>
       </c>
     </row>
     <row r="47">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3812320088927899</v>
+        <v>0.3506355658261655</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.04897142543330835</v>
+        <v>-0.02705524795165459</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.2600788467442285</v>
+        <v>0.3361721451421815</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.02086692991362549</v>
+        <v>-0.004299653309375318</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2252819540275444</v>
+        <v>0.2725189155278496</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,21 +4252,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.003686077971889468</v>
+        <v>0.01220872988801625</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.221913728826842</v>
+        <v>0.2438688682502028</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.001496162620509889</v>
+        <v>0.01795848024086544</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2109407511963826</v>
+        <v>0.2370015801610488</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.002700505335562209</v>
+        <v>0.02532187833132027</v>
       </c>
     </row>
     <row r="52">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1974549397560355</v>
+        <v>0.226619733041562</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.01130033010396914</v>
+        <v>0.02723386179371468</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1951694920130669</v>
+        <v>0.2150456657449937</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.01508623740435255</v>
+        <v>0.03168966999482925</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1924058226806387</v>
+        <v>0.2138958041918853</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.01509930151548455</v>
+        <v>0.03234598996409632</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8864689486904751</v>
+        <v>0.8372505760264604</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1551204889936314</v>
+        <v>-0.1305894133623726</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7300165274356081</v>
+        <v>0.6253236881775166</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4628,21 +4628,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1245932023042156</v>
+        <v>-0.102519052843061</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5651810358294154</v>
+        <v>0.5516155178388513</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4673,21 +4673,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1073737598438051</v>
+        <v>-0.1024492021948765</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4759561947599442</v>
+        <v>0.4895406658157264</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09198525675551616</v>
+        <v>-0.09285240582392029</v>
       </c>
     </row>
     <row r="63">
@@ -4741,21 +4741,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4624638519155564</v>
+        <v>0.4511551984183082</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.03920558990832024</v>
+        <v>-0.03885169835472935</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4333855756177889</v>
+        <v>0.4171750735609296</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.03326106750869062</v>
+        <v>-0.03422267650895294</v>
       </c>
     </row>
     <row r="65">
@@ -4831,21 +4831,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3836242622361901</v>
+        <v>0.3974791652989205</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4853,21 +4853,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.008855061759825644</v>
+        <v>-0.01154006174473565</v>
       </c>
     </row>
     <row r="66">
@@ -4876,21 +4876,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3271805384029947</v>
+        <v>0.3131111658743115</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4898,21 +4898,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.006894166886446507</v>
+        <v>0.005104123305394559</v>
       </c>
     </row>
     <row r="67">
@@ -4921,21 +4921,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2807453801241315</v>
+        <v>0.3065968053399128</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.002781613103763236</v>
+        <v>0.03658644891484508</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2144489492875454</v>
+        <v>0.2108909240068455</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01009509108577467</v>
+        <v>0.03686571198737609</v>
       </c>
     </row>
     <row r="69"/>
@@ -5072,21 +5072,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.502751086630683</v>
+        <v>2.338149206675457</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.04917461059879757</v>
+        <v>0.03063232188572851</v>
       </c>
     </row>
     <row r="74">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.461348218786648</v>
+        <v>2.283015791705671</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.07424122664321553</v>
+        <v>0.09423050267042576</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.211989506371251</v>
+        <v>2.114332425213759</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5184,21 +5184,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1472392526365811</v>
+        <v>0.1586442514897863</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.476457904866404</v>
+        <v>1.464323436170802</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1484833000356527</v>
+        <v>0.1695147284013139</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.213561636710333</v>
+        <v>1.150048794677982</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1487354264102507</v>
+        <v>0.1818045519851466</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.095942214572911</v>
+        <v>1.07322398903673</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1983626660727478</v>
+        <v>0.182409661660081</v>
       </c>
     </row>
     <row r="79">
@@ -5342,21 +5342,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9457420463790664</v>
+        <v>0.9563452776739159</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2216429482211051</v>
+        <v>0.1917300313852894</v>
       </c>
     </row>
     <row r="80">
@@ -5387,21 +5387,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9266944460403128</v>
+        <v>0.8987513880469906</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2270597096581521</v>
+        <v>0.2266687733192547</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8616504185354006</v>
+        <v>0.8175344399939908</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2364459347677013</v>
+        <v>0.2806344068334923</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8306239404429978</v>
+        <v>0.7873244882407229</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2889267194365044</v>
+        <v>0.282931821114097</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -689,10 +689,10 @@
         <v>0.5516155178388513</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.571346484039333</v>
+        <v>0.5713465852969499</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1625830479018018</v>
+        <v>0.1625830728740973</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.4895406658157264</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.9563452776739159</v>
+        <v>0.956345029965413</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2506866153488698</v>
+        <v>0.2506865625623933</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.4511551984183082</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.464323436170802</v>
+        <v>1.464323223363207</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3507217788546291</v>
+        <v>0.3507217399739291</v>
       </c>
     </row>
     <row r="6">
@@ -857,10 +857,10 @@
         <v>0.6253236881775166</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.283015791705671</v>
+        <v>2.28301614997986</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.4862469985628759</v>
+        <v>0.4862470526273857</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.3131111658743115</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4556166634843244</v>
+        <v>0.4556168015549942</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1333107445908881</v>
+        <v>0.1333107804238041</v>
       </c>
     </row>
     <row r="8">
@@ -963,10 +963,10 @@
         <v>0.02532187833132027</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1630678328676129</v>
+        <v>0.1630679115178717</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3974791652989205</v>
+        <v>0.3974792788472514</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>2.338149206675457</v>
@@ -1025,10 +1025,10 @@
         <v>0.03658644891484508</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.3585925287741762</v>
+        <v>0.3585923827545414</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1075493179767508</v>
+        <v>0.1075492782974627</v>
       </c>
     </row>
     <row r="10">
@@ -1134,7 +1134,7 @@
         <v>0.2765481001322279</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3065968053399128</v>
+        <v>0.3065966973751848</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>0.8175344399939908</v>
@@ -1249,10 +1249,10 @@
         <v>0.1415029599497304</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.8987513880469906</v>
+        <v>0.8987517837019652</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2382909572411127</v>
+        <v>0.2382910432513097</v>
       </c>
     </row>
     <row r="14">
@@ -1305,10 +1305,10 @@
         <v>0.06625127043635581</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.1818045519851466</v>
+        <v>0.1818046542273863</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.05726020587720959</v>
+        <v>0.05726023636635946</v>
       </c>
     </row>
     <row r="15">
@@ -1355,7 +1355,7 @@
         <v>0.2150456657449937</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1236989211846975</v>
+        <v>0.1236987942594066</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>0.2108909240068455</v>
@@ -1520,7 +1520,7 @@
         <v>0.01133472052802831</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.09549378088975713</v>
+        <v>0.0954936516942515</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>0.1978165841167467</v>
@@ -1579,16 +1579,16 @@
         <v>0.1366061767187048</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1106429904592299</v>
+        <v>0.1106430711370801</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2032053422948674</v>
+        <v>0.2032054369806695</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4404276566499508</v>
+        <v>0.4404277923525819</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1293550125691092</v>
+        <v>0.1293550480346046</v>
       </c>
     </row>
     <row r="20">
@@ -1635,7 +1635,7 @@
         <v>0.04830781385610994</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1118038849530716</v>
+        <v>0.1118037843046817</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0.1282440086089214</v>
@@ -1697,10 +1697,10 @@
         <v>0.1259072024986083</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6625809488320764</v>
+        <v>0.6625808440577143</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1846614779155331</v>
+        <v>0.1846614530300974</v>
       </c>
     </row>
     <row r="22">
@@ -1750,13 +1750,13 @@
         <v>0.1181057150698988</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1018737201255013</v>
+        <v>0.1018738137294304</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1917300313852894</v>
+        <v>0.1917299218923489</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.0602117861463356</v>
+        <v>0.06021175367653497</v>
       </c>
     </row>
     <row r="23">
@@ -1915,10 +1915,10 @@
         <v>-0.102519052843061</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5325490575205594</v>
+        <v>0.5325489563164001</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1529349249360146</v>
+        <v>0.1529348995574225</v>
       </c>
     </row>
     <row r="26">
@@ -1968,13 +1968,13 @@
         <v>0.08121097204116801</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.06425189734771108</v>
+        <v>0.06425179124142399</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.282931821114097</v>
+        <v>0.2829320524008649</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.08659539232173197</v>
+        <v>0.08659545761881615</v>
       </c>
     </row>
     <row r="27">
@@ -2027,10 +2027,10 @@
         <v>0.03686571198737609</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.03063232188572851</v>
+        <v>0.03063239787941074</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.01010825290880701</v>
+        <v>0.01010827773558653</v>
       </c>
     </row>
     <row r="28">
@@ -2083,10 +2083,10 @@
         <v>0.005104123305394559</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3791743449403977</v>
+        <v>0.3791744513960797</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1131142005739663</v>
+        <v>0.1131142292136444</v>
       </c>
     </row>
     <row r="29">
@@ -2189,16 +2189,16 @@
         <v>0.03168966999482925</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.05177276076161863</v>
+        <v>-0.05177269763024461</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.03885169835472935</v>
+        <v>-0.03885176321834227</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.182409661660081</v>
+        <v>0.182409759825005</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.0574406218406327</v>
+        <v>0.05744065110391849</v>
       </c>
     </row>
     <row r="31">
@@ -2301,16 +2301,16 @@
         <v>0.02723386179371468</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.05903635570049104</v>
+        <v>-0.05903624779054151</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>-0.03422267650895294</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3497243053390235</v>
+        <v>0.3497244163525575</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1051342098171384</v>
+        <v>0.1051342401158817</v>
       </c>
     </row>
     <row r="33">
@@ -2354,19 +2354,19 @@
         <v>-0.07415632593271049</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1086564030270418</v>
+        <v>-0.1086565004945307</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.03260528621594105</v>
+        <v>-0.03260540102519505</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>-0.01154006174473565</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4306034598122714</v>
+        <v>0.4306032087346576</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1267816273239972</v>
+        <v>0.1267815614055074</v>
       </c>
     </row>
     <row r="34">
@@ -2419,10 +2419,10 @@
         <v>-0.09285240582392029</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2860823081421777</v>
+        <v>0.2860824198352034</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08748411357027774</v>
+        <v>0.08748414505203361</v>
       </c>
     </row>
   </sheetData>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1086564030270418</v>
+        <v>-0.1086565004945307</v>
       </c>
     </row>
     <row r="46">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.03885169835472935</v>
+        <v>-0.03885176321834227</v>
       </c>
     </row>
     <row r="64">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3974791652989205</v>
+        <v>0.3974792788472514</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3065968053399128</v>
+        <v>0.3065966973751848</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.03063232188572851</v>
+        <v>0.03063239787941074</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.283015791705671</v>
+        <v>2.28301614997986</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.464323436170802</v>
+        <v>1.464323223363207</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1818045519851466</v>
+        <v>0.1818046542273863</v>
       </c>
     </row>
     <row r="78">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.182409661660081</v>
+        <v>0.182409759825005</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9563452776739159</v>
+        <v>0.956345029965413</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1917300313852894</v>
+        <v>0.1917299218923489</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8987513880469906</v>
+        <v>0.8987517837019652</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.282931821114097</v>
+        <v>0.2829320524008649</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -491,9 +491,9 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>213.38</v>
+        <v>213.08</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.03456700408090785</v>
+        <v>-0.001405956719902512</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.02770437275608861</v>
+        <v>-0.03909807516999009</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.002710795535870059</v>
+        <v>0.006233506603987582</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>-0.0382656078839807</v>
+        <v>-0.03961776481533752</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.04668720396173598</v>
+        <v>-0.08905135096805994</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4653745226082946</v>
+        <v>0.4633142694510595</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.70507416680841</v>
+        <v>0.7137480668130991</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8372505760264604</v>
+        <v>0.8031457666284911</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.114332425213759</v>
+        <v>2.141324511609163</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4603433897383722</v>
+        <v>0.4645502176415688</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>93.02</v>
+        <v>94.89</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.01189720367371472</v>
+        <v>0.02010323386440827</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.002145511424776703</v>
+        <v>0.0121599934895833</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.002478669309944781</v>
+        <v>0.008824174490730252</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.02920999634737864</v>
+        <v>0.04990044559953688</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1308046952030995</v>
+        <v>0.1913370693259553</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.1711182957213895</v>
+        <v>0.1946615607031636</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4985419339931072</v>
+        <v>0.5412360524232969</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5516155178388513</v>
+        <v>0.5838436366271247</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.5713465852969499</v>
+        <v>0.6227855525187258</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1625830728740973</v>
+        <v>0.1751330593286864</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>29.47</v>
+        <v>28.89</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.003746549751914685</v>
+        <v>-0.01968102942721228</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.0369281390205316</v>
+        <v>-0.03956118806768272</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.02963455716195573</v>
+        <v>-0.05464660031015633</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.002722011751188802</v>
+        <v>-0.01701258966939978</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1611505235551927</v>
+        <v>0.1311667327343133</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2370015801610488</v>
+        <v>0.2126561156603912</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.2035559144319676</v>
+        <v>0.1840444316451022</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4895406658157264</v>
+        <v>0.4657904834346305</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.956345029965413</v>
+        <v>0.9355672630862324</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2506865625623933</v>
+        <v>0.2462430691473438</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>54.43</v>
+        <v>54.28</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.01466331188774683</v>
+        <v>-0.002755861198564857</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01874888935713925</v>
+        <v>-0.01844485482524372</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.00657055309976351</v>
+        <v>0.001845671346582423</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.02332674049414463</v>
+        <v>-0.02601831643369268</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.01018369442076783</v>
+        <v>-0.05171213858093671</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3950366858964738</v>
+        <v>0.3911921584232372</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3706345928104713</v>
+        <v>0.3809694112604924</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4511551984183082</v>
+        <v>0.4333207855939192</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.464323223363207</v>
+        <v>1.504296710346266</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3507217399739291</v>
+        <v>0.3579859010255115</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>57.38</v>
+        <v>29.29</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.05795433899425395</v>
+        <v>0.0006833091032072414</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.06471063577418834</v>
+        <v>-0.00475702984018711</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.04318826246236196</v>
+        <v>-0.004080208517761141</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-0.1069260534145489</v>
+        <v>0.02448411189938704</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.1737940447876787</v>
+        <v>0.1655392715354886</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3506355658261655</v>
+        <v>0.2447188151710744</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4820959578268682</v>
+        <v>0.1570156126023448</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.6253236881775166</v>
+        <v>0.3288281026570252</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.28301614997986</v>
+        <v>0.4597964588966101</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.4862470526273857</v>
+        <v>0.1343944731787368</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.27</v>
+        <v>57.44</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.01210236447255841</v>
+        <v>0.001045617941389132</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.01381401088936685</v>
+        <v>-0.06525633989330892</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.008468834557021521</v>
+        <v>-0.02528426388512894</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.02378455059624152</v>
+        <v>-0.1059922392730119</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.168463127713784</v>
+        <v>-0.2139044906718722</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2438688682502028</v>
+        <v>0.3520478146060717</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1535822713225479</v>
+        <v>0.4978236742974924</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3131111658743115</v>
+        <v>0.6142558544249008</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4556168015549942</v>
+        <v>2.39551894493584</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1333107804238041</v>
+        <v>0.503033703984618</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>65.61</v>
+        <v>65.39</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.02742363621743527</v>
+        <v>-0.00335316596031876</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.04358597566000655</v>
+        <v>-0.04204516051514617</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.038117556209042</v>
+        <v>-0.0004585567125728884</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.05026411602834768</v>
+        <v>0.04674240614513714</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2007686922262557</v>
+        <v>0.1237326161343932</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.02532187833132027</v>
+        <v>0.02188380391052958</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1630679115178717</v>
+        <v>0.1601497902246516</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3974792788472514</v>
+        <v>0.3746214930367548</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.338149206675457</v>
+        <v>2.261512719619074</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4945206319333748</v>
+        <v>0.4829950184671301</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>24.11</v>
+        <v>53.48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.03832908369145405</v>
+        <v>0.02629051843865482</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02117746662745867</v>
+        <v>0.03723813261843523</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.01752242417007022</v>
+        <v>0.02707892943491341</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.01174992394217189</v>
+        <v>0.03864823847154297</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2164480818154417</v>
+        <v>0.2072234867556377</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.3361721451421815</v>
+        <v>0.2092434778558478</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.04316102138241007</v>
+        <v>0.02881987914937834</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.03658644891484508</v>
+        <v>0.1072592400466046</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.3585923827545414</v>
+        <v>0.2185718709943452</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1075492782974627</v>
+        <v>0.06811262792705763</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>34.45</v>
+        <v>23.88</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01592453311581354</v>
+        <v>-0.009539670002588485</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.02380278069696218</v>
+        <v>0.02489270140333377</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.01683790345811442</v>
+        <v>0.004627627298467329</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01742469409192848</v>
+        <v>0.002098163542619602</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.02164885871321176</v>
+        <v>0.1815932826594537</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1325508023821431</v>
+        <v>0.3234255038108744</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1634272665119099</v>
+        <v>0.05060863568617968</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4171750735609296</v>
+        <v>0.0146189444475735</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6508697636382796</v>
+        <v>0.3694760986985599</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.181873344278805</v>
+        <v>0.1104989501843903</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>15.08</v>
+        <v>34.13</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01630789310138248</v>
+        <v>-0.009288815318937993</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.006675593092494658</v>
+        <v>-0.0104378252488263</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01823089104924835</v>
+        <v>-0.03314442476579327</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.009370839843033218</v>
+        <v>0.007974024007581626</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.05216844322227077</v>
+        <v>0.01819810865218163</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2138958041918853</v>
+        <v>0.1220307471395001</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2765481001322279</v>
+        <v>0.1366016151932823</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3065966973751848</v>
+        <v>0.4212009236958159</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8175344399939908</v>
+        <v>0.6560561487341372</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2203775683459672</v>
+        <v>0.1831097112386688</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>45.56</v>
+        <v>15.15</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02267120434404535</v>
+        <v>0.004641889600687454</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.007296083006733678</v>
+        <v>0.005976042258029723</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.008487472974385457</v>
+        <v>0.02364860968140503</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.007518800163858197</v>
+        <v>0.01405622784773763</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1616522171152097</v>
+        <v>-0.0625000147536251</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2725189155278496</v>
+        <v>0.2195305745016818</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.04688493100565649</v>
+        <v>0.293759442529278</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.0394644277496965</v>
+        <v>0.3105343079697374</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.2806344068334923</v>
+        <v>0.8415332719640614</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.08594639670712589</v>
+        <v>0.2257254116820402</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>17.38</v>
+        <v>45.33</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.005720845771654548</v>
+        <v>-0.005048277772247034</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.02633060003690746</v>
+        <v>0.0209459520994324</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.01473924251008818</v>
+        <v>0.008453861216139114</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.03337043363434367</v>
+        <v>0.002432565399870024</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.08354103296478543</v>
+        <v>0.1444080063762554</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.226619733041562</v>
+        <v>0.2660948865718264</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1041989886635752</v>
+        <v>0.05010943842815885</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1415029599497304</v>
+        <v>0.03026956363188993</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.8987517837019652</v>
+        <v>0.2827961032235751</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2382910432513097</v>
+        <v>0.08655707497377918</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>52.11</v>
+        <v>37.89</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.01539362666066069</v>
+        <v>-0.001581063823050344</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.006861074937606793</v>
+        <v>-0.005250741983151785</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.01734863643452478</v>
+        <v>0.01663533470001921</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.01204115190666322</v>
+        <v>-0.04870706382678769</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.1886405207340194</v>
+        <v>0.04207917364174318</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.1782662473541392</v>
+        <v>0.2131246009995302</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.006853220497689216</v>
+        <v>0.1186039563294887</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.06625127043635581</v>
+        <v>0.216044466277648</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.1818046542273863</v>
+        <v>1.157840064800576</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.05726023636635946</v>
+        <v>0.2922297963076455</v>
       </c>
     </row>
     <row r="15">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>37.95</v>
+        <v>17.3</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.005242483746790483</v>
+        <v>-0.004602987777274747</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01658459152935554</v>
+        <v>-0.01424501486427832</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.009308571888885897</v>
+        <v>-0.01029750056576673</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.04720062720784091</v>
+        <v>-0.0378198177134772</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.02761983345071117</v>
+        <v>0.08057457774744869</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2150456657449937</v>
+        <v>0.2209736174030075</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1236987942594066</v>
+        <v>0.09781173112358466</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2108909240068455</v>
+        <v>0.1418597576347436</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.150048794677982</v>
+        <v>0.897044424354257</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2906726445505012</v>
+        <v>0.2379197744662085</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>96.97</v>
+        <v>70.77</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01592461310695659</v>
+        <v>-0.001411120356143214</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.007878009616284487</v>
+        <v>0.003829739617963179</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.0007223910600819838</v>
+        <v>0.01915314163161796</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.00543588491586533</v>
+        <v>0.01608033155277622</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.09632565931513315</v>
+        <v>0.02997200988314952</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1545550462069933</v>
+        <v>0.09394777830232015</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.09665853566571769</v>
+        <v>0.2191054628774021</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.08587028815598874</v>
+        <v>0.2016489442426179</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.5427828253166105</v>
+        <v>0.8023949053199899</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.155495517801677</v>
+        <v>0.2169796525413428</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>116.12</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.01779302720528886</v>
+        <v>-0.004434364233914967</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.004969959013087166</v>
+        <v>0.009727019132296677</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.01450291521393665</v>
+        <v>-0.004023515819875811</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.005906984217387778</v>
+        <v>-0.009846144456129857</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.01868589282156208</v>
+        <v>0.09604903393053621</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2087020205625962</v>
+        <v>0.1494353286040069</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1167948393493303</v>
+        <v>0.08070835526502895</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1627452743479818</v>
+        <v>0.09748438882703425</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.09423050267042576</v>
+        <v>0.5440811522684965</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.03047218199378476</v>
+        <v>0.1558195621869314</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>70.87</v>
+        <v>114</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.0004231139443053866</v>
+        <v>-0.01825699876367282</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.01098436931842728</v>
+        <v>-0.01969215665576263</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.01956553831901986</v>
+        <v>-0.0209550188100871</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.01751616933202538</v>
+        <v>-0.02405613917750671</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.01133472052802831</v>
+        <v>-0.0006136556063074394</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.0954936516942515</v>
+        <v>0.186634749267536</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1978165841167467</v>
+        <v>0.093899519604556</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2039406096059813</v>
+        <v>0.1554113317658457</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7873244882407229</v>
+        <v>0.07039700058046483</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2135782990890678</v>
+        <v>0.02293560326685506</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>116.65</v>
+        <v>115.7</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.005950348800051408</v>
+        <v>-0.008144059710328944</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01884092754032396</v>
+        <v>-0.01246164790228121</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.0245839526886934</v>
+        <v>-0.00822909895192292</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.05904654047548541</v>
+        <v>-0.06670972163449362</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.04822124796379323</v>
+        <v>-0.05850762858748859</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1366061767187048</v>
+        <v>0.127349588148379</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1106430711370801</v>
+        <v>0.1081931226394308</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2032054369806695</v>
+        <v>0.1910349527423556</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4404277923525819</v>
+        <v>0.4353182425038489</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1293550480346046</v>
+        <v>0.1280180997233655</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>93.7</v>
+        <v>93.03</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01209759229894303</v>
+        <v>-0.007150460947350945</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.006468037600918963</v>
+        <v>-0.004494362575291788</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.008990016669278345</v>
+        <v>-0.01607619485351963</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.0187454283754519</v>
+        <v>-0.02576185086926286</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.005942553027325825</v>
+        <v>0.004115731944799528</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.04830781385610994</v>
+        <v>0.04081192977232884</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1118037843046817</v>
+        <v>0.1050040521374107</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1282440086089214</v>
+        <v>0.1320778960942863</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1586442514897863</v>
+        <v>0.1604585064422448</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.0503080733172081</v>
+        <v>0.05085599326770773</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>50.32</v>
+        <v>99.25</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.02386032125005444</v>
+        <v>0.002930486238988284</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.02120210378959497</v>
+        <v>-0.03349890310275405</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.01967664329245</v>
+        <v>-0.02676998692948152</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.06084363614823518</v>
+        <v>-0.02781855656543464</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.05697153074877592</v>
+        <v>-0.04932951581042178</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.07821578561047815</v>
+        <v>0.01517499364193675</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0672295198404611</v>
+        <v>0.1253756725036319</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1259072024986083</v>
+        <v>0.1099250050211091</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6625808440577143</v>
+        <v>0.2045961140005763</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1846614530300974</v>
+        <v>0.06401353519365705</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>98.95999999999999</v>
+        <v>50.15</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.0150293830783722</v>
+        <v>-0.003378342010657787</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.03931660001716819</v>
+        <v>-0.0290416254731074</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.04377233426229266</v>
+        <v>-0.008305283201105129</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.03065919645112447</v>
+        <v>-0.06401642754681225</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.04377233426229266</v>
+        <v>-0.07284153476787292</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.01220872988801625</v>
+        <v>0.0745732039253959</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1181057150698988</v>
+        <v>0.05876832908814644</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1018738137294304</v>
+        <v>0.1086928746667666</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1917299218923489</v>
+        <v>0.6725907097293116</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06021175367653497</v>
+        <v>0.1870341863607372</v>
       </c>
     </row>
     <row r="23">
@@ -1768,52 +1768,46 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>17.11</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.01663699868774859</v>
+        <v>-0.008647708866762471</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.03496891979087802</v>
+        <v>-0.04082518527861434</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.04199327963994048</v>
+        <v>-0.02835017437899257</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.05521810967959917</v>
+        <v>-0.1212001765066288</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1391478088476084</v>
+        <v>-0.07588602246085363</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1175702247812171</v>
+        <v>0.03117236976104776</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>-0.124808118768799</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>-0.1305894133623726</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>0.1695147284013139</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>0.05358254072171498</v>
-      </c>
+        <v>0.08182692312466711</v>
+      </c>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1824,46 +1818,52 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>67.06999999999999</v>
+        <v>13.36</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.02173275841347755</v>
+        <v>0.002250542621372364</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.03911179423458266</v>
+        <v>-0.02765648622787376</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03426922041755698</v>
+        <v>-0.03607503696864223</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.1135342790313271</v>
+        <v>-0.0511363828785657</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.05026908685485187</v>
+        <v>-0.06377020125401156</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.04016743491084385</v>
+        <v>-0.002058787241032811</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.09248859634896767</v>
-      </c>
-      <c r="N24" s="6" t="inlineStr"/>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr"/>
+        <v>0.1398501569137662</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0.05029669866319919</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0.04043209981986795</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0.01329970041612283</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1874,51 +1874,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>177.06</v>
+        <v>40.69</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.002478886993838025</v>
+        <v>-0.0007368023844480653</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.04374598154738096</v>
+        <v>-0.0190453453289684</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.0502601270466323</v>
+        <v>-0.04393803304140798</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.04198684914026696</v>
+        <v>-0.07015538877005734</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05720087219634085</v>
+        <v>-0.0515152172625627</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1488064052286029</v>
+        <v>0.01720844600535476</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.07085305521871677</v>
+        <v>0.07563740505164329</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.102519052843061</v>
+        <v>0.06703458781580718</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5325489563164001</v>
+        <v>0.2862922573727951</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1529348995574225</v>
+        <v>0.08754328656634303</v>
       </c>
     </row>
     <row r="26">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>40.72</v>
+        <v>16.83</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.006829238519435954</v>
+        <v>-0.01636473855390208</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01903148958741996</v>
+        <v>-0.01923076495573639</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.04435577006749181</v>
+        <v>-0.03497709814631744</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.06946977187917691</v>
+        <v>-0.07067921830515389</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.05740739579717502</v>
+        <v>0.09784735860829485</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.01795848024086544</v>
+        <v>0.09928148023704697</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.08121097204116801</v>
+        <v>-0.1297828443163674</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.06425179124142399</v>
+        <v>-0.1495705333443849</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2829320524008649</v>
+        <v>0.1543209884618488</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.08659545761881615</v>
+        <v>0.04900010282973066</v>
       </c>
     </row>
     <row r="27">
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>13.33</v>
+        <v>174.19</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.0118606263993174</v>
+        <v>-0.01620916726962984</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.04169661610844377</v>
+        <v>-0.03995811233711433</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.0478571483067104</v>
+        <v>-0.04490625190337449</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.05326704574317853</v>
+        <v>-0.05751544454905744</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.0612675983975316</v>
+        <v>0.0285191415543693</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.004299653309375318</v>
+        <v>0.1301852100458303</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1326026182027622</v>
+        <v>-0.0757076303706905</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.03686571198737609</v>
+        <v>-0.1119119177679682</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.03063239787941074</v>
+        <v>0.5162720721463814</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.01010827773558653</v>
+        <v>0.1488386693727046</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>17.04</v>
+        <v>25.98</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.004717089349841386</v>
+        <v>-0.011415568362661</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.0229357572408978</v>
+        <v>-0.0420354447536696</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.02012642244998775</v>
+        <v>-0.04939628193334666</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.05595558804564704</v>
+        <v>-0.1542968709982232</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.03126772213129458</v>
+        <v>-0.09791665866419097</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.04149936155635459</v>
+        <v>-0.03816196528175475</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.001663633825651489</v>
+        <v>0.03607906542502515</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.005104123305394559</v>
+        <v>0.06946059574937169</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3791744513960797</v>
+        <v>1.054922436910451</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1131142292136444</v>
+        <v>0.2713500506754893</v>
       </c>
     </row>
     <row r="29">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>26.28</v>
+        <v>16.65</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.01277235694473711</v>
+        <v>-0.02288739882881641</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.04366808135300149</v>
+        <v>-0.02972029332265691</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.04954788248773179</v>
+        <v>-0.03534186571624864</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.1445312085270407</v>
+        <v>-0.07756230901416172</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.0746478507169247</v>
+        <v>-0.05879032697173103</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.02705524795165459</v>
+        <v>0.01766215028845664</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.04968130826340422</v>
+        <v>-0.01790009562918382</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.09414847723344577</v>
+        <v>-0.02412501098354669</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.07322398903673</v>
+        <v>0.3687219249483871</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2751132005680523</v>
+        <v>0.1102950612799392</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>54.33</v>
+        <v>53.32</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.0003682647257952087</v>
+        <v>-0.01859013624500117</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01807337731622372</v>
+        <v>-0.01840942572934667</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.009119095081204454</v>
+        <v>-0.01678037719147252</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.01771830623583326</v>
+        <v>-0.03597905675387958</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.01558247539506374</v>
+        <v>-0.04495794472344639</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.03168966999482925</v>
+        <v>0.01251041846706524</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.05177269763024461</v>
+        <v>-0.07771316444569198</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.03885176321834227</v>
+        <v>-0.06339100867247549</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.182409759825005</v>
+        <v>0.164136011887956</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.05744065110391849</v>
+        <v>0.05196488070146388</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>15.83</v>
+        <v>15.53</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.01021058370345274</v>
+        <v>-0.01895137032095628</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02942977056735263</v>
+        <v>-0.02633229349946276</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.05209585625673141</v>
+        <v>-0.05707344381132506</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.09594519036068927</v>
+        <v>-0.1130782678486055</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.01615911910603796</v>
+        <v>-0.05477787921410271</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.03234598996409632</v>
+        <v>0.01278161880893247</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.05559277790358019</v>
+        <v>-0.08599847198542665</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1024492021948765</v>
+        <v>-0.1147684487102421</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2266687733192547</v>
+        <v>0.2189498505766296</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.07047312855644439</v>
+        <v>0.06822305310015331</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>62.6</v>
+        <v>61.22</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.001276353392871354</v>
+        <v>-0.02204468509673307</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02019096772344553</v>
+        <v>-0.03301216406969798</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02370561770666735</v>
+        <v>-0.02809970488330293</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.05122771613889754</v>
+        <v>-0.07214310236512378</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.05180245899489133</v>
+        <v>-0.08394434320881161</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.02723386179371468</v>
+        <v>0.004588814789771245</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.05903624779054151</v>
+        <v>-0.0839700686820275</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.03422267650895294</v>
+        <v>-0.06643883643702964</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3497244163525575</v>
+        <v>0.3441189223333569</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1051342401158817</v>
+        <v>0.1036022189675243</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>124.38</v>
+        <v>122.9</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01605890633559004</v>
+        <v>-0.0118989850476009</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03078005549190954</v>
+        <v>-0.05081861614751859</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.008134005263552124</v>
+        <v>-0.02745905788782599</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.06142474159831091</v>
+        <v>-0.07259283456408072</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.07415632593271049</v>
+        <v>-0.09330850235352839</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1086565004945307</v>
+        <v>-0.1192625834674225</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.03260540102519505</v>
+        <v>-0.04941664701621107</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.01154006174473565</v>
+        <v>-0.02800838475755341</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4306032087346576</v>
+        <v>0.4191737600030447</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1267815614055074</v>
+        <v>0.123772820861098</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>112.98</v>
+        <v>111.77</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01370580229591822</v>
+        <v>-0.01070991925929099</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.03715692105871604</v>
+        <v>-0.03886838280914839</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.030963145161227</v>
+        <v>-0.02545998549290851</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.09832401751606645</v>
+        <v>-0.1079808944865113</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1000477733550843</v>
+        <v>-0.1179766764016905</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.03445672507691699</v>
+        <v>-0.04479761559269468</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.04846613873624017</v>
+        <v>-0.05962650078683707</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09285240582392029</v>
+        <v>-0.1016849909659044</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2860824198352034</v>
+        <v>0.2993116624658307</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08748414505203361</v>
+        <v>0.09120022169762065</v>
       </c>
     </row>
   </sheetData>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.05026411602834768</v>
+        <v>0.04990044559953688</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1445312085270407</v>
+        <v>-0.1542968709982232</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02920999634737864</v>
+        <v>0.04674240614513714</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1135342790313271</v>
+        <v>-0.1212001765066288</v>
       </c>
     </row>
     <row r="19">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E19" s="11" t="n">
-        <v>0.02378455059624152</v>
+        <v>0.03864823847154297</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1069260534145489</v>
+        <v>-0.1130782678486055</v>
       </c>
     </row>
     <row r="20">
@@ -3163,21 +3163,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.01751616933202538</v>
+        <v>0.02448411189938704</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09832401751606645</v>
+        <v>-0.1079808944865113</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.01742469409192848</v>
+        <v>0.01608033155277622</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.09594519036068927</v>
+        <v>-0.1059922392730119</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01204115190666322</v>
+        <v>0.01405622784773763</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.06946977187917691</v>
+        <v>-0.07756230901416172</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.01174992394217189</v>
+        <v>0.007974024007581626</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.06142474159831091</v>
+        <v>-0.07259283456408072</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.009370839843033218</v>
+        <v>0.002432565399870024</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06084363614823518</v>
+        <v>-0.07214310236512378</v>
       </c>
     </row>
     <row r="25">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.007518800163858197</v>
+        <v>0.002098163542619602</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.05904654047548541</v>
+        <v>-0.07067921830515389</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002722011751188802</v>
+        <v>-0.009846144456129857</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.05595558804564704</v>
+        <v>-0.07015538877005734</v>
       </c>
     </row>
     <row r="27"/>
@@ -3539,21 +3539,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2164480818154417</v>
+        <v>0.2072234867556377</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1737940447876787</v>
+        <v>-0.2139044906718722</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2007686922262557</v>
+        <v>0.1913370693259553</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1000477733550843</v>
+        <v>-0.1179766764016905</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1886405207340194</v>
+        <v>0.1815932826594537</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.0746478507169247</v>
+        <v>-0.09791665866419097</v>
       </c>
     </row>
     <row r="34">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.168463127713784</v>
+        <v>0.1655392715354886</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.07415632593271049</v>
+        <v>-0.09330850235352839</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1616522171152097</v>
+        <v>0.1444080063762554</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.0612675983975316</v>
+        <v>-0.08905135096805994</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1611505235551927</v>
+        <v>0.1311667327343133</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.05740739579717502</v>
+        <v>-0.08394434320881161</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1391478088476084</v>
+        <v>0.1237326161343932</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.05697153074877592</v>
+        <v>-0.07588602246085363</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1308046952030995</v>
+        <v>0.09784735860829485</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.05216844322227077</v>
+        <v>-0.07284153476787292</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.09632565931513315</v>
+        <v>0.09604903393053621</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.05180245899489133</v>
+        <v>-0.06377020125401156</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.08354103296478543</v>
+        <v>0.08057457774744869</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.05026908685485187</v>
+        <v>-0.0625000147536251</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4653745226082946</v>
+        <v>0.4633142694510595</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1086565004945307</v>
+        <v>-0.1192625834674225</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3950366858964738</v>
+        <v>0.3911921584232372</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.03445672507691699</v>
+        <v>-0.04479761559269468</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3506355658261655</v>
+        <v>0.3520478146060717</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.02705524795165459</v>
+        <v>-0.03816196528175475</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3361721451421815</v>
+        <v>0.3234255038108744</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.004299653309375318</v>
+        <v>-0.002058787241032811</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2725189155278496</v>
+        <v>0.2660948865718264</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,21 +4252,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.01220872988801625</v>
+        <v>0.004588814789771245</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2438688682502028</v>
+        <v>0.2447188151710744</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.01795848024086544</v>
+        <v>0.01251041846706524</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2370015801610488</v>
+        <v>0.2209736174030075</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.02532187833132027</v>
+        <v>0.01278161880893247</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.226619733041562</v>
+        <v>0.2195305745016818</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.02723386179371468</v>
+        <v>0.01517499364193675</v>
       </c>
     </row>
     <row r="53">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2150456657449937</v>
+        <v>0.2131246009995302</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.03168966999482925</v>
+        <v>0.01720844600535476</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2138958041918853</v>
+        <v>0.2126561156603912</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.03234598996409632</v>
+        <v>0.01766215028845664</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8372505760264604</v>
+        <v>0.8031457666284911</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1305894133623726</v>
+        <v>-0.1495705333443849</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.6253236881775166</v>
+        <v>0.6142558544249008</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4628,21 +4628,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.102519052843061</v>
+        <v>-0.1147684487102421</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5516155178388513</v>
+        <v>0.5838436366271247</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4673,21 +4673,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1024492021948765</v>
+        <v>-0.1119119177679682</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4895406658157264</v>
+        <v>0.4657904834346305</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09285240582392029</v>
+        <v>-0.1016849909659044</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4511551984183082</v>
+        <v>0.4333207855939192</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.03885176321834227</v>
+        <v>-0.06643883643702964</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4171750735609296</v>
+        <v>0.4212009236958159</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4808,21 +4808,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K64" s="11" t="n">
-        <v>-0.03422267650895294</v>
+        <v>-0.06339100867247549</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3974792788472514</v>
+        <v>0.3746214930367548</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.01154006174473565</v>
+        <v>-0.02800838475755341</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3131111658743115</v>
+        <v>0.3288281026570252</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.005104123305394559</v>
+        <v>-0.02412501098354669</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3065966973751848</v>
+        <v>0.3105343079697374</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.03658644891484508</v>
+        <v>0.0146189444475735</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2108909240068455</v>
+        <v>0.216044466277648</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.03686571198737609</v>
+        <v>0.03026956363188993</v>
       </c>
     </row>
     <row r="69"/>
@@ -5072,21 +5072,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.338149206675457</v>
+        <v>2.39551894493584</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.03063239787941074</v>
+        <v>0.04043209981986795</v>
       </c>
     </row>
     <row r="74">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.28301614997986</v>
+        <v>2.261512719619074</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09423050267042576</v>
+        <v>0.07039700058046483</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.114332425213759</v>
+        <v>2.141324511609163</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5184,21 +5184,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1586442514897863</v>
+        <v>0.1543209884618488</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.464323223363207</v>
+        <v>1.504296710346266</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1695147284013139</v>
+        <v>0.1604585064422448</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.150048794677982</v>
+        <v>1.157840064800576</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1818046542273863</v>
+        <v>0.164136011887956</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.07322398903673</v>
+        <v>1.054922436910451</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5319,21 +5319,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.182409759825005</v>
+        <v>0.2045961140005763</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.956345029965413</v>
+        <v>0.9355672630862324</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1917299218923489</v>
+        <v>0.2185718709943452</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8987517837019652</v>
+        <v>0.897044424354257</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2266687733192547</v>
+        <v>0.2189498505766296</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8175344399939908</v>
+        <v>0.8415332719640614</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2806344068334923</v>
+        <v>0.2827961032235751</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7873244882407229</v>
+        <v>0.8023949053199899</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2829320524008649</v>
+        <v>0.2862922573727951</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -686,7 +686,7 @@
         <v>0.5412360524232969</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5838436366271247</v>
+        <v>0.5838435357798388</v>
       </c>
       <c r="O3" s="6" t="n">
         <v>0.6227855525187258</v>
@@ -745,10 +745,10 @@
         <v>0.4657904834346305</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.9355672630862324</v>
+        <v>0.9355675104289576</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2462430691473438</v>
+        <v>0.2462431222324093</v>
       </c>
     </row>
     <row r="5">
@@ -798,7 +798,7 @@
         <v>0.3809694112604924</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4333207855939192</v>
+        <v>0.4333209299739369</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>1.504296710346266</v>
@@ -857,10 +857,10 @@
         <v>0.3288281026570252</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4597964588966101</v>
+        <v>0.4597963201267128</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1343944731787368</v>
+        <v>0.1343944372331296</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.6142558544249008</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.39551894493584</v>
+        <v>2.395518562086477</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.503033703984618</v>
+        <v>0.5030336474949202</v>
       </c>
     </row>
     <row r="8">
@@ -963,7 +963,7 @@
         <v>0.02188380391052958</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1601497902246516</v>
+        <v>0.1601498687440395</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>0.3746214930367548</v>
@@ -1193,10 +1193,10 @@
         <v>0.3105343079697374</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8415332719640614</v>
+        <v>0.8415334854388807</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2257254116820402</v>
+        <v>0.2257254590450184</v>
       </c>
     </row>
     <row r="13">
@@ -1361,10 +1361,10 @@
         <v>0.1418597576347436</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.897044424354257</v>
+        <v>0.8970442259691986</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2379197744662085</v>
+        <v>0.2379197313140307</v>
       </c>
     </row>
     <row r="16">
@@ -1411,16 +1411,16 @@
         <v>0.09394777830232015</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2191054628774021</v>
+        <v>0.2191055429886479</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>0.2016489442426179</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8023949053199899</v>
+        <v>0.802394555100173</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2169796525413428</v>
+        <v>0.2169795737183617</v>
       </c>
     </row>
     <row r="17">
@@ -1470,13 +1470,13 @@
         <v>0.08070835526502895</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.09748438882703425</v>
+        <v>0.09748448401444554</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5440811522684965</v>
+        <v>0.5440810580593658</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1558195621869314</v>
+        <v>0.1558195386802312</v>
       </c>
     </row>
     <row r="18">
@@ -1585,10 +1585,10 @@
         <v>0.1910349527423556</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4353182425038489</v>
+        <v>0.4353183783518262</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1280180997233655</v>
+        <v>0.1280181353110534</v>
       </c>
     </row>
     <row r="20">
@@ -1635,16 +1635,16 @@
         <v>0.04081192977232884</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1050040521374107</v>
+        <v>0.1050041522744714</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0.1320778960942863</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1604585064422448</v>
+        <v>0.1604587273222327</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05085599326770773</v>
+        <v>0.05085605994050502</v>
       </c>
     </row>
     <row r="21">
@@ -1691,7 +1691,7 @@
         <v>0.01517499364193675</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1253756725036319</v>
+        <v>0.1253755751494601</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>0.1099250050211091</v>
@@ -1859,10 +1859,10 @@
         <v>0.05029669866319919</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.04043209981986795</v>
+        <v>0.04043202254805656</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.01329970041612283</v>
+        <v>0.0132996753305501</v>
       </c>
     </row>
     <row r="25">
@@ -2024,7 +2024,7 @@
         <v>-0.0757076303706905</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1119119177679682</v>
+        <v>-0.1119118486789593</v>
       </c>
       <c r="O27" s="6" t="n">
         <v>0.5162720721463814</v>
@@ -2077,7 +2077,7 @@
         <v>-0.03816196528175475</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.03607906542502515</v>
+        <v>0.03607914423419878</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>0.06946059574937169</v>
@@ -2195,10 +2195,10 @@
         <v>-0.06339100867247549</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.164136011887956</v>
+        <v>0.1641361088445663</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.05196488070146388</v>
+        <v>0.05196490990622626</v>
       </c>
     </row>
     <row r="31">
@@ -2301,16 +2301,16 @@
         <v>0.004588814789771245</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.0839700686820275</v>
+        <v>-0.08397017325417311</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.06643883643702964</v>
+        <v>-0.06643872782389604</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3441189223333569</v>
+        <v>0.3441186971833021</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1036022189675243</v>
+        <v>0.1036021573469563</v>
       </c>
     </row>
     <row r="33">
@@ -2354,7 +2354,7 @@
         <v>-0.09330850235352839</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1192625834674225</v>
+        <v>-0.1192624871596978</v>
       </c>
       <c r="M33" s="6" t="n">
         <v>-0.04941664701621107</v>
@@ -2363,10 +2363,10 @@
         <v>-0.02800838475755341</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4191737600030447</v>
+        <v>0.4191738850316449</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.123772820861098</v>
+        <v>0.1237728538623983</v>
       </c>
     </row>
     <row r="34">
@@ -2419,10 +2419,10 @@
         <v>-0.1016849909659044</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2993116624658307</v>
+        <v>0.2993117777027257</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09120022169762065</v>
+        <v>0.09120025395739972</v>
       </c>
     </row>
   </sheetData>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1192625834674225</v>
+        <v>-0.1192624871596978</v>
       </c>
     </row>
     <row r="46">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5838436366271247</v>
+        <v>0.5838435357798388</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1119119177679682</v>
+        <v>-0.1119118486789593</v>
       </c>
     </row>
     <row r="62">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4333207855939192</v>
+        <v>0.4333209299739369</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.06643883643702964</v>
+        <v>-0.06643872782389604</v>
       </c>
     </row>
     <row r="64">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.39551894493584</v>
+        <v>2.395518562086477</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.04043209981986795</v>
+        <v>0.04043202254805656</v>
       </c>
     </row>
     <row r="74">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1604585064422448</v>
+        <v>0.1604587273222327</v>
       </c>
     </row>
     <row r="77">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.164136011887956</v>
+        <v>0.1641361088445663</v>
       </c>
     </row>
     <row r="78">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9355672630862324</v>
+        <v>0.9355675104289576</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.897044424354257</v>
+        <v>0.8970442259691986</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8415332719640614</v>
+        <v>0.8415334854388807</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8023949053199899</v>
+        <v>0.802394555100173</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,10 +490,10 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>213.08</v>
+        <v>213.88</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.001405956719902512</v>
+        <v>0.003754472709232015</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.03909807516999009</v>
+        <v>-0.02878937563685102</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.006233506603987582</v>
+        <v>0.0004210281093897095</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>-0.03961776481533752</v>
+        <v>-0.03601203592290536</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.08905135096805994</v>
+        <v>-0.08071863871613683</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4633142694510595</v>
+        <v>0.4231315892419893</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7137480668130991</v>
+        <v>0.7231104360808718</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8031457666284911</v>
+        <v>0.8079478770558193</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.141324511609163</v>
+        <v>2.153118883409304</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4645502176415688</v>
+        <v>0.466380854844467</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>94.89</v>
+        <v>92.44</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.02010323386440827</v>
+        <v>-0.02581933780167622</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.0121599934895833</v>
+        <v>-0.02272961179535571</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.008824174490730252</v>
+        <v>-0.02097008860343619</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.04990044559953688</v>
+        <v>0.02279271133647187</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1913370693259553</v>
+        <v>0.1687951286086971</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.1946615607031636</v>
+        <v>0.156122317730071</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5412360524232969</v>
+        <v>0.5455436976625052</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5838435357798388</v>
+        <v>0.5178751870050209</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.6227855525187258</v>
+        <v>0.580886304158565</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1751330593286864</v>
+        <v>0.1649310265509898</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>28.89</v>
+        <v>54.45</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.01968102942721228</v>
+        <v>0.003131945237025757</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.03956118806768272</v>
+        <v>-0.01447962420019089</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.05464660031015633</v>
+        <v>0.004056817675828661</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.01701258966939978</v>
+        <v>-0.02296785913889698</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1311667327343133</v>
+        <v>-0.02349350068197298</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2126561156603912</v>
+        <v>0.3734302905087741</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.1840444316451022</v>
+        <v>0.3805433098434892</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4657904834346305</v>
+        <v>0.4443688325576396</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.9355675104289576</v>
+        <v>1.512140030500334</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2462431222324093</v>
+        <v>0.3594021360210098</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>54.28</v>
+        <v>28.85</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.002755861198564857</v>
+        <v>-0.001384527830521232</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01844485482524372</v>
+        <v>-0.02959970313879146</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.001845671346582423</v>
+        <v>-0.06634301819962463</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.02601831643369268</v>
+        <v>-0.01837356309605453</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.05171213858093671</v>
+        <v>0.1371698631107134</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3911921584232372</v>
+        <v>0.1922506943303155</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3809694112604924</v>
+        <v>0.190834085655889</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4333209299739369</v>
+        <v>0.4693611041383818</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.504296710346266</v>
+        <v>0.9328874163426437</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3579859010255115</v>
+        <v>0.2456676507670512</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29.29</v>
+        <v>57.84</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.0006833091032072414</v>
+        <v>0.006963815032072551</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.00475702984018711</v>
+        <v>-0.06073402999771782</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.004080208517761141</v>
+        <v>-0.02609865723168725</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.02448411189938704</v>
+        <v>-0.09976653459007179</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1655392715354886</v>
+        <v>-0.169323532470071</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2447188151710744</v>
+        <v>0.3291223970192416</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1570156126023448</v>
+        <v>0.509628275265853</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3288281026570252</v>
+        <v>0.6239044670412621</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4597963201267128</v>
+        <v>2.419164325290817</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1343944372331296</v>
+        <v>0.5065145293192554</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>57.44</v>
+        <v>29.29</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.001045617941389132</v>
+        <v>0</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.06525633989330892</v>
+        <v>0.003769726154939423</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.02528426388512894</v>
+        <v>-0.01744376248678337</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.1059922392730119</v>
+        <v>0.02448411189938704</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.2139044906718722</v>
+        <v>0.1687949537003668</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3520478146060717</v>
+        <v>0.2271223811249856</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4978236742974924</v>
+        <v>0.163107185410001</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.6142558544249008</v>
+        <v>0.3298278603183313</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.395518562086477</v>
+        <v>0.4597964588966101</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5030336474949202</v>
+        <v>0.1343944731787368</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>65.39</v>
+        <v>53.74</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.00335316596031876</v>
+        <v>0.004861670502168458</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.04204516051514617</v>
+        <v>0.04572878608151387</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.0004585567125728884</v>
+        <v>0.01876780433112413</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.04674240614513714</v>
+        <v>0.04369780397464917</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1237326161343932</v>
+        <v>0.2128187770912586</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.02188380391052958</v>
+        <v>0.1976590437392864</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1601498687440395</v>
+        <v>0.03904742264573935</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3746214930367548</v>
+        <v>0.1114963213826101</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.261512719619074</v>
+        <v>0.2244962723475745</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4829950184671301</v>
+        <v>0.06984079861236703</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>53.48</v>
+        <v>23.73</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.02629051843865482</v>
+        <v>-0.006281391281483528</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.03723813261843523</v>
+        <v>0.02240415675464402</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.02707892943491341</v>
+        <v>0.0206451416015625</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.03864823847154297</v>
+        <v>-0.004196407125047763</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2072234867556377</v>
+        <v>0.1882824415706124</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2092434778558478</v>
+        <v>0.303246899966469</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.02881987914937834</v>
+        <v>0.0373193382722925</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1072592400466046</v>
+        <v>0.01562570918714701</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2185718709943452</v>
+        <v>0.3608738834719947</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.06811262792705763</v>
+        <v>0.1081689052370598</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>23.88</v>
+        <v>15.09</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.009539670002588485</v>
+        <v>-0.003960360887996117</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.02489270140333377</v>
+        <v>0.005329774982422819</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.004627627298467329</v>
+        <v>0.01684636101276604</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.002098163542619602</v>
+        <v>0.01004019922474053</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1815932826594537</v>
+        <v>-0.03946530134014004</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.3234255038108744</v>
+        <v>0.202315605061469</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.05060863568617968</v>
+        <v>0.2969360922377167</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.0146189444475735</v>
+        <v>0.3032319353271951</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3694760986985599</v>
+        <v>0.8342401356198315</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1104989501843903</v>
+        <v>0.2241051658832365</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>34.13</v>
+        <v>34.18</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.009288815318937993</v>
+        <v>0.001464964415347048</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.0104378252488263</v>
+        <v>-0.001168933784349013</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.03314442476579327</v>
+        <v>-0.03826675788737477</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.007974024007581626</v>
+        <v>0.009450670084346857</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.01819810865218163</v>
+        <v>0.02735196377791937</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1220307471395001</v>
+        <v>0.1129660790048386</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1366016151932823</v>
+        <v>0.1447752444107915</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4212009236958159</v>
+        <v>0.41047057023418</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6560561487341372</v>
+        <v>0.6584823655517116</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1831097112386688</v>
+        <v>0.183687203737831</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>15.15</v>
+        <v>64.66</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.004641889600687454</v>
+        <v>-0.011163721277762</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.005976042258029723</v>
+        <v>-0.06181071706347563</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.02364860968140503</v>
+        <v>-0.03779752085538235</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.01405622784773763</v>
+        <v>0.03505686567331878</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.0625000147536251</v>
+        <v>0.08508144817148988</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2195305745016818</v>
+        <v>0.002071747591572803</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.293759442529278</v>
+        <v>0.1542375258933812</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.3105343079697374</v>
+        <v>0.392537693918489</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8415334854388807</v>
+        <v>2.225102407491725</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2257254590450184</v>
+        <v>0.4774558200173336</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>45.33</v>
+        <v>44.86</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.005048277772247034</v>
+        <v>-0.0103684359523043</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.0209459520994324</v>
+        <v>0.0108156721650281</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.008453861216139114</v>
+        <v>-0.004659398400146286</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.002432565399870024</v>
+        <v>-0.007961092450982532</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1444080063762554</v>
+        <v>0.1189823008133801</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2660948865718264</v>
+        <v>0.2420531141843112</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.05010943842815885</v>
+        <v>0.03740533719744654</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.03026956363188993</v>
+        <v>0.02329777626097917</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2827961032235751</v>
+        <v>0.2694955139874358</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08655707497377918</v>
+        <v>0.08278872168531293</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>37.89</v>
+        <v>69.58</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.001581063823050344</v>
+        <v>-0.01681496210906364</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.005250741983151785</v>
+        <v>-0.0002873080963333718</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.01663533470001921</v>
+        <v>-0.008125440946910589</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.04870706382678769</v>
+        <v>-0.001005020722048555</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.04207917364174318</v>
+        <v>0.02819582101075357</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2131246009995302</v>
+        <v>0.07424691616000123</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1186039563294887</v>
+        <v>0.2065359659571271</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.216044466277648</v>
+        <v>0.189458904508452</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.157840064800576</v>
+        <v>0.7720875311160065</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2922297963076455</v>
+        <v>0.2101198640713609</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>17.3</v>
+        <v>16.96</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.004602987777274747</v>
+        <v>-0.01965318887757705</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01424501486427832</v>
+        <v>-0.02863688580858259</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.01029750056576673</v>
+        <v>-0.04072405024180603</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.0378198177134772</v>
+        <v>-0.0567297265702158</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.08057457774744869</v>
+        <v>0.04497840806074005</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2209736174030075</v>
+        <v>0.1887112639509667</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.09781173112358466</v>
+        <v>0.08072588160067906</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1418597576347436</v>
+        <v>0.1228843371891877</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8970442259691986</v>
+        <v>0.859761257487109</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2379197313140307</v>
+        <v>0.2297563263491766</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>70.77</v>
+        <v>36.92</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.001411120356143214</v>
+        <v>-0.02560045490441809</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.003829739617963179</v>
+        <v>-0.02739728505295858</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01915314163161796</v>
+        <v>-0.0299527893644721</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.01608033155277622</v>
+        <v>-0.07306059574018153</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.02997200988314952</v>
+        <v>0.006817562380238007</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.09394777830232015</v>
+        <v>0.1743469118621237</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2191055429886479</v>
+        <v>0.09586036367457296</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2016489442426179</v>
+        <v>0.192582405361815</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.802394555100173</v>
+        <v>1.102598605922819</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2169795737183617</v>
+        <v>0.281107156882251</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>96.54000000000001</v>
+        <v>95.67</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.004434364233914967</v>
+        <v>-0.009011836941489992</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.009727019132296677</v>
+        <v>0.008113768500376928</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.004023515819875811</v>
+        <v>-0.020075787561328</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.009846144456129857</v>
+        <v>-0.01876924954927883</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.09604903393053621</v>
+        <v>0.0815057558115917</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1494353286040069</v>
+        <v>0.1304914851114538</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.08070835526502895</v>
+        <v>0.07869482624410495</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.09748448401444554</v>
+        <v>0.09832463262491498</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5440810580593658</v>
+        <v>0.5301660513396915</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1558195386802312</v>
+        <v>0.1523370373183539</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>114</v>
+        <v>112.83</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.01825699876367282</v>
+        <v>-0.0102631418328536</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.01969215665576263</v>
+        <v>-0.02404635208563399</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.0209550188100871</v>
+        <v>-0.03638222427253923</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.02405613917750671</v>
+        <v>-0.03407238944203073</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.0006136556063074394</v>
+        <v>-0.008175108014344845</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.186634749267536</v>
+        <v>0.1732349379152753</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.093899519604556</v>
+        <v>0.1007032468349724</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1554113317658457</v>
+        <v>0.155056163979137</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.07039700058046483</v>
+        <v>0.05941136434604655</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.02293560326685506</v>
+        <v>0.01942405148148429</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>115.7</v>
+        <v>92.63</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.008144059710328944</v>
+        <v>-0.004299704731028364</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01246164790228121</v>
+        <v>0.005754601390637326</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.00822909895192292</v>
+        <v>-0.02474211434468299</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.06670972163449362</v>
+        <v>-0.02995078724822853</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.05850762858748859</v>
+        <v>-0.002559652379539368</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.127349588148379</v>
+        <v>0.03289795397507334</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1081931226394308</v>
+        <v>0.1039591302679519</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1910349527423556</v>
+        <v>0.1205959689664335</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4353183783518262</v>
+        <v>0.1554689874770572</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1280181353110534</v>
+        <v>0.04934773926099223</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>93.03</v>
+        <v>113.75</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.007150460947350945</v>
+        <v>-0.01685390665234421</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.004494362575291788</v>
+        <v>-0.01412720828756719</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.01607619485351963</v>
+        <v>-0.02993349882556384</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.02576185086926286</v>
+        <v>-0.08243930886560624</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.004115731944799528</v>
+        <v>-0.06823395892951001</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.04081192977232884</v>
+        <v>0.09414233924823501</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1050041522744714</v>
+        <v>0.09307658436441479</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1320778960942863</v>
+        <v>0.1705182560208782</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1604587273222327</v>
+        <v>0.4111276563866904</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05085605994050502</v>
+        <v>0.1216450253536356</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>99.25</v>
+        <v>98.44</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.002930486238988284</v>
+        <v>-0.00816118446945846</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.03349890310275405</v>
+        <v>-0.03442858864054588</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.02676998692948152</v>
+        <v>-0.05218561657128573</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.02781855656543464</v>
+        <v>-0.03575270866308855</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.04932951581042178</v>
+        <v>-0.0588009763057652</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.01517499364193675</v>
+        <v>0.002711956661538339</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1253755751494601</v>
+        <v>0.1212730658587793</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1099250050211091</v>
+        <v>0.1075858223279176</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2045961140005763</v>
+        <v>0.1947652935357511</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.06401353519365705</v>
+        <v>0.0611111208523818</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>50.15</v>
+        <v>50.06</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.003378342010657787</v>
+        <v>-0.001794619139571685</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.0290416254731074</v>
+        <v>-0.02130987527021699</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.008305283201105129</v>
+        <v>-0.012623261933287</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.06401642754681225</v>
+        <v>-0.06569616158026148</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.07284153476787292</v>
+        <v>-0.07089828543238086</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.0745732039253959</v>
+        <v>0.06098313073779282</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.05876832908814644</v>
+        <v>0.05752659927889892</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1086928746667666</v>
+        <v>0.1083891908875607</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6725907097293116</v>
+        <v>0.6695889402206827</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1870341863607372</v>
+        <v>0.1863236445767378</v>
       </c>
     </row>
     <row r="23">
@@ -1768,46 +1768,52 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>66.48999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.008647708866762471</v>
+        <v>-0.004490978105107568</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.04082518527861434</v>
+        <v>-0.02061853715348017</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02835017437899257</v>
+        <v>-0.04999998637608116</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.1212001765066288</v>
+        <v>-0.05539770860779125</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.07588602246085363</v>
+        <v>-0.06073443968535208</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.03117236976104776</v>
+        <v>-0.007268915195823289</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.08182692312466711</v>
-      </c>
-      <c r="N23" s="6" t="inlineStr"/>
-      <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="6" t="inlineStr"/>
+        <v>0.135671147686522</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0.05605174979270555</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>0.03575946511494044</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0.01178049663777636</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1818,52 +1824,46 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>13.36</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.002250542621372364</v>
+        <v>-0.001353531971455602</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02765648622787376</v>
+        <v>-0.02796071001285749</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03607503696864223</v>
+        <v>-0.03136398876970981</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.0511363828785657</v>
+        <v>-0.1223896601642367</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.06377020125401156</v>
+        <v>-0.0835058064486236</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>-0.002058787241032811</v>
+        <v>0.01856111426840679</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1398501569137662</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>0.05029669866319919</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>0.04043202254805656</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>0.0132996753305501</v>
-      </c>
+        <v>0.08540370647118745</v>
+      </c>
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>40.69</v>
+        <v>40.41</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.0007368023844480653</v>
+        <v>-0.006881267848288464</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.0190453453289684</v>
+        <v>-0.01559072841761799</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.04393803304140798</v>
+        <v>-0.04219006487878907</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.07015538877005734</v>
+        <v>-0.07655389859721828</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0515152172625627</v>
+        <v>-0.06023256168809044</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.01720844600535476</v>
+        <v>0.001979510440054177</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.07563740505164329</v>
+        <v>0.07607188278364463</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.06703458781580718</v>
+        <v>0.06546470583206299</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2862922573727951</v>
+        <v>0.2774409358186334</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.08754328656634303</v>
+        <v>0.08504298379794117</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.83</v>
+        <v>16.57</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.01636473855390208</v>
+        <v>-0.0154486173535634</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01923076495573639</v>
+        <v>-0.01603328119460734</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.03497709814631744</v>
+        <v>-0.06752958537011045</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.07067921830515389</v>
+        <v>-0.08503593946027199</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.09784735860829485</v>
+        <v>0.06696715902995409</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.09928148023704697</v>
+        <v>0.06490997737597737</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.1297828443163674</v>
+        <v>-0.1471950882877605</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.1495705333443849</v>
+        <v>-0.1618614410139183</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.1543209884618488</v>
+        <v>0.1364883252079148</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.04900010282973066</v>
+        <v>0.04357017741050351</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>174.19</v>
+        <v>170.63</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01620916726962984</v>
+        <v>-0.02043743905331907</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.03995811233711433</v>
+        <v>-0.04670652189387658</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.04490625190337449</v>
+        <v>-0.06025225532910472</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.05751544454905744</v>
+        <v>-0.07677741520978065</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.0285191415543693</v>
+        <v>-0.003329392964895983</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1301852100458303</v>
+        <v>0.101456692769903</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.0757076303706905</v>
+        <v>-0.09726993453467991</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1119118486789593</v>
+        <v>-0.1302357206980945</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5162720721463814</v>
+        <v>0.4852832554435931</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1488386693727046</v>
+        <v>0.1409582728077503</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>25.98</v>
+        <v>26.09</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.011415568362661</v>
+        <v>0.00423404974171504</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.0420354447536696</v>
+        <v>-0.02138033376168791</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.04939628193334666</v>
+        <v>-0.03762450884542579</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.1542968709982232</v>
+        <v>-0.1507161218833056</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.09791665866419097</v>
+        <v>-0.1034364326262532</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-0.03816196528175475</v>
+        <v>-0.04918180697159102</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.03607914423419878</v>
+        <v>0.04782481734826827</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.06946059574937169</v>
+        <v>0.0709694896781965</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.054922436910451</v>
+        <v>1.063623236387196</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2713500506754893</v>
+        <v>0.2731418759990218</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16.65</v>
+        <v>16.56</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.02288739882881641</v>
+        <v>-0.005405414693687272</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02972029332265691</v>
+        <v>-0.01779366153907413</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.03534186571624864</v>
+        <v>-0.04055624296969096</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.07756230901416172</v>
+        <v>-0.08254846726302756</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.05879032697173103</v>
+        <v>-0.06334846266408267</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.01766215028845664</v>
+        <v>0.001827292686340742</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.01790009562918382</v>
+        <v>-0.01839232089680742</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.02412501098354669</v>
+        <v>-0.02987308873285388</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3687219249483871</v>
+        <v>0.3613234153436993</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1102950612799392</v>
+        <v>0.1082909107627832</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>53.32</v>
+        <v>52.87</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01859013624500117</v>
+        <v>-0.008439624259471534</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01840942572934667</v>
+        <v>-0.01563954881598073</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.01678037719147252</v>
+        <v>-0.02901748042086516</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.03597905675387958</v>
+        <v>-0.04411503129313821</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.04495794472344639</v>
+        <v>-0.04376925200887383</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.01251041846706524</v>
+        <v>-0.002292856791149434</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.07771316444569198</v>
+        <v>-0.08646510905921656</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.06339100867247549</v>
+        <v>-0.07541821997190412</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1641361088445663</v>
+        <v>0.154311237499035</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.05196490990622626</v>
+        <v>0.04899714906155617</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>15.53</v>
+        <v>15.46</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01895137032095628</v>
+        <v>-0.004507385449312284</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02633229349946276</v>
+        <v>-0.01214054856323021</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.05707344381132506</v>
+        <v>-0.06642508836172911</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.1130782678486055</v>
+        <v>-0.1170759659587837</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.05477787921410271</v>
+        <v>-0.06303030071836524</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.01278161880893247</v>
+        <v>-0.00226639788786287</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.08599847198542665</v>
+        <v>-0.08554590325765055</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1147684487102421</v>
+        <v>-0.1170482663661582</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2189498505766296</v>
+        <v>0.213455573756699</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.06822305310015331</v>
+        <v>0.06661567129718815</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>61.22</v>
+        <v>60.83</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.02204468509673307</v>
+        <v>-0.006370457070761226</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.03301216406969798</v>
+        <v>-0.02609665829827368</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02809970488330293</v>
+        <v>-0.03977895349272731</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.07214310236512378</v>
+        <v>-0.07805397489931643</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.08394434320881161</v>
+        <v>-0.08950749807009772</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.004588814789771245</v>
+        <v>-0.01503596712145727</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.08397017325417311</v>
+        <v>-0.09071137937397378</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.06643872782389604</v>
+        <v>-0.07688878880518779</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3441186971833021</v>
+        <v>0.3355562704406345</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1036021573469563</v>
+        <v>0.1012537414069197</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>122.9</v>
+        <v>122.87</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.0118989850476009</v>
+        <v>-0.0002440909595152752</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.05081861614751859</v>
+        <v>-0.03955286130323754</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.02745905788782599</v>
+        <v>-0.0302288420987471</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.07259283456408072</v>
+        <v>-0.07281920626895333</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.09330850235352839</v>
+        <v>-0.09902607556138221</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1192624871596978</v>
+        <v>-0.1250023226684728</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.04941664701621107</v>
+        <v>-0.04901600234025616</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.02800838475755341</v>
+        <v>-0.01013423850891393</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4191738850316449</v>
+        <v>0.4188274775163285</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1237728538623983</v>
+        <v>0.123681412157238</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>111.77</v>
+        <v>111.19</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01070991925929099</v>
+        <v>-0.005189176157107234</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.03886838280914839</v>
+        <v>-0.02873865145923826</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02545998549290851</v>
+        <v>-0.03329850733299455</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.1079808944865113</v>
+        <v>-0.112609738760526</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1179766764016905</v>
+        <v>-0.1293555458577632</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.04479761559269468</v>
+        <v>-0.0617523788873594</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.05962650078683707</v>
+        <v>-0.06041229717229402</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.1016849909659044</v>
+        <v>-0.1010400782681766</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2993117777027257</v>
+        <v>0.2925691907274217</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09120025395739972</v>
+        <v>0.08930943850823847</v>
       </c>
     </row>
   </sheetData>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.04990044559953688</v>
+        <v>0.04369780397464917</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1542968709982232</v>
+        <v>-0.1507161218833056</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.04674240614513714</v>
+        <v>0.03505686567331878</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1212001765066288</v>
+        <v>-0.1223896601642367</v>
       </c>
     </row>
     <row r="19">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.03864823847154297</v>
+        <v>0.02448411189938704</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1130782678486055</v>
+        <v>-0.1170759659587837</v>
       </c>
     </row>
     <row r="20">
@@ -3163,21 +3163,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.02448411189938704</v>
+        <v>0.02279271133647187</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1079808944865113</v>
+        <v>-0.112609738760526</v>
       </c>
     </row>
     <row r="21">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.01608033155277622</v>
+        <v>0.01004019922474053</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.1059922392730119</v>
+        <v>-0.09976653459007179</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01405622784773763</v>
+        <v>0.009450670084346857</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.07756230901416172</v>
+        <v>-0.08503593946027199</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.007974024007581626</v>
+        <v>-0.001005020722048555</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.07259283456408072</v>
+        <v>-0.08254846726302756</v>
       </c>
     </row>
     <row r="24">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.002432565399870024</v>
+        <v>-0.004196407125047763</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.07214310236512378</v>
+        <v>-0.08243930886560624</v>
       </c>
     </row>
     <row r="25">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.002098163542619602</v>
+        <v>-0.007961092450982532</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07067921830515389</v>
+        <v>-0.07805397489931643</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.009846144456129857</v>
+        <v>-0.01837356309605453</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07015538877005734</v>
+        <v>-0.07677741520978065</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2072234867556377</v>
+        <v>0.2128187770912586</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2139044906718722</v>
+        <v>-0.169323532470071</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.1913370693259553</v>
+        <v>0.1882824415706124</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1179766764016905</v>
+        <v>-0.1293555458577632</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1815932826594537</v>
+        <v>0.1687951286086971</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.09791665866419097</v>
+        <v>-0.1034364326262532</v>
       </c>
     </row>
     <row r="34">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1655392715354886</v>
+        <v>0.1687949537003668</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.09330850235352839</v>
+        <v>-0.09902607556138221</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1444080063762554</v>
+        <v>0.1371698631107134</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08905135096805994</v>
+        <v>-0.08950749807009772</v>
       </c>
     </row>
     <row r="36">
@@ -3764,21 +3764,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1311667327343133</v>
+        <v>0.1189823008133801</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08394434320881161</v>
+        <v>-0.0835058064486236</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1237326161343932</v>
+        <v>0.08508144817148988</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.07588602246085363</v>
+        <v>-0.08071863871613683</v>
       </c>
     </row>
     <row r="38">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.09784735860829485</v>
+        <v>0.0815057558115917</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.07284153476787292</v>
+        <v>-0.07089828543238086</v>
       </c>
     </row>
     <row r="39">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.09604903393053621</v>
+        <v>0.06696715902995409</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.06377020125401156</v>
+        <v>-0.06823395892951001</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.08057457774744869</v>
+        <v>0.04497840806074005</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.0625000147536251</v>
+        <v>-0.06334846266408267</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4633142694510595</v>
+        <v>0.4231315892419893</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1192624871596978</v>
+        <v>-0.1250023226684728</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3911921584232372</v>
+        <v>0.3734302905087741</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.04479761559269468</v>
+        <v>-0.0617523788873594</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3520478146060717</v>
+        <v>0.3291223970192416</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.03816196528175475</v>
+        <v>-0.04918180697159102</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3234255038108744</v>
+        <v>0.303246899966469</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.002058787241032811</v>
+        <v>-0.01503596712145727</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2660948865718264</v>
+        <v>0.2420531141843112</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,21 +4252,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.004588814789771245</v>
+        <v>-0.007268915195823289</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2447188151710744</v>
+        <v>0.2271223811249856</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.01251041846706524</v>
+        <v>-0.002292856791149434</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2209736174030075</v>
+        <v>0.202315605061469</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.01278161880893247</v>
+        <v>-0.00226639788786287</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2195305745016818</v>
+        <v>0.1976590437392864</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.01517499364193675</v>
+        <v>0.001827292686340742</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2131246009995302</v>
+        <v>0.1922506943303155</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.01720844600535476</v>
+        <v>0.001979510440054177</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2126561156603912</v>
+        <v>0.1887112639509667</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.01766215028845664</v>
+        <v>0.002071747591572803</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8031457666284911</v>
+        <v>0.8079478770558193</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1495705333443849</v>
+        <v>-0.1618614410139183</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.6142558544249008</v>
+        <v>0.6239044670412621</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4628,21 +4628,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1147684487102421</v>
+        <v>-0.1302357206980945</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5838435357798388</v>
+        <v>0.5178751870050209</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4673,21 +4673,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1119118486789593</v>
+        <v>-0.1170482663661582</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4657904834346305</v>
+        <v>0.4693611041383818</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1016849909659044</v>
+        <v>-0.1010400782681766</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4333209299739369</v>
+        <v>0.4443688325576396</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.06643872782389604</v>
+        <v>-0.07688878880518779</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4212009236958159</v>
+        <v>0.41047057023418</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.06339100867247549</v>
+        <v>-0.07541821997190412</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3746214930367548</v>
+        <v>0.392537693918489</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4853,21 +4853,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.02800838475755341</v>
+        <v>-0.02987308873285388</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3288281026570252</v>
+        <v>0.3298278603183313</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4898,21 +4898,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.02412501098354669</v>
+        <v>-0.01013423850891393</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3105343079697374</v>
+        <v>0.3032319353271951</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.0146189444475735</v>
+        <v>0.01562570918714701</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.216044466277648</v>
+        <v>0.192582405361815</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.03026956363188993</v>
+        <v>0.02329777626097917</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.395518562086477</v>
+        <v>2.419164325290817</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.04043202254805656</v>
+        <v>0.03575946511494044</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.261512719619074</v>
+        <v>2.225102407491725</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.07039700058046483</v>
+        <v>0.05941136434604655</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.141324511609163</v>
+        <v>2.153118883409304</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1543209884618488</v>
+        <v>0.1364883252079148</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.504296710346266</v>
+        <v>1.512140030500334</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1604587273222327</v>
+        <v>0.154311237499035</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.157840064800576</v>
+        <v>1.102598605922819</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1641361088445663</v>
+        <v>0.1554689874770572</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.054922436910451</v>
+        <v>1.063623236387196</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2045961140005763</v>
+        <v>0.1947652935357511</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9355675104289576</v>
+        <v>0.9328874163426437</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2185718709943452</v>
+        <v>0.213455573756699</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8970442259691986</v>
+        <v>0.859761257487109</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5409,21 +5409,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2189498505766296</v>
+        <v>0.2244962723475745</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8415334854388807</v>
+        <v>0.8342401356198315</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2827961032235751</v>
+        <v>0.2694955139874358</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.802394555100173</v>
+        <v>0.7720875311160065</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2862922573727951</v>
+        <v>0.2774409358186334</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -689,10 +689,10 @@
         <v>0.5178751870050209</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.580886304158565</v>
+        <v>0.5808862010246805</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1649310265509898</v>
+        <v>0.1649310012183933</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.4443688325576396</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.512140030500334</v>
+        <v>1.512140251565298</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3594021360210098</v>
+        <v>0.3594021758961987</v>
       </c>
     </row>
     <row r="5">
@@ -910,13 +910,13 @@
         <v>0.163107185410001</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3298278603183313</v>
+        <v>0.3298279754783136</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4597964588966101</v>
+        <v>0.4597963201267128</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1343944731787368</v>
+        <v>0.1343944372331296</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.1114963213826101</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.2244962723475745</v>
+        <v>0.2244961659143303</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.06984079861236703</v>
+        <v>0.06984076761550373</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.01562570918714701</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.3608738834719947</v>
+        <v>0.3608737346154052</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1081689052370598</v>
+        <v>0.1081688648320789</v>
       </c>
     </row>
     <row r="10">
@@ -1137,10 +1137,10 @@
         <v>0.41047057023418</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6584823655517116</v>
+        <v>0.6584822120618494</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.183687203737831</v>
+        <v>0.1836871672217173</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.392537693918489</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>2.225102407491725</v>
+        <v>2.225102100673371</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.4774558200173336</v>
+        <v>0.4774557731650151</v>
       </c>
     </row>
     <row r="13">
@@ -1243,7 +1243,7 @@
         <v>0.2420531141843112</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.03740533719744654</v>
+        <v>0.0374054287136083</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>0.02329777626097917</v>
@@ -1302,7 +1302,7 @@
         <v>0.2065359659571271</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.189458904508452</v>
+        <v>0.1894589820750161</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>0.7720875311160065</v>
@@ -1417,10 +1417,10 @@
         <v>0.192582405361815</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.102598605922819</v>
+        <v>1.102598834314984</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.281107156882251</v>
+        <v>0.2811072032684745</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.09832463262491498</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5301660513396915</v>
+        <v>0.5301662380599697</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1523370373183539</v>
+        <v>0.1523370841901042</v>
       </c>
     </row>
     <row r="18">
@@ -1529,10 +1529,10 @@
         <v>0.155056163979137</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.05941136434604655</v>
+        <v>0.05941144023783096</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.01942405148148429</v>
+        <v>0.01942407582390393</v>
       </c>
     </row>
     <row r="19">
@@ -1579,16 +1579,16 @@
         <v>0.03289795397507334</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1039591302679519</v>
+        <v>0.1039592306473189</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>0.1205959689664335</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1554689874770572</v>
+        <v>0.1554688775119331</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.04934773926099223</v>
+        <v>0.0493477059724432</v>
       </c>
     </row>
     <row r="20">
@@ -1697,10 +1697,10 @@
         <v>0.1075858223279176</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1947652935357511</v>
+        <v>0.1947651829030248</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.0611111208523818</v>
+        <v>0.0611110881001693</v>
       </c>
     </row>
     <row r="22">
@@ -1753,10 +1753,10 @@
         <v>0.1083891908875607</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6695889402206827</v>
+        <v>0.6695891526372539</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1863236445767378</v>
+        <v>0.1863236948874827</v>
       </c>
     </row>
     <row r="23">
@@ -1803,16 +1803,16 @@
         <v>-0.007268915195823289</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.135671147686522</v>
+        <v>0.1356712401677653</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>0.05605174979270555</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.03575946511494044</v>
+        <v>0.03575954203972587</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.01178049663777636</v>
+        <v>0.01178052168573984</v>
       </c>
     </row>
     <row r="24">
@@ -2027,10 +2027,10 @@
         <v>-0.1302357206980945</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.4852832554435931</v>
+        <v>0.4852833540836397</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1409582728077503</v>
+        <v>0.1409582980653734</v>
       </c>
     </row>
     <row r="28">
@@ -2077,16 +2077,16 @@
         <v>-0.04918180697159102</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.04782481734826827</v>
+        <v>0.04782473708195267</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.0709694896781965</v>
+        <v>0.07096957352957989</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.063623236387196</v>
+        <v>1.063622925060219</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2731418759990218</v>
+        <v>0.2731418119751527</v>
       </c>
     </row>
     <row r="29">
@@ -2195,10 +2195,10 @@
         <v>-0.07541821997190412</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.154311237499035</v>
+        <v>0.1543111413607019</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.04899714906155617</v>
+        <v>0.04899711993918521</v>
       </c>
     </row>
     <row r="31">
@@ -2301,7 +2301,7 @@
         <v>-0.01503596712145727</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.09071137937397378</v>
+        <v>-0.09071148307324561</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>-0.07688878880518779</v>
@@ -2360,7 +2360,7 @@
         <v>-0.04901600234025616</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.01013423850891393</v>
+        <v>-0.01013429934997567</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>0.4188274775163285</v>
@@ -2413,16 +2413,16 @@
         <v>-0.0617523788873594</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.06041229717229402</v>
+        <v>-0.06041235774806553</v>
       </c>
       <c r="N34" s="6" t="n">
         <v>-0.1010400782681766</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2925691907274217</v>
+        <v>0.2925693053663116</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08930943850823847</v>
+        <v>0.08930947071211648</v>
       </c>
     </row>
   </sheetData>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3298278603183313</v>
+        <v>0.3298279754783136</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.01013423850891393</v>
+        <v>-0.01013429934997567</v>
       </c>
     </row>
     <row r="67">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.03575946511494044</v>
+        <v>0.03575954203972587</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.225102407491725</v>
+        <v>2.225102100673371</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.05941136434604655</v>
+        <v>0.05941144023783096</v>
       </c>
     </row>
     <row r="75">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.512140030500334</v>
+        <v>1.512140251565298</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.154311237499035</v>
+        <v>0.1543111413607019</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.102598605922819</v>
+        <v>1.102598834314984</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1554689874770572</v>
+        <v>0.1554688775119331</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.063623236387196</v>
+        <v>1.063622925060219</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1947652935357511</v>
+        <v>0.1947651829030248</v>
       </c>
     </row>
     <row r="79">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2244962723475745</v>
+        <v>0.2244961659143303</v>
       </c>
     </row>
     <row r="81">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -494,9 +494,9 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>213.88</v>
+        <v>217.9</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.003754472709232015</v>
+        <v>0.01879553451419858</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.02878937563685102</v>
+        <v>0.004934704867379791</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.0004210281093897095</v>
+        <v>0.01278178051598333</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>-0.03601203592290536</v>
+        <v>-0.0403840803802904</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.08071863871613683</v>
+        <v>-0.06692932370364979</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4231315892419893</v>
+        <v>0.4373145960217601</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7231104360808718</v>
+        <v>0.7834815540848381</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8079478770558193</v>
+        <v>0.8440775434138634</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.153118883409304</v>
+        <v>2.212383438209795</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.466380854844467</v>
+        <v>0.4755110267157092</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>92.44</v>
+        <v>92.95</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.02581933780167622</v>
+        <v>0.005517032598081117</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.02272961179535571</v>
+        <v>-0.01032795186982716</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.02097008860343619</v>
+        <v>-0.01032795186982716</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.02279271133647187</v>
+        <v>0.01918859713332188</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1687951286086971</v>
+        <v>0.1910558157073041</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.156122317730071</v>
+        <v>0.1500206818184822</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5455436976625052</v>
+        <v>0.5317025285558048</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5178751870050209</v>
+        <v>0.5237976953563297</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.5808862010246805</v>
+        <v>0.5896080017295902</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1649310012183933</v>
+        <v>0.1670693942678061</v>
       </c>
     </row>
     <row r="4">
@@ -704,12 +704,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>54.45</v>
+        <v>59.71</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.003131945237025757</v>
+        <v>0.03233054852959061</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.01447962420019089</v>
+        <v>-0.005993018348268486</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.004056817675828661</v>
+        <v>0.002350166029304157</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.02296785913889698</v>
+        <v>-0.08364033565587259</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.02349350068197298</v>
+        <v>-0.1507608994764571</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3734302905087741</v>
+        <v>0.3680673420555107</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.3805433098434892</v>
+        <v>0.6146978745361615</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4443688325576396</v>
+        <v>0.6888177318429052</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.512140251565298</v>
+        <v>2.529707783440276</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3594021758961987</v>
+        <v>0.5225781188491017</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>28.85</v>
+        <v>55.72</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.001384527830521232</v>
+        <v>0.02332415867711202</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.02959970313879146</v>
+        <v>0.01808883038091014</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.06634301819962463</v>
+        <v>0.01143585163133531</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.01837356309605453</v>
+        <v>-0.004822297725836866</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1371698631107134</v>
+        <v>0.006139403142475741</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.1922506943303155</v>
+        <v>0.3986434177744502</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.190834085655889</v>
+        <v>0.4442319074325618</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4693611041383818</v>
+        <v>0.4837573741349757</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.9328874163426437</v>
+        <v>1.570733583190849</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2456676507670512</v>
+        <v>0.3698899840955474</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>57.84</v>
+        <v>29.83</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.006963815032072551</v>
+        <v>0.01843629195287755</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.06073402999771782</v>
+        <v>0.03361050910742436</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.02609865723168725</v>
+        <v>-0.001673334620644784</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-0.09976653459007179</v>
+        <v>0.03468609096934916</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.169323532470071</v>
+        <v>0.1889198781303818</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3291223970192416</v>
+        <v>0.2502109197347488</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.509628275265853</v>
+        <v>0.1923977993930779</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.6239044670412621</v>
+        <v>0.3589464221228102</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.419164325290817</v>
+        <v>0.4867096926046048</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5065145293192554</v>
+        <v>0.1413234073240552</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="F7" s="5" t="n">
-        <v>29.29</v>
+        <v>29.33</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0</v>
+        <v>0.01663776554209795</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.003769726154939423</v>
+        <v>-0.0006814465929717572</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.01744376248678337</v>
+        <v>-0.05050176422033714</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.02448411189938704</v>
+        <v>-0.01610196413403908</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1687949537003668</v>
+        <v>0.1293800808313368</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2271223811249856</v>
+        <v>0.2096887169266946</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.163107185410001</v>
+        <v>0.222753453876013</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3298279754783136</v>
+        <v>0.4881147689712686</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4597963201267128</v>
+        <v>0.9650464695499184</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1343944372331296</v>
+        <v>0.2525380898293048</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>53.74</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.004861670502168458</v>
+        <v>0.03170422682120222</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.04572878608151387</v>
+        <v>-0.001795641826935701</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.01876780433112413</v>
+        <v>-0.04344707301562711</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.04369780397464917</v>
+        <v>0.04807537290238106</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2128187770912586</v>
+        <v>0.1503707044941132</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1976590437392864</v>
+        <v>0.04187661433857359</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.03904742264573935</v>
+        <v>0.1839703719430934</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.1114963213826101</v>
+        <v>0.4414295053115522</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.2244961659143303</v>
+        <v>2.327351469194655</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.06984076761550373</v>
+        <v>0.492907475318181</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>23.73</v>
+        <v>54.78</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.006281391281483528</v>
+        <v>0.01935238311030418</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02240415675464402</v>
+        <v>0.07622784159338925</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.0206451416015625</v>
+        <v>0.03456086855504381</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.004196407125047763</v>
+        <v>0.06555142855256024</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1882824415706124</v>
+        <v>0.2613400505265124</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.303246899966469</v>
+        <v>0.2028488262081827</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0373193382722925</v>
+        <v>0.06237749763521516</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.01562570918714701</v>
+        <v>0.1386754261752221</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.3608737346154052</v>
+        <v>0.2481931933271839</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1081688648320789</v>
+        <v>0.07669807514690286</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>15.09</v>
+        <v>24.02</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.003960360887996117</v>
+        <v>0.01222085634730763</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.005329774982422819</v>
+        <v>0.03802943350590149</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01684636101276604</v>
+        <v>-0.002491672181581528</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01004019922474053</v>
+        <v>0.03223033885887938</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.03946530134014004</v>
+        <v>0.2336929278311957</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.202315605061469</v>
+        <v>0.3112862746412872</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2969360922377167</v>
+        <v>0.05942520448792421</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3032319353271951</v>
+        <v>0.0251788938837838</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.8342401356198315</v>
+        <v>0.3775049277087084</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2241051658832365</v>
+        <v>0.1126648973826596</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>34.18</v>
+        <v>34.7</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.001464964415347048</v>
+        <v>0.0152135884470701</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.001168933784349013</v>
+        <v>0.02359879649119878</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.03826675788737477</v>
+        <v>-0.0261016075581324</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.009450670084346857</v>
+        <v>0.01729698452156692</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.02735196377791937</v>
+        <v>0.04204208882746174</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1129660790048386</v>
+        <v>0.1429690617709116</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1447752444107915</v>
+        <v>0.1699962062959539</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.41047057023418</v>
+        <v>0.4330506190907064</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6584822120618494</v>
+        <v>0.6837136778829447</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1836871672217173</v>
+        <v>0.189659690812662</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>64.66</v>
+        <v>15.23</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.011163721277762</v>
+        <v>0.009277626788123605</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.06181071706347563</v>
+        <v>0.01196008964918671</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.03779752085538235</v>
+        <v>0.0166889190680628</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.03505686567331878</v>
+        <v>0.02146208572093045</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.08508144817148988</v>
+        <v>-0.02434337750150883</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.002071747591572803</v>
+        <v>0.206844468109723</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1542375258933812</v>
+        <v>0.322814528534489</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.392537693918489</v>
+        <v>0.3068641535954162</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>2.225102100673371</v>
+        <v>0.8512577456399875</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.4774557731650151</v>
+        <v>0.2278791631409118</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>44.86</v>
+        <v>45.03</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.0103684359523043</v>
+        <v>0.003789526674818688</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.0108156721650281</v>
+        <v>0.01808725402080569</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.004659398400146286</v>
+        <v>-0.01980844306954432</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.007961092450982532</v>
+        <v>0.01533258914479041</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1189823008133801</v>
+        <v>0.1469689430577219</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2420531141843112</v>
+        <v>0.2421226841358493</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0374054287136083</v>
+        <v>0.0447853242917724</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.02329777626097917</v>
+        <v>0.01531311442006222</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2694955139874358</v>
+        <v>0.2743063011012541</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08278872168531293</v>
+        <v>0.08415474985028393</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>69.58</v>
+        <v>68.87</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.01681496210906364</v>
+        <v>-0.01020406820621511</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.0002873080963333718</v>
+        <v>-0.01431229369815534</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.008125440946910589</v>
+        <v>-0.02863185804806945</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.001005020722048555</v>
+        <v>-0.003616898004425551</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.02819582101075357</v>
+        <v>0.03602888508436064</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.07424691616000123</v>
+        <v>0.05131486434880217</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2065359659571271</v>
+        <v>0.2077462270678434</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1894589820750161</v>
+        <v>0.1670858011977108</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7720875311160065</v>
+        <v>0.7540048586724777</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2101198640713609</v>
+        <v>0.2059896964157419</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="F15" s="5" t="n">
-        <v>16.96</v>
+        <v>36.99</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.01965318887757705</v>
+        <v>0.001896086484109549</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02863688580858259</v>
+        <v>-0.02785801786722031</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.04072405024180603</v>
+        <v>-0.03872135866670379</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.0567297265702158</v>
+        <v>-0.06567311099015338</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.04497840806074005</v>
+        <v>0.02267081976867558</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1887112639509667</v>
+        <v>0.1751116507957571</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.08072588160067906</v>
+        <v>0.09586441926867462</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1228843371891877</v>
+        <v>0.1802597209746171</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.859761257487109</v>
+        <v>1.106585085895849</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2297563263491766</v>
+        <v>0.2819162959084498</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>36.92</v>
+        <v>16.96</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.02560045490441809</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02739728505295858</v>
+        <v>-0.02584725829313217</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.0299527893644721</v>
+        <v>-0.05462661206305475</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.07306059574018153</v>
+        <v>-0.04665552492075764</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.006817562380238007</v>
+        <v>0.0534160672438706</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1743469118621237</v>
+        <v>0.1805581703369346</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.09586036367457296</v>
+        <v>0.08008224826167454</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.192582405361815</v>
+        <v>0.1118689523946714</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.102598834314984</v>
+        <v>0.859761257487109</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2811072032684745</v>
+        <v>0.2297563263491766</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>95.67</v>
+        <v>95.27</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.009011836941489992</v>
+        <v>-0.004181055017608903</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.008113768500376928</v>
+        <v>0</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.020075787561328</v>
+        <v>-0.03981056771860347</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.01876924954927883</v>
+        <v>-0.00884317602192175</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.0815057558115917</v>
+        <v>0.08175311653447559</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1304914851114538</v>
+        <v>0.1234200031128068</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.07869482624410495</v>
+        <v>0.07418474382836826</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.09832463262491498</v>
+        <v>0.09026631887980607</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5301662380599697</v>
+        <v>0.5237683428929627</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1523370841901042</v>
+        <v>0.150728799003228</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>112.83</v>
+        <v>111.69</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.0102631418328536</v>
+        <v>-0.01010369025213176</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02404635208563399</v>
+        <v>-0.02598757979527111</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.03638222427253923</v>
+        <v>-0.05009354735434945</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.03407238944203073</v>
+        <v>-0.02895143713135284</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.008175108014344845</v>
+        <v>-0.004456725101339876</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1732349379152753</v>
+        <v>0.1630740795707009</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1007032468349724</v>
+        <v>0.09318077393779811</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.155056163979137</v>
+        <v>0.139680327505765</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.05941144023783096</v>
+        <v>0.04870740007110563</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.01942407582390393</v>
+        <v>0.0159791081349181</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>92.63</v>
+        <v>114.56</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.004299704731028364</v>
+        <v>0.007120857657967106</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.005754601390637326</v>
+        <v>-0.009168008673305583</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.02474211434468299</v>
+        <v>-0.02791685157509616</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.02995078724822853</v>
+        <v>-0.07050711920005071</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.002559652379539368</v>
+        <v>-0.03202366678826851</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.03289795397507334</v>
+        <v>0.08281251307038429</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1039592306473189</v>
+        <v>0.1110670599307431</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1205959689664335</v>
+        <v>0.1939871919743137</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1554688775119331</v>
+        <v>0.4211760955650405</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.0493477059724432</v>
+        <v>0.1243010890002874</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>113.75</v>
+        <v>92.69</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.01685390665234421</v>
+        <v>0.0006477943405753805</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.01412720828756719</v>
+        <v>0.006843416245058132</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.02993349882556384</v>
+        <v>-0.02318470821364749</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.08243930886560624</v>
+        <v>-0.01404105589649274</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.06823395892951001</v>
+        <v>0.02084988140843769</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.09414233924823501</v>
+        <v>0.03402458308363765</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.09307658436441479</v>
+        <v>0.1028806375159363</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1705182560208782</v>
+        <v>0.1167350072290034</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4111276563866904</v>
+        <v>0.1562174937478551</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1216450253536356</v>
+        <v>0.04957427752689259</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>98.44</v>
+        <v>50.73</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.00816118446945846</v>
+        <v>0.01338390232851228</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.03442858864054588</v>
+        <v>0.003362305465345994</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.05218561657128573</v>
+        <v>-0.01437733943882524</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.03575270866308855</v>
+        <v>-0.0494659816841635</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.0588009763057652</v>
+        <v>-0.04660777269135541</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.002711956661538339</v>
+        <v>0.07003774583249744</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1212730658587793</v>
+        <v>0.09301420340296152</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1075858223279176</v>
+        <v>0.1227350175950717</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1947651829030248</v>
+        <v>0.6919346631551204</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.0611110881001693</v>
+        <v>0.1915927788110614</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>50.06</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.001794619139571685</v>
+        <v>0.01117430360463301</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.02130987527021699</v>
+        <v>-0.00420166239287767</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.012623261933287</v>
+        <v>-0.03891086985779213</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.06569616158026148</v>
+        <v>-0.02248846974712482</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.07089828543238086</v>
+        <v>-0.03602557760743941</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.06098313073779282</v>
+        <v>0.01002499727112482</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.05752659927889892</v>
+        <v>0.1308604811413565</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1083891908875607</v>
+        <v>0.1174496135576972</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6695891526372539</v>
+        <v>0.2081158517930282</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1863236948874827</v>
+        <v>0.06504884955770063</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13.3</v>
+        <v>40.53</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.004490978105107568</v>
+        <v>0.002969535568866144</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.02061853715348017</v>
+        <v>-0.003197271731507634</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.04999998637608116</v>
+        <v>-0.03015080422652749</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.05539770860779125</v>
+        <v>-0.04624793074762923</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.06073443968535208</v>
+        <v>-0.01444096332455969</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.007268915195823289</v>
+        <v>0.02259474503120229</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1356712401677653</v>
+        <v>0.0979962570949382</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.05605174979270555</v>
+        <v>0.09200876468742414</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.03575954203972587</v>
+        <v>0.3079072982946125</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.01178052168573984</v>
+        <v>0.09360122424110329</v>
       </c>
     </row>
     <row r="24">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>66.47</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.001353531971455602</v>
+        <v>0.001054212247223241</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02796071001285749</v>
+        <v>-0.0167159360787642</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03136398876970981</v>
+        <v>-0.04097527684212843</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.1223896601642367</v>
+        <v>-0.1213483161931652</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.0835058064486236</v>
+        <v>-0.08241304554803153</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.01856111426840679</v>
+        <v>0.01605018467053765</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.08540370647118745</v>
+        <v>0.1134205464343021</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1874,51 +1874,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>40.41</v>
+        <v>13.29</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.006881267848288464</v>
+        <v>-0.0007518968976257812</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.01559072841761799</v>
+        <v>-0.009687042749765618</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.04219006487878907</v>
+        <v>-0.04457224244142821</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.07655389859721828</v>
+        <v>-0.04319657067238025</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.06023256168809044</v>
+        <v>-0.05476532253081279</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.001979510440054177</v>
+        <v>-0.0137995141031112</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.07607188278364463</v>
+        <v>0.1292039639055345</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.06546470583206299</v>
+        <v>0.05120836828416087</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2774409358186334</v>
+        <v>0.03498075765337982</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.08504298379794117</v>
+        <v>0.01152687322417179</v>
       </c>
     </row>
     <row r="26">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.57</v>
+        <v>16.72</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.0154486173535634</v>
+        <v>0.009661826846140142</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01603328119460734</v>
+        <v>-0.002386689438011569</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.06752958537011045</v>
+        <v>-0.0379746765984883</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.08503593946027199</v>
+        <v>-0.06067415561779566</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.06696715902995409</v>
+        <v>-0.02677537739523239</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.06490997737597737</v>
+        <v>0.008075904556049007</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.1471950882877605</v>
+        <v>-0.005967193871036613</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.1618614410139183</v>
+        <v>-0.01906579282482268</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.1364883252079148</v>
+        <v>0.3744762864643463</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.04357017741050351</v>
+        <v>0.1118488481473632</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>170.63</v>
+        <v>171.3</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.02043743905331907</v>
+        <v>0.003926614017302876</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.04670652189387658</v>
+        <v>-0.02979154156982999</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.06025225532910472</v>
+        <v>-0.08307463689114725</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.07677741520978065</v>
+        <v>-0.05951463914689514</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.003329392964895983</v>
+        <v>0.01360948551335994</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.101456692769903</v>
+        <v>0.08299275719604049</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.09726993453467991</v>
+        <v>-0.08900826101570192</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1302357206980945</v>
+        <v>-0.1295994882877993</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.4852833540836397</v>
+        <v>0.491115389494083</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1409582980653734</v>
+        <v>0.1424496900169046</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>26.09</v>
+        <v>16.5</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.00423404974171504</v>
+        <v>-0.00422448377268736</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02138033376168791</v>
+        <v>-0.01138409394714535</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.03762450884542579</v>
+        <v>-0.0828237793260157</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.1507161218833056</v>
+        <v>-0.06937391844293217</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.1034364326262532</v>
+        <v>0.07843135910493748</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-0.04918180697159102</v>
+        <v>0.05229589788678424</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.04782473708195267</v>
+        <v>-0.1450776864117118</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.07096957352957989</v>
+        <v>-0.1782868494675429</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.063622925060219</v>
+        <v>0.1316872487202254</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2731418119751527</v>
+        <v>0.04209858813263767</v>
       </c>
     </row>
     <row r="29">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16.56</v>
+        <v>53.34</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.005405414693687272</v>
+        <v>0.008889752793614702</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01779366153907413</v>
+        <v>-0.009102761690491179</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.04055624296969096</v>
+        <v>-0.03770521632836321</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.08254846726302756</v>
+        <v>-0.02307689298069138</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.06334846266408267</v>
+        <v>-0.005592827003619294</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.001827292686340742</v>
+        <v>0.001759539069540628</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.01839232089680742</v>
+        <v>-0.06548231807921956</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.02987308873285388</v>
+        <v>-0.07174566710981289</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3613234153436993</v>
+        <v>0.1645726820543136</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1082909107627832</v>
+        <v>0.05209639576237635</v>
       </c>
     </row>
     <row r="30">
@@ -2154,51 +2154,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>52.87</v>
+        <v>25.93</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.008439624259471534</v>
+        <v>-0.006132611976862656</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01563954881598073</v>
+        <v>-0.02150942244619691</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.02901748042086516</v>
+        <v>-0.05537342133031342</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.04411503129313821</v>
+        <v>-0.1509495897889026</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.04376925200887383</v>
+        <v>-0.1183270846749952</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.002292856791149434</v>
+        <v>-0.0560417878312689</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.08646510905921656</v>
+        <v>0.05507966499553518</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.07541821997190412</v>
+        <v>0.0708526380604213</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1543111413607019</v>
+        <v>1.050967371685437</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.04899711993918521</v>
+        <v>0.2705338800869628</v>
       </c>
     </row>
     <row r="31">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>15.46</v>
+        <v>61.47</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.004507385449312284</v>
+        <v>0.01052111409475098</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01214054856323021</v>
+        <v>-0.01014488355713095</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.06642508836172911</v>
+        <v>-0.04371495973797046</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.1170759659587837</v>
+        <v>-0.05634016277759624</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.06303030071836524</v>
+        <v>-0.05532501138781232</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.00226639788786287</v>
+        <v>-0.01016275993836646</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.08554590325765055</v>
+        <v>-0.07164213877994796</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1170482663661582</v>
+        <v>-0.06549180939178301</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.213455573756699</v>
+        <v>0.3496075842724156</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.06661567129718815</v>
+        <v>0.1051023524070223</v>
       </c>
     </row>
     <row r="32">
@@ -2266,51 +2266,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>60.83</v>
+        <v>123.87</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.006370457070761226</v>
+        <v>0.008138682979135892</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02609665829827368</v>
+        <v>-0.02094525740433306</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03977895349272731</v>
+        <v>-0.03113019769292125</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.07805397489931643</v>
+        <v>-0.06159088828346948</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.08950749807009772</v>
+        <v>-0.08163010074647759</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.01503596712145727</v>
+        <v>-0.118188385056026</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.09071148307324561</v>
+        <v>-0.02284185963204288</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.07688878880518779</v>
+        <v>-0.005358517530522855</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3355562704406345</v>
+        <v>0.4303749905733449</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1012537414069197</v>
+        <v>0.1267216412986329</v>
       </c>
     </row>
     <row r="33">
@@ -2322,51 +2322,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>122.87</v>
+        <v>15.36</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.0002440909595152752</v>
+        <v>-0.006468329962676544</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03955286130323754</v>
+        <v>-0.0160153751120079</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.0302288420987471</v>
+        <v>-0.0685263875151827</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.07281920626895333</v>
+        <v>-0.1095652372940726</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.09902607556138221</v>
+        <v>-0.05476925189678483</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1250023226684728</v>
+        <v>-0.0230604679312999</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.04901600234025616</v>
+        <v>-0.09373796213175734</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.01013429934997567</v>
+        <v>-0.1219074140284571</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4188274775163285</v>
+        <v>0.2056066329549593</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.123681412157238</v>
+        <v>0.06431098076183384</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>111.19</v>
+        <v>111.28</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.005189176157107234</v>
+        <v>0.0008093923546592663</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02873865145923826</v>
+        <v>-0.01189845440068438</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.03329850733299455</v>
+        <v>-0.04060694172961843</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.112609738760526</v>
+        <v>-0.1110401141715303</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1293555458577632</v>
+        <v>-0.1115369358938373</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.0617523788873594</v>
+        <v>-0.06252027842437347</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.06041235774806553</v>
+        <v>-0.04867618336687429</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.1010400782681766</v>
+        <v>-0.09264520720424807</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2925693053663116</v>
+        <v>0.2936156158116408</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08930947071211648</v>
+        <v>0.08960331658790976</v>
       </c>
     </row>
   </sheetData>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.04369780397464917</v>
+        <v>0.06555142855256024</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1507161218833056</v>
+        <v>-0.1509495897889026</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.03505686567331878</v>
+        <v>0.04807537290238106</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1223896601642367</v>
+        <v>-0.1213483161931652</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.02448411189938704</v>
+        <v>0.03468609096934916</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1170759659587837</v>
+        <v>-0.1110401141715303</v>
       </c>
     </row>
     <row r="20">
@@ -3163,21 +3163,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.02279271133647187</v>
+        <v>0.03223033885887938</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.112609738760526</v>
+        <v>-0.1095652372940726</v>
       </c>
     </row>
     <row r="21">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.01004019922474053</v>
+        <v>0.02146208572093045</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.09976653459007179</v>
+        <v>-0.08364033565587259</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.009450670084346857</v>
+        <v>0.01918859713332188</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.08503593946027199</v>
+        <v>-0.07050711920005071</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.001005020722048555</v>
+        <v>0.01729698452156692</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.08254846726302756</v>
+        <v>-0.06937391844293217</v>
       </c>
     </row>
     <row r="24">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.004196407125047763</v>
+        <v>0.01533258914479041</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.08243930886560624</v>
+        <v>-0.06567311099015338</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.007961092450982532</v>
+        <v>-0.003616898004425551</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07805397489931643</v>
+        <v>-0.06159088828346948</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.01837356309605453</v>
+        <v>-0.004822297725836866</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07677741520978065</v>
+        <v>-0.06067415561779566</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2128187770912586</v>
+        <v>0.2613400505265124</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.169323532470071</v>
+        <v>-0.1507608994764571</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.1882824415706124</v>
+        <v>0.2336929278311957</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3606,21 +3606,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1293555458577632</v>
+        <v>-0.1183270846749952</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1687951286086971</v>
+        <v>0.1910558157073041</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1034364326262532</v>
+        <v>-0.1115369358938373</v>
       </c>
     </row>
     <row r="34">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1687949537003668</v>
+        <v>0.1889198781303818</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.09902607556138221</v>
+        <v>-0.08241304554803153</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1371698631107134</v>
+        <v>0.1503707044941132</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08950749807009772</v>
+        <v>-0.08163010074647759</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1189823008133801</v>
+        <v>0.1469689430577219</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.0835058064486236</v>
+        <v>-0.06692932370364979</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.08508144817148988</v>
+        <v>0.1293800808313368</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.08071863871613683</v>
+        <v>-0.05532501138781232</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.0815057558115917</v>
+        <v>0.08175311653447559</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.07089828543238086</v>
+        <v>-0.05476925189678483</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.06696715902995409</v>
+        <v>0.07843135910493748</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.06823395892951001</v>
+        <v>-0.05476532253081279</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.04497840806074005</v>
+        <v>0.0534160672438706</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.06334846266408267</v>
+        <v>-0.04660777269135541</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4231315892419893</v>
+        <v>0.4373145960217601</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1250023226684728</v>
+        <v>-0.118188385056026</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3734302905087741</v>
+        <v>0.3986434177744502</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.0617523788873594</v>
+        <v>-0.06252027842437347</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3291223970192416</v>
+        <v>0.3680673420555107</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.04918180697159102</v>
+        <v>-0.0560417878312689</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.303246899966469</v>
+        <v>0.3112862746412872</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>Leisure</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K48" s="11" t="n">
-        <v>-0.01503596712145727</v>
+        <v>-0.0230604679312999</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2420531141843112</v>
+        <v>0.2502109197347488</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.007268915195823289</v>
+        <v>-0.0137995141031112</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2271223811249856</v>
+        <v>0.2421226841358493</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.002292856791149434</v>
+        <v>-0.01016275993836646</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.202315605061469</v>
+        <v>0.2096887169266946</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.00226639788786287</v>
+        <v>0.001759539069540628</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1976590437392864</v>
+        <v>0.206844468109723</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.001827292686340742</v>
+        <v>0.008075904556049007</v>
       </c>
     </row>
     <row r="53">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1922506943303155</v>
+        <v>0.2028488262081827</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.001979510440054177</v>
+        <v>0.01002499727112482</v>
       </c>
     </row>
     <row r="54">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1887112639509667</v>
+        <v>0.1805581703369346</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.002071747591572803</v>
+        <v>0.01605018467053765</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8079478770558193</v>
+        <v>0.8440775434138634</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1618614410139183</v>
+        <v>-0.1782868494675429</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.6239044670412621</v>
+        <v>0.6888177318429052</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1302357206980945</v>
+        <v>-0.1295994882877993</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5178751870050209</v>
+        <v>0.5237976953563297</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1170482663661582</v>
+        <v>-0.1219074140284571</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4693611041383818</v>
+        <v>0.4881147689712686</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1010400782681766</v>
+        <v>-0.09264520720424807</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4443688325576396</v>
+        <v>0.4837573741349757</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4763,21 +4763,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K63" s="11" t="n">
-        <v>-0.07688878880518779</v>
+        <v>-0.07174566710981289</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.41047057023418</v>
+        <v>0.4414295053115522</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.07541821997190412</v>
+        <v>-0.06549180939178301</v>
       </c>
     </row>
     <row r="65">
@@ -4831,21 +4831,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.392537693918489</v>
+        <v>0.4330506190907064</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.02987308873285388</v>
+        <v>-0.01906579282482268</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3298279754783136</v>
+        <v>0.3589464221228102</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.01013429934997567</v>
+        <v>-0.005358517530522855</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3032319353271951</v>
+        <v>0.3068641535954162</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.01562570918714701</v>
+        <v>0.01531311442006222</v>
       </c>
     </row>
     <row r="68">
@@ -4966,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.192582405361815</v>
+        <v>0.1939871919743137</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.02329777626097917</v>
+        <v>0.0251788938837838</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.419164325290817</v>
+        <v>2.529707783440276</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.03575954203972587</v>
+        <v>0.03498075765337982</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.225102100673371</v>
+        <v>2.327351469194655</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.05941144023783096</v>
+        <v>0.04870740007110563</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.153118883409304</v>
+        <v>2.212383438209795</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1364883252079148</v>
+        <v>0.1316872487202254</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.512140251565298</v>
+        <v>1.570733583190849</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1543111413607019</v>
+        <v>0.1562174937478551</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.102598834314984</v>
+        <v>1.106585085895849</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1554688775119331</v>
+        <v>0.1645726820543136</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.063622925060219</v>
+        <v>1.050967371685437</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5319,21 +5319,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1947651829030248</v>
+        <v>0.2056066329549593</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9328874163426437</v>
+        <v>0.9650464695499184</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.213455573756699</v>
+        <v>0.2081158517930282</v>
       </c>
     </row>
     <row r="80">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2244961659143303</v>
+        <v>0.2481931933271839</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8342401356198315</v>
+        <v>0.8512577456399875</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2694955139874358</v>
+        <v>0.2743063011012541</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7720875311160065</v>
+        <v>0.7540048586724777</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2774409358186334</v>
+        <v>0.2936156158116408</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,16 +489,16 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>217.9</v>
+        <v>220.67</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.01879553451419858</v>
+        <v>0.01271227329073188</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.004934704867379791</v>
+        <v>-0.001583594682606937</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.01278178051598333</v>
+        <v>0.005513494113101425</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>-0.0403840803802904</v>
+        <v>0.01368917127161673</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.06692932370364979</v>
+        <v>-0.08473665457228874</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4373145960217601</v>
+        <v>0.4704232687116929</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7834815540848381</v>
+        <v>0.7817697980903962</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8440775434138634</v>
+        <v>0.8417451983777373</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.212383438209795</v>
+        <v>2.248007702599178</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4755110267157092</v>
+        <v>0.4809452967848464</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>92.95</v>
+        <v>92.7</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.005517032598081117</v>
+        <v>-0.002689618162539653</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.01032795186982716</v>
+        <v>-0.01529639314576614</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.01032795186982716</v>
+        <v>-0.005578247861527053</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.01918859713332188</v>
+        <v>0.002270505885209051</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1910558157073041</v>
+        <v>0.2071883818599847</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.1500206818184822</v>
+        <v>0.1436817247733226</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5317025285558048</v>
+        <v>0.5493765035423204</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5237976953563297</v>
+        <v>0.5250890768951346</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.5896080017295902</v>
+        <v>0.5757029672167258</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1670693942678061</v>
+        <v>0.1636564585347886</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>59.71</v>
+        <v>61.4</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.03233054852959061</v>
+        <v>0.02830350807769033</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.005993018348268486</v>
+        <v>0.008044683626569071</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.002350166029304157</v>
+        <v>0.0008150456886955038</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.08364033565587259</v>
+        <v>-0.009197993926031933</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.1507608994764571</v>
+        <v>-0.1718370376133064</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3680673420555107</v>
+        <v>0.4219889293367276</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.6146978745361615</v>
+        <v>0.6176490481778882</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.6888177318429052</v>
+        <v>0.6895014400863915</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.529707783440276</v>
+        <v>2.615402144379184</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5225781188491017</v>
+        <v>0.5348014603680586</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>55.72</v>
+        <v>56.02</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.02332415867711202</v>
+        <v>0.005384049362674448</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.01808883038091014</v>
+        <v>0.01412018022441375</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.01143585163133531</v>
+        <v>0.009915255542761292</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.004822297725836866</v>
+        <v>0.02751283909401359</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.006139403142475741</v>
+        <v>-0.02199717786985378</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3986434177744502</v>
+        <v>0.423094701605035</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4442319074325618</v>
+        <v>0.427343143516377</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4837573741349757</v>
+        <v>0.4607633828642956</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.570733583190849</v>
+        <v>1.580565558174238</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3698899840955474</v>
+        <v>0.3716341800969374</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29.83</v>
+        <v>66.98</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01843629195287755</v>
+        <v>0.004047433310845117</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.03361050910742436</v>
+        <v>-0.007115264364857432</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.001673334620644784</v>
+        <v>-0.02361508969710302</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.03468609096934916</v>
+        <v>0.08294268406423599</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1889198781303818</v>
+        <v>0.1888534464950116</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2502109197347488</v>
+        <v>0.1138189716195872</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1923977993930779</v>
+        <v>0.1853476114528747</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3589464221228102</v>
+        <v>0.4469651888399189</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4867096926046048</v>
+        <v>2.330154795132791</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1413234073240552</v>
+        <v>0.4933266206460751</v>
       </c>
     </row>
     <row r="7">
@@ -872,12 +872,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.33</v>
+        <v>29.51</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.01663776554209795</v>
+        <v>-0.01072744537856718</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.0006814465929717572</v>
+        <v>0.02040111172307779</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.05050176422033714</v>
+        <v>-0.005727765314891164</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.01610196413403908</v>
+        <v>0.01618454884769616</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1293800808313368</v>
+        <v>0.1733598678522108</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2096887169266946</v>
+        <v>0.2592952320643853</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.222753453876013</v>
+        <v>0.1764888515307159</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4881147689712686</v>
+        <v>0.3258495666664554</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.9650464695499184</v>
+        <v>0.4815594825715603</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2525380898293048</v>
+        <v>0.1400039710981913</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>66.70999999999999</v>
+        <v>28.95</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.03170422682120222</v>
+        <v>-0.0129559891495078</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.001795641826935701</v>
+        <v>-0.01396457216923741</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.04344707301562711</v>
+        <v>-0.05392155548891608</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.04807537290238106</v>
+        <v>-0.03820596690883238</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1503707044941132</v>
+        <v>0.1117511422849802</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.04187661433857359</v>
+        <v>0.2260375767649816</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1839703719430934</v>
+        <v>0.2195952086366291</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.4414295053115522</v>
+        <v>0.437335107589871</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.327351469194655</v>
+        <v>0.9576802847471548</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.492907475318181</v>
+        <v>0.250971039549817</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>54.78</v>
+        <v>54.5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.01935238311030418</v>
+        <v>-0.005111332339107211</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.07622784159338925</v>
+        <v>0.06196415284656553</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.03456086855504381</v>
+        <v>0.0386887503729636</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.06555142855256024</v>
+        <v>0.06653623536996367</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2613400505265124</v>
+        <v>0.2383549665652738</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2028488262081827</v>
+        <v>0.209195092547108</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.06237749763521516</v>
+        <v>0.05055559371104135</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1386754261752221</v>
+        <v>0.1201004784801531</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2481931933271839</v>
+        <v>0.2525295457040069</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.07669807514690286</v>
+        <v>0.07794348755508862</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>24.02</v>
+        <v>34.39</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01222085634730763</v>
+        <v>-0.008933756958936612</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03802943350590149</v>
+        <v>0.0141551030491367</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.002491672181581528</v>
+        <v>-0.02550301792377996</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.03223033885887938</v>
+        <v>-0.0117816050689874</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.2336929278311957</v>
+        <v>0.05296998010774367</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.3112862746412872</v>
+        <v>0.1531380757419629</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.05942520448792421</v>
+        <v>0.154743183880713</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.0251788938837838</v>
+        <v>0.397800097976367</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3775049277087084</v>
+        <v>0.6863036643319076</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1126648973826596</v>
+        <v>0.1902693795763102</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>34.7</v>
+        <v>23.73</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.0152135884470701</v>
+        <v>-0.01207331015822732</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.02359879649119878</v>
+        <v>0.02196383479600361</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.0261016075581324</v>
+        <v>0.005082546750640571</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.01729698452156692</v>
+        <v>0.02240415675464402</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.04204208882746174</v>
+        <v>0.2200513424889987</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1429690617709116</v>
+        <v>0.3117948947209375</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1699962062959539</v>
+        <v>0.03071460348731336</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4330506190907064</v>
+        <v>-0.00074413970903775</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6837136778829447</v>
+        <v>0.3635000085483462</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.189659690812662</v>
+        <v>0.1088812710744027</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>15.23</v>
+        <v>15.15</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.009277626788123605</v>
+        <v>-0.005252785693407036</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.01196008964918671</v>
+        <v>-0.01174170294009147</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.0166889190680628</v>
+        <v>0.0113484700593367</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.02146208572093045</v>
+        <v>0.02851324435480462</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.02434337750150883</v>
+        <v>-0.03931520743413597</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.206844468109723</v>
+        <v>0.2234082853451778</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.322814528534489</v>
+        <v>0.3105343079697374</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.3068641535954162</v>
+        <v>0.3010452144392286</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8512577456399875</v>
+        <v>0.8432790144038897</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2278791631409118</v>
+        <v>0.2261126116843735</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>45.03</v>
+        <v>44.53</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.003789526674818688</v>
+        <v>-0.01110370893969204</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.01808725402080569</v>
+        <v>-0.0004489440652343246</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.01980844306954432</v>
+        <v>-0.01547647070581515</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.01533258914479041</v>
+        <v>-0.001345623975906873</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1469689430577219</v>
+        <v>0.1488648273381925</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2421226841358493</v>
+        <v>0.2516062334606712</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0447853242917724</v>
+        <v>0.02777824490769443</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.01531311442006222</v>
+        <v>0.006707605557814134</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2743063011012541</v>
+        <v>0.2559053233200359</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08415474985028393</v>
+        <v>0.07891103179346848</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>68.87</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.01020406820621511</v>
+        <v>-0.008421690255899894</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.01431229369815534</v>
+        <v>-0.03681241966403759</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.02863185804806945</v>
+        <v>-0.02582022251058891</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.003616898004425551</v>
+        <v>-0.009284772766791627</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.03602888508436064</v>
+        <v>0.04156323847496157</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.05131486434880217</v>
+        <v>0.0707486166911</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2077462270678434</v>
+        <v>0.1940924692884189</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1670858011977108</v>
+        <v>0.15858735267935</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7540048586724777</v>
+        <v>0.7404590943626992</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2059896964157419</v>
+        <v>0.2028771458011847</v>
       </c>
     </row>
     <row r="15">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>36.99</v>
+        <v>16.93</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.001896086484109549</v>
+        <v>-0.00176879604459057</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02785801786722031</v>
+        <v>-0.03146448807001412</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.03872135866670379</v>
+        <v>-0.05154061941920218</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.06567311099015338</v>
+        <v>-0.04780654379322713</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.02267081976867558</v>
+        <v>0.05482872959166585</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1751116507957571</v>
+        <v>0.1923728777699036</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.09586441926867462</v>
+        <v>0.07688910640802815</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1802597209746171</v>
+        <v>0.1011256639978564</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.106585085895849</v>
+        <v>0.8582004157621155</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2819162959084498</v>
+        <v>0.2294121975514942</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="F16" s="5" t="n">
-        <v>16.96</v>
+        <v>36.91</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>-0.002162796091497832</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02584725829313217</v>
+        <v>-0.03250331923645267</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.05462661206305475</v>
+        <v>-0.04353460219053973</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.04665552492075764</v>
+        <v>-0.06200759139326706</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.0534160672438706</v>
+        <v>0.01876898464718568</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1805581703369346</v>
+        <v>0.1847152849538078</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.08008224826167454</v>
+        <v>0.09260979866114361</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1118689523946714</v>
+        <v>0.1522577117102291</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.859761257487109</v>
+        <v>1.122143959257931</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2297563263491766</v>
+        <v>0.2850645618029339</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>95.27</v>
+        <v>94.78</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.004181055017608903</v>
+        <v>-0.005143254760523686</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0</v>
+        <v>-0.007019362916361516</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.03981056771860347</v>
+        <v>-0.0302844193694205</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.00884317602192175</v>
+        <v>-0.01833251389450585</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.08175311653447559</v>
+        <v>0.08493587588260731</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1234200031128068</v>
+        <v>0.131520781475017</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.07418474382836826</v>
+        <v>0.06865993803099113</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.09026631887980607</v>
+        <v>0.0781787385963737</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5237683428929627</v>
+        <v>0.5035807007013016</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.150728799003228</v>
+        <v>0.1456243807500741</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>111.69</v>
+        <v>111.21</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.01010369025213176</v>
+        <v>-0.00429763941661121</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02598757979527111</v>
+        <v>-0.02524320576616135</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.05009354735434945</v>
+        <v>-0.04704368472438269</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.02895143713135284</v>
+        <v>-0.03371272375425882</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.004456725101339876</v>
+        <v>-0.008823510612270491</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1630740795707009</v>
+        <v>0.1767008419296208</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.09318077393779811</v>
+        <v>0.09155783051889244</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.139680327505765</v>
+        <v>0.1337489280090298</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.04870740007110563</v>
+        <v>0.04278627245173139</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.0159791081349181</v>
+        <v>0.0140633848766214</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>114.56</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.007120857657967106</v>
+        <v>-0.006688992666430971</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.009168008673305583</v>
+        <v>-0.00550877215536405</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.02791685157509616</v>
+        <v>-0.02375143592149753</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.07050711920005071</v>
+        <v>-0.02694993635317688</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.03202366678826851</v>
+        <v>0.0161383271228408</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.08281251307038429</v>
+        <v>0.05011602983395558</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1110670599307431</v>
+        <v>0.1011221632720918</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1939871919743137</v>
+        <v>0.1172304185397421</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4211760955650405</v>
+        <v>0.1480034984819236</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1243010890002874</v>
+        <v>0.0470829081227162</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>92.69</v>
+        <v>113.96</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.0006477943405753805</v>
+        <v>-0.005237416959739449</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.006843416245058132</v>
+        <v>-0.01724732680053809</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.02318470821364749</v>
+        <v>-0.04146690495824013</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.01404105589649274</v>
+        <v>-0.06244346998537897</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.02084988140843769</v>
+        <v>-0.04484115818956147</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.03402458308363765</v>
+        <v>0.09214838015158788</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1028806375159363</v>
+        <v>0.09917241402655308</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1167350072290034</v>
+        <v>0.1749019988482992</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1562174937478551</v>
+        <v>0.4214667969149617</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.04957427752689259</v>
+        <v>0.124377742311842</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>50.73</v>
+        <v>40.23</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01338390232851228</v>
+        <v>-0.00740190589923706</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.003362305465345994</v>
+        <v>-0.01878049896984568</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.01437733943882524</v>
+        <v>-0.03083591498564042</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.0494659816841635</v>
+        <v>-0.04914282179920637</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.04660777269135541</v>
+        <v>-0.02103647080315818</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.07003774583249744</v>
+        <v>0.03049320176908576</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.09301420340296152</v>
+        <v>0.09674156245888921</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1227350175950717</v>
+        <v>0.08223952880024399</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6919346631551204</v>
+        <v>0.3095887029232329</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1915927788110614</v>
+        <v>0.09406965671666523</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>99.54000000000001</v>
+        <v>98.36</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01117430360463301</v>
+        <v>-0.01185453379870038</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.00420166239287767</v>
+        <v>-0.02100129973838172</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.03891086985779213</v>
+        <v>-0.04514126229925997</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.02248846974712482</v>
+        <v>-0.02236358201322286</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.03602557760743941</v>
+        <v>-0.04029658834521188</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.01002499727112482</v>
+        <v>0.02075517679904726</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1308604811413565</v>
+        <v>0.1156452024089591</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1174496135576972</v>
+        <v>0.1043208096236172</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2081158517930282</v>
+        <v>0.1959868584922333</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06504884955770063</v>
+        <v>0.06147263527258273</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>40.53</v>
+        <v>50.79</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.002969535568866144</v>
+        <v>0.001182759192439153</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.003197271731507634</v>
+        <v>-0.01474293565045914</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.03015080422652749</v>
+        <v>-0.01205988978262906</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.04624793074762923</v>
+        <v>-0.02831451175196043</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.01444096332455969</v>
+        <v>-0.0597926604010629</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.02259474503120229</v>
+        <v>0.08279366307253366</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0979962570949382</v>
+        <v>0.08125491016459496</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.09200876468742414</v>
+        <v>0.1138861066984622</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3079072982946125</v>
+        <v>0.7005723946127251</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.09360122424110329</v>
+        <v>0.1936171265727689</v>
       </c>
     </row>
     <row r="24">
@@ -1841,25 +1841,25 @@
         <v>66.47</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.001054212247223241</v>
+        <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.0167159360787642</v>
+        <v>-0.03048419504543365</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.04097527684212843</v>
+        <v>-0.04770776053670711</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.1213483161931652</v>
+        <v>-0.1051426721451499</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.08241304554803153</v>
+        <v>-0.0916917061559247</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.01605018467053765</v>
+        <v>0.02120148963672874</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1134205464343021</v>
+        <v>0.09964105355747499</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.29</v>
+        <v>13.17</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.0007518968976257812</v>
+        <v>-0.009029336787323095</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.009687042749765618</v>
+        <v>-0.0237212527986348</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.04457224244142821</v>
+        <v>-0.05319912144038141</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.04319657067238025</v>
+        <v>-0.04703325852993379</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.05476532253081279</v>
+        <v>-0.06794055416643974</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.0137995141031112</v>
+        <v>-0.008980125631481761</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1292039639055345</v>
+        <v>0.1227102610369692</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.05120836828416087</v>
+        <v>0.04091779130819928</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.03498075765337982</v>
+        <v>0.0290226228935293</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.01152687322417179</v>
+        <v>0.009582097768329412</v>
       </c>
     </row>
     <row r="26">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.72</v>
+        <v>172.67</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.009661826846140142</v>
+        <v>0.007997636268421759</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.002386689438011569</v>
+        <v>-0.02721127792143485</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.0379746765984883</v>
+        <v>-0.06745520223663715</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.06067415561779566</v>
+        <v>-0.05126374632447628</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.02677537739523239</v>
+        <v>0.02988187043662927</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.008075904556049007</v>
+        <v>0.1001478517073042</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.005967193871036613</v>
+        <v>-0.08119646703870464</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.01906579282482268</v>
+        <v>-0.1298216665550374</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.3744762864643463</v>
+        <v>0.5022879285153103</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1118488481473632</v>
+        <v>0.1452959523084107</v>
       </c>
     </row>
     <row r="27">
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>171.3</v>
+        <v>16.69</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.003926614017302876</v>
+        <v>-0.001794185438327989</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02979154156982999</v>
+        <v>-0.01591972670931507</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.08307463689114725</v>
+        <v>-0.04300458583905242</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.05951463914689514</v>
+        <v>-0.06130484310985351</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.01360948551335994</v>
+        <v>-0.04245552255661311</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.08299275719604049</v>
+        <v>0.02835750224671996</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.08900826101570192</v>
+        <v>-0.01311943472047583</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1295994882877993</v>
+        <v>-0.02225729533072018</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.491115389494083</v>
+        <v>0.3809630937704842</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1424496900169046</v>
+        <v>0.113595218210695</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.5</v>
+        <v>16.35</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.00422448377268736</v>
+        <v>-0.009090885971531737</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01138409394714535</v>
+        <v>-0.02852047203875618</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.0828237793260157</v>
+        <v>-0.07783413403250083</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.06937391844293217</v>
+        <v>-0.08042746062714434</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.07843135910493748</v>
+        <v>0.05893787731980193</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.05229589788678424</v>
+        <v>0.0777851219012029</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1450776864117118</v>
+        <v>-0.1606775787638069</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1782868494675429</v>
+        <v>-0.1885855736476543</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1316872487202254</v>
+        <v>0.1299239861608481</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.04209858813263767</v>
+        <v>0.04155708146490156</v>
       </c>
     </row>
     <row r="29">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>53.34</v>
+        <v>25.96</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.008889752793614702</v>
+        <v>0.001156913958496375</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.009102761690491179</v>
+        <v>-0.02479345356698903</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.03770521632836321</v>
+        <v>-0.05531297245574751</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.02307689298069138</v>
+        <v>-0.1510791645114397</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.005592827003619294</v>
+        <v>-0.106983166253878</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.001759539069540628</v>
+        <v>-0.04803898569706577</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.06548231807921956</v>
+        <v>0.03649465163143861</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.07174566710981289</v>
+        <v>0.05882939606614279</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.1645726820543136</v>
+        <v>1.051997391453868</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.05209639576237635</v>
+        <v>0.2707465368093185</v>
       </c>
     </row>
     <row r="30">
@@ -2154,51 +2154,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>25.93</v>
+        <v>52.42</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.006132611976862656</v>
+        <v>-0.01724788115880693</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02150942244619691</v>
+        <v>-0.03480027907484429</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.05537342133031342</v>
+        <v>-0.05259359417689546</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.1509495897889026</v>
+        <v>-0.02871971496571368</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.1183270846749952</v>
+        <v>-0.03033672147030253</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.0560417878312689</v>
+        <v>0.005147236687525814</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.05507966499553518</v>
+        <v>-0.09410358592001478</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.0708526380604213</v>
+        <v>-0.0885889937089398</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1.050967371685437</v>
+        <v>0.1562201959575169</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2705338800869628</v>
+        <v>0.04957509518376635</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>61.47</v>
+        <v>61.2</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.01052111409475098</v>
+        <v>-0.00439239388973256</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01014488355713095</v>
+        <v>-0.02361199002920422</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.04371495973797046</v>
+        <v>-0.0421035944969006</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.05634016277759624</v>
+        <v>-0.0555555882604345</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.05532501138781232</v>
+        <v>-0.07538905415336894</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.01016275993836646</v>
+        <v>0.007721976194258406</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.07164213877994796</v>
+        <v>-0.08764512863674623</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.06549180939178301</v>
+        <v>-0.06869068228197528</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3496075842724156</v>
+        <v>0.3588443090690705</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1051023524070223</v>
+        <v>0.1076177323745673</v>
       </c>
     </row>
     <row r="32">
@@ -2266,51 +2266,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>123.87</v>
+        <v>15.31</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.008138682979135892</v>
+        <v>-0.003255158735554486</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02094525740433306</v>
+        <v>-0.0229738133327686</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03113019769292125</v>
+        <v>-0.06131202201531794</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.06159088828346948</v>
+        <v>-0.1109174779267584</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.08163010074647759</v>
+        <v>-0.06816797716103873</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.118188385056026</v>
+        <v>-0.002182262217172215</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.02284185963204288</v>
+        <v>-0.1043203988688807</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.005358517530522855</v>
+        <v>-0.1251906018402621</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4303749905733449</v>
+        <v>0.2045077827037423</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1267216412986329</v>
+        <v>0.06398752703161481</v>
       </c>
     </row>
     <row r="33">
@@ -2322,51 +2322,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>15.36</v>
+        <v>122.25</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.006468329962676544</v>
+        <v>-0.01307824905676558</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.0160153751120079</v>
+        <v>-0.03290881687836156</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.0685263875151827</v>
+        <v>-0.04737786756255924</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.1095652372940726</v>
+        <v>-0.06515258846906058</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.05476925189678483</v>
+        <v>-0.1014720143660832</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.0230604679312999</v>
+        <v>-0.1251482468570465</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.09373796213175734</v>
+        <v>-0.0499488082168682</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.1219074140284571</v>
+        <v>-0.01979040032074253</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2056066329549593</v>
+        <v>0.4118077441899193</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.06431098076183384</v>
+        <v>0.1218251873172513</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>111.28</v>
+        <v>111.31</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0008093923546592663</v>
+        <v>0.0002695792561642207</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.01189845440068438</v>
+        <v>-0.02828463908202705</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04060694172961843</v>
+        <v>-0.05138911681855673</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.1110401141715303</v>
+        <v>-0.09164357167481152</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1115369358938373</v>
+        <v>-0.1286888645119864</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.06252027842437347</v>
+        <v>-0.04439273654263642</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.04867618336687429</v>
+        <v>-0.05465964051388705</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09264520720424807</v>
+        <v>-0.09986438388694741</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2936156158116408</v>
+        <v>0.2984002744598795</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08960331658790976</v>
+        <v>0.09094502518544956</v>
       </c>
     </row>
   </sheetData>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.06555142855256024</v>
+        <v>0.08294268406423599</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1509495897889026</v>
+        <v>-0.1510791645114397</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.04807537290238106</v>
+        <v>0.06653623536996367</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1213483161931652</v>
+        <v>-0.1109174779267584</v>
       </c>
     </row>
     <row r="19">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.03468609096934916</v>
+        <v>0.02851324435480462</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1110401141715303</v>
+        <v>-0.1051426721451499</v>
       </c>
     </row>
     <row r="20">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.03223033885887938</v>
+        <v>0.02751283909401359</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1095652372940726</v>
+        <v>-0.09164357167481152</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.02146208572093045</v>
+        <v>0.02240415675464402</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08364033565587259</v>
+        <v>-0.08042746062714434</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01918859713332188</v>
+        <v>0.01618454884769616</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.07050711920005071</v>
+        <v>-0.06515258846906058</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.01729698452156692</v>
+        <v>0.01368917127161673</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.06937391844293217</v>
+        <v>-0.06244346998537897</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01533258914479041</v>
+        <v>0.002270505885209051</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06567311099015338</v>
+        <v>-0.06200759139326706</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.003616898004425551</v>
+        <v>-0.001345623975906873</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06159088828346948</v>
+        <v>-0.06130484310985351</v>
       </c>
     </row>
     <row r="26">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.004822297725836866</v>
+        <v>-0.009197993926031933</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06067415561779566</v>
+        <v>-0.0555555882604345</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2613400505265124</v>
+        <v>0.2383549665652738</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1507608994764571</v>
+        <v>-0.1718370376133064</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2336929278311957</v>
+        <v>0.2200513424889987</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3606,21 +3606,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1183270846749952</v>
+        <v>-0.1286888645119864</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1910558157073041</v>
+        <v>0.2071883818599847</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1115369358938373</v>
+        <v>-0.106983166253878</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1889198781303818</v>
+        <v>0.1888534464950116</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.08241304554803153</v>
+        <v>-0.1014720143660832</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1503707044941132</v>
+        <v>0.1733598678522108</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08163010074647759</v>
+        <v>-0.0916917061559247</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1469689430577219</v>
+        <v>0.1488648273381925</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.06692932370364979</v>
+        <v>-0.08473665457228874</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1293800808313368</v>
+        <v>0.1117511422849802</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.05532501138781232</v>
+        <v>-0.07538905415336894</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.08175311653447559</v>
+        <v>0.08493587588260731</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.05476925189678483</v>
+        <v>-0.06816797716103873</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.07843135910493748</v>
+        <v>0.05893787731980193</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.05476532253081279</v>
+        <v>-0.06794055416643974</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0534160672438706</v>
+        <v>0.05482872959166585</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.04660777269135541</v>
+        <v>-0.0597926604010629</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4373145960217601</v>
+        <v>0.4704232687116929</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.118188385056026</v>
+        <v>-0.1251482468570465</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3986434177744502</v>
+        <v>0.423094701605035</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.06252027842437347</v>
+        <v>-0.04803898569706577</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3680673420555107</v>
+        <v>0.4219889293367276</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.0560417878312689</v>
+        <v>-0.04439273654263642</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3112862746412872</v>
+        <v>0.3117948947209375</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0230604679312999</v>
+        <v>-0.008980125631481761</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2502109197347488</v>
+        <v>0.2592952320643853</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,21 +4252,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0137995141031112</v>
+        <v>-0.002182262217172215</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2421226841358493</v>
+        <v>0.2516062334606712</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01016275993836646</v>
+        <v>0.005147236687525814</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2096887169266946</v>
+        <v>0.2260375767649816</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.001759539069540628</v>
+        <v>0.007721976194258406</v>
       </c>
     </row>
     <row r="52">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.206844468109723</v>
+        <v>0.2234082853451778</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.008075904556049007</v>
+        <v>0.02075517679904726</v>
       </c>
     </row>
     <row r="53">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2028488262081827</v>
+        <v>0.209195092547108</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.01002499727112482</v>
+        <v>0.02120148963672874</v>
       </c>
     </row>
     <row r="54">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1805581703369346</v>
+        <v>0.1923728777699036</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.01605018467053765</v>
+        <v>0.02835750224671996</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8440775434138634</v>
+        <v>0.8417451983777373</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1782868494675429</v>
+        <v>-0.1885855736476543</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.6888177318429052</v>
+        <v>0.6895014400863915</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1295994882877993</v>
+        <v>-0.1298216665550374</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5237976953563297</v>
+        <v>0.5250890768951346</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1219074140284571</v>
+        <v>-0.1251906018402621</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4881147689712686</v>
+        <v>0.4607633828642956</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09264520720424807</v>
+        <v>-0.09986438388694741</v>
       </c>
     </row>
     <row r="63">
@@ -4741,21 +4741,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4837573741349757</v>
+        <v>0.4469651888399189</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.07174566710981289</v>
+        <v>-0.0885889937089398</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4414295053115522</v>
+        <v>0.437335107589871</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.06549180939178301</v>
+        <v>-0.06869068228197528</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4330506190907064</v>
+        <v>0.397800097976367</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.01906579282482268</v>
+        <v>-0.02225729533072018</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3589464221228102</v>
+        <v>0.3258495666664554</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.005358517530522855</v>
+        <v>-0.01979040032074253</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3068641535954162</v>
+        <v>0.3010452144392286</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.01531311442006222</v>
+        <v>-0.00074413970903775</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1939871919743137</v>
+        <v>0.1749019988482992</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.0251788938837838</v>
+        <v>0.006707605557814134</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.529707783440276</v>
+        <v>2.615402144379184</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.03498075765337982</v>
+        <v>0.0290226228935293</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.327351469194655</v>
+        <v>2.330154795132791</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.04870740007110563</v>
+        <v>0.04278627245173139</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.212383438209795</v>
+        <v>2.248007702599178</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1316872487202254</v>
+        <v>0.1299239861608481</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.570733583190849</v>
+        <v>1.580565558174238</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1562174937478551</v>
+        <v>0.1480034984819236</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.106585085895849</v>
+        <v>1.122143959257931</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1645726820543136</v>
+        <v>0.1562201959575169</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.050967371685437</v>
+        <v>1.051997391453868</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5319,21 +5319,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2056066329549593</v>
+        <v>0.1959868584922333</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9650464695499184</v>
+        <v>0.9576802847471548</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2081158517930282</v>
+        <v>0.2045077827037423</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.859761257487109</v>
+        <v>0.8582004157621155</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2481931933271839</v>
+        <v>0.2525295457040069</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8512577456399875</v>
+        <v>0.8432790144038897</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2743063011012541</v>
+        <v>0.2559053233200359</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7540048586724777</v>
+        <v>0.7404590943626992</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2936156158116408</v>
+        <v>0.2984002744598795</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.8417451983777373</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.248007702599178</v>
+        <v>2.248006973123559</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4809452967848464</v>
+        <v>0.4809451859154903</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.5250890768951346</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.5757029672167258</v>
+        <v>0.5757030693880663</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1636564585347886</v>
+        <v>0.1636564836859624</v>
       </c>
     </row>
     <row r="4">
@@ -742,13 +742,13 @@
         <v>0.6176490481778882</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.6895014400863915</v>
+        <v>0.6895012627455426</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.615402144379184</v>
+        <v>2.615401738333522</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5348014603680586</v>
+        <v>0.5348014029102275</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.4607633828642956</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.580565558174238</v>
+        <v>1.58056578490832</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3716341800969374</v>
+        <v>0.3716342202685199</v>
       </c>
     </row>
     <row r="6">
@@ -913,10 +913,10 @@
         <v>0.3258495666664554</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4815594825715603</v>
+        <v>0.4815596244443459</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1400039710981913</v>
+        <v>0.1400040074867706</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.437335107589871</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.9576802847471548</v>
+        <v>0.9576801584961006</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.250971039549817</v>
+        <v>0.2509710126580551</v>
       </c>
     </row>
     <row r="9">
@@ -1081,10 +1081,10 @@
         <v>0.397800097976367</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6863036643319076</v>
+        <v>0.6863035066182002</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1902693795763102</v>
+        <v>0.1902693424691535</v>
       </c>
     </row>
     <row r="11">
@@ -1190,13 +1190,13 @@
         <v>0.3105343079697374</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.3010452144392286</v>
+        <v>0.3010453209938473</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8432790144038897</v>
+        <v>0.8432788005241871</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2261126116843735</v>
+        <v>0.2261125642615274</v>
       </c>
     </row>
     <row r="13">
@@ -1302,13 +1302,13 @@
         <v>0.1940924692884189</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.15858735267935</v>
+        <v>0.1585874276619603</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7404590943626992</v>
+        <v>0.7404585867274993</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2028771458011847</v>
+        <v>0.2028770288544852</v>
       </c>
     </row>
     <row r="15">
@@ -1358,13 +1358,13 @@
         <v>0.07688910640802815</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1011256639978564</v>
+        <v>0.1011255956984602</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8582004157621155</v>
+        <v>0.8582002212582749</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2294121975514942</v>
+        <v>0.2294121546559773</v>
       </c>
     </row>
     <row r="16">
@@ -1473,10 +1473,10 @@
         <v>0.0781787385963737</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5035807007013016</v>
+        <v>0.5035807916919774</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1456243807500741</v>
+        <v>0.1456244038596053</v>
       </c>
     </row>
     <row r="18">
@@ -1585,10 +1585,10 @@
         <v>0.1172304185397421</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1480034984819236</v>
+        <v>0.1480036076909153</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.0470829081227162</v>
+        <v>0.04708294132553736</v>
       </c>
     </row>
     <row r="20">
@@ -1635,16 +1635,16 @@
         <v>0.09214838015158788</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.09917241402655308</v>
+        <v>0.09917233314131924</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0.1749019988482992</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4214667969149617</v>
+        <v>0.4214666616419886</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.124377742311842</v>
+        <v>0.1243777066449461</v>
       </c>
     </row>
     <row r="21">
@@ -1691,16 +1691,16 @@
         <v>0.03049320176908576</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.09674156245888921</v>
+        <v>0.09674144840276511</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.08223952880024399</v>
+        <v>0.08223963986004224</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3095887029232329</v>
+        <v>0.3095889468566111</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.09406965671666523</v>
+        <v>0.09406972464641283</v>
       </c>
     </row>
     <row r="22">
@@ -1753,10 +1753,10 @@
         <v>0.1043208096236172</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1959868584922333</v>
+        <v>0.1959867475429946</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06147263527258273</v>
+        <v>0.06147260244903796</v>
       </c>
     </row>
     <row r="23">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>66.47</v>
+        <v>66.95</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0</v>
+        <v>0.00722123843424205</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.03048419504543365</v>
+        <v>-0.0234830902520905</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.04770776053670711</v>
+        <v>-0.04083103121646425</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.1051426721451499</v>
+        <v>-0.09868069401608126</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.0916917061559247</v>
+        <v>-0.08513259539427698</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.02120148963672874</v>
+        <v>0.02857582908279888</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.09964105355747499</v>
+        <v>0.1075818237972948</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         <v>-0.1298216665550374</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.5022879285153103</v>
+        <v>0.5022878287959429</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1452959523084107</v>
+        <v>0.145295926967465</v>
       </c>
     </row>
     <row r="27">
@@ -2021,7 +2021,7 @@
         <v>0.02835750224671996</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.01311943472047583</v>
+        <v>-0.01311954602245213</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>-0.02225729533072018</v>
@@ -2139,10 +2139,10 @@
         <v>0.05882939606614279</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.051997391453868</v>
+        <v>1.051997546139172</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2707465368093185</v>
+        <v>0.2707465687401274</v>
       </c>
     </row>
     <row r="30">
@@ -2189,10 +2189,10 @@
         <v>0.005147236687525814</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.09410358592001478</v>
+        <v>-0.09410352619996154</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.0885889937089398</v>
+        <v>-0.08858905415828289</v>
       </c>
       <c r="O30" s="6" t="n">
         <v>0.1562201959575169</v>
@@ -2307,10 +2307,10 @@
         <v>-0.1251906018402621</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2045077827037423</v>
+        <v>0.204507873077874</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06398752703161481</v>
+        <v>0.06398755364191655</v>
       </c>
     </row>
     <row r="33">
@@ -2360,7 +2360,7 @@
         <v>-0.0499488082168682</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.01979040032074253</v>
+        <v>-0.01979028039589981</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>0.4118077441899193</v>
@@ -2416,7 +2416,7 @@
         <v>-0.05465964051388705</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09986438388694741</v>
+        <v>-0.09986432835130254</v>
       </c>
       <c r="O34" s="6" t="n">
         <v>0.2984002744598795</v>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1051426721451499</v>
+        <v>-0.09868069401608126</v>
       </c>
     </row>
     <row r="20">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.0916917061559247</v>
+        <v>-0.08513259539427698</v>
       </c>
     </row>
     <row r="36">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.02120148963672874</v>
+        <v>0.02835750224671996</v>
       </c>
     </row>
     <row r="54">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.02835750224671996</v>
+        <v>0.02857582908279888</v>
       </c>
     </row>
     <row r="55"/>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.6895014400863915</v>
+        <v>0.6895012627455426</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09986438388694741</v>
+        <v>-0.09986432835130254</v>
       </c>
     </row>
     <row r="63">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.0885889937089398</v>
+        <v>-0.08858905415828289</v>
       </c>
     </row>
     <row r="64">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.01979040032074253</v>
+        <v>-0.01979028039589981</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3010452144392286</v>
+        <v>0.3010453209938473</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.615402144379184</v>
+        <v>2.615401738333522</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.248007702599178</v>
+        <v>2.248006973123559</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.580565558174238</v>
+        <v>1.58056578490832</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1480034984819236</v>
+        <v>0.1480036076909153</v>
       </c>
     </row>
     <row r="77">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.051997391453868</v>
+        <v>1.051997546139172</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1959868584922333</v>
+        <v>0.1959867475429946</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9576802847471548</v>
+        <v>0.9576801584961006</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2045077827037423</v>
+        <v>0.204507873077874</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8582004157621155</v>
+        <v>0.8582002212582749</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8432790144038897</v>
+        <v>0.8432788005241871</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7404590943626992</v>
+        <v>0.7404585867274993</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,13 +489,13 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>220.67</v>
+        <v>226.38</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.01271227329073188</v>
+        <v>0.02587577269790708</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.001583594682606937</v>
+        <v>0.06092417144305329</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.005513494113101425</v>
+        <v>0.0315319327314505</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.01368917127161673</v>
+        <v>0.04990265285822426</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.08473665457228874</v>
+        <v>-0.06105350828727529</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4704232687116929</v>
+        <v>0.5454874824810154</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7817697980903962</v>
+        <v>0.8117475317815148</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8417451983777373</v>
+        <v>0.8934668677374331</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.248006973123559</v>
+        <v>2.451744974992017</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4809451859154903</v>
+        <v>0.5112845194533644</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>92.7</v>
+        <v>63.56</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.002689618162539653</v>
+        <v>0.03517914973506486</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.01529639314576614</v>
+        <v>0.1077030357291133</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.005578247861527053</v>
+        <v>0.03602286803808408</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.002270505885209051</v>
+        <v>0.04884493355942854</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2071883818599847</v>
+        <v>-0.14270296875447</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.1436817247733226</v>
+        <v>0.5055043672338237</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5493765035423204</v>
+        <v>0.6206910974434574</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5250890768951346</v>
+        <v>0.7603483322944291</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.5757030693880663</v>
+        <v>2.905679076938151</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1636564836859624</v>
+        <v>0.5748245813786581</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>61.4</v>
+        <v>90.53</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.02830350807769033</v>
+        <v>-0.02340882675710232</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.008044683626569071</v>
+        <v>-0.02676841489603654</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.0008150456886955038</v>
+        <v>-0.02885649438083071</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.009197993926031933</v>
+        <v>-0.02013205566229237</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.1718370376133064</v>
+        <v>0.1789295181658375</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.4219889293367276</v>
+        <v>0.1009245914379124</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.6176490481778882</v>
+        <v>0.5068580373754752</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.6895012627455426</v>
+        <v>0.5066335144894758</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.615401738333522</v>
+        <v>0.593056894371246</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5348014029102275</v>
+        <v>0.1679128285251008</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>56.02</v>
+        <v>57.71</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.005384049362674448</v>
+        <v>0.03016777245446756</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.01412018022441375</v>
+        <v>0.06026086277616605</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.009915255542761292</v>
+        <v>0.04038214917027072</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.02751283909401359</v>
+        <v>0.0734747188665239</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.02199717786985378</v>
+        <v>0.007506988727995489</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.423094701605035</v>
+        <v>0.5036925043736638</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.427343143516377</v>
+        <v>0.4402642762558553</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4607633828642956</v>
+        <v>0.4953026696224148</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.58056578490832</v>
+        <v>1.743518945110235</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3716342202685199</v>
+        <v>0.3999181831625858</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>66.98</v>
+        <v>29.73</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.004047433310845117</v>
+        <v>0.007455076640059621</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.007115264364857432</v>
+        <v>0.01571571839011177</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.02361508969710302</v>
+        <v>0.001684610395769726</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.08294268406423599</v>
+        <v>-0.02268246325861545</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1888534464950116</v>
+        <v>0.1821073555934194</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1138189716195872</v>
+        <v>0.2882090360442082</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1853476114528747</v>
+        <v>0.1743964683453709</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4469651888399189</v>
+        <v>0.3498048435110988</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.330154795132791</v>
+        <v>0.5120325123597118</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.4933266206460751</v>
+        <v>0.147766936311706</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="F7" s="5" t="n">
-        <v>29.51</v>
+        <v>29.16</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.01072744537856718</v>
+        <v>0.007253854194763543</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.02040111172307779</v>
+        <v>-0.01051915416237914</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.005727765314891164</v>
+        <v>-0.04705884039562402</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.01618454884769616</v>
+        <v>-0.06207784804449834</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1733598678522108</v>
+        <v>0.1198156229719771</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2592952320643853</v>
+        <v>0.2496568360714926</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1764888515307159</v>
+        <v>0.2031533964433394</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3258495666664554</v>
+        <v>0.4559063328177873</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4815596244443459</v>
+        <v>1.00049501274334</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1400040074867706</v>
+        <v>0.2600249874828229</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>28.95</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.0129559891495078</v>
+        <v>-0.01403407575835758</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.01396457216923741</v>
+        <v>0.006553883572254282</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.05392155548891608</v>
+        <v>-0.03731774949761102</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.03820596690883238</v>
+        <v>-0.07129798412751209</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1117511422849802</v>
+        <v>0.1721689871613161</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2260375767649816</v>
+        <v>0.2085945981682438</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2195952086366291</v>
+        <v>0.1415297219247289</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.437335107589871</v>
+        <v>0.3704061445399354</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.9576801584961006</v>
+        <v>2.363165775883104</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2509710126580551</v>
+        <v>0.4982447284279621</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>54.5</v>
+        <v>24.44</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.005111332339107211</v>
+        <v>0.02991997494806431</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.06196415284656553</v>
+        <v>0.01368726318340996</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.0386887503729636</v>
+        <v>0.03515459137015653</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.06653623536996367</v>
+        <v>0.04892709589379751</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2383549665652738</v>
+        <v>0.2565552480916218</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.209195092547108</v>
+        <v>0.3788716336223201</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.05055559371104135</v>
+        <v>0.04887145790164471</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1201004784801531</v>
+        <v>0.01625866472090487</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2525295457040069</v>
+        <v>0.4548303833133658</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.07794348755508862</v>
+        <v>0.1331066477557512</v>
       </c>
     </row>
     <row r="10">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>34.39</v>
+        <v>55.07</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.008933756958936612</v>
+        <v>0.01045870999677456</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.0141551030491367</v>
+        <v>0.05680289867209587</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.02550301792377996</v>
+        <v>0.04955209479002654</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.0117816050689874</v>
+        <v>0.01642671437126997</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.05296998010774367</v>
+        <v>0.2513065620336454</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1531380757419629</v>
+        <v>0.2325659766071275</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.154743183880713</v>
+        <v>0.05657341265731652</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.397800097976367</v>
+        <v>0.1378323847239165</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6863035066182002</v>
+        <v>0.2981376982172252</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1902693424691535</v>
+        <v>0.09087147941184592</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>23.73</v>
+        <v>34.9</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01207331015822732</v>
+        <v>0.01482995479156601</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.02196383479600361</v>
+        <v>0.01306243114582317</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.005082546750640571</v>
+        <v>-0.01105127173507214</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02240415675464402</v>
+        <v>-0.04462078587152207</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.2200513424889987</v>
+        <v>0.0685854773096175</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3117948947209375</v>
+        <v>0.1908857304600364</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.03071460348731336</v>
+        <v>0.157491410691178</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>-0.00074413970903775</v>
+        <v>0.4328915075796376</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3635000085483462</v>
+        <v>0.7407405927535182</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1088812710744027</v>
+        <v>0.2029419926239515</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>15.15</v>
+        <v>15.44</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.005252785693407036</v>
+        <v>0.01914191215545125</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.01174170294009147</v>
+        <v>0.02387265639911051</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.0113484700593367</v>
+        <v>0.03070761363176255</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.02851324435480462</v>
+        <v>0.03763437242173873</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.03931520743413597</v>
+        <v>-0.02092586352576231</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2234082853451778</v>
+        <v>0.2598457371103255</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.3105343079697374</v>
+        <v>0.3302304780617729</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.3010453209938473</v>
+        <v>0.3216965083565604</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8432788005241871</v>
+        <v>0.9241593040990503</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2261125642615274</v>
+        <v>0.2437898498627746</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>44.53</v>
+        <v>45.27</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.01110370893969204</v>
+        <v>0.01661804847861004</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.0004489440652343246</v>
+        <v>-0.006365252563345081</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.01547647070581515</v>
+        <v>0.0008843890323277925</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.001345623975906873</v>
+        <v>-0.001543883868298179</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1488648273381925</v>
+        <v>0.1679567187342685</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2516062334606712</v>
+        <v>0.2775700753477526</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.02777824490769443</v>
+        <v>0.03682061315500684</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.006707605557814134</v>
+        <v>0.01975919703127405</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2559053233200359</v>
+        <v>0.321356097974852</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.07891103179346848</v>
+        <v>0.09733683520357794</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>68.29000000000001</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.008421690255899894</v>
+        <v>0.00981107277731752</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.03681241966403759</v>
+        <v>-0.02695080553247886</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.02582022251058891</v>
+        <v>-0.01626247381544943</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.009284772766791627</v>
+        <v>-0.003035985109609785</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.04156323847496157</v>
+        <v>0.05178209120981769</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.0707486166911</v>
+        <v>0.07396810553937971</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1940924692884189</v>
+        <v>0.1968000150415552</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1585874276619603</v>
+        <v>0.1755531097538177</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7404585867274993</v>
+        <v>0.7679144185249582</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2028770288544852</v>
+        <v>0.2091692083005452</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>16.93</v>
+        <v>17.01</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.00176879604459057</v>
+        <v>0.004725335042173429</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.03146448807001412</v>
+        <v>-0.02128877731593892</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.05154061941920218</v>
+        <v>-0.04705883107206565</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.04780654379322713</v>
+        <v>-0.03461978327454507</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.05482872959166585</v>
+        <v>0.05981314875109667</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1923728777699036</v>
+        <v>0.1955182838855885</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.07688910640802815</v>
+        <v>0.07430870763748954</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1011255956984602</v>
+        <v>0.1083513369264086</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8582002212582749</v>
+        <v>0.9114752959922017</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2294121546559773</v>
+        <v>0.2410508123446489</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>36.91</v>
+        <v>36.95</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.002162796091497832</v>
+        <v>0.001083741958621154</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.03250331923645267</v>
+        <v>-0.02635046060332524</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.04353460219053973</v>
+        <v>-0.04249804050696426</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.06200759139326706</v>
+        <v>-0.02788733505397833</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.01876898464718568</v>
+        <v>0.01987306734198979</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1847152849538078</v>
+        <v>0.1774987863323056</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.09260979866114361</v>
+        <v>0.09114625870187876</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1522577117102291</v>
+        <v>0.1594403595499807</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.122143959257931</v>
+        <v>1.177581471690906</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2850645618029339</v>
+        <v>0.2961585755153788</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>94.78</v>
+        <v>111.07</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.005143254760523686</v>
+        <v>-0.001258874119242637</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.007019362916361516</v>
+        <v>-0.04348951887969588</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.0302844193694205</v>
+        <v>-0.04824333676645198</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.01833251389450585</v>
+        <v>-0.03425791120966404</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.08493587588260731</v>
+        <v>-0.01007127704236244</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.131520781475017</v>
+        <v>0.2029675889973441</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06865993803099113</v>
+        <v>0.08626832459844236</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0781787385963737</v>
+        <v>0.1356541142104832</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5035807916919774</v>
+        <v>0.02369577500046582</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1456244038596053</v>
+        <v>0.007837012456045622</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>111.21</v>
+        <v>93.89</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.00429763941661121</v>
+        <v>-0.009390160383108581</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02524320576616135</v>
+        <v>-0.03176241922535017</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.04704368472438269</v>
+        <v>-0.03939020419754091</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.03371272375425882</v>
+        <v>-0.03455013481081293</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.008823510612270491</v>
+        <v>0.07474815400268109</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1767008419296208</v>
+        <v>0.1220788120782066</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.09155783051889244</v>
+        <v>0.05896702107694041</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1337489280090298</v>
+        <v>0.06747460265979766</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.04278627245173139</v>
+        <v>0.494371101195469</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.0140633848766214</v>
+        <v>0.1432805631288463</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>92.06999999999999</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.006688992666430971</v>
+        <v>-0.00271532530497065</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.00550877215536405</v>
+        <v>-0.02006400549251286</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.02375143592149753</v>
+        <v>-0.02640226835148118</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.02694993635317688</v>
+        <v>-0.04064360491964025</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.0161383271228408</v>
+        <v>0.01337918100985358</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.05011602983395558</v>
+        <v>0.06204347580916525</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1011221632720918</v>
+        <v>0.1066460105537068</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1172304185397421</v>
+        <v>0.1203955214084829</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1480036076909153</v>
+        <v>0.159912430933103</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.04708294132553736</v>
+        <v>0.05069113407531223</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>113.96</v>
+        <v>113.9</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.005237416959739449</v>
+        <v>-0.0005264791073689157</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.01724732680053809</v>
+        <v>-0.02357479609110769</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.04146690495824013</v>
+        <v>-0.04197155260650121</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.06244346998537897</v>
+        <v>-0.06578081334903763</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.04484115818956147</v>
+        <v>-0.04534402936399329</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.09214838015158788</v>
+        <v>0.1058946400436933</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.09917233314131924</v>
+        <v>0.09859372271517186</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1749019988482992</v>
+        <v>0.1675340149806841</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4214666616419886</v>
+        <v>0.4389402015427948</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1243777066449461</v>
+        <v>0.1289661365197052</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>40.23</v>
+        <v>40.59</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.00740190589923706</v>
+        <v>0.008948561134672905</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01878049896984568</v>
+        <v>-0.003192560516160792</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.03083591498564042</v>
+        <v>-0.02216329092136016</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.04914282179920637</v>
+        <v>-0.04681355961051703</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.02103647080315818</v>
+        <v>-0.01227615581352515</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.03049320176908576</v>
+        <v>0.07489083575990696</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.09674144840276511</v>
+        <v>0.1101567459934489</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.08223963986004224</v>
+        <v>0.09732966622606787</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3095889468566111</v>
+        <v>0.3676423475337309</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.09406972464641283</v>
+        <v>0.1100030699624885</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>98.36</v>
+        <v>51.29</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01185453379870038</v>
+        <v>0.009844457392934158</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.02100129973838172</v>
+        <v>0.01927665394646061</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.04514126229925997</v>
+        <v>-0.002334155460823384</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.02236358201322286</v>
+        <v>-0.01441199052277919</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.04029658834521188</v>
+        <v>-0.05053682930585712</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.02075517679904726</v>
+        <v>0.1215206488477221</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1156452024089591</v>
+        <v>0.08441127627982459</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1043208096236172</v>
+        <v>0.1190621407571228</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1959867475429946</v>
+        <v>0.7651447297226068</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06147260244903796</v>
+        <v>0.2085374332154863</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>50.79</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.001182759192439153</v>
+        <v>-0.003558341520427555</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01474293565045914</v>
+        <v>-0.009599807569028673</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.01205988978262906</v>
+        <v>-0.04853897579176347</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.02831451175196043</v>
+        <v>-0.06327052748700368</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.0597926604010629</v>
+        <v>-0.04371154084219908</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.08279366307253366</v>
+        <v>0.05635752248395964</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.08125491016459496</v>
+        <v>0.1053516472633347</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1138861066984622</v>
+        <v>0.09839597386018806</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.7005723946127251</v>
+        <v>0.2367855892312036</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1936171265727689</v>
+        <v>0.0734079449228846</v>
       </c>
     </row>
     <row r="24">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>66.95</v>
+        <v>67.45</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.00722123843424205</v>
+        <v>0.00746826023586733</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.0234830902520905</v>
+        <v>0.005665681454405824</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.04083103121646425</v>
+        <v>-0.03366770774742023</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.09868069401608126</v>
+        <v>-0.06514212721050205</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.08513259539427698</v>
+        <v>-0.07830012753536886</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.02857582908279888</v>
+        <v>0.06354460573400389</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1075818237972948</v>
+        <v>0.1017640575517047</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.17</v>
+        <v>13.11</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.009029336787323095</v>
+        <v>-0.004555840491200946</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.0237212527986348</v>
+        <v>-0.01650414615813767</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.05319912144038141</v>
+        <v>-0.05751259522002794</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.04703325852993379</v>
+        <v>-0.06423986848688445</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.06794055416643974</v>
+        <v>-0.07218686832997456</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.008980125631481761</v>
+        <v>0.01193415331900005</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1227102610369692</v>
+        <v>0.1185206249862696</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.04091779130819928</v>
+        <v>0.04016389498082029</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.0290226228935293</v>
+        <v>0.06149389168274144</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.009582097768329412</v>
+        <v>0.02009158849586967</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>172.67</v>
+        <v>174.87</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.007997636268421759</v>
+        <v>0.01274104923595143</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.02721127792143485</v>
+        <v>-0.01236870253927069</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.06745520223663715</v>
+        <v>-0.0555736030536037</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05126374632447628</v>
+        <v>-0.05593046941268864</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.02988187043662927</v>
+        <v>0.04300364605507623</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1001478517073042</v>
+        <v>0.1196448018536018</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.08119646703870464</v>
+        <v>-0.07546028206646516</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.1298216665550374</v>
+        <v>-0.1179951981937968</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.5022878287959429</v>
+        <v>0.574267806494795</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.145295926967465</v>
+        <v>0.1633030625456946</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>16.69</v>
+        <v>16.83</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.001794185438327989</v>
+        <v>0.008388219602674996</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.01591972670931507</v>
+        <v>-0.01232400120530097</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.04300458583905242</v>
+        <v>-0.03497709814631744</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.06130484310985351</v>
+        <v>-0.04753820876972348</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.04245552255661311</v>
+        <v>-0.03442342920048935</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.02835750224671996</v>
+        <v>0.05403316899665445</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.01311954602245213</v>
+        <v>7.797731381531392e-05</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.02225729533072018</v>
+        <v>-0.00776960305575447</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.3809630937704842</v>
+        <v>0.4468325025796569</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.113595218210695</v>
+        <v>0.1310264259698866</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.35</v>
+        <v>16.56</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.009090885971531737</v>
+        <v>0.01284398040202239</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02852047203875618</v>
+        <v>-0.03214501021562965</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.07783413403250083</v>
+        <v>-0.06598985372260024</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.08042746062714434</v>
+        <v>-0.08508292171661791</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.05893787731980193</v>
+        <v>0.07253885466305676</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.0777851219012029</v>
+        <v>0.10252989089509</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1606775787638069</v>
+        <v>-0.1555329448995106</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1885855736476543</v>
+        <v>-0.1789787107930872</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1299239861608481</v>
+        <v>0.1905103988209815</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.04155708146490156</v>
+        <v>0.05984998435369349</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>25.96</v>
+        <v>26.22</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.001156913958496375</v>
+        <v>0.01001541749041701</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02479345356698903</v>
+        <v>-0.0022831572193035</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.05531297245574751</v>
+        <v>-0.04585153747711079</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.1510791645114397</v>
+        <v>-0.09053071860071138</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.106983166253878</v>
+        <v>-0.09803922983794033</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.04803898569706577</v>
+        <v>0.002550419855511965</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.03649465163143861</v>
+        <v>0.01785092724642068</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.05882939606614279</v>
+        <v>0.06645507975005227</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.051997546139172</v>
+        <v>1.131087935548486</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2707465687401274</v>
+        <v>0.2868673734811156</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>52.42</v>
+        <v>52.8</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01724788115880693</v>
+        <v>0.007249162178345037</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.03480027907484429</v>
+        <v>-0.02816128368174653</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.05259359417689546</v>
+        <v>-0.0457256914922809</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.02871971496571368</v>
+        <v>-0.0546105518422495</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.03033672147030253</v>
+        <v>-0.02330747510585507</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.005147236687525814</v>
+        <v>0.03855736810417332</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.09410352619996154</v>
+        <v>-0.09152169361344065</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.08858905415828289</v>
+        <v>-0.08212174318314136</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1562201959575169</v>
+        <v>0.1961695308864919</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.04957509518376635</v>
+        <v>0.06152667485090091</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>61.2</v>
+        <v>61.99</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.00439239388973256</v>
+        <v>0.01290851153070149</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02361199002920422</v>
+        <v>-0.009744357995575159</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.0421035944969006</v>
+        <v>-0.02973857770124633</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.0555555882604345</v>
+        <v>-0.05329874006637858</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.07538905415336894</v>
+        <v>-0.06345370309749487</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.007721976194258406</v>
+        <v>0.04731087550248225</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.08764512863674623</v>
+        <v>-0.07376683646337234</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.06869068228197528</v>
+        <v>-0.05640638026789657</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3588443090690705</v>
+        <v>0.4364472918662554</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1076177323745673</v>
+        <v>0.1283137958928831</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>15.31</v>
+        <v>15.4</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.003255158735554486</v>
+        <v>0.005878458291761923</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.0229738133327686</v>
+        <v>-0.02716363280152889</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.06131202201531794</v>
+        <v>-0.05579398388775669</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.1109174779267584</v>
+        <v>-0.111367588786639</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.06816797716103873</v>
+        <v>-0.0626902414798518</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.002182262217172215</v>
+        <v>0.0194249869526415</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.1043203988688807</v>
+        <v>-0.1066038112687155</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1251906018402621</v>
+        <v>-0.1209015369348776</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.204507873077874</v>
+        <v>0.2535959797534413</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06398755364191655</v>
+        <v>0.07824932985197819</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>122.25</v>
+        <v>121.82</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01307824905676558</v>
+        <v>-0.003517384909413335</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03290881687836156</v>
+        <v>-0.02058206797816442</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.04737786756255924</v>
+        <v>-0.05072860627556786</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.06515258846906058</v>
+        <v>-0.04169291171526757</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1014720143660832</v>
+        <v>-0.1046324831434375</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1251482468570465</v>
+        <v>-0.08455000096319765</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.0499488082168682</v>
+        <v>-0.04484725575283166</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.01979028039589981</v>
+        <v>-0.03093135201514952</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4118077441899193</v>
+        <v>0.4317719550909433</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1218251873172513</v>
+        <v>0.1270883232372704</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>111.31</v>
+        <v>111.81</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0002695792561642207</v>
+        <v>0.004491959491210951</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02828463908202705</v>
+        <v>-0.01035586620265438</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.05138911681855673</v>
+        <v>-0.04712799515838373</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.09164357167481152</v>
+        <v>-0.07694212751714757</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1286888645119864</v>
+        <v>-0.1247749701871331</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.04439273654263642</v>
+        <v>-0.009818600477822348</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.05465964051388705</v>
+        <v>-0.04167676420771438</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09986432835130254</v>
+        <v>-0.09153219929935608</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2984002744598795</v>
+        <v>0.3500958967574377</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09094502518544956</v>
+        <v>0.105235618355831</v>
       </c>
     </row>
   </sheetData>
@@ -2562,17 +2562,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.08294268406423599</v>
+        <v>0.0734747188665239</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3050,21 +3050,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1510791645114397</v>
+        <v>-0.111367588786639</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.06653623536996367</v>
+        <v>0.04990265285822426</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1109174779267584</v>
+        <v>-0.09053071860071138</v>
       </c>
     </row>
     <row r="19">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.02851324435480462</v>
+        <v>0.04892709589379751</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.09868069401608126</v>
+        <v>-0.08508292171661791</v>
       </c>
     </row>
     <row r="20">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.02751283909401359</v>
+        <v>0.04884493355942854</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09164357167481152</v>
+        <v>-0.07694212751714757</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.02240415675464402</v>
+        <v>0.03763437242173873</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08042746062714434</v>
+        <v>-0.07129798412751209</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E22" s="11" t="n">
-        <v>0.01618454884769616</v>
+        <v>0.01642671437126997</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.06515258846906058</v>
+        <v>-0.06578081334903763</v>
       </c>
     </row>
     <row r="23">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.01368917127161673</v>
+        <v>-0.001543883868298179</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.06244346998537897</v>
+        <v>-0.06514212721050205</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.002270505885209051</v>
+        <v>-0.003035985109609785</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06200759139326706</v>
+        <v>-0.06423986848688445</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.001345623975906873</v>
+        <v>-0.01441199052277919</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06130484310985351</v>
+        <v>-0.06327052748700368</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.009197993926031933</v>
+        <v>-0.02013205566229237</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.0555555882604345</v>
+        <v>-0.06207784804449834</v>
       </c>
     </row>
     <row r="27"/>
@@ -3539,21 +3539,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2383549665652738</v>
+        <v>0.2565552480916218</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1718370376133064</v>
+        <v>-0.14270296875447</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2200513424889987</v>
+        <v>0.2513065620336454</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1286888645119864</v>
+        <v>-0.1247749701871331</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2071883818599847</v>
+        <v>0.1821073555934194</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.106983166253878</v>
+        <v>-0.1046324831434375</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1888534464950116</v>
+        <v>0.1789295181658375</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1014720143660832</v>
+        <v>-0.09803922983794033</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1733598678522108</v>
+        <v>0.1721689871613161</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08513259539427698</v>
+        <v>-0.07830012753536886</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1488648273381925</v>
+        <v>0.1679567187342685</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08473665457228874</v>
+        <v>-0.07218686832997456</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1117511422849802</v>
+        <v>0.1198156229719771</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.07538905415336894</v>
+        <v>-0.06345370309749487</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.08493587588260731</v>
+        <v>0.07474815400268109</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.06816797716103873</v>
+        <v>-0.0626902414798518</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.05893787731980193</v>
+        <v>0.07253885466305676</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.06794055416643974</v>
+        <v>-0.06105350828727529</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.05482872959166585</v>
+        <v>0.0685854773096175</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.0597926604010629</v>
+        <v>-0.05053682930585712</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4704232687116929</v>
+        <v>0.5454874824810154</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1251482468570465</v>
+        <v>-0.08455000096319765</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.423094701605035</v>
+        <v>0.5055043672338237</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.04803898569706577</v>
+        <v>-0.009818600477822348</v>
       </c>
     </row>
     <row r="47">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4219889293367276</v>
+        <v>0.5036925043736638</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.04439273654263642</v>
+        <v>0.002550419855511965</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3117948947209375</v>
+        <v>0.3788716336223201</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.008980125631481761</v>
+        <v>0.01193415331900005</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2592952320643853</v>
+        <v>0.2882090360442082</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.002182262217172215</v>
+        <v>0.0194249869526415</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2516062334606712</v>
+        <v>0.2775700753477526</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.005147236687525814</v>
+        <v>0.03855736810417332</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2260375767649816</v>
+        <v>0.2598457371103255</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.007721976194258406</v>
+        <v>0.04731087550248225</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2234082853451778</v>
+        <v>0.2496568360714926</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.02075517679904726</v>
+        <v>0.05403316899665445</v>
       </c>
     </row>
     <row r="53">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.209195092547108</v>
+        <v>0.2325659766071275</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.02835750224671996</v>
+        <v>0.05635752248395964</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1923728777699036</v>
+        <v>0.2085945981682438</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.02857582908279888</v>
+        <v>0.06204347580916525</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8417451983777373</v>
+        <v>0.8934668677374331</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1885855736476543</v>
+        <v>-0.1789787107930872</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.6895012627455426</v>
+        <v>0.7603483322944291</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4628,21 +4628,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1298216665550374</v>
+        <v>-0.1209015369348776</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5250890768951346</v>
+        <v>0.5066335144894758</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4673,21 +4673,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1251906018402621</v>
+        <v>-0.1179951981937968</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4607633828642956</v>
+        <v>0.4953026696224148</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09986432835130254</v>
+        <v>-0.09153219929935608</v>
       </c>
     </row>
     <row r="63">
@@ -4741,21 +4741,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4469651888399189</v>
+        <v>0.4559063328177873</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.08858905415828289</v>
+        <v>-0.08212174318314136</v>
       </c>
     </row>
     <row r="64">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.437335107589871</v>
+        <v>0.4328915075796376</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.06869068228197528</v>
+        <v>-0.05640638026789657</v>
       </c>
     </row>
     <row r="65">
@@ -4831,21 +4831,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.397800097976367</v>
+        <v>0.3704061445399354</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4853,21 +4853,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.02225729533072018</v>
+        <v>-0.03093135201514952</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3258495666664554</v>
+        <v>0.3498048435110988</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4898,21 +4898,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.01979028039589981</v>
+        <v>-0.00776960305575447</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3010453209938473</v>
+        <v>0.3216965083565604</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.00074413970903775</v>
+        <v>0.01625866472090487</v>
       </c>
     </row>
     <row r="68">
@@ -4966,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1749019988482992</v>
+        <v>0.1755531097538177</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.006707605557814134</v>
+        <v>0.01975919703127405</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.615401738333522</v>
+        <v>2.905679076938151</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5094,21 +5094,21 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.0290226228935293</v>
+        <v>0.02369577500046582</v>
       </c>
     </row>
     <row r="74">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.330154795132791</v>
+        <v>2.451744974992017</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5139,21 +5139,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.04278627245173139</v>
+        <v>0.06149389168274144</v>
       </c>
     </row>
     <row r="75">
@@ -5162,21 +5162,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.248006973123559</v>
+        <v>2.363165775883104</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5184,21 +5184,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1299239861608481</v>
+        <v>0.159912430933103</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.58056578490832</v>
+        <v>1.743518945110235</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1480036076909153</v>
+        <v>0.1905103988209815</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.122143959257931</v>
+        <v>1.177581471690906</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1562201959575169</v>
+        <v>0.1961695308864919</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.051997546139172</v>
+        <v>1.131087935548486</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1959867475429946</v>
+        <v>0.2367855892312036</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9576801584961006</v>
+        <v>1.00049501274334</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.204507873077874</v>
+        <v>0.2535959797534413</v>
       </c>
     </row>
     <row r="80">
@@ -5387,21 +5387,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8582002212582749</v>
+        <v>0.9241593040990503</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2525295457040069</v>
+        <v>0.2981376982172252</v>
       </c>
     </row>
     <row r="81">
@@ -5432,21 +5432,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8432788005241871</v>
+        <v>0.9114752959922017</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2559053233200359</v>
+        <v>0.321356097974852</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7404585867274993</v>
+        <v>0.7679144185249582</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2984002744598795</v>
+        <v>0.3500958967574377</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.8934668677374331</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.451744974992017</v>
+        <v>2.451745376532615</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5112845194533644</v>
+        <v>0.5112845780558075</v>
       </c>
     </row>
     <row r="3">
@@ -686,7 +686,7 @@
         <v>0.6206910974434574</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7603483322944291</v>
+        <v>0.7603481463113813</v>
       </c>
       <c r="O3" s="6" t="n">
         <v>2.905679076938151</v>
@@ -745,10 +745,10 @@
         <v>0.5066335144894758</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.593056894371246</v>
+        <v>0.5930570013087801</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1679128285251008</v>
+        <v>0.1679128546580273</v>
       </c>
     </row>
     <row r="5">
@@ -854,7 +854,7 @@
         <v>0.1743964683453709</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3498048435110988</v>
+        <v>0.3498047266211666</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>0.5120325123597118</v>
@@ -913,10 +913,10 @@
         <v>0.4559063328177873</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.00049501274334</v>
+        <v>1.000495143627636</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2600249874828229</v>
+        <v>0.2600250149622685</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.3704061445399354</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.363165775883104</v>
+        <v>2.36316610256089</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4982447284279621</v>
+        <v>0.4982447769381346</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.01625866472090487</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4548303833133658</v>
+        <v>0.4548302181348547</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1331066477557512</v>
+        <v>0.1331066048722009</v>
       </c>
     </row>
     <row r="10">
@@ -1137,10 +1137,10 @@
         <v>0.4328915075796376</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7407405927535182</v>
+        <v>0.740740427148799</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2029419926239515</v>
+        <v>0.2029419544768016</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.3216965083565604</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.9241593040990503</v>
+        <v>0.9241588467321356</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2437898498627746</v>
+        <v>0.2437897513143903</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.01975919703127405</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.321356097974852</v>
+        <v>0.3213562451008338</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09733683520357794</v>
+        <v>0.09733687593111884</v>
       </c>
     </row>
     <row r="14">
@@ -1302,13 +1302,13 @@
         <v>0.1968000150415552</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1755531097538177</v>
+        <v>0.1755531861985156</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7679144185249582</v>
+        <v>0.7679142456288315</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2091692083005452</v>
+        <v>0.2091691688829738</v>
       </c>
     </row>
     <row r="15">
@@ -1355,16 +1355,16 @@
         <v>0.1955182838855885</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.07430870763748954</v>
+        <v>0.07430864293009209</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1083513369264086</v>
+        <v>0.1083514057996771</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.9114752959922017</v>
+        <v>0.9114750911435545</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2410508123446489</v>
+        <v>0.2410507680110758</v>
       </c>
     </row>
     <row r="16">
@@ -1417,10 +1417,10 @@
         <v>0.1594403595499807</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.177581471690906</v>
+        <v>1.177581226917401</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2961585755153788</v>
+        <v>0.2961585269499876</v>
       </c>
     </row>
     <row r="17">
@@ -1529,10 +1529,10 @@
         <v>0.06747460265979766</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.494371101195469</v>
+        <v>0.494371010464064</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1432805631288463</v>
+        <v>0.1432805399905834</v>
       </c>
     </row>
     <row r="19">
@@ -1585,10 +1585,10 @@
         <v>0.1203955214084829</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.159912430933103</v>
+        <v>0.1599125427231747</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05069113407531223</v>
+        <v>0.05069116782982386</v>
       </c>
     </row>
     <row r="20">
@@ -1697,10 +1697,10 @@
         <v>0.09732966622606787</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3676423475337309</v>
+        <v>0.3676422596403681</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1100030699624885</v>
+        <v>0.1100030461838779</v>
       </c>
     </row>
     <row r="22">
@@ -1803,16 +1803,16 @@
         <v>0.05635752248395964</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1053516472633347</v>
+        <v>0.1053515521545652</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>0.09839597386018806</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2367855892312036</v>
+        <v>0.2367854701595278</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.0734079449228846</v>
+        <v>0.07340791047539197</v>
       </c>
     </row>
     <row r="24">
@@ -1915,10 +1915,10 @@
         <v>0.04016389498082029</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.06149389168274144</v>
+        <v>0.0614939736484954</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02009158849586967</v>
+        <v>0.02009161475212817</v>
       </c>
     </row>
     <row r="26">
@@ -1965,7 +1965,7 @@
         <v>0.1196448018536018</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.07546028206646516</v>
+        <v>-0.07546035665221884</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>-0.1179951981937968</v>
@@ -2139,10 +2139,10 @@
         <v>0.06645507975005227</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.131087935548486</v>
+        <v>1.131087770363672</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2868673734811156</v>
+        <v>0.2868673402319084</v>
       </c>
     </row>
     <row r="30">
@@ -2189,7 +2189,7 @@
         <v>0.03855736810417332</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.09152169361344065</v>
+        <v>-0.09152175324212886</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>-0.08212174318314136</v>
@@ -2248,7 +2248,7 @@
         <v>-0.07376683646337234</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.05640638026789657</v>
+        <v>-0.05640627068608706</v>
       </c>
       <c r="O31" s="6" t="n">
         <v>0.4364472918662554</v>
@@ -2301,16 +2301,16 @@
         <v>0.0194249869526415</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.1066038112687155</v>
+        <v>-0.1066037124139498</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>-0.1209015369348776</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2535959797534413</v>
+        <v>0.2535960770717589</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07824932985197819</v>
+        <v>0.07824935775395225</v>
       </c>
     </row>
     <row r="33">
@@ -2354,19 +2354,19 @@
         <v>-0.1046324831434375</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.08455000096319765</v>
+        <v>-0.08455010593452339</v>
       </c>
       <c r="M33" s="6" t="n">
         <v>-0.04484725575283166</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.03093135201514952</v>
+        <v>-0.03093146964309423</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4317719550909433</v>
+        <v>0.4317718267045072</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1270883232372704</v>
+        <v>0.1270882895487451</v>
       </c>
     </row>
     <row r="34">
@@ -2419,10 +2419,10 @@
         <v>-0.09153219929935608</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.3500958967574377</v>
+        <v>0.350095772380852</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.105235618355831</v>
+        <v>0.1052355844161585</v>
       </c>
     </row>
   </sheetData>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.08455000096319765</v>
+        <v>-0.08455010593452339</v>
       </c>
     </row>
     <row r="46">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7603483322944291</v>
+        <v>0.7603481463113813</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.05640638026789657</v>
+        <v>-0.05640627068608706</v>
       </c>
     </row>
     <row r="65">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.03093135201514952</v>
+        <v>-0.03093146964309423</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3498048435110988</v>
+        <v>0.3498047266211666</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1755531097538177</v>
+        <v>0.1755531861985156</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.451744974992017</v>
+        <v>2.451745376532615</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.06149389168274144</v>
+        <v>0.0614939736484954</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.363165775883104</v>
+        <v>2.36316610256089</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.159912430933103</v>
+        <v>0.1599125427231747</v>
       </c>
     </row>
     <row r="76">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.177581471690906</v>
+        <v>1.177581226917401</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.131087935548486</v>
+        <v>1.131087770363672</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2367855892312036</v>
+        <v>0.2367854701595278</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.00049501274334</v>
+        <v>1.000495143627636</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2535959797534413</v>
+        <v>0.2535960770717589</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9241593040990503</v>
+        <v>0.9241588467321356</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.9114752959922017</v>
+        <v>0.9114750911435545</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.321356097974852</v>
+        <v>0.3213562451008338</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7679144185249582</v>
+        <v>0.7679142456288315</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3500958967574377</v>
+        <v>0.350095772380852</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>226.38</v>
+        <v>224.76</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.02587577269790708</v>
+        <v>-0.007156154876907905</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.06092417144305329</v>
+        <v>0.05086959685635284</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.0315319327314505</v>
+        <v>0.02061571728710909</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.04990265285822426</v>
+        <v>0.0423893868686942</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.06105350828727529</v>
+        <v>-0.02244260483299854</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5454874824810154</v>
+        <v>0.4909636487125268</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.8117475317815148</v>
+        <v>0.7822712190442611</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8934668677374331</v>
+        <v>0.8633082549832547</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.451745376532615</v>
+        <v>2.405645004293508</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5112845780558075</v>
+        <v>0.5045263284648158</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>63.56</v>
+        <v>63.99</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.03517914973506486</v>
+        <v>0.006765265825756872</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.1077030357291133</v>
+        <v>0.106327826930404</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.03602286803808408</v>
+        <v>0.0391360795023028</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.04884493355942854</v>
+        <v>0.05594064834495649</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.14270296875447</v>
+        <v>-0.07994250365673405</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.5055043672338237</v>
+        <v>0.4854336322337052</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6206910974434574</v>
+        <v>0.5911982557579765</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7603481463113813</v>
+        <v>0.7607686856706917</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.905679076938151</v>
+        <v>2.88972643374662</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5748245813786581</v>
+        <v>0.5726775457257061</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>90.53</v>
+        <v>58.04</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.02340882675710232</v>
+        <v>0.005718278223703521</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.02676841489603654</v>
+        <v>0.06593204962875543</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.02885649438083071</v>
+        <v>0.05049775412719182</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.02013205566229237</v>
+        <v>0.0796131459751146</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1789295181658375</v>
+        <v>0.05508094321842716</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.1009245914379124</v>
+        <v>0.4890365033625279</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5068580373754752</v>
+        <v>0.4275023284532531</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5066335144894758</v>
+        <v>0.5003346329140537</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.5930570013087801</v>
+        <v>1.750402351180679</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1679128546580273</v>
+        <v>0.4010879895006731</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>57.71</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.03016777245446756</v>
+        <v>-0.003866104924781455</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.06026086277616605</v>
+        <v>-0.02444831324688668</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.04038214917027072</v>
+        <v>-0.04662222437308938</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.0734747188665239</v>
+        <v>-0.02392032794753185</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.007506988727995489</v>
+        <v>0.1530494995630243</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5036925043736638</v>
+        <v>0.0837864440425351</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4402642762558553</v>
+        <v>0.4788003025141327</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4953026696224148</v>
+        <v>0.4805276432656855</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.743518945110235</v>
+        <v>0.5845382463546294</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3999181831625858</v>
+        <v>0.1658273568968209</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29.73</v>
+        <v>24.79</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.007455076640059621</v>
+        <v>0.01432080089286392</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.01571571839011177</v>
+        <v>0.04466925384487896</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.001684610395769726</v>
+        <v>0.06807418756477679</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-0.02268246325861545</v>
+        <v>0.06394857198522264</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1821073555934194</v>
+        <v>0.2958704653980722</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2882090360442082</v>
+        <v>0.3766430060728798</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1743964683453709</v>
+        <v>0.05974115346763531</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3498047266211666</v>
+        <v>0.04317643294996332</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.5120325123597118</v>
+        <v>0.4762547103032859</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.147766936311706</v>
+        <v>0.1386417367710424</v>
       </c>
     </row>
     <row r="7">
@@ -872,12 +872,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.16</v>
+        <v>29.54</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.007253854194763543</v>
+        <v>-0.006390804898569247</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.01051915416237914</v>
+        <v>0.008535336025458085</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.04705884039562402</v>
+        <v>0.01233723805985387</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.06207784804449834</v>
+        <v>-0.02892830895987986</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1198156229719771</v>
+        <v>0.1489693491808712</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2496568360714926</v>
+        <v>0.2716585138031582</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2031533964433394</v>
+        <v>0.1555437039283121</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4559063328177873</v>
+        <v>0.3351506074549102</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.000495143627636</v>
+        <v>0.5085404262883497</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2600250149622685</v>
+        <v>0.1468826540679797</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>66.04000000000001</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.01403407575835758</v>
+        <v>-0.005905502487004721</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.006553883572254282</v>
+        <v>0.01531082288431218</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.03731774949761102</v>
+        <v>-0.04744626712047473</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.07129798412751209</v>
+        <v>-0.07678243619193326</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1721689871613161</v>
+        <v>0.2337906907620375</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2085945981682438</v>
+        <v>0.1614293843539931</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1415297219247289</v>
+        <v>0.09436575447232221</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3704061445399354</v>
+        <v>0.3268225837837604</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.36316610256089</v>
+        <v>2.347996314233302</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4982447769381346</v>
+        <v>0.495988736700117</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>24.44</v>
+        <v>28.86</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.02991997494806431</v>
+        <v>-0.01028803973355208</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.01368726318340996</v>
+        <v>0.0003466283795356961</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.03515459137015653</v>
+        <v>-0.02926333485638943</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.04892709589379751</v>
+        <v>-0.07172722841079515</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2565552480916218</v>
+        <v>0.07047483643918939</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.3788716336223201</v>
+        <v>0.2312314721696944</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.04887145790164471</v>
+        <v>0.1708440263821842</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.01625866472090487</v>
+        <v>0.4235753710800747</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4548302181348547</v>
+        <v>1.001379846724848</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1331066048722009</v>
+        <v>0.2602107329410939</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>55.07</v>
+        <v>55.55</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01045870999677456</v>
+        <v>0.008716171143931195</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.05680289867209587</v>
+        <v>0.03368063829664902</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.04955209479002654</v>
+        <v>0.08094959908191912</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01642671437126997</v>
+        <v>0.02528606356899354</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.2513065620336454</v>
+        <v>0.262499982660467</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2325659766071275</v>
+        <v>0.2351183960906673</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.05657341265731652</v>
+        <v>0.05415017230626895</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1378323847239165</v>
+        <v>0.1517002410866624</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2981376982172252</v>
+        <v>0.3147001746511604</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.09087147941184592</v>
+        <v>0.09549123435717877</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>34.9</v>
+        <v>15.31</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01482995479156601</v>
+        <v>-0.008419634993498737</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01306243114582317</v>
+        <v>0.0145792090658845</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.01105127173507214</v>
+        <v>0.01998668795205027</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.04462078587152207</v>
+        <v>0.02889786974923947</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.0685854773096175</v>
+        <v>-0.00519817556344393</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1908857304600364</v>
+        <v>0.2373123967168911</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.157491410691178</v>
+        <v>0.3011772900671479</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4328915075796376</v>
+        <v>0.296018040289366</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.740740427148799</v>
+        <v>0.9116703386889844</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2029419544768016</v>
+        <v>0.2410930222658272</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>15.44</v>
+        <v>34.47</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01914191215545125</v>
+        <v>-0.01232092511104699</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.02387265639911051</v>
+        <v>0.008484520565771536</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03070761363176255</v>
+        <v>0.007305668938689225</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.03763437242173873</v>
+        <v>-0.05639194162145</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.02092586352576231</v>
+        <v>0.03606855264287878</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2598457371103255</v>
+        <v>0.168047470061049</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.3302304780617729</v>
+        <v>0.1339558389771123</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.3216965083565604</v>
+        <v>0.4141355272735183</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.9241588467321356</v>
+        <v>0.7244827064677377</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2437897513143903</v>
+        <v>0.1991852586379659</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>45.27</v>
+        <v>44.81</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.01661804847861004</v>
+        <v>-0.01016123436759908</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.006365252563345081</v>
+        <v>-0.001114561666969993</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.0008843890323277925</v>
+        <v>0.009689055764460441</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.001543883868298179</v>
+        <v>-0.0116894304700752</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1679567187342685</v>
+        <v>0.1611816842733544</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2775700753477526</v>
+        <v>0.2446958818248786</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.03682061315500684</v>
+        <v>0.01922897047459537</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.01975919703127405</v>
+        <v>0.02333320410999895</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3213562451008338</v>
+        <v>0.3090722334450464</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09733687593111884</v>
+        <v>0.09392581311121706</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>68.95999999999999</v>
+        <v>67.94</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.00981107277731752</v>
+        <v>-0.01479113481160232</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.02695080553247886</v>
+        <v>-0.02356998198462934</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.01626247381544943</v>
+        <v>-0.02385051823430817</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.003035985109609785</v>
+        <v>-0.01778221425616988</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.05178209120981769</v>
+        <v>0.02234278795148392</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.07396810553937971</v>
+        <v>0.03852124435973026</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1968000150415552</v>
+        <v>0.1640776218025399</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1755531861985156</v>
+        <v>0.1447532374675038</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7679142456288315</v>
+        <v>0.7479589634493378</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2091691688829738</v>
+        <v>0.2046024556951467</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>17.01</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.004725335042173429</v>
+        <v>0.005772149652128133</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02128877731593892</v>
+        <v>-0.003022765708724506</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.04705883107206565</v>
+        <v>0.002714440870161816</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.03461978327454507</v>
+        <v>-0.0351060562375104</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.05981314875109667</v>
+        <v>0.00891869362417852</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1955182838855885</v>
+        <v>0.06475322168252751</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.07430864293009209</v>
+        <v>0.120536380059459</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1083514057996771</v>
+        <v>0.1455759348116181</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.9114750911435545</v>
+        <v>0.1728144030863978</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2410507680110758</v>
+        <v>0.05457247131717313</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>36.95</v>
+        <v>16.52</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.001083741958621154</v>
+        <v>-0.02880657051880442</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02635046060332524</v>
+        <v>-0.02594331665452831</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.04249804050696426</v>
+        <v>-0.05383726666657929</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.02788733505397833</v>
+        <v>-0.06242907656510555</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.01987306734198979</v>
+        <v>0.01661541278545675</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1774987863323056</v>
+        <v>0.1467843651814005</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.09114625870187876</v>
+        <v>0.03359336742709451</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1594403595499807</v>
+        <v>0.08302338408435772</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.177581226917401</v>
+        <v>0.8670913656457084</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2961585269499876</v>
+        <v>0.2313698721234987</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>111.07</v>
+        <v>109.36</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.001258874119242637</v>
+        <v>-0.01539568820717607</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.04348951887969588</v>
+        <v>-0.03075424235035384</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.04824333676645198</v>
+        <v>-0.05406106709630432</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.03425791120966404</v>
+        <v>-0.04912617529722696</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.01007127704236244</v>
+        <v>-0.04296837469989345</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2029675889973441</v>
+        <v>0.1874050208706606</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.08626832459844236</v>
+        <v>0.06912933294140466</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1356541142104832</v>
+        <v>0.09277462243941126</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.02369577500046582</v>
+        <v>0.007461834759782793</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.007837012456045622</v>
+        <v>0.002481117219399476</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>93.89</v>
+        <v>35.92</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.009390160383108581</v>
+        <v>-0.02787557706973653</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.03176241922535017</v>
+        <v>-0.02708559180918746</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.03939020419754091</v>
+        <v>-0.05374080518252156</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.03455013481081293</v>
+        <v>-0.05498553656614802</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.07474815400268109</v>
+        <v>-0.03466812543044773</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1220788120782066</v>
+        <v>0.1284986595784741</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.05896702107694041</v>
+        <v>0.05675082026527711</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.06747460265979766</v>
+        <v>0.1378517574223792</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.494371010464064</v>
+        <v>1.136790789949186</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1432805399905834</v>
+        <v>0.2880142494592159</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>91.81999999999999</v>
+        <v>113.52</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.00271532530497065</v>
+        <v>-0.003336302701683058</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.02006400549251286</v>
+        <v>-0.00202200753348214</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.02640226835148118</v>
+        <v>-0.01612065049946487</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.04064360491964025</v>
+        <v>-0.06889765134542547</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.01337918100985358</v>
+        <v>-0.04709141895149838</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.06204347580916525</v>
+        <v>0.08319137610570126</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1066460105537068</v>
+        <v>0.09154131196001725</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1203955214084829</v>
+        <v>0.1603587488149234</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1599125427231747</v>
+        <v>0.4422787264345127</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05069116782982386</v>
+        <v>0.1298385773108111</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>113.9</v>
+        <v>51.29</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.0005264791073689157</v>
+        <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.02357479609110769</v>
+        <v>0.02457050556320173</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.04197155260650121</v>
+        <v>0.002737035884106565</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.06578081334903763</v>
+        <v>-0.01441199052277919</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.04534402936399329</v>
+        <v>-0.0295174570223995</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1058946400436933</v>
+        <v>0.0990001781893024</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.09859372271517186</v>
+        <v>0.0772474780716601</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1675340149806841</v>
+        <v>0.1207445375506302</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4389402015427948</v>
+        <v>0.7716843918129195</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1289661365197052</v>
+        <v>0.2100280921039601</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>40.59</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.008948561134672905</v>
+        <v>0.01020304028368479</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.003192560516160792</v>
+        <v>0.005790325890772774</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.02216329092136016</v>
+        <v>-0.02883761549796116</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.04681355961051703</v>
+        <v>-0.05371303894403867</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.01227615581352515</v>
+        <v>-0.01256601724363438</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.07489083575990696</v>
+        <v>0.05066066241602174</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1101567459934489</v>
+        <v>0.09882103209647819</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.09732966622606787</v>
+        <v>0.1132837964395512</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3676422596403681</v>
+        <v>0.2544524935568542</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1100030461838779</v>
+        <v>0.0784948436101176</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>51.29</v>
+        <v>92.02</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.009844457392934158</v>
+        <v>-0.01991695344273481</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01927665394646061</v>
+        <v>-0.0381519974468203</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.002334155460823384</v>
+        <v>-0.03034778542155381</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.01441199052277919</v>
+        <v>-0.05377895482708062</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.05053682930585712</v>
+        <v>0.0296519392977832</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1215206488477221</v>
+        <v>0.0897618050086102</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.08441127627982459</v>
+        <v>0.03010957406803705</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1190621407571228</v>
+        <v>0.04000376294190322</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7651447297226068</v>
+        <v>0.4617173211741348</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2085374332154863</v>
+        <v>0.1348918166015203</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
       <c r="F23" s="5" t="n">
-        <v>98.01000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.003558341520427555</v>
+        <v>0.02212051635755174</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.009599807569028673</v>
+        <v>0.007518753861753602</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.04853897579176347</v>
+        <v>-0.01325480899757314</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.06327052748700368</v>
+        <v>-0.04354037119100373</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.04371154084219908</v>
+        <v>-0.04490378663089967</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.05635752248395964</v>
+        <v>0.01963100477163393</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1053515521545652</v>
+        <v>0.1376123926068931</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.09839597386018806</v>
+        <v>0.07559302066113638</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2367854701595278</v>
+        <v>0.08720720057097475</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.07340791047539197</v>
+        <v>0.02826275808739331</v>
       </c>
     </row>
     <row r="24">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>67.45</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.00746826023586733</v>
+        <v>0.003409983207413481</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.005665681454405824</v>
+        <v>0.0192770896066623</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03366770774742023</v>
+        <v>-0.009222621518578999</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.06514212721050205</v>
+        <v>-0.06195427756297156</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.07830012753536886</v>
+        <v>-0.05908522149268203</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.06354460573400389</v>
+        <v>0.04784028707975718</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1017640575517047</v>
+        <v>0.09003060297713494</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1874,51 +1874,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.11</v>
+        <v>39.92</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.004555840491200946</v>
+        <v>-0.01650657750982687</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.01650414615813767</v>
+        <v>-0.01212575303927343</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.05751259522002794</v>
+        <v>-0.02752743213439701</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.06423986848688445</v>
+        <v>-0.06254740547012205</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.07218686832997456</v>
+        <v>-0.05296147615391944</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.01193415331900005</v>
+        <v>0.0492893214474972</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1185206249862696</v>
+        <v>0.08719185174496014</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.04016389498082029</v>
+        <v>0.07250990234171617</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.0614939736484954</v>
+        <v>0.3561638279092376</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02009161475212817</v>
+        <v>0.1068889506230382</v>
       </c>
     </row>
     <row r="26">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>174.87</v>
+        <v>16.71</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01274104923595143</v>
+        <v>-0.007130174674829903</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01236870253927069</v>
+        <v>0.009057948270998706</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.0555736030536037</v>
+        <v>-0.008896887333847969</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05593046941268864</v>
+        <v>-0.05432942771229665</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.04300364605507623</v>
+        <v>-0.02622382091730135</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1196448018536018</v>
+        <v>0.02899522867488513</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.07546035665221884</v>
+        <v>-0.006561724731417917</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.1179951981937968</v>
+        <v>0.001361994189922111</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.574267806494795</v>
+        <v>0.4397702113561186</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1633030625456946</v>
+        <v>0.1291831649638715</v>
       </c>
     </row>
     <row r="27">
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>16.83</v>
+        <v>169.65</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.008388219602674996</v>
+        <v>-0.02985075408279725</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.01232400120530097</v>
+        <v>-0.005743485660691383</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.03497709814631744</v>
+        <v>-0.05218174931580966</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.04753820876972348</v>
+        <v>-0.08411165680731225</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.03442342920048935</v>
+        <v>0.02724795741028352</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.05403316899665445</v>
+        <v>0.07867274392468238</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>7.797731381531392e-05</v>
+        <v>-0.1185655066825563</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.00776960305575447</v>
+        <v>-0.1395666855084909</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.4468325025796569</v>
+        <v>0.5350993590533515</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1310264259698866</v>
+        <v>0.1535741001725419</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.56</v>
+        <v>26</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01284398040202239</v>
+        <v>-0.008390515603196147</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.03214501021562965</v>
+        <v>-0.003449603375297983</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.06598985372260024</v>
+        <v>-0.02475618346547648</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.08508292171661791</v>
+        <v>-0.09816163479691964</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.07253885466305676</v>
+        <v>-0.09533750149405662</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.10252989089509</v>
+        <v>-0.0137574856353867</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1555329448995106</v>
+        <v>-0.01573525287571775</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1789787107930872</v>
+        <v>0.04544256736961616</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1905103988209815</v>
+        <v>1.130399006901708</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05984998435369349</v>
+        <v>0.286728687611653</v>
       </c>
     </row>
     <row r="29">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>26.22</v>
+        <v>52.6</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.01001541749041701</v>
+        <v>-0.003787893292223177</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.0022831572193035</v>
+        <v>-0.00510687465894466</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.04585153747711079</v>
+        <v>-0.02066655425939967</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.09053071860071138</v>
+        <v>-0.05819158619146492</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.09803922983794033</v>
+        <v>-0.006610052573659875</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.002550419855511965</v>
+        <v>-0.0002661602058228185</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.01785092724642068</v>
+        <v>-0.09277684839630929</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.06645507975005227</v>
+        <v>-0.08028056938295947</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.131087770363672</v>
+        <v>0.1949007949179877</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2868673402319084</v>
+        <v>0.06115123377641241</v>
       </c>
     </row>
     <row r="30">
@@ -2154,51 +2154,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>52.8</v>
+        <v>16.21</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.007249162178345037</v>
+        <v>-0.02113528941770459</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02816128368174653</v>
+        <v>-0.02172604809787726</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.0457256914922809</v>
+        <v>-0.03741098945408372</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.0546105518422495</v>
+        <v>-0.104419958959338</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.02330747510585507</v>
+        <v>0.06295075963755115</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.03855736810417332</v>
+        <v>0.05533850565067566</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.09152175324212886</v>
+        <v>-0.1804854134602302</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.08212174318314136</v>
+        <v>-0.1878757601205108</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1961695308864919</v>
+        <v>0.169552632468015</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.06152667485090091</v>
+        <v>0.05359392283046582</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>61.99</v>
+        <v>61.37</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.01290851153070149</v>
+        <v>-0.01000165719946089</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.009744357995575159</v>
+        <v>0.008877150823204394</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02973857770124633</v>
+        <v>-0.01745117144676456</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.05329874006637858</v>
+        <v>-0.06276732153853237</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.06345370309749487</v>
+        <v>-0.04333597081634755</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.04731087550248225</v>
+        <v>0.01115484937430478</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.07376683646337234</v>
+        <v>-0.08588841706612249</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.05640627068608706</v>
+        <v>-0.05346574719936592</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4364472918662554</v>
+        <v>0.4339866316864631</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1283137958928831</v>
+        <v>0.1276691536811871</v>
       </c>
     </row>
     <row r="32">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>15.4</v>
+        <v>111.43</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.005878458291761923</v>
+        <v>-0.003398598172930201</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02716363280152889</v>
+        <v>0.002158448228256837</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.05579398388775669</v>
+        <v>-0.02664223412230604</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.111367588786639</v>
+        <v>-0.08007923031607667</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.0626902414798518</v>
+        <v>-0.1114743875982951</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.0194249869526415</v>
+        <v>-0.04375871718405566</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.1066037124139498</v>
+        <v>-0.05067973717886387</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1209015369348776</v>
+        <v>-0.08679479033552739</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2535960770717589</v>
+        <v>0.3475362963345685</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07824935775395225</v>
+        <v>0.1045367170838813</v>
       </c>
     </row>
     <row r="33">
@@ -2322,51 +2322,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>121.82</v>
+        <v>14.93</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.003517384909413335</v>
+        <v>-0.03051943668809953</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.02058206797816442</v>
+        <v>-0.03428200075442667</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.05072860627556786</v>
+        <v>-0.04600634702265305</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.04169291171526757</v>
+        <v>-0.1384881493996585</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1046324831434375</v>
+        <v>-0.08348683449460303</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.08455010593452339</v>
+        <v>-0.02814898027355806</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.04484725575283166</v>
+        <v>-0.1274188603947317</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.03093146964309423</v>
+        <v>-0.1485569417134568</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4317718267045072</v>
+        <v>0.2175589293765205</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1270882895487451</v>
+        <v>0.0678165885810269</v>
       </c>
     </row>
     <row r="34">
@@ -2378,51 +2378,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>111.81</v>
+        <v>119.42</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.004491959491210951</v>
+        <v>-0.01970121106461364</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.01035586620265438</v>
+        <v>-0.0280784935339532</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04712799515838373</v>
+        <v>-0.06652077007683843</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.07694212751714757</v>
+        <v>-0.06057272192628038</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1247749701871331</v>
+        <v>-0.1311786318790679</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.009818600477822348</v>
+        <v>-0.1155339823380489</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.04167676420771438</v>
+        <v>-0.0725618796980364</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09153219929935608</v>
+        <v>-0.06216888190463032</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.350095772380852</v>
+        <v>0.4056872045575803</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1052355844161585</v>
+        <v>0.1202017080792708</v>
       </c>
     </row>
   </sheetData>
@@ -2539,17 +2539,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.0734747188665239</v>
+        <v>0.0796131459751146</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.111367588786639</v>
+        <v>-0.1384881493996585</v>
       </c>
     </row>
     <row r="18">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.04990265285822426</v>
+        <v>0.06394857198522264</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.09053071860071138</v>
+        <v>-0.104419958959338</v>
       </c>
     </row>
     <row r="19">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.04892709589379751</v>
+        <v>0.05594064834495649</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.08508292171661791</v>
+        <v>-0.09816163479691964</v>
       </c>
     </row>
     <row r="20">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04884493355942854</v>
+        <v>0.0423893868686942</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.07694212751714757</v>
+        <v>-0.08411165680731225</v>
       </c>
     </row>
     <row r="21">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.03763437242173873</v>
+        <v>0.02889786974923947</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.07129798412751209</v>
+        <v>-0.08007923031607667</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01642671437126997</v>
+        <v>0.02528606356899354</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.06578081334903763</v>
+        <v>-0.07678243619193326</v>
       </c>
     </row>
     <row r="23">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.001543883868298179</v>
+        <v>-0.0116894304700752</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.06514212721050205</v>
+        <v>-0.07172722841079515</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.003035985109609785</v>
+        <v>-0.01441199052277919</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06423986848688445</v>
+        <v>-0.06889765134542547</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.01441199052277919</v>
+        <v>-0.01778221425616988</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06327052748700368</v>
+        <v>-0.06276732153853237</v>
       </c>
     </row>
     <row r="26">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.02013205566229237</v>
+        <v>-0.02392032794753185</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06207784804449834</v>
+        <v>-0.06254740547012205</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2565552480916218</v>
+        <v>0.2958704653980722</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3561,21 +3561,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.14270296875447</v>
+        <v>-0.1311786318790679</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2513065620336454</v>
+        <v>0.262499982660467</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1247749701871331</v>
+        <v>-0.1114743875982951</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1821073555934194</v>
+        <v>0.2337906907620375</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1046324831434375</v>
+        <v>-0.09533750149405662</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1789295181658375</v>
+        <v>0.1611816842733544</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.09803922983794033</v>
+        <v>-0.08348683449460303</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1721689871613161</v>
+        <v>0.1530494995630243</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.07830012753536886</v>
+        <v>-0.07994250365673405</v>
       </c>
     </row>
     <row r="36">
@@ -3764,21 +3764,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1679567187342685</v>
+        <v>0.1489693491808712</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.07218686832997456</v>
+        <v>-0.05908522149268203</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1198156229719771</v>
+        <v>0.07047483643918939</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.06345370309749487</v>
+        <v>-0.05296147615391944</v>
       </c>
     </row>
     <row r="38">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.07474815400268109</v>
+        <v>0.06295075963755115</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.0626902414798518</v>
+        <v>-0.04709141895149838</v>
       </c>
     </row>
     <row r="39">
@@ -3899,21 +3899,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.07253885466305676</v>
+        <v>0.05508094321842716</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.06105350828727529</v>
+        <v>-0.04490378663089967</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0685854773096175</v>
+        <v>0.03606855264287878</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.05053682930585712</v>
+        <v>-0.04333597081634755</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5454874824810154</v>
+        <v>0.4909636487125268</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.08455010593452339</v>
+        <v>-0.1155339823380489</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5055043672338237</v>
+        <v>0.4890365033625279</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.009818600477822348</v>
+        <v>-0.04375871718405566</v>
       </c>
     </row>
     <row r="47">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5036925043736638</v>
+        <v>0.4854336322337052</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0.002550419855511965</v>
+        <v>-0.02814898027355806</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3788716336223201</v>
+        <v>0.3766430060728798</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>0.01193415331900005</v>
+        <v>-0.0137574856353867</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2882090360442082</v>
+        <v>0.2716585138031582</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.0194249869526415</v>
+        <v>-0.0002661602058228185</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2775700753477526</v>
+        <v>0.2446958818248786</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.03855736810417332</v>
+        <v>0.01115484937430478</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2598457371103255</v>
+        <v>0.2373123967168911</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.04731087550248225</v>
+        <v>0.01963100477163393</v>
       </c>
     </row>
     <row r="52">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2496568360714926</v>
+        <v>0.2351183960906673</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.05403316899665445</v>
+        <v>0.02899522867488513</v>
       </c>
     </row>
     <row r="53">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2325659766071275</v>
+        <v>0.2312314721696944</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.05635752248395964</v>
+        <v>0.03852124435973026</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2085945981682438</v>
+        <v>0.1874050208706606</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.06204347580916525</v>
+        <v>0.04784028707975718</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8934668677374331</v>
+        <v>0.8633082549832547</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1789787107930872</v>
+        <v>-0.1878757601205108</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7603481463113813</v>
+        <v>0.7607686856706917</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1209015369348776</v>
+        <v>-0.1485569417134568</v>
       </c>
     </row>
     <row r="61">
@@ -4651,21 +4651,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5066335144894758</v>
+        <v>0.5003346329140537</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1179951981937968</v>
+        <v>-0.1395666855084909</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4953026696224148</v>
+        <v>0.4805276432656855</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09153219929935608</v>
+        <v>-0.08679479033552739</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4559063328177873</v>
+        <v>0.4235753710800747</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.08212174318314136</v>
+        <v>-0.08028056938295947</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4328915075796376</v>
+        <v>0.4141355272735183</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4808,21 +4808,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.05640627068608706</v>
+        <v>-0.06216888190463032</v>
       </c>
     </row>
     <row r="65">
@@ -4831,21 +4831,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3704061445399354</v>
+        <v>0.3351506074549102</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4853,21 +4853,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.03093146964309423</v>
+        <v>-0.05346574719936592</v>
       </c>
     </row>
     <row r="66">
@@ -4876,21 +4876,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3498047266211666</v>
+        <v>0.3268225837837604</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.00776960305575447</v>
+        <v>0.001361994189922111</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3216965083565604</v>
+        <v>0.296018040289366</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.01625866472090487</v>
+        <v>0.02333320410999895</v>
       </c>
     </row>
     <row r="68">
@@ -4966,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1755531861985156</v>
+        <v>0.1603587488149234</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01975919703127405</v>
+        <v>0.04000376294190322</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.905679076938151</v>
+        <v>2.88972643374662</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.02369577500046582</v>
+        <v>0.007461834759782793</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.451745376532615</v>
+        <v>2.405645004293508</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.0614939736484954</v>
+        <v>0.08720720057097475</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.36316610256089</v>
+        <v>2.347996314233302</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5184,21 +5184,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1599125427231747</v>
+        <v>0.169552632468015</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.743518945110235</v>
+        <v>1.750402351180679</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1905103988209815</v>
+        <v>0.1728144030863978</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.177581226917401</v>
+        <v>1.136790789949186</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1961695308864919</v>
+        <v>0.1949007949179877</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.131087770363672</v>
+        <v>1.130399006901708</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5319,21 +5319,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2367854701595278</v>
+        <v>0.2175589293765205</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.000495143627636</v>
+        <v>1.001379846724848</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2535960770717589</v>
+        <v>0.2544524935568542</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9241588467321356</v>
+        <v>0.9116703386889844</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5409,21 +5409,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2981376982172252</v>
+        <v>0.3090722334450464</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.9114750911435545</v>
+        <v>0.8670913656457084</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3213562451008338</v>
+        <v>0.3147001746511604</v>
       </c>
     </row>
     <row r="82">
@@ -5477,21 +5477,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7679142456288315</v>
+        <v>0.7716843918129195</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.350095772380852</v>
+        <v>0.3475362963345685</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,16 +489,16 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>224.76</v>
+        <v>222.78</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.007156154876907905</v>
+        <v>-0.008809377896113246</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.05086959685635284</v>
+        <v>0.02239561734513318</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.02061571728710909</v>
+        <v>0.02744083797443397</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.0423893868686942</v>
+        <v>0.06161540290545942</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.02244260483299854</v>
+        <v>-0.03386962870301413</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4909636487125268</v>
+        <v>0.4807790745991607</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7822712190442611</v>
+        <v>0.7614378436399092</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8633082549832547</v>
+        <v>0.8639287376899445</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.405645004293508</v>
+        <v>2.375643780706422</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5045263284648158</v>
+        <v>0.5000953688558623</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>63.99</v>
+        <v>63.73</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.006765265825756872</v>
+        <v>-0.004063168142062423</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.106327826930404</v>
+        <v>0.06732541482836929</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.0391360795023028</v>
+        <v>0.06092891403372969</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.05594064834495649</v>
+        <v>0.08421233184310495</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.07994250365673405</v>
+        <v>-0.07917930378163773</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4854336322337052</v>
+        <v>0.4638548758954113</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5911982557579765</v>
+        <v>0.58113606187791</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7607686856706917</v>
+        <v>0.7629263727878655</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.88972643374662</v>
+        <v>2.873921821219683</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5726775457257061</v>
+        <v>0.5705446365553226</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>58.04</v>
+        <v>58.07</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.005718278223703521</v>
+        <v>0.000516863866707018</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.06593204962875543</v>
+        <v>0.04217513321316901</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.05049775412719182</v>
+        <v>0.06102686242506428</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.0796131459751146</v>
+        <v>0.1016884975042718</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.05508094321842716</v>
+        <v>0.06452796529779281</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.4890365033625279</v>
+        <v>0.494253397080755</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4275023284532531</v>
+        <v>0.4292591592490453</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5003346329140537</v>
+        <v>0.5071046579583625</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.750402351180679</v>
+        <v>1.751824183499994</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4010879895006731</v>
+        <v>0.4013293807291709</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>90.18000000000001</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.003866104924781455</v>
+        <v>0.00365936826278479</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.02444831324688668</v>
+        <v>-0.02625061745155721</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.04662222437308938</v>
+        <v>-0.03630745420779147</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.02392032794753185</v>
+        <v>-0.01286945439803922</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1530494995630243</v>
+        <v>0.1805139467564376</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.0837864440425351</v>
+        <v>0.064280386686554</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4788003025141327</v>
+        <v>0.4885728238739269</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4805276432656855</v>
+        <v>0.4700995471479641</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5845382463546294</v>
+        <v>0.5903366553245082</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1658273568968209</v>
+        <v>0.1672476896727886</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>24.79</v>
+        <v>24.66</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01432080089286392</v>
+        <v>-0.005244092913034404</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.04466925384487896</v>
+        <v>0.0266444370296246</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.06807418756477679</v>
+        <v>0.06568714338184622</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.06394857198522264</v>
+        <v>0.06753244329787012</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2958704653980722</v>
+        <v>0.3013192007696226</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3766430060728798</v>
+        <v>0.429562521388525</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.05974115346763531</v>
+        <v>0.0545952261998226</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.04317643294996332</v>
+        <v>0.0448674344255664</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4762547103032859</v>
+        <v>0.4685132602378685</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1386417367710424</v>
+        <v>0.1366479093654267</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.54</v>
+        <v>64.88</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.006390804898569247</v>
+        <v>-0.01172893000097508</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.008535336025458085</v>
+        <v>-0.02743219691454979</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.01233723805985387</v>
+        <v>-0.02917858034130094</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.02892830895987986</v>
+        <v>-0.09499239721123243</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1489693491808712</v>
+        <v>0.2744057640517945</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2716585138031582</v>
+        <v>0.1389596352736653</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1555437039283121</v>
+        <v>0.08914771522926479</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3351506074549102</v>
+        <v>0.3458013217699889</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5085404262883497</v>
+        <v>2.308727899820137</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1468826540679797</v>
+        <v>0.4901169374794057</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>65.65000000000001</v>
+        <v>29.99</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.005905502487004721</v>
+        <v>0.01523354237116092</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.01531082288431218</v>
+        <v>0.005363722689283534</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.04744626712047473</v>
+        <v>0.03915450924700581</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.07678243619193326</v>
+        <v>-0.006295577605578528</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2337906907620375</v>
+        <v>0.1442197946845736</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1614293843539931</v>
+        <v>0.2964819251994251</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.09436575447232221</v>
+        <v>0.1682239372944905</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3268225837837604</v>
+        <v>0.3580328773332477</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.347996314233302</v>
+        <v>0.5315208407908225</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.495988736700117</v>
+        <v>0.1526770251559681</v>
       </c>
     </row>
     <row r="9">
@@ -984,12 +984,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.86</v>
+        <v>56.83</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01028803973355208</v>
+        <v>0.02304235124345744</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.0003466283795356961</v>
+        <v>0.03742247348374494</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.02926333485638943</v>
+        <v>0.1165029494578858</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.07172722841079515</v>
+        <v>0.05907569870773033</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.07047483643918939</v>
+        <v>0.2476400171883311</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2312314721696944</v>
+        <v>0.267508011024129</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1708440263821842</v>
+        <v>0.07737132759864185</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4235753710800747</v>
+        <v>0.1882578684881846</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.001379846724848</v>
+        <v>0.3449939578553072</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2602107329410939</v>
+        <v>0.1038416525585706</v>
       </c>
     </row>
     <row r="10">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>55.55</v>
+        <v>29</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.008716171143931195</v>
+        <v>0.004850983599710146</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03368063829664902</v>
+        <v>-0.0112512759824227</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.08094959908191912</v>
+        <v>-0.01192505543170963</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.02528606356899354</v>
+        <v>-0.05996759671293039</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.262499982660467</v>
+        <v>0.06149342327752882</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2351183960906673</v>
+        <v>0.2469017415133465</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.05415017230626895</v>
+        <v>0.1683377054052886</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1517002410866624</v>
+        <v>0.4304811118581353</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3147001746511604</v>
+        <v>1.011088374534185</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.09549123435717877</v>
+        <v>0.2622451727952857</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>15.31</v>
+        <v>34.87</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.008419634993498737</v>
+        <v>0.01160422677738104</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0145792090658845</v>
+        <v>0.004899082570824387</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01998668795205027</v>
+        <v>0.02861349151460568</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02889786974923947</v>
+        <v>-0.03859943502093977</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.00519817556344393</v>
+        <v>0.04151730611271054</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2373123967168911</v>
+        <v>0.1831663483843711</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.3011772900671479</v>
+        <v>0.1414163587726294</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.296018040289366</v>
+        <v>0.4211448948210701</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.9116703386889844</v>
+        <v>0.7444941613300426</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2410930222658272</v>
+        <v>0.2038060087196267</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>34.47</v>
+        <v>15.23</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.01232092511104699</v>
+        <v>-0.005225400077577103</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.008484520565771536</v>
+        <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.007305668938689225</v>
+        <v>0.01196008964918671</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.05639194162145</v>
+        <v>0.03044653703621369</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.03606855264287878</v>
+        <v>0.001314891784299554</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.168047470061049</v>
+        <v>0.2269425622012269</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1339558389771123</v>
+        <v>0.2964425991861297</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4141355272735183</v>
+        <v>0.2943781181546894</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.7244827064677377</v>
+        <v>0.9016810963528972</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1991852586379659</v>
+        <v>0.2389275101270529</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>44.81</v>
+        <v>45.13</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.01016123436759908</v>
+        <v>0.007141256081615532</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.001114561666969993</v>
+        <v>0.002220792616684175</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.009689055764460441</v>
+        <v>0.02034821467767522</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.0116894304700752</v>
+        <v>-0.01074085653752743</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1611816842733544</v>
+        <v>0.1607510243904162</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2446958818248786</v>
+        <v>0.2801137397107469</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.01922897047459537</v>
+        <v>0.02455081891344024</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.02333320410999895</v>
+        <v>0.03381291072569104</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3090722334450464</v>
+        <v>0.31842065349341</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09392581311121706</v>
+        <v>0.09652364042840356</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>67.94</v>
+        <v>68.28</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.01479113481160232</v>
+        <v>0.005004361578936578</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.02356998198462934</v>
+        <v>-0.008566922371938457</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.02385051823430817</v>
+        <v>-0.02275660376101729</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.01778221425616988</v>
+        <v>-0.01000438493829003</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.02234278795148392</v>
+        <v>0.04235421959958985</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.03852124435973026</v>
+        <v>0.03903306816863839</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1640776218025399</v>
+        <v>0.1732462863276225</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1447532374675038</v>
+        <v>0.1631933920354438</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7479589634493378</v>
+        <v>0.7567063821275812</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2046024556951467</v>
+        <v>0.2066085351074562</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>92.34999999999999</v>
+        <v>16.47</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.005772149652128133</v>
+        <v>-0.003026703572861056</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.003022765708724506</v>
+        <v>-0.02889149749817921</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.002714440870161816</v>
+        <v>-0.05399198979300068</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.0351060562375104</v>
+        <v>-0.07263518574901295</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.00891869362417852</v>
+        <v>0.01792330053825419</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.06475322168252751</v>
+        <v>0.1386404076361361</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.120536380059459</v>
+        <v>0.02566373689104862</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1455759348116181</v>
+        <v>0.08573662727471287</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1728144030863978</v>
+        <v>0.8614404341725495</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.05457247131717313</v>
+        <v>0.2301263302885324</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16.52</v>
+        <v>91.58</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.02880657051880442</v>
+        <v>-0.008337808941947911</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02594331665452831</v>
+        <v>-0.01197540814666875</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.05383726666657929</v>
+        <v>-0.00521394460426261</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.06242907656510555</v>
+        <v>-0.05840016636252898</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.01661541278545675</v>
+        <v>-0.01057789445086277</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1467843651814005</v>
+        <v>0.05987555821151935</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.03359336742709451</v>
+        <v>0.1021996844607285</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.08302338408435772</v>
+        <v>0.1354775739950138</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8670913656457084</v>
+        <v>0.1630354752942598</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2313698721234987</v>
+        <v>0.05163327830794606</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>109.36</v>
+        <v>36.11</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.01539568820717607</v>
+        <v>0.005289600531508842</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.03075424235035384</v>
+        <v>-0.02379024136750751</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.05406106709630432</v>
+        <v>-0.05098551026564635</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.04912617529722696</v>
+        <v>-0.05098551026564635</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.04296837469989345</v>
+        <v>-0.03629571833587575</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1874050208706606</v>
+        <v>0.1227404392318319</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06912933294140466</v>
+        <v>0.05780549516836686</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.09277462243941126</v>
+        <v>0.1461853666971134</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.007461834759782793</v>
+        <v>1.148094047107517</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.002481117219399476</v>
+        <v>0.2902813814626417</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>35.92</v>
+        <v>108.98</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.02787557706973653</v>
+        <v>-0.003474737118664528</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02708559180918746</v>
+        <v>-0.02426357798581258</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.05374080518252156</v>
+        <v>-0.04962060611205865</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.05498553656614802</v>
+        <v>-0.06027418979212418</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.03466812543044773</v>
+        <v>-0.04945484599636463</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1284986595784741</v>
+        <v>0.1787994262232986</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.05675082026527711</v>
+        <v>0.06150042826447444</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1378517574223792</v>
+        <v>0.07891922472229629</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>1.136790789949186</v>
+        <v>0.003961240289918289</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2880142494592159</v>
+        <v>0.00131867376512651</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>113.52</v>
+        <v>50.99</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.003336302701683058</v>
+        <v>-0.005849078411104602</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.00202200753348214</v>
+        <v>0.005125214637820008</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.01612065049946487</v>
+        <v>0.008504752640353663</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.06889765134542547</v>
+        <v>-0.0100950623182029</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.04709141895149838</v>
+        <v>-0.03610585618750373</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.08319137610570126</v>
+        <v>0.08477611329819279</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.09154131196001725</v>
+        <v>0.06896053968791183</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1603587488149234</v>
+        <v>0.1141892148716792</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4422787264345127</v>
+        <v>0.7613216708854755</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1298385773108111</v>
+        <v>0.2076642943531208</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>51.29</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0</v>
+        <v>-0.006085607248671243</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02457050556320173</v>
+        <v>-0.03999157859601998</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.002737035884106565</v>
+        <v>-0.03999157859601998</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.01441199052277919</v>
+        <v>-0.07560140663391801</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.0295174570223995</v>
+        <v>0.01837213640722357</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.0990001781893024</v>
+        <v>0.0823752575279233</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0772474780716601</v>
+        <v>0.02220179724977434</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1207445375506302</v>
+        <v>0.02912121029240966</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7716843918129195</v>
+        <v>0.4528217956142466</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2100280921039601</v>
+        <v>0.1325849392185305</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>99.01000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01020304028368479</v>
+        <v>-0.01191799090714274</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.005790325890772774</v>
+        <v>-0.01717901415254974</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.02883761549796116</v>
+        <v>-0.0213084961277159</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.05371303894403867</v>
+        <v>-0.06668572680900975</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.01256601724363438</v>
+        <v>-0.02365264660049549</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.05066066241602174</v>
+        <v>0.01771343072061371</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.09882103209647819</v>
+        <v>0.0853813994023398</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1132837964395512</v>
+        <v>0.1080788695063124</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2544524935568542</v>
+        <v>0.239501940145201</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.0784948436101176</v>
+        <v>0.07419321189691885</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>92.02</v>
+        <v>112.41</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01991695344273481</v>
+        <v>-0.009777951143243202</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.0381519974468203</v>
+        <v>-0.01876740522261899</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.03034778542155381</v>
+        <v>-0.02776335416206821</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.05377895482708062</v>
+        <v>-0.07777500840929663</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.0296519392977832</v>
+        <v>-0.07306005793860637</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.0897618050086102</v>
+        <v>0.07307705333228953</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03010957406803705</v>
+        <v>0.07687068938109087</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.04000376294190322</v>
+        <v>0.1542183623120366</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.4617173211741348</v>
+        <v>0.4281760570766222</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1348918166015203</v>
+        <v>0.12614397071846</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13.4</v>
+        <v>39.8</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.02212051635755174</v>
+        <v>-0.003005985405533318</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.007518753861753602</v>
+        <v>-0.01801133886560147</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.01325480899757314</v>
+        <v>-0.02115102345250741</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.04354037119100373</v>
+        <v>-0.07092227696163378</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.04490378663089967</v>
+        <v>-0.05404965061784472</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.01963100477163393</v>
+        <v>0.05397029520434993</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1376123926068931</v>
+        <v>0.07563861503627645</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.07559302066113638</v>
+        <v>0.08302690239427202</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.08720720057097475</v>
+        <v>0.3520871316244805</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.02826275808739331</v>
+        <v>0.1057787162260431</v>
       </c>
     </row>
     <row r="24">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>67.68000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.003409983207413481</v>
+        <v>-0.00398931208405684</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.0192770896066623</v>
+        <v>0.01414175453803779</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.009222621518578999</v>
+        <v>-0.002810574205625915</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.06195427756297156</v>
+        <v>-0.05495581197698329</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.05908522149268203</v>
+        <v>-0.07556218657699443</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.04784028707975718</v>
+        <v>0.03421300009961059</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.09003060297713494</v>
+        <v>0.08237002221197565</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1874,51 +1874,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>39.92</v>
+        <v>13.24</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01650657750982687</v>
+        <v>-0.01194028746022147</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.01212575303927343</v>
+        <v>-0.003762241601082073</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.02752743213439701</v>
+        <v>-0.01341283935562321</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.06254740547012205</v>
+        <v>-0.05360972210652548</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.05296147615391944</v>
+        <v>-0.07087720904433936</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0492893214474972</v>
+        <v>-0.01102232275025083</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.08719185174496014</v>
+        <v>0.1212581542344919</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.07250990234171617</v>
+        <v>0.06941314154196143</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.3561638279092376</v>
+        <v>0.07422546782827988</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1068889506230382</v>
+        <v>0.02415372315432385</v>
       </c>
     </row>
     <row r="26">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.71</v>
+        <v>168.19</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.007130174674829903</v>
+        <v>-0.008605903375210056</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.009057948270998706</v>
+        <v>-0.01815528636862829</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.008896887333847969</v>
+        <v>-0.04740595396989522</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05432942771229665</v>
+        <v>-0.09463315619711588</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.02622382091730135</v>
+        <v>0.0464783546787384</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.02899522867488513</v>
+        <v>0.08247151349404236</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.006561724731417917</v>
+        <v>-0.1268614644218524</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.001361994189922111</v>
+        <v>-0.1259732443540131</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4397702113561186</v>
+        <v>0.5218884422979915</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1291831649638715</v>
+        <v>0.1502553792759302</v>
       </c>
     </row>
     <row r="27">
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>169.65</v>
+        <v>16.63</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.02985075408279725</v>
+        <v>-0.004787548060394164</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.005743485660691383</v>
+        <v>-0.005382784466743784</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.05218174931580966</v>
+        <v>-0.007756626869921401</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.08411165680731225</v>
+        <v>-0.07302125609216592</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.02724795741028352</v>
+        <v>-0.04535022457332927</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.07867274392468238</v>
+        <v>0.02762875754626704</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.1185655066825563</v>
+        <v>-0.01859831324115935</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1395666855084909</v>
+        <v>-0.003928576855098176</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5350993590533515</v>
+        <v>0.4328771245328495</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1535741001725419</v>
+        <v>0.1273782444572917</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>26</v>
+        <v>16.38</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.008390515603196147</v>
+        <v>0.01048735878441764</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.003449603375297983</v>
+        <v>-0.007272778135357427</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.02475618346547648</v>
+        <v>-0.01857407809295308</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.09816163479691964</v>
+        <v>-0.1019737189523846</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.09533750149405662</v>
+        <v>0.04932732357620417</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-0.0137574856353867</v>
+        <v>0.09345792131588215</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.01573525287571775</v>
+        <v>-0.174811141260351</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.04544256736961616</v>
+        <v>-0.1772978761275247</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.130399006901708</v>
+        <v>0.1818181505419671</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.286728687611653</v>
+        <v>0.05726426101977822</v>
       </c>
     </row>
     <row r="29">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>52.6</v>
+        <v>25.86</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.003787893292223177</v>
+        <v>-0.005384591909555314</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.00510687465894466</v>
+        <v>-0.002699563979960518</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02066655425939967</v>
+        <v>-0.02415092036409194</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.05819158619146492</v>
+        <v>-0.08718670384773419</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.006610052573659875</v>
+        <v>-0.103328693705604</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.0002661602058228185</v>
+        <v>-0.01683686755149805</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.09277684839630929</v>
+        <v>-0.02320573755917432</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.08028056938295947</v>
+        <v>0.05306977400234758</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.1949007949179877</v>
+        <v>1.11892767764502</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.06115123377641241</v>
+        <v>0.2844150269626948</v>
       </c>
     </row>
     <row r="30">
@@ -2154,51 +2154,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>16.21</v>
+        <v>51.94</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.02113528941770459</v>
+        <v>-0.01254752598019226</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02172604809787726</v>
+        <v>-0.02624674769167545</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.03741098945408372</v>
+        <v>-0.03511059149277895</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.104419958959338</v>
+        <v>-0.05563638860529119</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.06295075963755115</v>
+        <v>-0.02000002591115124</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.05533850565067566</v>
+        <v>-0.01422492243653217</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.1804854134602302</v>
+        <v>-0.1047008901071905</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.1878757601205108</v>
+        <v>-0.09376267929386783</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.169552632468015</v>
+        <v>0.1799077461500018</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.05359392283046582</v>
+        <v>0.05669426593793991</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>61.37</v>
+        <v>61.09</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01000165719946089</v>
+        <v>-0.004562470004401464</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.008877150823204394</v>
+        <v>-0.006181894591979487</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.01745117144676456</v>
+        <v>-0.01626406354831234</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.06276732153853237</v>
+        <v>-0.06718579714011286</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.04333597081634755</v>
+        <v>-0.06015384380634015</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.01115484937430478</v>
+        <v>0.01050180323063965</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.08588841706612249</v>
+        <v>-0.09339832436056195</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.05346574719936592</v>
+        <v>-0.06201535086383458</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4339866316864631</v>
+        <v>0.427444110692681</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1276691536811871</v>
+        <v>0.1259515532971016</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>111.43</v>
+        <v>110.66</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.003398598172930201</v>
+        <v>-0.006910137673495464</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.002158448228256837</v>
+        <v>-0.005571487454966162</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02664223412230604</v>
+        <v>-0.01740364976622366</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.08007923031607667</v>
+        <v>-0.08302947147603434</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.1114743875982951</v>
+        <v>-0.1461419872640922</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.04375871718405566</v>
+        <v>-0.05708424519038746</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.05067973717886387</v>
+        <v>-0.06153080875488792</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.08679479033552739</v>
+        <v>-0.08569698860016806</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3475362963345685</v>
+        <v>0.3382246350068643</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1045367170838813</v>
+        <v>0.1019866673746121</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>14.93</v>
+        <v>14.92</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.03051943668809953</v>
+        <v>-0.0006698076810064402</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03428200075442667</v>
+        <v>-0.02864580665482153</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.04600634702265305</v>
+        <v>-0.04420240842786638</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.1384881493996585</v>
+        <v>-0.1498575085526386</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.08348683449460303</v>
+        <v>-0.1039038787911419</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.02814898027355806</v>
+        <v>-0.02216443383930533</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.1274188603947317</v>
+        <v>-0.1297317996494841</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.1485569417134568</v>
+        <v>-0.1454007306023674</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2175589293765205</v>
+        <v>0.2167433044234623</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.0678165885810269</v>
+        <v>0.06757809707081153</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>119.42</v>
+        <v>118.3</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01970121106461364</v>
+        <v>-0.009378622796518798</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.0280784935339532</v>
+        <v>-0.04496649367336769</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.06652077007683843</v>
+        <v>-0.06496991629314175</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.06057272192628038</v>
+        <v>-0.07614213016503446</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1311786318790679</v>
+        <v>-0.1472995927051191</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1155339823380489</v>
+        <v>-0.1320728968809224</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.0725618796980364</v>
+        <v>-0.0857392756771953</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.06216888190463032</v>
+        <v>-0.07758501713025512</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4056872045575803</v>
+        <v>0.3925036694420077</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1202017080792708</v>
+        <v>0.1166886862313132</v>
       </c>
     </row>
   </sheetData>
@@ -2719,17 +2719,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.0796131459751146</v>
+        <v>0.1016884975042718</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1384881493996585</v>
+        <v>-0.1498575085526386</v>
       </c>
     </row>
     <row r="18">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.06394857198522264</v>
+        <v>0.08421233184310495</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.104419958959338</v>
+        <v>-0.1019737189523846</v>
       </c>
     </row>
     <row r="19">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05594064834495649</v>
+        <v>0.06753244329787012</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.09816163479691964</v>
+        <v>-0.09499239721123243</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.0423893868686942</v>
+        <v>0.06161540290545942</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.08411165680731225</v>
+        <v>-0.09463315619711588</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.02889786974923947</v>
+        <v>0.05907569870773033</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08007923031607667</v>
+        <v>-0.08718670384773419</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.02528606356899354</v>
+        <v>0.03044653703621369</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.07678243619193326</v>
+        <v>-0.08302947147603434</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.0116894304700752</v>
+        <v>-0.006295577605578528</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.07172722841079515</v>
+        <v>-0.07777500840929663</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01441199052277919</v>
+        <v>-0.01000438493829003</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06889765134542547</v>
+        <v>-0.07614213016503446</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.01778221425616988</v>
+        <v>-0.0100950623182029</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06276732153853237</v>
+        <v>-0.07560140663391801</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.02392032794753185</v>
+        <v>-0.01074085653752743</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06254740547012205</v>
+        <v>-0.07302125609216592</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2958704653980722</v>
+        <v>0.3013192007696226</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1311786318790679</v>
+        <v>-0.1472995927051191</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.262499982660467</v>
+        <v>0.2744057640517945</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1114743875982951</v>
+        <v>-0.1461419872640922</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2337906907620375</v>
+        <v>0.2476400171883311</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.09533750149405662</v>
+        <v>-0.1039038787911419</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1611816842733544</v>
+        <v>0.1805139467564376</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.08348683449460303</v>
+        <v>-0.103328693705604</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1530494995630243</v>
+        <v>0.1607510243904162</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.07994250365673405</v>
+        <v>-0.07917930378163773</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1489693491808712</v>
+        <v>0.1442197946845736</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.05908522149268203</v>
+        <v>-0.07556218657699443</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.07047483643918939</v>
+        <v>0.06452796529779281</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.05296147615391944</v>
+        <v>-0.07306005793860637</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.06295075963755115</v>
+        <v>0.06149342327752882</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.04709141895149838</v>
+        <v>-0.07087720904433936</v>
       </c>
     </row>
     <row r="39">
@@ -3899,21 +3899,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.05508094321842716</v>
+        <v>0.04932732357620417</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.04490378663089967</v>
+        <v>-0.06015384380634015</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.03606855264287878</v>
+        <v>0.0464783546787384</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.04333597081634755</v>
+        <v>-0.05404965061784472</v>
       </c>
     </row>
     <row r="41"/>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4909636487125268</v>
+        <v>0.494253397080755</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1155339823380489</v>
+        <v>-0.1320728968809224</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4890365033625279</v>
+        <v>0.4807790745991607</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.04375871718405566</v>
+        <v>-0.05708424519038746</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4854336322337052</v>
+        <v>0.4638548758954113</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.02814898027355806</v>
+        <v>-0.02216443383930533</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3766430060728798</v>
+        <v>0.429562521388525</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0137574856353867</v>
+        <v>-0.01683686755149805</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2716585138031582</v>
+        <v>0.2964819251994251</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0002661602058228185</v>
+        <v>-0.01422492243653217</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2446958818248786</v>
+        <v>0.2801137397107469</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.01115484937430478</v>
+        <v>-0.01102232275025083</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2373123967168911</v>
+        <v>0.267508011024129</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.01963100477163393</v>
+        <v>0.01050180323063965</v>
       </c>
     </row>
     <row r="52">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2351183960906673</v>
+        <v>0.2469017415133465</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.02899522867488513</v>
+        <v>0.01771343072061371</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2312314721696944</v>
+        <v>0.2269425622012269</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.03852124435973026</v>
+        <v>0.02762875754626704</v>
       </c>
     </row>
     <row r="54">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1874050208706606</v>
+        <v>0.1831663483843711</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.04784028707975718</v>
+        <v>0.03421300009961059</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8633082549832547</v>
+        <v>0.8639287376899445</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1878757601205108</v>
+        <v>-0.1772978761275247</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7607686856706917</v>
+        <v>0.7629263727878655</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1485569417134568</v>
+        <v>-0.1454007306023674</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5003346329140537</v>
+        <v>0.5071046579583625</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1395666855084909</v>
+        <v>-0.1259732443540131</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4805276432656855</v>
+        <v>0.4700995471479641</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.08679479033552739</v>
+        <v>-0.09376267929386783</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4235753710800747</v>
+        <v>0.4304811118581353</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.08028056938295947</v>
+        <v>-0.08569698860016806</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4141355272735183</v>
+        <v>0.4211448948210701</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.06216888190463032</v>
+        <v>-0.07758501713025512</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3351506074549102</v>
+        <v>0.3580328773332477</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.05346574719936592</v>
+        <v>-0.06201535086383458</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3268225837837604</v>
+        <v>0.3458013217699889</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.001361994189922111</v>
+        <v>-0.003928576855098176</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.296018040289366</v>
+        <v>0.2943781181546894</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.02333320410999895</v>
+        <v>0.02912121029240966</v>
       </c>
     </row>
     <row r="68">
@@ -4966,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1603587488149234</v>
+        <v>0.1882578684881846</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.04000376294190322</v>
+        <v>0.03381291072569104</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.88972643374662</v>
+        <v>2.873921821219683</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.007461834759782793</v>
+        <v>0.003961240289918289</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.405645004293508</v>
+        <v>2.375643780706422</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.08720720057097475</v>
+        <v>0.07422546782827988</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.347996314233302</v>
+        <v>2.308727899820137</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5184,21 +5184,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.169552632468015</v>
+        <v>0.1630354752942598</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.750402351180679</v>
+        <v>1.751824183499994</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1728144030863978</v>
+        <v>0.1799077461500018</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.136790789949186</v>
+        <v>1.148094047107517</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1949007949179877</v>
+        <v>0.1818181505419671</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.130399006901708</v>
+        <v>1.11892767764502</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2175589293765205</v>
+        <v>0.2167433044234623</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.001379846724848</v>
+        <v>1.011088374534185</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2544524935568542</v>
+        <v>0.239501940145201</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9116703386889844</v>
+        <v>0.9016810963528972</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3090722334450464</v>
+        <v>0.31842065349341</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8670913656457084</v>
+        <v>0.8614404341725495</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3147001746511604</v>
+        <v>0.3382246350068643</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7716843918129195</v>
+        <v>0.7613216708854755</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3475362963345685</v>
+        <v>0.3449939578553072</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.8639287376899445</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.375643780706422</v>
+        <v>2.375643390470677</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5000953688558623</v>
+        <v>0.5000953110505078</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.7629263727878655</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.873921821219683</v>
+        <v>2.873922270366081</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5705446365553226</v>
+        <v>0.5705446972521626</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +742,7 @@
         <v>0.4292591592490453</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5071046579583625</v>
+        <v>0.5071048071673974</v>
       </c>
       <c r="O4" s="6" t="n">
         <v>1.751824183499994</v>
@@ -798,7 +798,7 @@
         <v>0.4885728238739269</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4700995471479641</v>
+        <v>0.4700996382350939</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>0.5903366553245082</v>
@@ -913,10 +913,10 @@
         <v>0.3458013217699889</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.308727899820137</v>
+        <v>2.30872757797917</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4901169374794057</v>
+        <v>0.4901168891646952</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.3580328773332477</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5315208407908225</v>
+        <v>0.5315206916146709</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1526770251559681</v>
+        <v>0.1526769877308753</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.1882578684881846</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.3449939578553072</v>
+        <v>0.3449940792845017</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1038416525585706</v>
+        <v>0.1038416857777034</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.4304811118581353</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.011088374534185</v>
+        <v>1.0110885075381</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2622451727952857</v>
+        <v>0.2622452006216025</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         <v>0.2943781181546894</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.9016810963528972</v>
+        <v>0.9016808699012293</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2389275101270529</v>
+        <v>0.2389274609500005</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.03381291072569104</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.31842065349341</v>
+        <v>0.3184205065660479</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09652364042840356</v>
+        <v>0.09652359969549296</v>
       </c>
     </row>
     <row r="14">
@@ -1299,7 +1299,7 @@
         <v>0.03903306816863839</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1732462863276225</v>
+        <v>0.1732462094243323</v>
       </c>
       <c r="N14" s="6" t="n">
         <v>0.1631933920354438</v>
@@ -1358,13 +1358,13 @@
         <v>0.02566373689104862</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.08573662727471287</v>
+        <v>0.08573655901641453</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8614404341725495</v>
+        <v>0.8614402335384506</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2301263302885324</v>
+        <v>0.2301262860924191</v>
       </c>
     </row>
     <row r="16">
@@ -1417,10 +1417,10 @@
         <v>0.1354775739950138</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1630354752942598</v>
+        <v>0.1630359260440251</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.05163327830794606</v>
+        <v>0.05163341416605238</v>
       </c>
     </row>
     <row r="17">
@@ -1697,10 +1697,10 @@
         <v>0.1080788695063124</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.239501940145201</v>
+        <v>0.23950182032987</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.07419321189691885</v>
+        <v>0.0741931772849469</v>
       </c>
     </row>
     <row r="22">
@@ -1753,10 +1753,10 @@
         <v>0.1542183623120366</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.4281760570766222</v>
+        <v>0.4281761955124972</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.12614397071846</v>
+        <v>0.1261440071048985</v>
       </c>
     </row>
     <row r="23">
@@ -1806,13 +1806,13 @@
         <v>0.07563861503627645</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.08302690239427202</v>
+        <v>0.08302701481736996</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3520871316244805</v>
+        <v>0.3520872192350304</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1057787162260431</v>
+        <v>0.1057787401095827</v>
       </c>
     </row>
     <row r="24">
@@ -1909,16 +1909,16 @@
         <v>-0.01102232275025083</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1212581542344919</v>
+        <v>0.1212582447917727</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0.06941314154196143</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.07422546782827988</v>
+        <v>0.07422555094780092</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02415372315432385</v>
+        <v>0.02415374956937577</v>
       </c>
     </row>
     <row r="26">
@@ -2024,13 +2024,13 @@
         <v>-0.01859831324115935</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.003928576855098176</v>
+        <v>-0.003928690648941635</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.4328771245328495</v>
+        <v>0.4328772422733274</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1273782444572917</v>
+        <v>0.1273782753364341</v>
       </c>
     </row>
     <row r="28">
@@ -2139,10 +2139,10 @@
         <v>0.05306977400234758</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.11892767764502</v>
+        <v>1.118927512066579</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2844150269626948</v>
+        <v>0.2844149935068663</v>
       </c>
     </row>
     <row r="30">
@@ -2195,10 +2195,10 @@
         <v>-0.09376267929386783</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1799077461500018</v>
+        <v>0.1799078483978758</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.05669426593793991</v>
+        <v>0.05669429646143898</v>
       </c>
     </row>
     <row r="31">
@@ -2304,13 +2304,13 @@
         <v>-0.06153080875488792</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.08569698860016806</v>
+        <v>-0.08569704623428798</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3382246350068643</v>
+        <v>0.3382247584757347</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1019866673746121</v>
+        <v>0.1019867012655453</v>
       </c>
     </row>
     <row r="33">
@@ -2357,16 +2357,16 @@
         <v>-0.02216443383930533</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.1297317996494841</v>
+        <v>-0.1297317028289365</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>-0.1454007306023674</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2167433044234623</v>
+        <v>0.2167434936836448</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.06757809707081153</v>
+        <v>0.06757815242349352</v>
       </c>
     </row>
     <row r="34">
@@ -2416,13 +2416,13 @@
         <v>-0.0857392756771953</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07758501713025512</v>
+        <v>-0.07758512687606789</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.3925036694420077</v>
+        <v>0.3925037944961418</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1166886862313132</v>
+        <v>0.1166887196594795</v>
       </c>
     </row>
   </sheetData>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5071046579583625</v>
+        <v>0.5071048071673974</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4700995471479641</v>
+        <v>0.4700996382350939</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.08569698860016806</v>
+        <v>-0.08569704623428798</v>
       </c>
     </row>
     <row r="64">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.07758501713025512</v>
+        <v>-0.07758512687606789</v>
       </c>
     </row>
     <row r="65">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.003928576855098176</v>
+        <v>-0.003928690648941635</v>
       </c>
     </row>
     <row r="67">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.873921821219683</v>
+        <v>2.873922270366081</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.375643780706422</v>
+        <v>2.375643390470677</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.07422546782827988</v>
+        <v>0.07422555094780092</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.308727899820137</v>
+        <v>2.30872757797917</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1630354752942598</v>
+        <v>0.1630359260440251</v>
       </c>
     </row>
     <row r="76">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1799077461500018</v>
+        <v>0.1799078483978758</v>
       </c>
     </row>
     <row r="77">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.11892767764502</v>
+        <v>1.118927512066579</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2167433044234623</v>
+        <v>0.2167434936836448</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.011088374534185</v>
+        <v>1.0110885075381</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.239501940145201</v>
+        <v>0.23950182032987</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9016810963528972</v>
+        <v>0.9016808699012293</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.31842065349341</v>
+        <v>0.3184205065660479</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8614404341725495</v>
+        <v>0.8614402335384506</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3382246350068643</v>
+        <v>0.3382247584757347</v>
       </c>
     </row>
     <row r="82">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3449939578553072</v>
+        <v>0.3449940792845017</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,15 +490,15 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>222.78</v>
+        <v>225.95</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.008809377896113246</v>
+        <v>0.01422927635476712</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.02239561734513318</v>
+        <v>0.02392712567684208</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.02744083797443397</v>
+        <v>0.02230564012524328</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.06161540290545942</v>
+        <v>0.06354436429240762</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.03386962870301413</v>
+        <v>-0.04424519500797952</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4807790745991607</v>
+        <v>0.494670341200514</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7614378436399092</v>
+        <v>0.7865018294988066</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8639287376899445</v>
+        <v>0.8866807328157909</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.375643390470677</v>
+        <v>2.419647224281389</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5000953110505078</v>
+        <v>0.5065854491922832</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>63.73</v>
+        <v>64.38</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.004063168142062423</v>
+        <v>0.01019924236388636</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.06732541482836929</v>
+        <v>0.04853413116419958</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.06092891403372969</v>
+        <v>0.0569692565210751</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.08421233184310495</v>
+        <v>0.07712894027685246</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.07917930378163773</v>
+        <v>-0.0868085495969082</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4638548758954113</v>
+        <v>0.4612829287670863</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.58113606187791</v>
+        <v>0.5972624517832839</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7629263727878655</v>
+        <v>0.790848784073902</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.873922270366081</v>
+        <v>2.882055805833148</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5705446972521626</v>
+        <v>0.5716430802804682</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>58.07</v>
+        <v>58.46</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.000516863866707018</v>
+        <v>0.006716021899397351</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.04217513321316901</v>
+        <v>0.04355584803232238</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.06102686242506428</v>
+        <v>0.05829104468077984</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1016884975042718</v>
+        <v>0.09722223017746368</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.06452796529779281</v>
+        <v>0.07463230596900527</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.494253397080755</v>
+        <v>0.4891013856229474</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4292591592490453</v>
+        <v>0.4388580950624763</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5071048071673974</v>
+        <v>0.5197252206684657</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.751824183499994</v>
+        <v>1.757107970044283</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4013293807291709</v>
+        <v>0.402225706324888</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>90.51000000000001</v>
+        <v>89.89</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.00365936826278479</v>
+        <v>-0.006850101999211544</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.02625061745155721</v>
+        <v>-0.03031281177023848</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.03630745420779147</v>
+        <v>-0.04514552822981355</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.01286945439803922</v>
+        <v>-0.003988926430488204</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1805139467564376</v>
+        <v>0.1552499962740392</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.064280386686554</v>
+        <v>0.06109638724788957</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4885728238739269</v>
+        <v>0.4783758554461683</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4700996382350939</v>
+        <v>0.4512520986661472</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5903366553245082</v>
+        <v>0.5570592747223819</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1672476896727886</v>
+        <v>0.1590487829048921</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>24.66</v>
+        <v>24.53</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.005244092913034404</v>
+        <v>-0.005271661053162791</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.0266444370296246</v>
+        <v>0.03371264896087678</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.06568714338184622</v>
+        <v>0.05641694280919274</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.06753244329787012</v>
+        <v>0.06374680202721561</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.3013192007696226</v>
+        <v>0.3188172141697132</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.429562521388525</v>
+        <v>0.4250422029408816</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0545952261998226</v>
+        <v>0.04903575761901369</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.0448674344255664</v>
+        <v>0.04876859575031633</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4685132602378685</v>
+        <v>0.4596041196003335</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1366479093654267</v>
+        <v>0.1343446492879437</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>64.88</v>
+        <v>65.11</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.01172893000097508</v>
+        <v>0.003545058055955508</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.02743219691454979</v>
+        <v>-0.02791882133264256</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.02917858034130094</v>
+        <v>-0.03483543590296301</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.09499239721123243</v>
+        <v>-0.1084485595142929</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2744057640517945</v>
+        <v>0.2598684254231856</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1389596352736653</v>
+        <v>0.1113954755237296</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.08914771522926479</v>
+        <v>0.09300880711126358</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3458013217699889</v>
+        <v>0.34021998106219</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.30872757797917</v>
+        <v>2.359743538059859</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4901168891646952</v>
+        <v>0.497736369118118</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>29.99</v>
+        <v>29.96</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01523354237116092</v>
+        <v>-0.001000356347931719</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.005363722689283534</v>
+        <v>0.01524902921384608</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03915450924700581</v>
+        <v>0.03596123808558382</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.006295577605578528</v>
+        <v>-0.01770494805007683</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1442197946845736</v>
+        <v>0.1162443708698688</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2964819251994251</v>
+        <v>0.2707935645744326</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1682239372944905</v>
+        <v>0.1670552970630121</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3580328773332477</v>
+        <v>0.3757751598842531</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5315206916146709</v>
+        <v>0.5237300162629703</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1526769877308753</v>
+        <v>0.1507191510085304</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>56.83</v>
+        <v>56.82</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.02304235124345744</v>
+        <v>-0.0001760009837796783</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.03742247348374494</v>
+        <v>0.04256880173989397</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1165029494578858</v>
+        <v>0.1071706943239654</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.05907569870773033</v>
+        <v>0.05378341291467503</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2476400171883311</v>
+        <v>0.2143620128882793</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.267508011024129</v>
+        <v>0.2655630893526155</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.07737132759864185</v>
+        <v>0.07718170918508838</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1882578684881846</v>
+        <v>0.2001292060659492</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.3449940792845017</v>
+        <v>0.3389247178441681</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1038416857777034</v>
+        <v>0.1021787994078256</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>29</v>
+        <v>28.92</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.004850983599710146</v>
+        <v>-0.002758618058829487</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.0112512759824227</v>
+        <v>-0.001036293121066678</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.01192505543170963</v>
+        <v>-0.01498639390022649</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.05996759671293039</v>
+        <v>-0.08248732054917596</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.06149342327752882</v>
+        <v>0.03842009623583897</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2469017415133465</v>
+        <v>0.2066260781611904</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1683377054052886</v>
+        <v>0.1651147079123463</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4304811118581353</v>
+        <v>0.4520929513620402</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.0110885075381</v>
+        <v>1.023608664767277</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2622452006216025</v>
+        <v>0.2648591790765253</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>34.87</v>
+        <v>35</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01160422677738104</v>
+        <v>0.003728163811222984</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.004899082570824387</v>
+        <v>0.01773773251462107</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.02861349151460568</v>
+        <v>0.03214391499536018</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.03859943502093977</v>
+        <v>-0.04917145628264863</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.04151730611271054</v>
+        <v>0.03642284647803584</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1831663483843711</v>
+        <v>0.1618106464571165</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1414163587726294</v>
+        <v>0.1456717459349433</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4211448948210701</v>
+        <v>0.4597343772311067</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7444941613300426</v>
+        <v>0.7547813279457798</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2038060087196267</v>
+        <v>0.2061676274695716</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>15.23</v>
+        <v>15.32</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.005225400077577103</v>
+        <v>0.005909399559619111</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>0.01122112743065773</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.01196008964918671</v>
+        <v>-0.0006523306543773089</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.03044653703621369</v>
+        <v>0.02680962576976276</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.001314891784299554</v>
+        <v>0.007894729412163404</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2269425622012269</v>
+        <v>0.2187293738637133</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2964425991861297</v>
+        <v>0.3041036906426111</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2943781181546894</v>
+        <v>0.2968644962464906</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.9016808699012293</v>
+        <v>0.9129188897862208</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2389274609500005</v>
+        <v>0.2413631578978561</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>45.13</v>
+        <v>44.85</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.007141256081615532</v>
+        <v>-0.006204356024089863</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.002220792616684175</v>
+        <v>0.007186159972970785</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.02034821467767522</v>
+        <v>0.006733989723864742</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.01074085653752743</v>
+        <v>-0.01816991737105234</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1607510243904162</v>
+        <v>0.1664498721505974</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2801137397107469</v>
+        <v>0.2653960640759456</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.02455081891344024</v>
+        <v>0.01819414086812854</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.03381291072569104</v>
+        <v>0.03216352860512739</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3184205065660479</v>
+        <v>0.3077273445705686</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09652359969549296</v>
+        <v>0.09355106608906905</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>68.28</v>
+        <v>68.08</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.005004361578936578</v>
+        <v>-0.002929070764758568</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.008566922371938457</v>
+        <v>-0.003075107360628326</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.02275660376101729</v>
+        <v>-0.03977432488199462</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.01000438493829003</v>
+        <v>-0.01972635244618504</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.04235421959958985</v>
+        <v>0.03554795874185901</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.03903306816863839</v>
+        <v>0.0186140524366869</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1732462094243323</v>
+        <v>0.1698097649304788</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1631933920354438</v>
+        <v>0.1634316858000591</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7567063821275812</v>
+        <v>0.7679070940500972</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2066085351074562</v>
+        <v>0.2091675384343257</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>16.47</v>
+        <v>16.61</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.003026703572861056</v>
+        <v>0.00850038268572062</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02889149749817921</v>
+        <v>-0.01890134016869394</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.05399198979300068</v>
+        <v>-0.04977110724646283</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.07263518574901295</v>
+        <v>-0.06369781146256337</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.01792330053825419</v>
+        <v>0.0272109172530357</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1386404076361361</v>
+        <v>0.1451989038555148</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.02566373689104862</v>
+        <v>0.03438227116148895</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.08573655901641453</v>
+        <v>0.09699464806552616</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8614402335384506</v>
+        <v>0.8718790414029898</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2301262860924191</v>
+        <v>0.2324214842514689</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>91.58</v>
+        <v>91.98</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.008337808941947911</v>
+        <v>0.004367782462123326</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01197540814666875</v>
+        <v>-0.0009774773345164744</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.00521394460426261</v>
+        <v>-0.006480864789957574</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.05840016636252898</v>
+        <v>-0.04485980849348858</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.01057789445086277</v>
+        <v>-0.0002342682058322776</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.05987555821151935</v>
+        <v>0.05879219732874597</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1021996844607285</v>
+        <v>0.1070139545612021</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1354775739950138</v>
+        <v>0.1519371907740708</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1630359260440251</v>
+        <v>0.1749919935660043</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.05163341416605238</v>
+        <v>0.05522475047182818</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>36.11</v>
+        <v>36.51</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.005289600531508842</v>
+        <v>0.0110772003439672</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.02379024136750751</v>
+        <v>-0.01083721288356909</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.05098551026564635</v>
+        <v>-0.04298828673003363</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.05098551026564635</v>
+        <v>-0.03769110060455005</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.03629571833587575</v>
+        <v>-0.0359123487908658</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1227404392318319</v>
+        <v>0.1296817150797744</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.05780549516836686</v>
+        <v>0.06952301856329623</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1461853666971134</v>
+        <v>0.1585470391455572</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.148094047107517</v>
+        <v>1.14954184928331</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2902813814626417</v>
+        <v>0.2905711969328317</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>108.98</v>
+        <v>110.37</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.003474737118664528</v>
+        <v>0.01275462788430914</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02426357798581258</v>
+        <v>-0.007553244715455709</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.04962060611205865</v>
+        <v>-0.0326057823710626</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.06027418979212418</v>
+        <v>-0.0475491425391229</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.04945484599636463</v>
+        <v>-0.05658599229052241</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1787994262232986</v>
+        <v>0.1916432679079685</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.06150042826447444</v>
+        <v>0.0750394712260225</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.07891922472229629</v>
+        <v>0.1124658564494398</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.003961240289918289</v>
+        <v>0.004036156197315455</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.00131867376512651</v>
+        <v>0.001343579385062244</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>50.99</v>
+        <v>91.92</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.005849078411104602</v>
+        <v>0.005029511142327969</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.005125214637820008</v>
+        <v>-0.03017514926341491</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.008504752640353663</v>
+        <v>-0.03698270185604113</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.0100950623182029</v>
+        <v>-0.06461787616809822</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.03610585618750373</v>
+        <v>0.034436164051042</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.08477611329819279</v>
+        <v>0.09391688215468652</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.06896053968791183</v>
+        <v>0.02734297257874974</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1141892148716792</v>
+        <v>0.03808937909214749</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7613216708854755</v>
+        <v>0.4582098403830419</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2076642943531208</v>
+        <v>0.133983341949238</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>91.45999999999999</v>
+        <v>51.28</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.006085607248671243</v>
+        <v>0.005687332639421117</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.03999157859601998</v>
+        <v>0.009647526185015964</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.03999157859601998</v>
+        <v>-0.00523764232317514</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.07560140663391801</v>
+        <v>-0.006971351948228843</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.01837213640722357</v>
+        <v>-0.04310508241675126</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.0823752575279233</v>
+        <v>0.08276525938331858</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.02220179724977434</v>
+        <v>0.07503998788267796</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.02912121029240966</v>
+        <v>0.1282805467652781</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4528217956142466</v>
+        <v>0.7665787631452823</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1325849392185305</v>
+        <v>0.2088646233745823</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>97.83</v>
+        <v>113.06</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.01191799090714274</v>
+        <v>0.005782349215450511</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01717901415254974</v>
+        <v>-0.007897521350555436</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.0213084961277159</v>
+        <v>-0.02500863701944633</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.06668572680900975</v>
+        <v>-0.07743782339324834</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.02365264660049549</v>
+        <v>-0.08237968997077971</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.01771343072061371</v>
+        <v>0.06863462546371912</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0853813994023398</v>
+        <v>0.0830975317669751</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1080788695063124</v>
+        <v>0.166286351907605</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.23950182032987</v>
+        <v>0.4287679766229302</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.0741931772849469</v>
+        <v>0.1262995291678342</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>112.41</v>
+        <v>98.05</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.009777951143243202</v>
+        <v>0.002248811372640658</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.01876740522261899</v>
+        <v>-0.003151662837231894</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.02776335416206821</v>
+        <v>-0.02408677355969457</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.07777500840929663</v>
+        <v>-0.06885090018882933</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.07306005793860637</v>
+        <v>-0.03427554190268223</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.07307705333228953</v>
+        <v>-0.001260585408683124</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.07687068938109087</v>
+        <v>0.0878222174369685</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1542183623120366</v>
+        <v>0.123039569296187</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.4281761955124972</v>
+        <v>0.2349363842402268</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1261440071048985</v>
+        <v>0.07287270220741138</v>
       </c>
     </row>
     <row r="23">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>39.8</v>
+        <v>39.67</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.003005985405533318</v>
+        <v>-0.003266358557971527</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01801133886560147</v>
+        <v>-0.01391999452306947</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02115102345250741</v>
+        <v>-0.03243906905011429</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.07092227696163378</v>
+        <v>-0.0758588710111</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.05404965061784472</v>
+        <v>-0.05845470257387209</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.05397029520434993</v>
+        <v>0.0524302818519935</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.07563861503627645</v>
+        <v>0.07212519364076808</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.08302701481736996</v>
+        <v>0.08232810951034142</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3520872192350304</v>
+        <v>0.348067823837122</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1057787401095827</v>
+        <v>0.1046819239253447</v>
       </c>
     </row>
     <row r="24">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>67.41</v>
+        <v>67.94</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.00398931208405684</v>
+        <v>0.007862316429375626</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.01414175453803779</v>
+        <v>0.01478723731577491</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.002810574205625915</v>
+        <v>-0.009043102964781058</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.05495581197698329</v>
+        <v>-0.04658994660815818</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.07556218657699443</v>
+        <v>-0.09012984990721506</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.03421300009961059</v>
+        <v>0.03456683928361071</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.08237002221197565</v>
+        <v>0.09087995782027658</v>
       </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.24</v>
+        <v>13.33</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01194028746022147</v>
+        <v>0.006797594723847222</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.003762241601082073</v>
+        <v>0.01214881142636504</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.01341283935562321</v>
+        <v>-0.0118606263993174</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.05360972210652548</v>
+        <v>-0.04853678044729437</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.07087720904433936</v>
+        <v>-0.07623010105378691</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.01102232275025083</v>
+        <v>-0.02992168106808624</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1212582447917727</v>
+        <v>0.1288800127477869</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.06941314154196143</v>
+        <v>0.09208821295532554</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.07422555094780092</v>
+        <v>0.07489263968453153</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02415374956937577</v>
+        <v>0.02436570383342485</v>
       </c>
     </row>
     <row r="26">
@@ -1930,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>168.19</v>
+        <v>16.72</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.008605903375210056</v>
+        <v>0.005411915642197895</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01815528636862829</v>
+        <v>0.001797410325761195</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.04740595396989522</v>
+        <v>-0.0141509306647245</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.09463315619711588</v>
+        <v>-0.0580282076983385</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0464783546787384</v>
+        <v>-0.02165013668401694</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.08247151349404236</v>
+        <v>0.02194059122457959</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.1268614644218524</v>
+        <v>-0.01328705010130982</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.1259732443540131</v>
+        <v>0.01001722057241983</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.5218884422979915</v>
+        <v>0.4341351216801219</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1502553792759302</v>
+        <v>0.1277080758957447</v>
       </c>
     </row>
     <row r="27">
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>16.63</v>
+        <v>168.68</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.004787548060394164</v>
+        <v>0.002913313676570661</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.005382784466743784</v>
+        <v>-0.02310769407236646</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.007756626869921401</v>
+        <v>-0.04969018210827469</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.07302125609216592</v>
+        <v>-0.09613119124850944</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.04535022457332927</v>
+        <v>0.06577360284517075</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.02762875754626704</v>
+        <v>0.08507492089374047</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.01859831324115935</v>
+        <v>-0.1243177379846117</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.003928690648941635</v>
+        <v>-0.1177282352756205</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.4328772422733274</v>
+        <v>0.5236759714550547</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1273782753364341</v>
+        <v>0.1507055459888083</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.38</v>
+        <v>16.4</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01048735878441764</v>
+        <v>0.001221029230061177</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.007272778135357427</v>
+        <v>0.003058057241222656</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.01857407809295308</v>
+        <v>-0.02554963203357474</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.1019737189523846</v>
+        <v>-0.104803499360122</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.04932732357620417</v>
+        <v>0.05874757010060438</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.09345792131588215</v>
+        <v>0.09698995503441488</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.174811141260351</v>
+        <v>-0.1738035615435091</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1772978761275247</v>
+        <v>-0.1662430322867481</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1818181505419671</v>
+        <v>0.1824080572347611</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05726426101977822</v>
+        <v>0.05744014355595395</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>25.86</v>
+        <v>26.06</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.005384591909555314</v>
+        <v>0.007733907612931912</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.002699563979960518</v>
+        <v>0.003852094953637364</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02415092036409194</v>
+        <v>-0.02103686535072036</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.08718670384773419</v>
+        <v>-0.08561405382658305</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.103328693705604</v>
+        <v>-0.1023079969153909</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.01683686755149805</v>
+        <v>-0.02366725005337944</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.02320573755917432</v>
+        <v>-0.01565130097661505</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.05306977400234758</v>
+        <v>0.06460734741761365</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.118927512066579</v>
+        <v>1.128101377967933</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2844149935068663</v>
+        <v>0.2862659435400627</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>51.94</v>
+        <v>52.45</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01254752598019226</v>
+        <v>0.009819063336829137</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02624674769167545</v>
+        <v>0.0005723501534173892</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.03511059149277895</v>
+        <v>-0.03424784686649429</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.05563638860529119</v>
+        <v>-0.04653695031275173</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.02000002591115124</v>
+        <v>-0.009629877838927881</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.01422492243653217</v>
+        <v>-0.01373155488070588</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.1047008901071905</v>
+        <v>-0.09590989144174644</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.09376267929386783</v>
+        <v>-0.07881490819506132</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1799078483978758</v>
+        <v>0.1935938700830331</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.05669429646143898</v>
+        <v>0.06076421396808152</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>61.09</v>
+        <v>61.26</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.004562470004401464</v>
+        <v>0.002782749525629402</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.006181894591979487</v>
+        <v>0.0009803522523823549</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.01626406354831234</v>
+        <v>-0.02265478584443026</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.06718579714011286</v>
+        <v>-0.05521280411093077</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.06015384380634015</v>
+        <v>-0.04668539861448018</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.01050180323063965</v>
+        <v>0.00305270427662796</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.09339832436056195</v>
+        <v>-0.09087547897774151</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.06201535086383458</v>
+        <v>-0.04493042281565462</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.427444110692681</v>
+        <v>0.4236547592167113</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1259515532971016</v>
+        <v>0.1249543380226836</v>
       </c>
     </row>
     <row r="32">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>110.66</v>
+        <v>15.1</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.006910137673495464</v>
+        <v>0.01206436355598806</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.005571487454966162</v>
+        <v>-0.01371652726265771</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.01740364976622366</v>
+        <v>-0.03637521965852009</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.08302947147603434</v>
+        <v>-0.1361555619618805</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.1461419872640922</v>
+        <v>-0.08262447014871754</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.05708424519038746</v>
+        <v>-0.01282003002658505</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.06153080875488792</v>
+        <v>-0.11923256768924</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.08569704623428798</v>
+        <v>-0.133826088164792</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3382247584757347</v>
+        <v>0.2359415774670888</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1019867012655453</v>
+        <v>0.07316371636132168</v>
       </c>
     </row>
     <row r="33">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>14.92</v>
+        <v>112.17</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.0006698076810064402</v>
+        <v>0.01364535023373548</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.02864580665482153</v>
+        <v>0.007726175808231872</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.04420240842786638</v>
+        <v>-0.02077699536801525</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.1498575085526386</v>
+        <v>-0.06509422378289131</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1039038787911419</v>
+        <v>-0.1487440651742613</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.02216443383930533</v>
+        <v>-0.04992285247520545</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.1297317028289365</v>
+        <v>-0.04872506795677789</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.1454007306023674</v>
+        <v>-0.06639364837498718</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2167434936836448</v>
+        <v>0.3500872320217507</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.06757815242349352</v>
+        <v>0.1052332539324308</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>118.3</v>
+        <v>118.8</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.009378622796518798</v>
+        <v>0.004226542579049974</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.04496649367336769</v>
+        <v>-0.02822083393245145</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.06496991629314175</v>
+        <v>-0.06020093655477532</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.07614213016503446</v>
+        <v>-0.07455006956020638</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1472995927051191</v>
+        <v>-0.1505276035974347</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1320728968809224</v>
+        <v>-0.1325167406368144</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.0857392756771953</v>
+        <v>-0.08187511379749191</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07758512687606789</v>
+        <v>-0.0655704847245161</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.3925037944961418</v>
+        <v>0.397684605111239</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1166887196594795</v>
+        <v>0.1180718859116741</v>
       </c>
     </row>
   </sheetData>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1016884975042718</v>
+        <v>0.09722223017746368</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1498575085526386</v>
+        <v>-0.1361555619618805</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.08421233184310495</v>
+        <v>0.07712894027685246</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1019737189523846</v>
+        <v>-0.1084485595142929</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.06753244329787012</v>
+        <v>0.06374680202721561</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.09499239721123243</v>
+        <v>-0.104803499360122</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.06161540290545942</v>
+        <v>0.06354436429240762</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09463315619711588</v>
+        <v>-0.09613119124850944</v>
       </c>
     </row>
     <row r="21">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.05907569870773033</v>
+        <v>0.05378341291467503</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08718670384773419</v>
+        <v>-0.08561405382658305</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.03044653703621369</v>
+        <v>0.02680962576976276</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.08302947147603434</v>
+        <v>-0.08248732054917596</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.006295577605578528</v>
+        <v>-0.003988926430488204</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.07777500840929663</v>
+        <v>-0.07743782339324834</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01000438493829003</v>
+        <v>-0.006971351948228843</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.07614213016503446</v>
+        <v>-0.0758588710111</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.0100950623182029</v>
+        <v>-0.01770494805007683</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07560140663391801</v>
+        <v>-0.07455006956020638</v>
       </c>
     </row>
     <row r="26">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.01074085653752743</v>
+        <v>-0.01816991737105234</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07302125609216592</v>
+        <v>-0.06885090018882933</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3013192007696226</v>
+        <v>0.3188172141697132</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1472995927051191</v>
+        <v>-0.1505276035974347</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2744057640517945</v>
+        <v>0.2598684254231856</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1461419872640922</v>
+        <v>-0.1487440651742613</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2476400171883311</v>
+        <v>0.2143620128882793</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1039038787911419</v>
+        <v>-0.1023079969153909</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1805139467564376</v>
+        <v>0.1664498721505974</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.103328693705604</v>
+        <v>-0.09012984990721506</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1607510243904162</v>
+        <v>0.1552499962740392</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.07917930378163773</v>
+        <v>-0.0868085495969082</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1442197946845736</v>
+        <v>0.1162443708698688</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.07556218657699443</v>
+        <v>-0.08262447014871754</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.06452796529779281</v>
+        <v>0.07463230596900527</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.07306005793860637</v>
+        <v>-0.08237968997077971</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.06149342327752882</v>
+        <v>0.06577360284517075</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.07087720904433936</v>
+        <v>-0.07623010105378691</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.04932732357620417</v>
+        <v>0.05874757010060438</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.06015384380634015</v>
+        <v>-0.05845470257387209</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0464783546787384</v>
+        <v>0.03842009623583897</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.05404965061784472</v>
+        <v>-0.05658599229052241</v>
       </c>
     </row>
     <row r="41"/>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.494253397080755</v>
+        <v>0.494670341200514</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1320728968809224</v>
+        <v>-0.1325167406368144</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4807790745991607</v>
+        <v>0.4891013856229474</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.05708424519038746</v>
+        <v>-0.04992285247520545</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4638548758954113</v>
+        <v>0.4612829287670863</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.02216443383930533</v>
+        <v>-0.02992168106808624</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.429562521388525</v>
+        <v>0.4250422029408816</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.01683686755149805</v>
+        <v>-0.02366725005337944</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2964819251994251</v>
+        <v>0.2707935645744326</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01422492243653217</v>
+        <v>-0.01373155488070588</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2801137397107469</v>
+        <v>0.2655630893526155</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01102232275025083</v>
+        <v>-0.01282003002658505</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.267508011024129</v>
+        <v>0.2653960640759456</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.01050180323063965</v>
+        <v>-0.001260585408683124</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2469017415133465</v>
+        <v>0.2187293738637133</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.01771343072061371</v>
+        <v>0.00305270427662796</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2269425622012269</v>
+        <v>0.2066260781611904</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.02762875754626704</v>
+        <v>0.0186140524366869</v>
       </c>
     </row>
     <row r="54">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1831663483843711</v>
+        <v>0.1916432679079685</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.03421300009961059</v>
+        <v>0.02194059122457959</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8639287376899445</v>
+        <v>0.8866807328157909</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1772978761275247</v>
+        <v>-0.1662430322867481</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7629263727878655</v>
+        <v>0.790848784073902</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1454007306023674</v>
+        <v>-0.133826088164792</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5071048071673974</v>
+        <v>0.5197252206684657</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1259732443540131</v>
+        <v>-0.1177282352756205</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4700996382350939</v>
+        <v>0.4597343772311067</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09376267929386783</v>
+        <v>-0.07881490819506132</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4304811118581353</v>
+        <v>0.4520929513620402</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.08569704623428798</v>
+        <v>-0.06639364837498718</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4211448948210701</v>
+        <v>0.4512520986661472</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.07758512687606789</v>
+        <v>-0.0655704847245161</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3580328773332477</v>
+        <v>0.3757751598842531</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06201535086383458</v>
+        <v>-0.04493042281565462</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3458013217699889</v>
+        <v>0.34021998106219</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.003928690648941635</v>
+        <v>0.01001722057241983</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2943781181546894</v>
+        <v>0.2968644962464906</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.02912121029240966</v>
+        <v>0.03216352860512739</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1882578684881846</v>
+        <v>0.2001292060659492</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.03381291072569104</v>
+        <v>0.03808937909214749</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.873922270366081</v>
+        <v>2.882055805833148</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.003961240289918289</v>
+        <v>0.004036156197315455</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.375643390470677</v>
+        <v>2.419647224281389</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.07422555094780092</v>
+        <v>0.07489263968453153</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.30872757797917</v>
+        <v>2.359743538059859</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1630359260440251</v>
+        <v>0.1749919935660043</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.751824183499994</v>
+        <v>1.757107970044283</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1799078483978758</v>
+        <v>0.1824080572347611</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.148094047107517</v>
+        <v>1.14954184928331</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1818181505419671</v>
+        <v>0.1935938700830331</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.118927512066579</v>
+        <v>1.128101377967933</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5319,21 +5319,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2167434936836448</v>
+        <v>0.2349363842402268</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.0110885075381</v>
+        <v>1.023608664767277</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.23950182032987</v>
+        <v>0.2359415774670888</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9016808699012293</v>
+        <v>0.9129188897862208</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3184205065660479</v>
+        <v>0.3077273445705686</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8614402335384506</v>
+        <v>0.8718790414029898</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3382247584757347</v>
+        <v>0.3389247178441681</v>
       </c>
     </row>
     <row r="82">
@@ -5477,21 +5477,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7613216708854755</v>
+        <v>0.7679070940500972</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3449940792845017</v>
+        <v>0.348067823837122</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,14 +490,14 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>225.95</v>
+        <v>221.81</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.01422927635476712</v>
+        <v>-0.01832263529791844</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.02392712567684208</v>
+        <v>-0.02018732761572495</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.02230564012524328</v>
+        <v>0.03950694761869067</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.06354436429240762</v>
+        <v>0.04410654777586842</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.04424519500797952</v>
+        <v>-0.01132163350042392</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.494670341200514</v>
+        <v>0.5568811354271337</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7865018294988066</v>
+        <v>0.7350617579547467</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8866807328157909</v>
+        <v>0.8626854823885952</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.419647224281389</v>
+        <v>2.36054970780648</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5065854491922832</v>
+        <v>0.4978561533788533</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>64.38</v>
+        <v>63.84</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01019924236388636</v>
+        <v>-0.008387653368553183</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.04853413116419958</v>
+        <v>0.004405267042906891</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.0569692565210751</v>
+        <v>0.1125827634057388</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.07712894027685246</v>
+        <v>0.07240049490459466</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.0868085495969082</v>
+        <v>-0.04115352362740232</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4612829287670863</v>
+        <v>0.5449436485573176</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5972624517832839</v>
+        <v>0.5817113298681487</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.790848784073902</v>
+        <v>0.7741052284312713</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.882055805833148</v>
+        <v>2.805422712807148</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5716430802804682</v>
+        <v>0.5612326867735029</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>58.46</v>
+        <v>57.89</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.006716021899397351</v>
+        <v>-0.009750251518146458</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.04355584803232238</v>
+        <v>0.003119048830902083</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.05829104468077984</v>
+        <v>0.06356786818065929</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.09722223017746368</v>
+        <v>0.0590925640551252</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.07463230596900527</v>
+        <v>0.09308913123869766</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.4891013856229474</v>
+        <v>0.5481590133252427</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4388580950624763</v>
+        <v>0.4211112927824234</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5197252206684657</v>
+        <v>0.4996148566609639</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.757107970044283</v>
+        <v>1.732395329860474</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.402225706324888</v>
+        <v>0.3980236279225515</v>
       </c>
     </row>
     <row r="5">
@@ -777,34 +777,34 @@
         <v>89.89</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.006850101999211544</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.03031281177023848</v>
+        <v>-0.007069473083819333</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.04514552822981355</v>
+        <v>-0.03364864939125189</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.003988926430488204</v>
+        <v>-0.01024003862916534</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1552499962740392</v>
+        <v>0.1573323227602319</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.06109638724788957</v>
+        <v>0.02911078989296589</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4783758554461683</v>
+        <v>0.4822472823827244</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4512520986661472</v>
+        <v>0.4369304926034507</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5570592747223819</v>
+        <v>0.5182317319457561</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1590487829048921</v>
+        <v>0.1493333835260315</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>24.53</v>
+        <v>24.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.005271661053162791</v>
+        <v>-0.009376332782174646</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.03371264896087678</v>
+        <v>-0.005728367182397442</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.05641694280919274</v>
+        <v>0.007880490331775736</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.06374680202721561</v>
+        <v>-0.01018329970546805</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.3188172141697132</v>
+        <v>0.250643276139707</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4250422029408816</v>
+        <v>0.476666425195664</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.04903575761901369</v>
+        <v>0.03838907116563073</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.04876859575031633</v>
+        <v>0.03139329434770444</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4596041196003335</v>
+        <v>0.457569484598169</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1343446492879437</v>
+        <v>0.1338173258079332</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>65.11</v>
+        <v>30.14</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.003545058055955508</v>
+        <v>0.006008021050610379</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.02791882133264256</v>
+        <v>0.01379077880003443</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.03483543590296301</v>
+        <v>0.029723229186148</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.1084485595142929</v>
+        <v>0.0210026735186486</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2598684254231856</v>
+        <v>0.09599997780539771</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1113954755237296</v>
+        <v>0.3130474306231268</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.09300880711126358</v>
+        <v>0.1785512567440042</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.34021998106219</v>
+        <v>0.3617594073147201</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.359743538059859</v>
+        <v>0.5391808290360343</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.497736369118118</v>
+        <v>0.1545955566341883</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="F8" s="5" t="n">
-        <v>29.96</v>
+        <v>57.4</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.001000356347931719</v>
+        <v>0.01020770563480866</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.01524902921384608</v>
+        <v>0.04230982102717662</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03596123808558382</v>
+        <v>0.1015160401759139</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.01770494805007683</v>
+        <v>0.07955620655642948</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1162443708698688</v>
+        <v>0.2081667765469739</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2707935645744326</v>
+        <v>0.3186660314802858</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1670552970630121</v>
+        <v>0.08192129454367336</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3757751598842531</v>
+        <v>0.2033085040918468</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5237300162629703</v>
+        <v>0.3535313592509419</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1507191510085304</v>
+        <v>0.1061722874838298</v>
       </c>
     </row>
     <row r="9">
@@ -984,12 +984,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>56.82</v>
+        <v>28.97</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.0001760009837796783</v>
+        <v>0.00172888094497381</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.04256880173989397</v>
+        <v>-0.006515793383122359</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1071706943239654</v>
+        <v>-0.01696640691041418</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.05378341291467503</v>
+        <v>-0.04389438802623147</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2143620128882793</v>
+        <v>0.01613465734057273</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2655630893526155</v>
+        <v>0.2425361717973855</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.07718170918508838</v>
+        <v>0.1743924442373972</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2001292060659492</v>
+        <v>0.4237258092304417</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.3389247178441681</v>
+        <v>1.001349682904236</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1021787994078256</v>
+        <v>0.2602044018155099</v>
       </c>
     </row>
     <row r="10">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>28.92</v>
+        <v>34.99</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.002758618058829487</v>
+        <v>-0.0002856663295200956</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.001036293121066678</v>
+        <v>0.002578800821001481</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.01498639390022649</v>
+        <v>0.01567491737498794</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.08248732054917596</v>
+        <v>-0.004268574666675407</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.03842009623583897</v>
+        <v>0.004017308765441374</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2066260781611904</v>
+        <v>0.1975446494871076</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1651147079123463</v>
+        <v>0.1469926768138119</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4520929513620402</v>
+        <v>0.4399509258507031</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.023608664767277</v>
+        <v>0.7657262435052801</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2648591790765253</v>
+        <v>0.2086701331958789</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>35</v>
+        <v>15.06</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.003728163811222984</v>
+        <v>-0.01697123240122245</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01773773251462107</v>
+        <v>-0.02461134527810449</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.03214391499536018</v>
+        <v>-0.001326227068338071</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.04917145628264863</v>
+        <v>0.01619438122365802</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.03642284647803584</v>
+        <v>-0.005284010692994334</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1618106464571165</v>
+        <v>0.2288392386771552</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1456717459349433</v>
+        <v>0.2845548024237707</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4597343772311067</v>
+        <v>0.274855107487797</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7547813279457798</v>
+        <v>0.8914942584907781</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2061676274695716</v>
+        <v>0.2367113382668937</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>15.32</v>
+        <v>61.99</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.005909399559619111</v>
+        <v>-0.04791888961200119</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.01122112743065773</v>
+        <v>-0.06132645640391432</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.0006523306543773089</v>
+        <v>-0.05517449928683016</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.02680962576976276</v>
+        <v>-0.1049667951708115</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.007894729412163404</v>
+        <v>0.1787412340483963</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2187293738637133</v>
+        <v>0.06487837320064349</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.3041036906426111</v>
+        <v>0.03621988770011741</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2968644962464906</v>
+        <v>0.2482751659617695</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.9129188897862208</v>
+        <v>2.37778876664296</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2413631578978561</v>
+        <v>0.5004130368703619</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>44.85</v>
+        <v>44.5</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.006204356024089863</v>
+        <v>-0.007803756656157845</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.007186159972970785</v>
+        <v>-0.01700906671034985</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.006733989723864742</v>
+        <v>-0.02326605226821676</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.01816991737105234</v>
+        <v>-0.03596186856367967</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1664498721505974</v>
+        <v>0.1234536560034918</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2653960640759456</v>
+        <v>0.3062058114216062</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.01819414086812854</v>
+        <v>0.009692099256056519</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.03216352860512739</v>
+        <v>0.02036254010566796</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3077273445705686</v>
+        <v>0.3105496285482887</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09355106608906905</v>
+        <v>0.09433718664977153</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>68.08</v>
+        <v>67.2</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.002929070764758568</v>
+        <v>-0.0129260408217422</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.003075107360628326</v>
+        <v>-0.02552207307999743</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.03977432488199462</v>
+        <v>-0.05178503818411162</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.01972635244618504</v>
+        <v>-0.03253674296024689</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.03554795874185901</v>
+        <v>0.002108195362015675</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.0186140524366869</v>
+        <v>0.02767308189520401</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1698097649304788</v>
+        <v>0.1620515292693105</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1634316858000591</v>
+        <v>0.143851868185926</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7679070940500972</v>
+        <v>0.7589449091964584</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2091675384343257</v>
+        <v>0.207120834605935</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>16.61</v>
+        <v>92.33</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.00850038268572062</v>
+        <v>0.003805158309930778</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01890134016869394</v>
+        <v>0.005554368742382243</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.04977110724646283</v>
+        <v>-0.0146210796350853</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.06369781146256337</v>
+        <v>-0.02871865976912458</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.0272109172530357</v>
+        <v>-0.01003521273659558</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1451989038555148</v>
+        <v>0.0599165423355621</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03438227116148895</v>
+        <v>0.1095705042343718</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.09699464806552616</v>
+        <v>0.1514242858590409</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8718790414029898</v>
+        <v>0.1996214146179041</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2324214842514689</v>
+        <v>0.06254680548385516</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>91.98</v>
+        <v>16.41</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.004367782462123326</v>
+        <v>-0.01204098468333648</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.0009774773345164744</v>
+        <v>-0.03527339055827683</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.006480864789957574</v>
+        <v>-0.05581124051744246</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.04485980849348858</v>
+        <v>-0.07653351577474954</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.0002342682058322776</v>
+        <v>0.01046798514100233</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.05879219732874597</v>
+        <v>0.163013232173294</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1070139545612021</v>
+        <v>0.02236640327877226</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1519371907740708</v>
+        <v>0.07581192948549864</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1749919935660043</v>
+        <v>0.8708022382481588</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.05522475047182818</v>
+        <v>0.2321851210637955</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>36.51</v>
+        <v>109.88</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.0110772003439672</v>
+        <v>-0.004439661873427259</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01083721288356909</v>
+        <v>-0.01071398617696862</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.04298828673003363</v>
+        <v>-0.05373755895254428</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.03769110060455005</v>
+        <v>-0.04535187914773764</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.0359123487908658</v>
+        <v>-0.078342592448013</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1296817150797744</v>
+        <v>0.2339134585941935</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06952301856329623</v>
+        <v>0.06390393640713432</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1585470391455572</v>
+        <v>0.09406444107547496</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.14954184928331</v>
+        <v>0.01130246474496932</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2905711969328317</v>
+        <v>0.003753382740588007</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>110.37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.01275462788430914</v>
+        <v>-0.01396873034728163</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.007553244715455709</v>
+        <v>-0.02571043960281316</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.0326057823710626</v>
+        <v>-0.05138341828029025</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.0475491425391229</v>
+        <v>-0.05263157894736847</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.05658599229052241</v>
+        <v>-0.04937942922175032</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1916432679079685</v>
+        <v>0.1418871480064161</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0750394712260225</v>
+        <v>0.05697507628115539</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1124658564494398</v>
+        <v>0.1344942087165373</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.004036156197315455</v>
+        <v>1.1404907541312</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.001343579385062244</v>
+        <v>0.2887572419603339</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>91.92</v>
+        <v>50.65</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.005029511142327969</v>
+        <v>-0.01228543815161542</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.03017514926341491</v>
+        <v>-0.01247805377704114</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.03698270185604113</v>
+        <v>0.006558065044834027</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.06461787616809822</v>
+        <v>-0.01497465325721148</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.034436164051042</v>
+        <v>-0.03962836719895702</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.09391688215468652</v>
+        <v>0.1130482703675075</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.02734297257874974</v>
+        <v>0.06436400662654584</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.03808937909214749</v>
+        <v>0.1017905349000625</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4582098403830419</v>
+        <v>0.7614428300265803</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.133983341949238</v>
+        <v>0.2076919849629899</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>51.28</v>
+        <v>91.73</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.005687332639421117</v>
+        <v>-0.002066958396392815</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.009647526185015964</v>
+        <v>-0.02300560279855524</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.00523764232317514</v>
+        <v>-0.0540373084232858</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.006971351948228843</v>
+        <v>-0.06502902062712679</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.04310508241675126</v>
+        <v>0.002294653863310625</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.08276525938331858</v>
+        <v>0.1137673047182033</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.07503998788267796</v>
+        <v>0.02814002646277913</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1282805467652781</v>
+        <v>0.02390812377677176</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7665787631452823</v>
+        <v>0.4735915085137068</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2088646233745823</v>
+        <v>0.1379566115351376</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>113.06</v>
+        <v>112.72</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.005782349215450511</v>
+        <v>-0.00300722046021995</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.007897521350555436</v>
+        <v>-0.01035996742201695</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.02500863701944633</v>
+        <v>-0.03369052939364003</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.07743782339324834</v>
+        <v>-0.06958316301279655</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.08237968997077971</v>
+        <v>-0.08957270460038758</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.06863462546371912</v>
+        <v>0.1006118294475968</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0830975317669751</v>
+        <v>0.08210094237561383</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.166286351907605</v>
+        <v>0.1570737220758671</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.4287679766229302</v>
+        <v>0.4230105985830031</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1262995291678342</v>
+        <v>0.1247846431777049</v>
       </c>
     </row>
     <row r="22">
@@ -1712,52 +1712,46 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>98.05</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.002248811372640658</v>
+        <v>-0.01162792003442548</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.003151662837231894</v>
+        <v>-0.004447671400096276</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.02408677355969457</v>
+        <v>0.001192810964942614</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.06885090018882933</v>
+        <v>-0.04616477172667821</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.03427554190268223</v>
+        <v>-0.08440135152847972</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>-0.001260585408683124</v>
+        <v>0.06875695637317314</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0878222174369685</v>
-      </c>
-      <c r="N22" s="6" t="n">
-        <v>0.123039569296187</v>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>0.2349363842402268</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>0.07287270220741138</v>
-      </c>
+        <v>0.08062443169359046</v>
+      </c>
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1768,51 +1762,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>39.67</v>
+        <v>96.94</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.003266358557971527</v>
+        <v>-0.01132076058952924</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01391999452306947</v>
+        <v>-0.01091724998982202</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.03243906905011429</v>
+        <v>-0.02041225405976543</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.0758588710111</v>
+        <v>-0.07101098362308578</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.05845470257387209</v>
+        <v>-0.03991283282732649</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0524302818519935</v>
+        <v>-0.002913308187985075</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.07212519364076808</v>
+        <v>0.07010665172046271</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.08232810951034142</v>
+        <v>0.09717032721979968</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.348067823837122</v>
+        <v>0.2265303756462367</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1046819239253447</v>
+        <v>0.07043286869025112</v>
       </c>
     </row>
     <row r="24">
@@ -1824,46 +1818,52 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>67.94</v>
+        <v>39.54</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.007862316429375626</v>
+        <v>-0.003276966458741426</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.01478723731577491</v>
+        <v>-0.0258684216090993</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.009043102964781058</v>
+        <v>-0.02897839562381543</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.04658994660815818</v>
+        <v>-0.0600102422249007</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.09012984990721506</v>
+        <v>-0.07487603636242901</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.03456683928361071</v>
+        <v>0.05553594103191895</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.09087995782027658</v>
-      </c>
-      <c r="N24" s="6" t="inlineStr"/>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr"/>
+        <v>0.06748646328361363</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0.06922212482074186</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0.3629315277456446</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0.1087271419120219</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.33</v>
+        <v>13.29</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.006797594723847222</v>
+        <v>-0.003000747342983168</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.01214881142636504</v>
+        <v>0.01373000075435571</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.0118606263993174</v>
+        <v>-0.003000747342983168</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.04853678044729437</v>
+        <v>-0.05274410443352529</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.07623010105378691</v>
+        <v>-0.07900210112357764</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.02992168106808624</v>
+        <v>-0.02235031738103122</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1288800127477869</v>
+        <v>0.1228772673671166</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.09208821295532554</v>
+        <v>0.07937305226126479</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.07489263968453153</v>
+        <v>0.07386317181972579</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02436570383342485</v>
+        <v>0.02403857397991183</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.72</v>
+        <v>16.68</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.005411915642197895</v>
+        <v>-0.002392285276397343</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.001797410325761195</v>
+        <v>-0.008912633345826149</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.0141509306647245</v>
+        <v>-0.02112679524703076</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.0580282076983385</v>
+        <v>-0.05173393061501641</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.02165013668401694</v>
+        <v>-0.03750719107858314</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.02194059122457959</v>
+        <v>0.04895063542777245</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.01328705010130982</v>
+        <v>-0.01874226197515794</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.01001722057241983</v>
+        <v>0.003566541141341473</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4341351216801219</v>
+        <v>0.4478434020211739</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1277080758957447</v>
+        <v>0.1312897800663071</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>168.68</v>
+        <v>166.04</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.002913313676570661</v>
+        <v>-0.01565093374602378</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02310769407236646</v>
+        <v>-0.05049466505181377</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.04969018210827469</v>
+        <v>-0.06223881409923848</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.09613119124850944</v>
+        <v>-0.1108493713083296</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.06577360284517075</v>
+        <v>0.05108559855079653</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.08507492089374047</v>
+        <v>0.09422641953784372</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.1243177379846117</v>
+        <v>-0.1367651244636909</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1177282352756205</v>
+        <v>-0.1365312695650518</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5236759714550547</v>
+        <v>0.5066205424145589</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1507055459888083</v>
+        <v>0.1463959106725001</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.4</v>
+        <v>16.27</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.001221029230061177</v>
+        <v>-0.007926778279904068</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.003058057241222656</v>
+        <v>-0.01751201796685609</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.02554963203357474</v>
+        <v>-0.04909410418604487</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.104803499360122</v>
+        <v>-0.1011049660297001</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.05874757010060438</v>
+        <v>0.02327049359184818</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.09698995503441488</v>
+        <v>0.1441631611982521</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1738035615435091</v>
+        <v>-0.1803526375268002</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1662430322867481</v>
+        <v>-0.1741116838750817</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1824080572347611</v>
+        <v>0.1824128042973008</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05744014355595395</v>
+        <v>0.05744155867028922</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>26.06</v>
+        <v>25.49</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.007733907612931912</v>
+        <v>-0.02187259042614897</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.003852094953637364</v>
+        <v>-0.02784132575718723</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02103686535072036</v>
+        <v>-0.03006091685259327</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.08561405382658305</v>
+        <v>-0.0980184159705958</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.1023079969153909</v>
+        <v>-0.1210344906510978</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.02366725005337944</v>
+        <v>0.001361388623889237</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.01565130097661505</v>
+        <v>-0.0283254372647902</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.06460734741761365</v>
+        <v>0.0277659280020186</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.128101377967933</v>
+        <v>1.088610555452277</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2862659435400627</v>
+        <v>0.2782598740752413</v>
       </c>
     </row>
     <row r="30">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>52.45</v>
+        <v>60.46</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.009819063336829137</v>
+        <v>-0.01305908029676428</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.0005723501534173892</v>
+        <v>-0.02468144140292239</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.03424784686649429</v>
+        <v>-0.03418529459762076</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.04653695031275173</v>
+        <v>-0.06263567310895102</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.009629877838927881</v>
+        <v>-0.07141762374887184</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.01373155488070588</v>
+        <v>0.03628725585579939</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.09590989144174644</v>
+        <v>-0.1005897355082609</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.07881490819506132</v>
+        <v>-0.07051461521472391</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1935938700830331</v>
+        <v>0.4210235868261363</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.06076421396808152</v>
+        <v>0.1242608706966921</v>
       </c>
     </row>
     <row r="31">
@@ -2210,51 +2210,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="F31" s="5" t="n">
-        <v>61.26</v>
+        <v>51.38</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.002782749525629402</v>
+        <v>-0.02040037520038074</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.0009803522523823549</v>
+        <v>-0.02689390510347978</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02265478584443026</v>
+        <v>-0.05429782189429733</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.05521280411093077</v>
+        <v>-0.05862954663953002</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.04668539861448018</v>
+        <v>-0.03962614825952837</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.00305270427662796</v>
+        <v>-0.0006892586715084859</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.09087547897774151</v>
+        <v>-0.1136038368981345</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.04493042281565462</v>
+        <v>-0.1059909409372767</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4236547592167113</v>
+        <v>0.1706199654888121</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1249543380226836</v>
+        <v>0.05391432844054656</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>15.1</v>
+        <v>15.08</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01206436355598806</v>
+        <v>-0.001324533593271671</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01371652726265771</v>
+        <v>-0.02077920147732826</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03637521965852009</v>
+        <v>-0.047378395680018</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.1361555619618805</v>
+        <v>-0.1201866709042302</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.08262447014871754</v>
+        <v>-0.09754633453458639</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.01282003002658505</v>
+        <v>0.02459629676355113</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.11923256768924</v>
+        <v>-0.1199126442728656</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.133826088164792</v>
+        <v>-0.1404190627530834</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2359415774670888</v>
+        <v>0.2305414077572892</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07316371636132168</v>
+        <v>0.0715984516755066</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>112.17</v>
+        <v>111.28</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.01364535023373548</v>
+        <v>-0.007934379996226482</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.007726175808231872</v>
+        <v>-0.004740173426970418</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.02077699536801525</v>
+        <v>-0.01504695102783771</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.06509422378289131</v>
+        <v>-0.05534808237310695</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1487440651742613</v>
+        <v>-0.1443291336563121</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.04992285247520545</v>
+        <v>-0.01987499748848587</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.04872506795677789</v>
+        <v>-0.05984418583275286</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.06639364837498718</v>
+        <v>-0.08335557014966644</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3500872320217507</v>
+        <v>0.3439853129692438</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1052332539324308</v>
+        <v>0.1035656506564331</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>118.8</v>
+        <v>117.93</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.004226542579049974</v>
+        <v>-0.007323255254488514</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02822083393245145</v>
+        <v>-0.03193235428824015</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.06020093655477532</v>
+        <v>-0.05185718837974118</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.07455006956020638</v>
+        <v>-0.06848339868438136</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1505276035974347</v>
+        <v>-0.1605158454299381</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1325167406368144</v>
+        <v>-0.1416307599561434</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.08187511379749191</v>
+        <v>-0.08725904570270737</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.0655704847245161</v>
+        <v>-0.08670735088120241</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.397684605111239</v>
+        <v>0.4874413556884669</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1180718859116741</v>
+        <v>0.1415106053262718</v>
       </c>
     </row>
   </sheetData>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.09722223017746368</v>
+        <v>0.07955620655642948</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1361555619618805</v>
+        <v>-0.1201866709042302</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.07712894027685246</v>
+        <v>0.07240049490459466</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1084485595142929</v>
+        <v>-0.1108493713083296</v>
       </c>
     </row>
     <row r="19">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.06374680202721561</v>
+        <v>0.0590925640551252</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.104803499360122</v>
+        <v>-0.1049667951708115</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.06354436429240762</v>
+        <v>0.04410654777586842</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09613119124850944</v>
+        <v>-0.1011049660297001</v>
       </c>
     </row>
     <row r="21">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.05378341291467503</v>
+        <v>0.0210026735186486</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08561405382658305</v>
+        <v>-0.0980184159705958</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.02680962576976276</v>
+        <v>0.01619438122365802</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.08248732054917596</v>
+        <v>-0.07653351577474954</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.003988926430488204</v>
+        <v>-0.004268574666675407</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.07743782339324834</v>
+        <v>-0.07101098362308578</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.006971351948228843</v>
+        <v>-0.01018329970546805</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.0758588710111</v>
+        <v>-0.06958316301279655</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.01770494805007683</v>
+        <v>-0.01024003862916534</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07455006956020638</v>
+        <v>-0.06848339868438136</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.01816991737105234</v>
+        <v>-0.01497465325721148</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06885090018882933</v>
+        <v>-0.06502902062712679</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3188172141697132</v>
+        <v>0.250643276139707</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1505276035974347</v>
+        <v>-0.1605158454299381</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2598684254231856</v>
+        <v>0.2081667765469739</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1487440651742613</v>
+        <v>-0.1443291336563121</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2143620128882793</v>
+        <v>0.1787412340483963</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1023079969153909</v>
+        <v>-0.1210344906510978</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1664498721505974</v>
+        <v>0.1573323227602319</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.09012984990721506</v>
+        <v>-0.09754633453458639</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1552499962740392</v>
+        <v>0.1234536560034918</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.0868085495969082</v>
+        <v>-0.08957270460038758</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1162443708698688</v>
+        <v>0.09599997780539771</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08262447014871754</v>
+        <v>-0.08440135152847972</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.07463230596900527</v>
+        <v>0.09308913123869766</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.08237968997077971</v>
+        <v>-0.07900210112357764</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.06577360284517075</v>
+        <v>0.05108559855079653</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.07623010105378691</v>
+        <v>-0.078342592448013</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.05874757010060438</v>
+        <v>0.02327049359184818</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.05845470257387209</v>
+        <v>-0.07487603636242901</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.03842009623583897</v>
+        <v>0.01613465734057273</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.05658599229052241</v>
+        <v>-0.07141762374887184</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.494670341200514</v>
+        <v>0.5568811354271337</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1325167406368144</v>
+        <v>-0.1416307599561434</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4891013856229474</v>
+        <v>0.5481590133252427</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.04992285247520545</v>
+        <v>-0.02235031738103122</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4612829287670863</v>
+        <v>0.5449436485573176</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.02992168106808624</v>
+        <v>-0.01987499748848587</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4250422029408816</v>
+        <v>0.476666425195664</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.02366725005337944</v>
+        <v>-0.002913308187985075</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E49" s="11" t="n">
-        <v>0.2707935645744326</v>
+        <v>0.3186660314802858</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01373155488070588</v>
+        <v>-0.0006892586715084859</v>
       </c>
     </row>
     <row r="50">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2655630893526155</v>
+        <v>0.3130474306231268</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01282003002658505</v>
+        <v>0.001361388623889237</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2653960640759456</v>
+        <v>0.3062058114216062</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.001260585408683124</v>
+        <v>0.02459629676355113</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2187293738637133</v>
+        <v>0.2425361717973855</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.00305270427662796</v>
+        <v>0.02767308189520401</v>
       </c>
     </row>
     <row r="53">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2066260781611904</v>
+        <v>0.2339134585941935</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.0186140524366869</v>
+        <v>0.02911078989296589</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1916432679079685</v>
+        <v>0.2288392386771552</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.02194059122457959</v>
+        <v>0.03628725585579939</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8866807328157909</v>
+        <v>0.8626854823885952</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1662430322867481</v>
+        <v>-0.1741116838750817</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.790848784073902</v>
+        <v>0.7741052284312713</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.133826088164792</v>
+        <v>-0.1404190627530834</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5197252206684657</v>
+        <v>0.4996148566609639</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1177282352756205</v>
+        <v>-0.1365312695650518</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4597343772311067</v>
+        <v>0.4399509258507031</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.07881490819506132</v>
+        <v>-0.1059909409372767</v>
       </c>
     </row>
     <row r="63">
@@ -4741,21 +4741,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4520929513620402</v>
+        <v>0.4369304926034507</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4763,21 +4763,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.06639364837498718</v>
+        <v>-0.08670735088120241</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4512520986661472</v>
+        <v>0.4237258092304417</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4808,21 +4808,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.0655704847245161</v>
+        <v>-0.08335557014966644</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3757751598842531</v>
+        <v>0.3617594073147201</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.04493042281565462</v>
+        <v>-0.07051461521472391</v>
       </c>
     </row>
     <row r="66">
@@ -4876,21 +4876,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.34021998106219</v>
+        <v>0.274855107487797</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.01001722057241983</v>
+        <v>0.003566541141341473</v>
       </c>
     </row>
     <row r="67">
@@ -4921,21 +4921,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2968644962464906</v>
+        <v>0.2482751659617695</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.03216352860512739</v>
+        <v>0.02036254010566796</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2001292060659492</v>
+        <v>0.2033085040918468</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.03808937909214749</v>
+        <v>0.02390812377677176</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.882055805833148</v>
+        <v>2.805422712807148</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.004036156197315455</v>
+        <v>0.01130246474496932</v>
       </c>
     </row>
     <row r="74">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.419647224281389</v>
+        <v>2.37778876664296</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.07489263968453153</v>
+        <v>0.07386317181972579</v>
       </c>
     </row>
     <row r="75">
@@ -5162,21 +5162,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.359743538059859</v>
+        <v>2.36054970780648</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5184,21 +5184,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1749919935660043</v>
+        <v>0.1706199654888121</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.757107970044283</v>
+        <v>1.732395329860474</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1824080572347611</v>
+        <v>0.1824128042973008</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.14954184928331</v>
+        <v>1.1404907541312</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1935938700830331</v>
+        <v>0.1996214146179041</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.128101377967933</v>
+        <v>1.088610555452277</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2349363842402268</v>
+        <v>0.2265303756462367</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.023608664767277</v>
+        <v>1.001349682904236</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2359415774670888</v>
+        <v>0.2305414077572892</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9129188897862208</v>
+        <v>0.8914942584907781</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3077273445705686</v>
+        <v>0.3105496285482887</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8718790414029898</v>
+        <v>0.8708022382481588</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3389247178441681</v>
+        <v>0.3439853129692438</v>
       </c>
     </row>
     <row r="82">
@@ -5477,21 +5477,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7679070940500972</v>
+        <v>0.7657262435052801</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.348067823837122</v>
+        <v>0.3535313592509419</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,13 +490,13 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>221.81</v>
+        <v>222.05</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.01832263529791844</v>
+        <v>0.001082031900300873</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.02018732761572495</v>
+        <v>-0.02202158085353656</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.03950694761869067</v>
+        <v>0.04209687039431875</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.04410654777586842</v>
+        <v>0.04523630436787496</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.01132163350042392</v>
+        <v>-0.03254618805180731</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5568811354271337</v>
+        <v>0.5585657304806424</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7350617579547467</v>
+        <v>0.7343926615284209</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8626854823885952</v>
+        <v>0.8404212756709013</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.36054970780648</v>
+        <v>2.367756388337809</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4978561533788533</v>
+        <v>0.4989261036943027</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>63.84</v>
+        <v>64.5</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.008387653368553183</v>
+        <v>0.01033834344979012</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.004405267042906891</v>
+        <v>-0.005243620559736817</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.1125827634057388</v>
+        <v>0.1229108903566059</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.07240049490459466</v>
+        <v>0.08348733953664333</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.04115352362740232</v>
+        <v>-0.06589432079166258</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.5449436485573176</v>
+        <v>0.5609158066066751</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5817113298681487</v>
+        <v>0.6071704358676919</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7741052284312713</v>
+        <v>0.7777897407255379</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.805422712807148</v>
+        <v>2.829588046579844</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5612326867735029</v>
+        <v>0.5645304482758564</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>57.89</v>
+        <v>57.64</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.009750251518146458</v>
+        <v>-0.004318535198407747</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.003119048830902083</v>
+        <v>-0.01132075224784146</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.06356786818065929</v>
+        <v>0.06190126540004837</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.0590925640551252</v>
+        <v>0.05451883553888104</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.09308913123869766</v>
+        <v>0.06111928780331999</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5481590133252427</v>
+        <v>0.5414732341334654</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4211112927824234</v>
+        <v>0.4226719792378122</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4996148566609639</v>
+        <v>0.4737878054870626</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.732395329860474</v>
+        <v>1.711975442500391</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3980236279225515</v>
+        <v>0.3945323205410043</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>89.89</v>
+        <v>88.86</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0</v>
+        <v>-0.01145843571354488</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.007069473083819333</v>
+        <v>-0.008148183473363102</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.03364864939125189</v>
+        <v>-0.06354725279885176</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.01024003862916534</v>
+        <v>-0.0215811395183737</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1573323227602319</v>
+        <v>0.1474689799704756</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.02911078989296589</v>
+        <v>0.01731879006486192</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4822472823827244</v>
+        <v>0.4525070774604436</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4369304926034507</v>
+        <v>0.4497605454866485</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5182317319457561</v>
+        <v>0.531732494319322</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1493333835260315</v>
+        <v>0.1527301220331159</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>24.3</v>
+        <v>57.51</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.009376332782174646</v>
+        <v>0.001916320430840113</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.005728367182397442</v>
+        <v>0.03009128488948098</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.007880490331775736</v>
+        <v>0.07535525081884398</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-0.01018329970546805</v>
+        <v>0.08162498217129399</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.250643276139707</v>
+        <v>0.2192071349155849</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.476666425195664</v>
+        <v>0.3211930181378664</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.03838907116563073</v>
+        <v>0.08613552158369919</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.03139329434770444</v>
+        <v>0.2072950215650444</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.457569484598169</v>
+        <v>0.3641776504681722</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1338173258079332</v>
+        <v>0.1090649405476425</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>30.14</v>
+        <v>30.08</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.006008021050610379</v>
+        <v>-0.00199069234098892</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.01379077880003443</v>
+        <v>-0.0003323439292497454</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.029723229186148</v>
+        <v>0.02697162797833563</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.0210026735186486</v>
+        <v>0.01897017131634571</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.09599997780539771</v>
+        <v>0.08670518757478152</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3130474306231268</v>
+        <v>0.3104335571596302</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1785512567440042</v>
+        <v>0.1827761016360856</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3617594073147201</v>
+        <v>0.3474457320700222</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5391808290360343</v>
+        <v>0.5482577639016775</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1545955566341883</v>
+        <v>0.1568607560322799</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>57.4</v>
+        <v>24.33</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01020770563480866</v>
+        <v>0.001234596197013493</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.04230982102717662</v>
+        <v>-0.007343953630962186</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1015160401759139</v>
+        <v>0.0188442537166742</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.07955620655642948</v>
+        <v>-0.008961275771543931</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2081667765469739</v>
+        <v>0.2331475158741099</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.3186660314802858</v>
+        <v>0.4784895119484682</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.08192129454367336</v>
+        <v>0.04374175213462617</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.2033085040918468</v>
+        <v>0.02522480569564034</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3535313592509419</v>
+        <v>0.4523472860499513</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1061722874838298</v>
+        <v>0.1324616203761058</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.97</v>
+        <v>62.5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.00172888094497381</v>
+        <v>0.00822710610944144</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.006515793383122359</v>
+        <v>-0.08585640647609138</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.01696640691041418</v>
+        <v>-0.04419635137824973</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.04389438802623147</v>
+        <v>-0.09760326202320835</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.01613465734057273</v>
+        <v>0.2030798668358595</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2425361717973855</v>
+        <v>0.07363924057061455</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1743924442373972</v>
+        <v>0.09343321411503225</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4237258092304417</v>
+        <v>0.243482418658308</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.001349682904236</v>
+        <v>2.420964221650252</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2602044018155099</v>
+        <v>0.5067788331173986</v>
       </c>
     </row>
     <row r="10">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>34.99</v>
+        <v>28.88</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.0002856663295200956</v>
+        <v>-0.00310666740493859</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.002578800821001481</v>
+        <v>-0.03022167579339585</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01567491737498794</v>
+        <v>-0.0003461484628974887</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.004268574666675407</v>
+        <v>-0.04686469016662931</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.004017308765441374</v>
+        <v>-0.005851982125943289</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1975446494871076</v>
+        <v>0.2386760251730056</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1469926768138119</v>
+        <v>0.1776145520056862</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4399509258507031</v>
+        <v>0.3999222257057726</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.7657262435052801</v>
+        <v>1.013037233998355</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2086701331958789</v>
+        <v>0.2626527703765784</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>15.06</v>
+        <v>14.96</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01697123240122245</v>
+        <v>-0.00664013138668107</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.02461134527810449</v>
+        <v>-0.03108805409853588</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.001326227068338071</v>
+        <v>-0.01254122674372271</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.01619438122365802</v>
+        <v>0.009446717017925987</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.005284010692994334</v>
+        <v>-0.0228608995347428</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2288392386771552</v>
+        <v>0.2206795846792298</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2845548024237707</v>
+        <v>0.2749546905657627</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.274855107487797</v>
+        <v>0.2704198402805134</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8914942584907781</v>
+        <v>0.8752643585657913</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2367113382668937</v>
+        <v>0.2331639868229143</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>61.99</v>
+        <v>34.83</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.04791888961200119</v>
+        <v>-0.004572730486908649</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.06132645640391432</v>
+        <v>-0.009103831605487223</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.05517449928683016</v>
+        <v>0.02050983712372068</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.1049667951708115</v>
+        <v>-0.008821786112070074</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1787412340483963</v>
+        <v>-0.01303482778517751</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.06487837320064349</v>
+        <v>0.1920686005589636</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.03621988770011741</v>
+        <v>0.1476198310937478</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2482751659617695</v>
+        <v>0.4021706404921317</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>2.37778876664296</v>
+        <v>0.7622511323996335</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.5004130368703619</v>
+        <v>0.207876687904639</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>44.5</v>
+        <v>44.43</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.007803756656157845</v>
+        <v>-0.001573026849982395</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01700906671034985</v>
+        <v>-0.01068803259557316</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.02326605226821676</v>
+        <v>-0.0198544339184723</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.03596186856367967</v>
+        <v>-0.03747832642883597</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1234536560034918</v>
+        <v>0.1030288394152565</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.3062058114216062</v>
+        <v>0.3041511146086369</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.009692099256056519</v>
+        <v>0.009957662979838133</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.02036254010566796</v>
+        <v>0.01155162405033439</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3105496285482887</v>
+        <v>0.3107973056254949</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09433718664977153</v>
+        <v>0.09440612087331002</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>67.2</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.0129260408217422</v>
+        <v>-0.00565472128980371</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.02552207307999743</v>
+        <v>-0.0260895044396382</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.05178503818411162</v>
+        <v>-0.0558145702360886</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.03253674296024689</v>
+        <v>-0.03800747803693239</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.002108195362015675</v>
+        <v>-0.01345442359626814</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.02767308189520401</v>
+        <v>0.02186187704005293</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1620515292693105</v>
+        <v>0.1560703278246764</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.143851868185926</v>
+        <v>0.1418992773094705</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7589449091964584</v>
+        <v>0.7506875235121249</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.207120834605935</v>
+        <v>0.2052289237563922</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>92.33</v>
+        <v>91.75</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.003805158309930778</v>
+        <v>-0.006281834935040642</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.005554368742382243</v>
+        <v>-0.01078167115902962</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.0146210796350853</v>
+        <v>-0.01375898953125354</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.02871865976912458</v>
+        <v>-0.03482008882393994</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.01003521273659558</v>
+        <v>-0.01129355363241746</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0599165423355621</v>
+        <v>0.05325832157169108</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1095705042343718</v>
+        <v>0.1037844215108186</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1514242858590409</v>
+        <v>0.1363552909424708</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1996214146179041</v>
+        <v>0.1924750807800979</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.06254680548385516</v>
+        <v>0.06043268225904042</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16.41</v>
+        <v>16.34</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01204098468333648</v>
+        <v>-0.004265673094156486</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.03527339055827683</v>
+        <v>-0.01802880096541193</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.05581124051744246</v>
+        <v>-0.05549127900630879</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.07653351577474954</v>
+        <v>-0.08047272190986454</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.01046798514100233</v>
+        <v>0.006157659044279784</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.163013232173294</v>
+        <v>0.1580521979206644</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.02236640327877226</v>
+        <v>0.02366089301500929</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.07581192948549864</v>
+        <v>0.0712228674835198</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8708022382481588</v>
+        <v>0.8700564398279138</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2321851210637955</v>
+        <v>0.232021361752379</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>109.88</v>
+        <v>109.59</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.004439661873427259</v>
+        <v>-0.00263925120837516</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01071398617696862</v>
+        <v>-0.01038469882664816</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.05373755895254428</v>
+        <v>-0.03868424265008219</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.04535187914773764</v>
+        <v>-0.04787143535427008</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.078342592448013</v>
+        <v>-0.07331308677258752</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2339134585941935</v>
+        <v>0.2306568510075684</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06390393640713432</v>
+        <v>0.06294857381010122</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.09406444107547496</v>
+        <v>0.08902451570896663</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.01130246474496932</v>
+        <v>0.02068459194871575</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.003753382740588007</v>
+        <v>0.006847863706068935</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>36</v>
+        <v>35.66</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.01396873034728163</v>
+        <v>-0.009444448682996986</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02571043960281316</v>
+        <v>-0.01898208131150869</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.05138341828029025</v>
+        <v>-0.05885456791127752</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.05263157894736847</v>
+        <v>-0.06157895138389191</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.04937942922175032</v>
+        <v>-0.05561436884184234</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1418871480064161</v>
+        <v>0.1311026534352957</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.05697507628115539</v>
+        <v>0.05731368801467118</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1344942087165373</v>
+        <v>0.1302678645323656</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>1.1404907541312</v>
+        <v>1.109835141322914</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2887572419603339</v>
+        <v>0.2825752072238583</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>50.65</v>
+        <v>50.71</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.01228543815161542</v>
+        <v>0.001184551960242253</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01247805377704114</v>
+        <v>-0.0145744269985093</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.006558065044834027</v>
+        <v>0.01116645147667183</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.01497465325721148</v>
+        <v>-0.01380783955183906</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.03962836719895702</v>
+        <v>-0.05356481240205169</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1130482703675075</v>
+        <v>0.1143667338780154</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.06436400662654584</v>
+        <v>0.0716226947630898</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1017905349000625</v>
+        <v>0.1012119582442601</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7614428300265803</v>
+        <v>0.7665244874588504</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2076919849629899</v>
+        <v>0.2088522430172191</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>91.73</v>
+        <v>113.31</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.002066958396392815</v>
+        <v>0.005234176113389388</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.02300560279855524</v>
+        <v>-0.009181558640729559</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.0540373084232858</v>
+        <v>-0.02065686648822984</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.06502902062712679</v>
+        <v>-0.06471319742914283</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.002294653863310625</v>
+        <v>-0.08995264946973835</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1137673047182033</v>
+        <v>0.1063726255954054</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.02814002646277913</v>
+        <v>0.09304527671507823</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.02390812377677176</v>
+        <v>0.1539835275835275</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4735915085137068</v>
+        <v>0.4348726057266532</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1379566115351376</v>
+        <v>0.1279013455036959</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>112.72</v>
+        <v>91.62</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.00300722046021995</v>
+        <v>-0.00119917809142045</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01035996742201695</v>
+        <v>-0.00919215381096794</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.03369052939364003</v>
+        <v>-0.05096331181154967</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.06958316301279655</v>
+        <v>-0.06615021734170468</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.08957270460038758</v>
+        <v>0.0004367865770644741</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1006118294475968</v>
+        <v>0.1124316993674448</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.08210094237561383</v>
+        <v>0.02544078017003493</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1570737220758671</v>
+        <v>0.02519356169656617</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.4230105985830031</v>
+        <v>0.4922774490377746</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1247846431777049</v>
+        <v>0.1427463918123877</v>
       </c>
     </row>
     <row r="22">
@@ -1726,28 +1726,28 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>67.15000000000001</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01162792003442548</v>
+        <v>0.001340228381915054</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.004447671400096276</v>
+        <v>-0.006060660057081169</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.001192810964942614</v>
+        <v>0.01127989207544666</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.04616477172667821</v>
+        <v>-0.04488641468207588</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.08440135152847972</v>
+        <v>-0.09257760798399162</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.06875695637317314</v>
+        <v>0.07018933477947376</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.08062443169359046</v>
+        <v>0.08574192689209426</v>
       </c>
       <c r="N22" s="6" t="inlineStr"/>
       <c r="O22" s="6" t="inlineStr"/>
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>96.94</v>
+        <v>96.38</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01132076058952924</v>
+        <v>-0.005776822507579049</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01091724998982202</v>
+        <v>-0.03552489783765111</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02041225405976543</v>
+        <v>-0.0289169042476779</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.07101098362308578</v>
+        <v>-0.07637758828218566</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.03991283282732649</v>
+        <v>-0.02793751114303256</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.002913308187985075</v>
+        <v>-0.00867330103125219</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.07010665172046271</v>
+        <v>0.07358025350247099</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.09717032721979968</v>
+        <v>0.08417562714170868</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2265303756462367</v>
+        <v>0.218409924730433</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.07043286869025112</v>
+        <v>0.0680653090075376</v>
       </c>
     </row>
     <row r="24">
@@ -1832,37 +1832,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>39.54</v>
+        <v>39.52</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.003276966458741426</v>
+        <v>-0.0005058284598020713</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.0258684216090993</v>
+        <v>-0.02516034619459018</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.02897839562381543</v>
+        <v>-0.02875394958055677</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.0600102422249007</v>
+        <v>-0.06048571579630579</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.07487603636242901</v>
+        <v>-0.06915689222481158</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.05553594103191895</v>
+        <v>0.0550020209126012</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.06748646328361363</v>
+        <v>0.06470390551614846</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.06922212482074186</v>
+        <v>0.06868128184015765</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3629315277456446</v>
+        <v>0.3589919098777725</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1087271419120219</v>
+        <v>0.1076578349217379</v>
       </c>
     </row>
     <row r="25">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.29</v>
+        <v>13.26</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.003000747342983168</v>
+        <v>-0.002257316257133324</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.01373000075435571</v>
+        <v>-0.008968601235628371</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.003000747342983168</v>
+        <v>-0.007484987302782686</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.05274410443352529</v>
+        <v>-0.05488236056625284</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.07900210112357764</v>
+        <v>-0.06882019367893399</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.02235031738103122</v>
+        <v>-0.02455718190338818</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1228772673671166</v>
+        <v>0.1203425782567233</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.07937305226126479</v>
+        <v>0.07608866759157085</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.07386317181972579</v>
+        <v>0.07217147195232032</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02403857397991183</v>
+        <v>0.02350055496877745</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.68</v>
+        <v>16.65</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.002392285276397343</v>
+        <v>-0.001798602283969886</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.008912633345826149</v>
+        <v>-0.01711929789755917</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.02112679524703076</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05173393061501641</v>
+        <v>-0.05343948413322341</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.03750719107858314</v>
+        <v>-0.03757223394194298</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.04895063542777245</v>
+        <v>0.04706399041912035</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.01874226197515794</v>
+        <v>-0.01779843331930631</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.003566541141341473</v>
+        <v>-0.001237727272779265</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4478434020211739</v>
+        <v>0.4427701586355572</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1312897800663071</v>
+        <v>0.1299668872317357</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>166.04</v>
+        <v>165.77</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01565093374602378</v>
+        <v>-0.001626048088345877</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.05049466505181377</v>
+        <v>-0.0293927584226884</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.06223881409923848</v>
+        <v>-0.04833801051112341</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.1108493713083296</v>
+        <v>-0.1122951729883652</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.05108559855079653</v>
+        <v>0.05821902796883061</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.09422641953784372</v>
+        <v>0.09244715476013665</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.1367651244636909</v>
+        <v>-0.1350244192175341</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1365312695650518</v>
+        <v>-0.1501758449251066</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5066205424145589</v>
+        <v>0.5144569266356585</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1463959106725001</v>
+        <v>0.1483800573023946</v>
       </c>
     </row>
     <row r="28">
@@ -2059,34 +2059,34 @@
         <v>16.27</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.007926778279904068</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01751201796685609</v>
+        <v>-0.01214322185360706</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.04909410418604487</v>
+        <v>-0.03327388404521558</v>
       </c>
       <c r="J28" s="6" t="n">
         <v>-0.1011049660297001</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.02327049359184818</v>
+        <v>0.01560549268766365</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0.1441631611982521</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1803526375268002</v>
+        <v>-0.1762025084676622</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1741116838750817</v>
+        <v>-0.1807653596302855</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1824128042973008</v>
+        <v>0.1849964311880545</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05744155867028922</v>
+        <v>0.05821118469103692</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>25.49</v>
+        <v>25.54</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.02187259042614897</v>
+        <v>0.001961598464423453</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02784132575718723</v>
+        <v>-0.01655750516735788</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.03006091685259327</v>
+        <v>-0.01693605213478422</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.0980184159705958</v>
+        <v>-0.0962490902804255</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.1210344906510978</v>
+        <v>-0.1262401192096176</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.001361388623889237</v>
+        <v>0.003325657586146891</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.0283254372647902</v>
+        <v>-0.02008779923207138</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.0277659280020186</v>
+        <v>0.03304214164717956</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.088610555452277</v>
+        <v>1.094127315713521</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2782598740752413</v>
+        <v>0.2793843303218881</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>60.46</v>
+        <v>60.51</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01305908029676428</v>
+        <v>0.0008269804468685749</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02468144140292239</v>
+        <v>-0.02935517848212132</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.03418529459762076</v>
+        <v>-0.01159756427658831</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.06263567310895102</v>
+        <v>-0.06186049113902015</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.07141762374887184</v>
+        <v>-0.08456883935899695</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.03628725585579939</v>
+        <v>0.03714424515373116</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.1005897355082609</v>
+        <v>-0.0909422104231471</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.07051461521472391</v>
+        <v>-0.07157224669180662</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4210235868261363</v>
+        <v>0.4136163275229117</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1242608706966921</v>
+        <v>0.1223040175231114</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>51.38</v>
+        <v>51.36</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.02040037520038074</v>
+        <v>-0.0003892654213291102</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02689390510347978</v>
+        <v>-0.02800907528316587</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.05429782189429733</v>
+        <v>-0.03675917283740937</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.05862954663953002</v>
+        <v>-0.0589959896056842</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.03962614825952837</v>
+        <v>-0.04553058354232875</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.0006892586715084859</v>
+        <v>-0.001078255788270366</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.1136038368981345</v>
+        <v>-0.1084329099823385</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1059909409372767</v>
+        <v>-0.1118845272496052</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1706199654888121</v>
+        <v>0.1715428467508013</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.05391432844054656</v>
+        <v>0.05419121371690827</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>15.08</v>
+        <v>15.3</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.001324533593271671</v>
+        <v>0.01458887719773561</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02077920147732826</v>
+        <v>0.0006540372077687984</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.047378395680018</v>
+        <v>-0.01481001585260977</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.1201866709042302</v>
+        <v>-0.1073511822891211</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.09754633453458639</v>
+        <v>-0.08602148148578581</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.02459629676355113</v>
+        <v>0.03954400631428912</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.1199126442728656</v>
+        <v>-0.102106883849108</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1404190627530834</v>
+        <v>-0.1287226612735046</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2305414077572892</v>
+        <v>0.256153193689705</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.0715984516755066</v>
+        <v>0.07898200648653741</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>111.28</v>
+        <v>111.12</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.007934379996226482</v>
+        <v>-0.00143777888632235</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.004740173426970418</v>
+        <v>-0.01993292081128362</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.01504695102783771</v>
+        <v>-0.005815459568815351</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.05534808237310695</v>
+        <v>-0.05670628295519475</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1443291336563121</v>
+        <v>-0.1471332529540555</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.01987499748848587</v>
+        <v>-0.02128420052305346</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.05984418583275286</v>
+        <v>-0.05673383511003005</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.08335557014966644</v>
+        <v>-0.08360743318401265</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3439853129692438</v>
+        <v>0.3482889039020496</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1035656506564331</v>
+        <v>0.1047423090676161</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>117.93</v>
+        <v>119.3</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.007323255254488514</v>
+        <v>0.0116170842282437</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.03193235428824015</v>
+        <v>-0.01826854552859525</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.05185718837974118</v>
+        <v>-0.02929209462510096</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.06848339868438136</v>
+        <v>-0.05766189186689052</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1605158454299381</v>
+        <v>-0.1476808984663163</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1416307599561434</v>
+        <v>-0.1316590121956204</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.08725904570270737</v>
+        <v>-0.07728507353388081</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.08670735088120241</v>
+        <v>-0.07840795489760333</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4874413556884669</v>
+        <v>0.5055344208200978</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1415106053262718</v>
+        <v>0.1461203658040313</v>
       </c>
     </row>
   </sheetData>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.07955620655642948</v>
+        <v>0.08348733953664333</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3050,21 +3050,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1201866709042302</v>
+        <v>-0.1122951729883652</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.07240049490459466</v>
+        <v>0.08162498217129399</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1108493713083296</v>
+        <v>-0.1073511822891211</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0590925640551252</v>
+        <v>0.05451883553888104</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1049667951708115</v>
+        <v>-0.1011049660297001</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04410654777586842</v>
+        <v>0.04523630436787496</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1011049660297001</v>
+        <v>-0.09760326202320835</v>
       </c>
     </row>
     <row r="21">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.0210026735186486</v>
+        <v>0.01897017131634571</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.0980184159705958</v>
+        <v>-0.0962490902804255</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01619438122365802</v>
+        <v>0.009446717017925987</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.07653351577474954</v>
+        <v>-0.08047272190986454</v>
       </c>
     </row>
     <row r="23">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.004268574666675407</v>
+        <v>-0.008821786112070074</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.07101098362308578</v>
+        <v>-0.07637758828218566</v>
       </c>
     </row>
     <row r="24">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01018329970546805</v>
+        <v>-0.008961275771543931</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06958316301279655</v>
+        <v>-0.06615021734170468</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Environment &amp; Alt Energy</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
       <c r="E25" s="11" t="n">
-        <v>-0.01024003862916534</v>
+        <v>-0.01380783955183906</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06848339868438136</v>
+        <v>-0.06471319742914283</v>
       </c>
     </row>
     <row r="26">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.01497465325721148</v>
+        <v>-0.0215811395183737</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06502902062712679</v>
+        <v>-0.06186049113902015</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.250643276139707</v>
+        <v>0.2331475158741099</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1605158454299381</v>
+        <v>-0.1476808984663163</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2081667765469739</v>
+        <v>0.2192071349155849</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1443291336563121</v>
+        <v>-0.1471332529540555</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1787412340483963</v>
+        <v>0.2030798668358595</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1210344906510978</v>
+        <v>-0.1262401192096176</v>
       </c>
     </row>
     <row r="34">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1573323227602319</v>
+        <v>0.1474689799704756</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.09754633453458639</v>
+        <v>-0.09257760798399162</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1234536560034918</v>
+        <v>0.1030288394152565</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08957270460038758</v>
+        <v>-0.08995264946973835</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.09599997780539771</v>
+        <v>0.08670518757478152</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08440135152847972</v>
+        <v>-0.08602148148578581</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.09308913123869766</v>
+        <v>0.06111928780331999</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.07900210112357764</v>
+        <v>-0.08456883935899695</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.05108559855079653</v>
+        <v>0.05821902796883061</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.078342592448013</v>
+        <v>-0.07331308677258752</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.02327049359184818</v>
+        <v>0.01560549268766365</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.07487603636242901</v>
+        <v>-0.06915689222481158</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.01613465734057273</v>
+        <v>0.006157659044279784</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.07141762374887184</v>
+        <v>-0.06882019367893399</v>
       </c>
     </row>
     <row r="41"/>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5568811354271337</v>
+        <v>0.5609158066066751</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1416307599561434</v>
+        <v>-0.1316590121956204</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5481590133252427</v>
+        <v>0.5585657304806424</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.02235031738103122</v>
+        <v>-0.02455718190338818</v>
       </c>
     </row>
     <row r="47">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5449436485573176</v>
+        <v>0.5414732341334654</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.01987499748848587</v>
+        <v>-0.02128420052305346</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.476666425195664</v>
+        <v>0.4784895119484682</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.002913308187985075</v>
+        <v>-0.00867330103125219</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3186660314802858</v>
+        <v>0.3211930181378664</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0006892586715084859</v>
+        <v>-0.001078255788270366</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3130474306231268</v>
+        <v>0.3104335571596302</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.001361388623889237</v>
+        <v>0.003325657586146891</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3062058114216062</v>
+        <v>0.3041511146086369</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.02459629676355113</v>
+        <v>0.01731879006486192</v>
       </c>
     </row>
     <row r="52">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2425361717973855</v>
+        <v>0.2386760251730056</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.02767308189520401</v>
+        <v>0.02186187704005293</v>
       </c>
     </row>
     <row r="53">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2339134585941935</v>
+        <v>0.2306568510075684</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.02911078989296589</v>
+        <v>0.03714424515373116</v>
       </c>
     </row>
     <row r="54">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2288392386771552</v>
+        <v>0.2206795846792298</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t>Leisure</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K54" s="11" t="n">
-        <v>0.03628725585579939</v>
+        <v>0.03954400631428912</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8626854823885952</v>
+        <v>0.8404212756709013</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1741116838750817</v>
+        <v>-0.1807653596302855</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7741052284312713</v>
+        <v>0.7777897407255379</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4628,21 +4628,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1404190627530834</v>
+        <v>-0.1501758449251066</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.4996148566609639</v>
+        <v>0.4737878054870626</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4673,21 +4673,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1365312695650518</v>
+        <v>-0.1287226612735046</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4399509258507031</v>
+        <v>0.4497605454866485</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1059909409372767</v>
+        <v>-0.1118845272496052</v>
       </c>
     </row>
     <row r="63">
@@ -4741,21 +4741,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4369304926034507</v>
+        <v>0.4021706404921317</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4763,21 +4763,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.08670735088120241</v>
+        <v>-0.08360743318401265</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4237258092304417</v>
+        <v>0.3999222257057726</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4808,21 +4808,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.08335557014966644</v>
+        <v>-0.07840795489760333</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3617594073147201</v>
+        <v>0.3474457320700222</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.07051461521472391</v>
+        <v>-0.07157224669180662</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.274855107487797</v>
+        <v>0.2704198402805134</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.003566541141341473</v>
+        <v>-0.001237727272779265</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2482751659617695</v>
+        <v>0.243482418658308</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.02036254010566796</v>
+        <v>0.01155162405033439</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2033085040918468</v>
+        <v>0.2072950215650444</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.02390812377677176</v>
+        <v>0.02519356169656617</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.805422712807148</v>
+        <v>2.829588046579844</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.01130246474496932</v>
+        <v>0.02068459194871575</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.37778876664296</v>
+        <v>2.420964221650252</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.07386317181972579</v>
+        <v>0.07217147195232032</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.36054970780648</v>
+        <v>2.367756388337809</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1706199654888121</v>
+        <v>0.1715428467508013</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.732395329860474</v>
+        <v>1.711975442500391</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1824128042973008</v>
+        <v>0.1849964311880545</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.1404907541312</v>
+        <v>1.109835141322914</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1996214146179041</v>
+        <v>0.1924750807800979</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.088610555452277</v>
+        <v>1.094127315713521</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2265303756462367</v>
+        <v>0.218409924730433</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.001349682904236</v>
+        <v>1.013037233998355</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2305414077572892</v>
+        <v>0.256153193689705</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8914942584907781</v>
+        <v>0.8752643585657913</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3105496285482887</v>
+        <v>0.3107973056254949</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8708022382481588</v>
+        <v>0.8700564398279138</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3439853129692438</v>
+        <v>0.3482889039020496</v>
       </c>
     </row>
     <row r="82">
@@ -5477,21 +5477,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7657262435052801</v>
+        <v>0.7665244874588504</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3535313592509419</v>
+        <v>0.3589919098777725</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.8404212756709013</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.367756388337809</v>
+        <v>2.367755998646628</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4989261036943027</v>
+        <v>0.4989260458795206</v>
       </c>
     </row>
     <row r="3">
@@ -801,10 +801,10 @@
         <v>0.4497605454866485</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.531732494319322</v>
+        <v>0.5317325950402332</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1527301220331159</v>
+        <v>0.1527301472995002</v>
       </c>
     </row>
     <row r="6">
@@ -857,10 +857,10 @@
         <v>0.2072950215650444</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3641776504681722</v>
+        <v>0.3641775270274243</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1090649405476425</v>
+        <v>0.1090649070955454</v>
       </c>
     </row>
     <row r="7">
@@ -966,13 +966,13 @@
         <v>0.04374175213462617</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02522480569564034</v>
+        <v>0.02522472329584158</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4523472860499513</v>
+        <v>0.4523471206905543</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1324616203761058</v>
+        <v>0.1324615773966753</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.243482418658308</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>2.420964221650252</v>
+        <v>2.42096457879739</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.5067788331173986</v>
+        <v>0.5067788855530759</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.3999222257057726</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.013037233998355</v>
+        <v>1.013037100182831</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2626527703765784</v>
+        <v>0.2626527423985323</v>
       </c>
     </row>
     <row r="11">
@@ -1134,13 +1134,13 @@
         <v>0.2749546905657627</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2704198402805134</v>
+        <v>0.270419737392924</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8752643585657913</v>
+        <v>0.8752646948332394</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2331639868229143</v>
+        <v>0.2331640605321452</v>
       </c>
     </row>
     <row r="12">
@@ -1249,10 +1249,10 @@
         <v>0.01155162405033439</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3107973056254949</v>
+        <v>0.3107971581041737</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09440612087331002</v>
+        <v>0.09440607981732008</v>
       </c>
     </row>
     <row r="14">
@@ -1296,7 +1296,7 @@
         <v>-0.01345442359626814</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.02186187704005293</v>
+        <v>0.02186175781488364</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>0.1560703278246764</v>
@@ -1305,10 +1305,10 @@
         <v>0.1418992773094705</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7506875235121249</v>
+        <v>0.7506876984850794</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2052289237563922</v>
+        <v>0.2052289639087048</v>
       </c>
     </row>
     <row r="15">
@@ -1355,10 +1355,10 @@
         <v>0.05325832157169108</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1037844215108186</v>
+        <v>0.103784522820876</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1363552909424708</v>
+        <v>0.136355183565231</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>0.1924750807800979</v>
@@ -1414,13 +1414,13 @@
         <v>0.02366089301500929</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.0712228674835198</v>
+        <v>0.0712228005092983</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8700564398279138</v>
+        <v>0.870056031614417</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.232021361752379</v>
+        <v>0.2320212721066381</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.08902451570896663</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.02068459194871575</v>
+        <v>0.02068473700359319</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.006847863706068935</v>
+        <v>0.006847911402222406</v>
       </c>
     </row>
     <row r="18">
@@ -1585,10 +1585,10 @@
         <v>0.1012119582442601</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7665244874588504</v>
+        <v>0.7665243700838045</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2088522430172191</v>
+        <v>0.2088522162435378</v>
       </c>
     </row>
     <row r="20">
@@ -1697,10 +1697,10 @@
         <v>0.02519356169656617</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.4922774490377746</v>
+        <v>0.492277634475879</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1427463918123877</v>
+        <v>0.1427464391469089</v>
       </c>
     </row>
     <row r="22">
@@ -2248,7 +2248,7 @@
         <v>-0.1084329099823385</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1118845272496052</v>
+        <v>-0.1118845858329147</v>
       </c>
       <c r="O31" s="6" t="n">
         <v>0.1715428467508013</v>
@@ -2304,13 +2304,13 @@
         <v>-0.102106883849108</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1287226612735046</v>
+        <v>-0.1287225666385604</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.256153193689705</v>
+        <v>0.2561532920441287</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07898200648653741</v>
+        <v>0.07898203464728804</v>
       </c>
     </row>
     <row r="33">
@@ -2360,13 +2360,13 @@
         <v>-0.05673383511003005</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.08360743318401265</v>
+        <v>-0.08360737552582687</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3482889039020496</v>
+        <v>0.3482891535303543</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1047423090676161</v>
+        <v>0.1047423772466074</v>
       </c>
     </row>
     <row r="34">
@@ -2416,13 +2416,13 @@
         <v>-0.07728507353388081</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07840795489760333</v>
+        <v>-0.07840784626577213</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5055344208200978</v>
+        <v>0.5055345657743766</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1461203658040313</v>
+        <v>0.1461204025872147</v>
       </c>
     </row>
   </sheetData>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.02186187704005293</v>
+        <v>0.02186175781488364</v>
       </c>
     </row>
     <row r="53">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1287226612735046</v>
+        <v>-0.1287225666385604</v>
       </c>
     </row>
     <row r="62">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1118845272496052</v>
+        <v>-0.1118845858329147</v>
       </c>
     </row>
     <row r="63">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.08360743318401265</v>
+        <v>-0.08360737552582687</v>
       </c>
     </row>
     <row r="64">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.07840795489760333</v>
+        <v>-0.07840784626577213</v>
       </c>
     </row>
     <row r="65">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.2704198402805134</v>
+        <v>0.270419737392924</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.02068459194871575</v>
+        <v>0.02068473700359319</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.420964221650252</v>
+        <v>2.42096457879739</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.367756388337809</v>
+        <v>2.367755998646628</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.013037233998355</v>
+        <v>1.013037100182831</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.256153193689705</v>
+        <v>0.2561532920441287</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8752643585657913</v>
+        <v>0.8752646948332394</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3107973056254949</v>
+        <v>0.3107971581041737</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8700564398279138</v>
+        <v>0.870056031614417</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3482889039020496</v>
+        <v>0.3482891535303543</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7665244874588504</v>
+        <v>0.7665243700838045</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.8404212756709013</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.367755998646628</v>
+        <v>2.367756388337809</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4989260458795206</v>
+        <v>0.4989261036943027</v>
       </c>
     </row>
     <row r="3">
@@ -745,10 +745,10 @@
         <v>0.4737878054870626</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.711975442500391</v>
+        <v>1.71197568587634</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3945323205410043</v>
+        <v>0.3945323622566743</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.4497605454866485</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5317325950402332</v>
+        <v>0.531732494319322</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1527301472995002</v>
+        <v>0.1527301220331159</v>
       </c>
     </row>
     <row r="6">
@@ -857,10 +857,10 @@
         <v>0.2072950215650444</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3641775270274243</v>
+        <v>0.3641776504681722</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1090649070955454</v>
+        <v>0.1090649405476425</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.3474457320700222</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5482577639016775</v>
+        <v>0.5482579159000112</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1568607560322799</v>
+        <v>0.1568607938900806</v>
       </c>
     </row>
     <row r="8">
@@ -966,7 +966,7 @@
         <v>0.04374175213462617</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02522472329584158</v>
+        <v>0.02522480569564034</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>0.4523471206905543</v>
@@ -1137,10 +1137,10 @@
         <v>0.270419737392924</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8752646948332394</v>
+        <v>0.8752644706549273</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2331640605321452</v>
+        <v>0.2331640113926559</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.4021706404921317</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.7622511323996335</v>
+        <v>0.7622509623357312</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.207876687904639</v>
+        <v>0.2078766490497475</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.01155162405033439</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3107971581041737</v>
+        <v>0.3107973056254949</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09440607981732008</v>
+        <v>0.09440612087331002</v>
       </c>
     </row>
     <row r="14">
@@ -1302,13 +1302,13 @@
         <v>0.1560703278246764</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1418992773094705</v>
+        <v>0.1418993517499623</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7506876984850794</v>
+        <v>0.7506875235121249</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2052289639087048</v>
+        <v>0.2052289237563922</v>
       </c>
     </row>
     <row r="15">
@@ -1355,16 +1355,16 @@
         <v>0.05325832157169108</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.103784522820876</v>
+        <v>0.1037844215108186</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.136355183565231</v>
+        <v>0.1363553983197312</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1924750807800979</v>
+        <v>0.1924749625351532</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.06043268225904042</v>
+        <v>0.06043264720846642</v>
       </c>
     </row>
     <row r="16">
@@ -1414,13 +1414,13 @@
         <v>0.02366089301500929</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.0712228005092983</v>
+        <v>0.0712228674835198</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.870056031614417</v>
+        <v>0.8700562357211432</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2320212721066381</v>
+        <v>0.2320213169295053</v>
       </c>
     </row>
     <row r="17">
@@ -1638,13 +1638,13 @@
         <v>0.09304527671507823</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1539835275835275</v>
+        <v>0.1539836172481444</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4348726057266532</v>
+        <v>0.4348727443538924</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1279013455036959</v>
+        <v>0.1279013818269774</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>0.02519356169656617</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.492277634475879</v>
+        <v>0.4922772635997161</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1427464391469089</v>
+        <v>0.1427463444778743</v>
       </c>
     </row>
     <row r="22">
@@ -1800,13 +1800,13 @@
         <v>0.07358025350247099</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.08417562714170868</v>
+        <v>0.08417572018873121</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.218409924730433</v>
+        <v>0.2184100422445554</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.0680653090075376</v>
+        <v>0.06806534334539349</v>
       </c>
     </row>
     <row r="24">
@@ -1853,16 +1853,16 @@
         <v>0.0550020209126012</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.06470390551614846</v>
+        <v>0.06470379609512134</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>0.06868128184015765</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3589919098777725</v>
+        <v>0.3589919990124941</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1076578349217379</v>
+        <v>0.1076578591384065</v>
       </c>
     </row>
     <row r="25">
@@ -1912,7 +1912,7 @@
         <v>0.1203425782567233</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.07608866759157085</v>
+        <v>0.07608858430928489</v>
       </c>
       <c r="O25" s="6" t="n">
         <v>0.07217147195232032</v>
@@ -1971,10 +1971,10 @@
         <v>-0.001237727272779265</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4427701586355572</v>
+        <v>0.4427702778640892</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1299668872317357</v>
+        <v>0.1299669183580354</v>
       </c>
     </row>
     <row r="27">
@@ -2139,10 +2139,10 @@
         <v>0.03304214164717956</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.094127315713521</v>
+        <v>1.094127151962013</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2793843303218881</v>
+        <v>0.2793842969744857</v>
       </c>
     </row>
     <row r="30">
@@ -2251,10 +2251,10 @@
         <v>-0.1118845858329147</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1715428467508013</v>
+        <v>0.1715429486924021</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.05419121371690827</v>
+        <v>0.0541912442936634</v>
       </c>
     </row>
     <row r="32">
@@ -2307,10 +2307,10 @@
         <v>-0.1287225666385604</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2561532920441287</v>
+        <v>0.2561530953352968</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07898203464728804</v>
+        <v>0.07898197832578968</v>
       </c>
     </row>
     <row r="33">
@@ -2363,10 +2363,10 @@
         <v>-0.08360737552582687</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3482891535303543</v>
+        <v>0.3482890287161904</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1047423772466074</v>
+        <v>0.1047423431571095</v>
       </c>
     </row>
     <row r="34">
@@ -2419,10 +2419,10 @@
         <v>-0.07840784626577213</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5055345657743766</v>
+        <v>0.5055344208200978</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1461204025872147</v>
+        <v>0.1461203658040313</v>
       </c>
     </row>
   </sheetData>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.367755998646628</v>
+        <v>2.367756388337809</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1715428467508013</v>
+        <v>0.1715429486924021</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.711975442500391</v>
+        <v>1.71197568587634</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1924750807800979</v>
+        <v>0.1924749625351532</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.094127315713521</v>
+        <v>1.094127151962013</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.218409924730433</v>
+        <v>0.2184100422445554</v>
       </c>
     </row>
     <row r="79">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2561532920441287</v>
+        <v>0.2561530953352968</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8752646948332394</v>
+        <v>0.8752644706549273</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3107971581041737</v>
+        <v>0.3107973056254949</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.870056031614417</v>
+        <v>0.8700562357211432</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3482891535303543</v>
+        <v>0.3482890287161904</v>
       </c>
     </row>
     <row r="82">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3589919098777725</v>
+        <v>0.3589919990124941</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -686,7 +686,7 @@
         <v>0.6071704358676919</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7777897407255379</v>
+        <v>0.7777895538032409</v>
       </c>
       <c r="O3" s="6" t="n">
         <v>2.829588046579844</v>
@@ -745,10 +745,10 @@
         <v>0.4737878054870626</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.71197568587634</v>
+        <v>1.711975442500391</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3945323622566743</v>
+        <v>0.3945323205410043</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.4497605454866485</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.531732494319322</v>
+        <v>0.5317325950402332</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1527301220331159</v>
+        <v>0.1527301472995002</v>
       </c>
     </row>
     <row r="6">
@@ -913,10 +913,10 @@
         <v>0.3474457320700222</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5482579159000112</v>
+        <v>0.5482577639016775</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1568607938900806</v>
+        <v>0.1568607560322799</v>
       </c>
     </row>
     <row r="8">
@@ -966,13 +966,13 @@
         <v>0.04374175213462617</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02522480569564034</v>
+        <v>0.02522472329584158</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4523471206905543</v>
+        <v>0.4523469553311947</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1324615773966753</v>
+        <v>0.1324615344172513</v>
       </c>
     </row>
     <row r="9">
@@ -1081,10 +1081,10 @@
         <v>0.3999222257057726</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.013037100182831</v>
+        <v>1.013037233998355</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2626527423985323</v>
+        <v>0.2626527703765784</v>
       </c>
     </row>
     <row r="11">
@@ -1134,13 +1134,13 @@
         <v>0.2749546905657627</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.270419737392924</v>
+        <v>0.2704198402805134</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8752644706549273</v>
+        <v>0.8752646948332394</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2331640113926559</v>
+        <v>0.2331640605321452</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.4021706404921317</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.7622509623357312</v>
+        <v>0.7622511323996335</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2078766490497475</v>
+        <v>0.207876687904639</v>
       </c>
     </row>
     <row r="13">
@@ -1246,13 +1246,13 @@
         <v>0.009957662979838133</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.01155162405033439</v>
+        <v>0.0115515361966807</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3107973056254949</v>
+        <v>0.3107971581041737</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09440612087331002</v>
+        <v>0.09440607981732008</v>
       </c>
     </row>
     <row r="14">
@@ -1296,19 +1296,19 @@
         <v>-0.01345442359626814</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.02186175781488364</v>
+        <v>0.02186187704005293</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>0.1560703278246764</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1418993517499623</v>
+        <v>0.1418992773094705</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7506875235121249</v>
+        <v>0.7506871735663203</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2052289237563922</v>
+        <v>0.2052288434517828</v>
       </c>
     </row>
     <row r="15">
@@ -1358,7 +1358,7 @@
         <v>0.1037844215108186</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1363553983197312</v>
+        <v>0.1363552909424708</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>0.1924749625351532</v>
@@ -1414,13 +1414,13 @@
         <v>0.02366089301500929</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.0712228674835198</v>
+        <v>0.0712228005092983</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8700562357211432</v>
+        <v>0.870056031614417</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2320213169295053</v>
+        <v>0.2320212721066381</v>
       </c>
     </row>
     <row r="17">
@@ -1529,10 +1529,10 @@
         <v>0.1302678645323656</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>1.109835141322914</v>
+        <v>1.109835379415481</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2825752072238583</v>
+        <v>0.2825752554695886</v>
       </c>
     </row>
     <row r="19">
@@ -1582,7 +1582,7 @@
         <v>0.0716226947630898</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1012119582442601</v>
+        <v>0.1012120494681001</v>
       </c>
       <c r="O19" s="6" t="n">
         <v>0.7665243700838045</v>
@@ -1638,13 +1638,13 @@
         <v>0.09304527671507823</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1539836172481444</v>
+        <v>0.1539835275835275</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4348727443538924</v>
+        <v>0.4348726057266532</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1279013818269774</v>
+        <v>0.1279013455036959</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>0.02519356169656617</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.4922772635997161</v>
+        <v>0.492277634475879</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1427463444778743</v>
+        <v>0.1427464391469089</v>
       </c>
     </row>
     <row r="22">
@@ -1859,10 +1859,10 @@
         <v>0.06868128184015765</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3589919990124941</v>
+        <v>0.3589918207430627</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1076578591384065</v>
+        <v>0.1076578107050712</v>
       </c>
     </row>
     <row r="25">
@@ -1912,7 +1912,7 @@
         <v>0.1203425782567233</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.07608858430928489</v>
+        <v>0.07608866759157085</v>
       </c>
       <c r="O25" s="6" t="n">
         <v>0.07217147195232032</v>
@@ -1971,10 +1971,10 @@
         <v>-0.001237727272779265</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4427702778640892</v>
+        <v>0.4427700394070448</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1299669183580354</v>
+        <v>0.1299668561054392</v>
       </c>
     </row>
     <row r="27">
@@ -2024,7 +2024,7 @@
         <v>-0.1350244192175341</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1501758449251066</v>
+        <v>-0.1501757784479711</v>
       </c>
       <c r="O27" s="6" t="n">
         <v>0.5144569266356585</v>
@@ -2195,10 +2195,10 @@
         <v>-0.07157224669180662</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4136163275229117</v>
+        <v>0.4136162015445362</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1223040175231114</v>
+        <v>0.1223039841840226</v>
       </c>
     </row>
     <row r="31">
@@ -2248,13 +2248,13 @@
         <v>-0.1084329099823385</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1118845858329147</v>
+        <v>-0.1118845272496052</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1715429486924021</v>
+        <v>0.1715428467508013</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.0541912442936634</v>
+        <v>0.05419121371690827</v>
       </c>
     </row>
     <row r="32">
@@ -2307,10 +2307,10 @@
         <v>-0.1287225666385604</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2561530953352968</v>
+        <v>0.256153193689705</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07898197832578968</v>
+        <v>0.07898200648653741</v>
       </c>
     </row>
     <row r="33">
@@ -2363,10 +2363,10 @@
         <v>-0.08360737552582687</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3482890287161904</v>
+        <v>0.3482889039020496</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1047423431571095</v>
+        <v>0.1047423090676161</v>
       </c>
     </row>
     <row r="34">
@@ -2419,10 +2419,10 @@
         <v>-0.07840784626577213</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5055344208200978</v>
+        <v>0.5055345657743766</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1461203658040313</v>
+        <v>0.1461204025872147</v>
       </c>
     </row>
   </sheetData>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.02186175781488364</v>
+        <v>0.02186187704005293</v>
       </c>
     </row>
     <row r="53">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7777897407255379</v>
+        <v>0.7777895538032409</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1501758449251066</v>
+        <v>-0.1501757784479711</v>
       </c>
     </row>
     <row r="61">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1118845858329147</v>
+        <v>-0.1118845272496052</v>
       </c>
     </row>
     <row r="63">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.270419737392924</v>
+        <v>0.2704198402805134</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.01155162405033439</v>
+        <v>0.0115515361966807</v>
       </c>
     </row>
     <row r="68">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1715429486924021</v>
+        <v>0.1715428467508013</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.71197568587634</v>
+        <v>1.711975442500391</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.109835141322914</v>
+        <v>1.109835379415481</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.013037100182831</v>
+        <v>1.013037233998355</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2561530953352968</v>
+        <v>0.256153193689705</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8752644706549273</v>
+        <v>0.8752646948332394</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3107973056254949</v>
+        <v>0.3107971581041737</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8700562357211432</v>
+        <v>0.870056031614417</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3482890287161904</v>
+        <v>0.3482889039020496</v>
       </c>
     </row>
     <row r="82">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3589919990124941</v>
+        <v>0.3589918207430627</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>222.05</v>
+        <v>221.39</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.001082031900300873</v>
+        <v>-0.002972319986663252</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.02202158085353656</v>
+        <v>-0.01499374977554113</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.04209687039431875</v>
+        <v>0.03511312107436493</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.04523630436787496</v>
+        <v>0.0421295276096163</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.03254618805180731</v>
+        <v>-0.05465648797266798</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5585657304806424</v>
+        <v>0.5955534152989539</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7343926615284209</v>
+        <v>0.7355988004056864</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8404212756709013</v>
+        <v>0.8223239158885782</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.367756388337809</v>
+        <v>2.357746338714539</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4989261036943027</v>
+        <v>0.4974395338607549</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>64.5</v>
+        <v>64.53</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01033834344979012</v>
+        <v>0.0004650973534399139</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.005243620559736817</v>
+        <v>0.008438773037441338</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.1229108903566059</v>
+        <v>0.1156638763668756</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.08348733953664333</v>
+        <v>0.08399126663074763</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.06589432079166258</v>
+        <v>-0.09647157051656619</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.5609158066066751</v>
+        <v>0.6313448386664984</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6071704358676919</v>
+        <v>0.6097525232330041</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7777895538032409</v>
+        <v>0.7520702072957179</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.829588046579844</v>
+        <v>2.831369177845073</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5645304482758564</v>
+        <v>0.5647729636722747</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>57.64</v>
+        <v>57.95</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.004318535198407747</v>
+        <v>0.005378233458945614</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.01132075224784146</v>
+        <v>-0.001550657325434579</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.06190126540004837</v>
+        <v>0.06427915428758313</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.05451883553888104</v>
+        <v>0.06019028402326487</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.06111928780331999</v>
+        <v>0.0417041101973652</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5414732341334654</v>
+        <v>0.5824935554351334</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4226719792378122</v>
+        <v>0.4337444448135737</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4737878054870626</v>
+        <v>0.4711595496238392</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.711975442500391</v>
+        <v>1.726561079565085</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3945323205410043</v>
+        <v>0.3970278920802612</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>88.86</v>
+        <v>88.73</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.01145843571354488</v>
+        <v>-0.001462944547884981</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.008148183473363102</v>
+        <v>-0.01607891930955074</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.06354725279885176</v>
+        <v>-0.04013413010048617</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.0215811395183737</v>
+        <v>-0.02301251205586308</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1474689799704756</v>
+        <v>0.1492035281577626</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.01731879006486192</v>
+        <v>0.02839488247490651</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4525070774604436</v>
+        <v>0.4370285954631488</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4497605454866485</v>
+        <v>0.4647340353381937</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5317325950402332</v>
+        <v>0.5294917551915015</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1527301472995002</v>
+        <v>0.1521677461950073</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>57.51</v>
+        <v>24.62</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.001916320430840113</v>
+        <v>0.01191947868626086</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.03009128488948098</v>
+        <v>-0.006857606696878515</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.07535525081884398</v>
+        <v>0.03750532297368925</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.08162498217129399</v>
+        <v>0.002851389179156394</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2192071349155849</v>
+        <v>0.2340852079048172</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3211930181378664</v>
+        <v>0.4821376634325114</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.08613552158369919</v>
+        <v>0.05825446485924024</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2072950215650444</v>
+        <v>0.04932812526801289</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3641776504681722</v>
+        <v>0.4696585085710727</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1090649405476425</v>
+        <v>0.1369433115041472</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="F7" s="5" t="n">
-        <v>30.08</v>
+        <v>57.04</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.00199069234098892</v>
+        <v>-0.008172446873987882</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.0003323439292497454</v>
+        <v>0.02682271285204152</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.02697162797833563</v>
+        <v>0.06140675723839495</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.01897017131634571</v>
+        <v>0.07278545946692105</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.08670518757478152</v>
+        <v>0.2211518311608913</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3104335571596302</v>
+        <v>0.3180479656575941</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1827761016360856</v>
+        <v>0.07814633484393241</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3474457320700222</v>
+        <v>0.1729036379504256</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5482577639016775</v>
+        <v>0.3530289810930396</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1568607560322799</v>
+        <v>0.1060354145157052</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>24.33</v>
+        <v>29.85</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.001234596197013493</v>
+        <v>-0.007646261396931253</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.007343953630962186</v>
+        <v>0.01049422668702205</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.0188442537166742</v>
+        <v>0.01911913446358127</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.008961275771543931</v>
+        <v>0.0111788590307853</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2331475158741099</v>
+        <v>0.08387797346222969</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.4784895119484682</v>
+        <v>0.3090223441374398</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.04374175213462617</v>
+        <v>0.1803262875005383</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02522472329584158</v>
+        <v>0.3132565596967947</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4523469553311947</v>
+        <v>0.5364195311651716</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1324615344172513</v>
+        <v>0.1539046933228596</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>62.5</v>
+        <v>28.83</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.00822710610944144</v>
+        <v>-0.001731275571796753</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.08585640647609138</v>
+        <v>-0.001039524809807069</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.04419635137824973</v>
+        <v>-0.0006932567590716143</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.09760326202320835</v>
+        <v>-0.04851483004516077</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2030798668358595</v>
+        <v>-0.007573126304038835</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.07363924057061455</v>
+        <v>0.235514632274501</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.09343321411503225</v>
+        <v>0.1914241584779632</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.243482418658308</v>
+        <v>0.3780539193590973</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>2.42096457879739</v>
+        <v>1.009552111810016</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.5067788855530759</v>
+        <v>0.2619236828317402</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>28.88</v>
+        <v>14.97</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.00310666740493859</v>
+        <v>0.0006684644957444252</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.03022167579339585</v>
+        <v>-0.02220771673867816</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.0003461484628974887</v>
+        <v>-0.007952278618002739</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.04686469016662931</v>
+        <v>0.01012149630859827</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.005851982125943289</v>
+        <v>-0.02981205632203854</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2386760251730056</v>
+        <v>0.2384055562476268</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1776145520056862</v>
+        <v>0.2694173218412927</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3999222257057726</v>
+        <v>0.2652297525499963</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.013037233998355</v>
+        <v>0.8765180183736909</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2626527703765784</v>
+        <v>0.2334387256425201</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>14.96</v>
+        <v>61.37</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.00664013138668107</v>
+        <v>-0.01808001708984375</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.03108805409853588</v>
+        <v>-0.06519424972605647</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.01254122674372271</v>
+        <v>-0.05088160445237566</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.009446717017925987</v>
+        <v>-0.113918610467648</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.0228608995347428</v>
+        <v>0.1792851239857223</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2206795846792298</v>
+        <v>0.05670751568678689</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2749546905657627</v>
+        <v>0.06367718193046068</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2704198402805134</v>
+        <v>0.2115636496948003</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8752646948332394</v>
+        <v>2.359113130059071</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2331640605321452</v>
+        <v>0.4976426869625299</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>34.83</v>
+        <v>34.35</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.004572730486908649</v>
+        <v>-0.01378131873957067</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.009103831605487223</v>
+        <v>-0.003481367633661581</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.02050983712372068</v>
+        <v>0.004973615196825154</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.008821786112070074</v>
+        <v>-0.02248152900537792</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.01303482778517751</v>
+        <v>-0.01434720292373293</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1920686005589636</v>
+        <v>0.1690048981997525</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1476198310937478</v>
+        <v>0.1358202404564801</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4021706404921317</v>
+        <v>0.3468486167896776</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.7622511323996335</v>
+        <v>0.7379649878448646</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.207876687904639</v>
+        <v>0.2023022902075839</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>44.43</v>
+        <v>44.14</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.001573026849982395</v>
+        <v>-0.006527141875656506</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01068803259557316</v>
+        <v>-0.01495206344809297</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.0198544339184723</v>
+        <v>-0.01604996011830151</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.03747832642883597</v>
+        <v>-0.04376084195062924</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1030288394152565</v>
+        <v>0.0901456547264794</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.3041511146086369</v>
+        <v>0.2834477351893188</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.009957662979838133</v>
+        <v>0.007896339346866732</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0115515361966807</v>
+        <v>0.009968994022164779</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3107971581041737</v>
+        <v>0.3022413990830206</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09440607981732008</v>
+        <v>0.09201976574083304</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>66.81999999999999</v>
+        <v>66.78</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.00565472128980371</v>
+        <v>-0.000598636870847602</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.0260895044396382</v>
+        <v>-0.01707394201390855</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.0558145702360886</v>
+        <v>-0.04024149149286349</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.03800747803693239</v>
+        <v>-0.03858336223005909</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.01345442359626814</v>
+        <v>0.0007164970735891174</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.02186187704005293</v>
+        <v>0.03023562685151071</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1560703278246764</v>
+        <v>0.1475689414163481</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1418992773094705</v>
+        <v>0.1346462564011093</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7506871735663203</v>
+        <v>0.749639672279427</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2052288434517828</v>
+        <v>0.2049884177371786</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>91.75</v>
+        <v>90.42</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.006281834935040642</v>
+        <v>-0.01449593276353878</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01078167115902962</v>
+        <v>-0.02089875838727406</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.01375898953125354</v>
+        <v>-0.02385835204579057</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.03482008882393994</v>
+        <v>-0.04881127192106649</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.01129355363241746</v>
+        <v>-0.0118440012333263</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.05325832157169108</v>
+        <v>0.03386991669916184</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1037844215108186</v>
+        <v>0.09025612559748208</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1363552909424708</v>
+        <v>0.1169305471037394</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1924749625351532</v>
+        <v>0.1751889256560402</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.06043264720846642</v>
+        <v>0.05528370009533368</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16.34</v>
+        <v>16.15</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.004265673094156486</v>
+        <v>-0.01162793955222363</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01802880096541193</v>
+        <v>-0.0223971446114285</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.05549127900630879</v>
+        <v>-0.04775940505114529</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.08047272190986454</v>
+        <v>-0.09116492951611732</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.006157659044279784</v>
+        <v>-0.006765105092444879</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1580521979206644</v>
+        <v>0.133504672606312</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.02366089301500929</v>
+        <v>0.01677893693251442</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.0712228005092983</v>
+        <v>0.06529832249739687</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.870056031614417</v>
+        <v>0.8483113348529188</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2320212721066381</v>
+        <v>0.2272273977004544</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>109.59</v>
+        <v>35.44</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.00263925120837516</v>
+        <v>-0.006169411711848038</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01038469882664816</v>
+        <v>-0.01336301689044384</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.03868424265008219</v>
+        <v>-0.04008666347879741</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.04787143535427008</v>
+        <v>-0.06736845719186879</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.07331308677258752</v>
+        <v>-0.05769747270478154</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2306568510075684</v>
+        <v>0.1203021676470917</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06294857381010122</v>
+        <v>0.05815392441037681</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.08902451570896663</v>
+        <v>0.1301461039849694</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.02068473700359319</v>
+        <v>1.096818936315644</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.006847911402222406</v>
+        <v>0.2799322344323758</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>35.66</v>
+        <v>108.34</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.009444448682996986</v>
+        <v>-0.01140615057733896</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.01898208131150869</v>
+        <v>-0.00932703243204247</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.05885456791127752</v>
+        <v>-0.0397944289665717</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.06157895138389191</v>
+        <v>-0.05873155713160483</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.05561436884184234</v>
+        <v>-0.08727886164031606</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1311026534352957</v>
+        <v>0.2163466566643109</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.05731368801467118</v>
+        <v>0.04929778535487284</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1302678645323656</v>
+        <v>0.07037429414462748</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>1.109835379415481</v>
+        <v>0.009042581501153668</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2825752554695886</v>
+        <v>0.003005153837665642</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>50.71</v>
+        <v>112.06</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.001184551960242253</v>
+        <v>-0.01103168323124892</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.0145744269985093</v>
+        <v>-0.01286116215333621</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.01116645147667183</v>
+        <v>-0.01485716432005491</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.01380783955183906</v>
+        <v>-0.07503098516547224</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.05356481240205169</v>
+        <v>-0.09299882808056792</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1143667338780154</v>
+        <v>0.09967089072730628</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0716226947630898</v>
+        <v>0.08361725429902234</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1012120494681001</v>
+        <v>0.1498648933441848</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7665243700838045</v>
+        <v>0.4190435456630801</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2088522162435378</v>
+        <v>0.1237384497324014</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>113.31</v>
+        <v>50.47</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.005234176113389388</v>
+        <v>-0.004732752279678509</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.009181558640729559</v>
+        <v>-0.01598751569871726</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.02065686648822984</v>
+        <v>0.008190168521067243</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.06471319742914283</v>
+        <v>-0.0184752427474012</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.08995264946973835</v>
+        <v>-0.07292427454357298</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1063726255954054</v>
+        <v>0.1249439139647659</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.09304527671507823</v>
+        <v>0.07191388656859599</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1539835275835275</v>
+        <v>0.08856507933321311</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4348726057266532</v>
+        <v>0.7581638478441828</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1279013455036959</v>
+        <v>0.2069421337236361</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>91.62</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.00119917809142045</v>
+        <v>-0.01386164848710747</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.00919215381096794</v>
+        <v>-0.0181482094095593</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.05096331181154967</v>
+        <v>-0.05560781641732171</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.06615021734170468</v>
+        <v>-0.07909491476867558</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.0004367865770644741</v>
+        <v>-0.008667993425695242</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1124316993674448</v>
+        <v>0.07661580032239312</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.02544078017003493</v>
+        <v>0.01133762428695229</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.02519356169656617</v>
+        <v>0.001989535183695157</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.492277634475879</v>
+        <v>0.4715921150277833</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1427464391469089</v>
+        <v>0.1374417124332401</v>
       </c>
     </row>
     <row r="22">
@@ -1726,28 +1726,28 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>67.23999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.001340228381915054</v>
+        <v>-0.01174897294208588</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.006060660057081169</v>
+        <v>-0.01817380838338334</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01127989207544666</v>
+        <v>0.00075294309057794</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.04488641468207588</v>
+        <v>-0.05610801835259482</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.09257760798399162</v>
+        <v>-0.1188172162676773</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.07018933477947376</v>
+        <v>0.0783836108419369</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.08574192689209426</v>
+        <v>0.07681085616742789</v>
       </c>
       <c r="N22" s="6" t="inlineStr"/>
       <c r="O22" s="6" t="inlineStr"/>
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>96.38</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.005776822507579049</v>
+        <v>-0.008404208151863379</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.03552489783765111</v>
+        <v>-0.03474398916458021</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.0289169042476779</v>
+        <v>-0.02915484229381571</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.07637758828218566</v>
+        <v>-0.08413990328398835</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.02793751114303256</v>
+        <v>-0.04276839743278205</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.00867330103125219</v>
+        <v>-0.0204249539011585</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.07358025350247099</v>
+        <v>0.06478768722323736</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.08417572018873121</v>
+        <v>0.06888492201306051</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2184100422445554</v>
+        <v>0.2081701541087022</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.06806534334539349</v>
+        <v>0.06506480656829616</v>
       </c>
     </row>
     <row r="24">
@@ -1832,37 +1832,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>39.52</v>
+        <v>39.06</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.0005058284598020713</v>
+        <v>-0.01163965281235946</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02516034619459018</v>
+        <v>-0.02154300689130062</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.02875394958055677</v>
+        <v>-0.03340753474928682</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.06048571579630579</v>
+        <v>-0.0714213358766892</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.06915689222481158</v>
+        <v>-0.06180782139489882</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.0550020209126012</v>
+        <v>0.03947464595705807</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.06470379609512134</v>
+        <v>0.05010382232501498</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.06868128184015765</v>
+        <v>0.0499485502554029</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3589918207430627</v>
+        <v>0.343173627774777</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1076578107050712</v>
+        <v>0.103343443792179</v>
       </c>
     </row>
     <row r="25">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.26</v>
+        <v>13.18</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.002257316257133324</v>
+        <v>-0.006033176645940386</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.008968601235628371</v>
+        <v>-0.01641785967294096</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.007484987302782686</v>
+        <v>-0.009022547657005053</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.05488236056625284</v>
+        <v>-0.06058442223615079</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.06882019367893399</v>
+        <v>-0.0866250847930784</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.02455718190338818</v>
+        <v>-0.03393238073581661</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1203425782567233</v>
+        <v>0.1135833535781323</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.07608866759157085</v>
+        <v>0.06456690147598731</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.07217147195232032</v>
+        <v>0.06570287206729386</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02350055496877745</v>
+        <v>0.02143808175415995</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.65</v>
+        <v>16.57</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.001798602283969886</v>
+        <v>-0.004804800332669057</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01711929789755917</v>
+        <v>-0.008378180569652338</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0</v>
+        <v>0.0006038785751414366</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05343948413322341</v>
+        <v>-0.05798751841475147</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.03757223394194298</v>
+        <v>-0.03774678539192411</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.04706399041912035</v>
+        <v>0.03714076826798496</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.01779843331930631</v>
+        <v>-0.01926307782516445</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.001237727272779265</v>
+        <v>0.0004533878273946801</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4427700394070448</v>
+        <v>0.435837817441737</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1299668561054392</v>
+        <v>0.1281541947975784</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>165.77</v>
+        <v>164.26</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.001626048088345877</v>
+        <v>-0.009109065130644134</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0293927584226884</v>
+        <v>-0.03177129138558799</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.04833801051112341</v>
+        <v>-0.03733229908978464</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.1122951729883652</v>
+        <v>-0.1203813340744013</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.05821902796883061</v>
+        <v>0.03314666854262405</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.09244715476013665</v>
+        <v>0.06753056609566443</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.1350244192175341</v>
+        <v>-0.1348566687393248</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1501757784479711</v>
+        <v>-0.1474368640589792</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5144569266356585</v>
+        <v>0.500661639853379</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1483800573023946</v>
+        <v>0.1448825263824935</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.27</v>
+        <v>16.11</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0</v>
+        <v>-0.00983404074434191</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01214322185360706</v>
+        <v>-0.006168937678527109</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.03327388404521558</v>
+        <v>-0.0277609591396879</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.1011049660297001</v>
+        <v>-0.1099447364186505</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.01560549268766365</v>
+        <v>0.01003139830719513</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1441631611982521</v>
+        <v>0.1218663645900984</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1762025084676622</v>
+        <v>-0.1793173051912436</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1807653596302855</v>
+        <v>-0.1742695837336306</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1849964311880545</v>
+        <v>0.1733431280018516</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05821118469103692</v>
+        <v>0.05473092064827267</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>25.54</v>
+        <v>25.3</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.001961598464423453</v>
+        <v>-0.009397089657928959</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01655750516735788</v>
+        <v>-0.02692310626690209</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.01693605213478422</v>
+        <v>-0.0302798356039482</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.0962490902804255</v>
+        <v>-0.1047417186074951</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.1262401192096176</v>
+        <v>-0.1464237598501302</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.003325657586146891</v>
+        <v>0.01700187882372828</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.02008779923207138</v>
+        <v>-0.02668969437605895</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.03304214164717956</v>
+        <v>0.006212588908945715</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.094127151962013</v>
+        <v>1.074448613572643</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2793842969744857</v>
+        <v>0.2753642150205216</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>60.51</v>
+        <v>60.39</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.0008269804468685749</v>
+        <v>-0.001983125685231846</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02935517848212132</v>
+        <v>-0.01596870717439702</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.01159756427658831</v>
+        <v>-0.007233312973231265</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.06186049113902015</v>
+        <v>-0.06372093969537307</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.08456883935899695</v>
+        <v>-0.08776431761977632</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.03714424515373116</v>
+        <v>0.03542521474727578</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.0909422104231471</v>
+        <v>-0.08923003637125138</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.07157224669180662</v>
+        <v>-0.06792370091179456</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4136162015445362</v>
+        <v>0.4108129486747381</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1223039841840226</v>
+        <v>0.121561636587131</v>
       </c>
     </row>
     <row r="31">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>51.36</v>
+        <v>15.17</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.0003892654213291102</v>
+        <v>-0.00849673940001916</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02800907528316587</v>
+        <v>0.01607500108589832</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.03675917283740937</v>
+        <v>-0.0187580828678825</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.0589959896056842</v>
+        <v>-0.1149357866689457</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.04553058354232875</v>
+        <v>-0.08449002077939538</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.001078255788270366</v>
+        <v>0.02740343511605681</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.1084329099823385</v>
+        <v>-0.1067553025056834</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1118845272496052</v>
+        <v>-0.1212458666746806</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1715428467508013</v>
+        <v>0.2454799873564217</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.05419121371690827</v>
+        <v>0.07591736723846476</v>
       </c>
     </row>
     <row r="32">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>15.3</v>
+        <v>50.64</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01458887719773561</v>
+        <v>-0.01401871518977371</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.0006540372077687984</v>
+        <v>-0.03726234108993298</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.01481001585260977</v>
+        <v>-0.04217892164343251</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.1073511822891211</v>
+        <v>-0.07218765681983697</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.08602148148578581</v>
+        <v>-0.06877531454591457</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.03954400631428912</v>
+        <v>-0.01272600720194661</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.102106883849108</v>
+        <v>-0.1158618972704618</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1287225666385604</v>
+        <v>-0.1249970256427495</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.256153193689705</v>
+        <v>0.1551193212495849</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07898200648653741</v>
+        <v>0.04924187792160084</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>111.12</v>
+        <v>110.01</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.00143777888632235</v>
+        <v>-0.009989206109749738</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01993292081128362</v>
+        <v>-0.01274340989909661</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.005815459568815351</v>
+        <v>-0.01061246766135837</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.05670628295519475</v>
+        <v>-0.06612903831678718</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1471332529540555</v>
+        <v>-0.1599083260787568</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.02128420052305346</v>
+        <v>-0.02149281471405839</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.05673383511003005</v>
+        <v>-0.061773901478403</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.08360737552582687</v>
+        <v>-0.09787518881816093</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3482889039020496</v>
+        <v>0.3348206917128302</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1047423090676161</v>
+        <v>0.1010515266426513</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>119.3</v>
+        <v>118.41</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0116170842282437</v>
+        <v>-0.007460179102110498</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.01826854552859525</v>
+        <v>-0.008457498930849794</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02929209462510096</v>
+        <v>-0.03629851863575972</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.05766189186689052</v>
+        <v>-0.06469190292830751</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1476808984663163</v>
+        <v>-0.1428135898652946</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1316590121956204</v>
+        <v>-0.1369685681169452</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.07728507353388081</v>
+        <v>-0.08465373366541651</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07840784626577213</v>
+        <v>-0.08481199010149587</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5055345657743766</v>
+        <v>0.4943025766506834</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1461204025872147</v>
+        <v>0.143263087778047</v>
       </c>
     </row>
   </sheetData>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.08348733953664333</v>
+        <v>0.08399126663074763</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1122951729883652</v>
+        <v>-0.1203813340744013</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.08162498217129399</v>
+        <v>0.07278545946692105</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1073511822891211</v>
+        <v>-0.1149357866689457</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05451883553888104</v>
+        <v>0.06019028402326487</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1011049660297001</v>
+        <v>-0.113918610467648</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04523630436787496</v>
+        <v>0.0421295276096163</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09760326202320835</v>
+        <v>-0.1099447364186505</v>
       </c>
     </row>
     <row r="21">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.01897017131634571</v>
+        <v>0.0111788590307853</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.0962490902804255</v>
+        <v>-0.1047417186074951</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.009446717017925987</v>
+        <v>0.01012149630859827</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.08047272190986454</v>
+        <v>-0.09116492951611732</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.008821786112070074</v>
+        <v>0.002851389179156394</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.07637758828218566</v>
+        <v>-0.08413990328398835</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.008961275771543931</v>
+        <v>-0.0184752427474012</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06615021734170468</v>
+        <v>-0.07909491476867558</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.01380783955183906</v>
+        <v>-0.02248152900537792</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06471319742914283</v>
+        <v>-0.07503098516547224</v>
       </c>
     </row>
     <row r="26">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.0215811395183737</v>
+        <v>-0.02301251205586308</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06186049113902015</v>
+        <v>-0.07218765681983697</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2331475158741099</v>
+        <v>0.2340852079048172</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3561,21 +3561,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1476808984663163</v>
+        <v>-0.1599083260787568</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2192071349155849</v>
+        <v>0.2211518311608913</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3606,21 +3606,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1471332529540555</v>
+        <v>-0.1464237598501302</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2030798668358595</v>
+        <v>0.1792851239857223</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1262401192096176</v>
+        <v>-0.1428135898652946</v>
       </c>
     </row>
     <row r="34">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1474689799704756</v>
+        <v>0.1492035281577626</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.09257760798399162</v>
+        <v>-0.1188172162676773</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1030288394152565</v>
+        <v>0.0901456547264794</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08995264946973835</v>
+        <v>-0.09647157051656619</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.08670518757478152</v>
+        <v>0.08387797346222969</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08602148148578581</v>
+        <v>-0.09299882808056792</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.06111928780331999</v>
+        <v>0.0417041101973652</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.08456883935899695</v>
+        <v>-0.08776431761977632</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.05821902796883061</v>
+        <v>0.03314666854262405</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.07331308677258752</v>
+        <v>-0.08727886164031606</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.01560549268766365</v>
+        <v>0.01003139830719513</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.06915689222481158</v>
+        <v>-0.0866250847930784</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.006157659044279784</v>
+        <v>0.0007164970735891174</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.06882019367893399</v>
+        <v>-0.08449002077939538</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5609158066066751</v>
+        <v>0.6313448386664984</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1316590121956204</v>
+        <v>-0.1369685681169452</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5585657304806424</v>
+        <v>0.5955534152989539</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.02455718190338818</v>
+        <v>-0.03393238073581661</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5414732341334654</v>
+        <v>0.5824935554351334</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.02128420052305346</v>
+        <v>-0.02149281471405839</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4784895119484682</v>
+        <v>0.4821376634325114</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.00867330103125219</v>
+        <v>-0.0204249539011585</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3211930181378664</v>
+        <v>0.3180479656575941</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.001078255788270366</v>
+        <v>-0.01272600720194661</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3104335571596302</v>
+        <v>0.3090223441374398</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.003325657586146891</v>
+        <v>0.01700187882372828</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3041511146086369</v>
+        <v>0.2834477351893188</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.01731879006486192</v>
+        <v>0.02740343511605681</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2386760251730056</v>
+        <v>0.2384055562476268</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.02186187704005293</v>
+        <v>0.02839488247490651</v>
       </c>
     </row>
     <row r="53">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2306568510075684</v>
+        <v>0.235514632274501</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.03714424515373116</v>
+        <v>0.03023562685151071</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2206795846792298</v>
+        <v>0.2163466566643109</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.03954400631428912</v>
+        <v>0.03386991669916184</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8404212756709013</v>
+        <v>0.8223239158885782</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1807653596302855</v>
+        <v>-0.1742695837336306</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7777895538032409</v>
+        <v>0.7520702072957179</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1501757784479711</v>
+        <v>-0.1474368640589792</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.4737878054870626</v>
+        <v>0.4711595496238392</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1287225666385604</v>
+        <v>-0.1249970256427495</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4497605454866485</v>
+        <v>0.4647340353381937</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1118845272496052</v>
+        <v>-0.1212458666746806</v>
       </c>
     </row>
     <row r="63">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.4021706404921317</v>
+        <v>0.3780539193590973</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.08360737552582687</v>
+        <v>-0.09787518881816093</v>
       </c>
     </row>
     <row r="64">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.3999222257057726</v>
+        <v>0.3468486167896776</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.07840784626577213</v>
+        <v>-0.08481199010149587</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.3474457320700222</v>
+        <v>0.3132565596967947</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.07157224669180662</v>
+        <v>-0.06792370091179456</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.2704198402805134</v>
+        <v>0.2652297525499963</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.001237727272779265</v>
+        <v>0.0004533878273946801</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.243482418658308</v>
+        <v>0.2115636496948003</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.0115515361966807</v>
+        <v>0.001989535183695157</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2072950215650444</v>
+        <v>0.1729036379504256</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.02519356169656617</v>
+        <v>0.006212588908945715</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.829588046579844</v>
+        <v>2.831369177845073</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.02068473700359319</v>
+        <v>0.009042581501153668</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.42096457879739</v>
+        <v>2.359113130059071</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.07217147195232032</v>
+        <v>0.06570287206729386</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.367756388337809</v>
+        <v>2.357746338714539</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1715428467508013</v>
+        <v>0.1551193212495849</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.711975442500391</v>
+        <v>1.726561079565085</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1849964311880545</v>
+        <v>0.1733431280018516</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.109835379415481</v>
+        <v>1.096818936315644</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1924749625351532</v>
+        <v>0.1751889256560402</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.094127151962013</v>
+        <v>1.074448613572643</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2184100422445554</v>
+        <v>0.2081701541087022</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.013037233998355</v>
+        <v>1.009552111810016</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.256153193689705</v>
+        <v>0.2454799873564217</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8752646948332394</v>
+        <v>0.8765180183736909</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3107971581041737</v>
+        <v>0.3022413990830206</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.870056031614417</v>
+        <v>0.8483113348529188</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3482889039020496</v>
+        <v>0.3348206917128302</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7665243700838045</v>
+        <v>0.7581638478441828</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3589918207430627</v>
+        <v>0.343173627774777</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -801,10 +801,10 @@
         <v>0.4647340353381937</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5294917551915015</v>
+        <v>0.5294918557650767</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1521677461950073</v>
+        <v>0.1521677714490668</v>
       </c>
     </row>
     <row r="6">
@@ -857,10 +857,10 @@
         <v>0.04932812526801289</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4696585085710727</v>
+        <v>0.4696583412406776</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1369433115041472</v>
+        <v>0.1369432683546266</v>
       </c>
     </row>
     <row r="7">
@@ -910,7 +910,7 @@
         <v>0.07814633484393241</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1729036379504256</v>
+        <v>0.1729035459467481</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>0.3530289810930396</v>
@@ -969,10 +969,10 @@
         <v>0.3132565596967947</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5364195311651716</v>
+        <v>0.5364193803290569</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1539046933228596</v>
+        <v>0.153904655561796</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.3780539193590973</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.009552111810016</v>
+        <v>1.009552245393886</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2619236828317402</v>
+        <v>0.2619237107936334</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.2652297525499963</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.8765180183736909</v>
+        <v>0.8765181305377678</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2334387256425201</v>
+        <v>0.2334387502177373</v>
       </c>
     </row>
     <row r="11">
@@ -1134,13 +1134,13 @@
         <v>0.06367718193046068</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2115636496948003</v>
+        <v>0.2115637409371509</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>2.359113130059071</v>
+        <v>2.359113480748983</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.4976426869625299</v>
+        <v>0.4976427390802709</v>
       </c>
     </row>
     <row r="12">
@@ -1249,10 +1249,10 @@
         <v>0.009968994022164779</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3022413990830206</v>
+        <v>0.3022415456414491</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09201976574083304</v>
+        <v>0.09201980670730192</v>
       </c>
     </row>
     <row r="14">
@@ -1305,10 +1305,10 @@
         <v>0.1346462564011093</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.749639672279427</v>
+        <v>0.7496393225430431</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2049884177371786</v>
+        <v>0.2049883374485861</v>
       </c>
     </row>
     <row r="15">
@@ -1361,10 +1361,10 @@
         <v>0.1169305471037394</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1751889256560402</v>
+        <v>0.1751891587178109</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.05528370009533368</v>
+        <v>0.05528376985610883</v>
       </c>
     </row>
     <row r="16">
@@ -1473,10 +1473,10 @@
         <v>0.1301461039849694</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.096818936315644</v>
+        <v>1.096818699691968</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2799322344323758</v>
+        <v>0.2799321862860662</v>
       </c>
     </row>
     <row r="18">
@@ -1582,13 +1582,13 @@
         <v>0.08361725429902234</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1498648933441848</v>
+        <v>0.1498648033254177</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4190435456630801</v>
+        <v>0.4190436827610273</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1237384497324014</v>
+        <v>0.1237384859216197</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.08856507933321311</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7581638478441828</v>
+        <v>0.7581639646637217</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2069421337236361</v>
+        <v>0.2069421604550128</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>0.001989535183695157</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.4715921150277833</v>
+        <v>0.4715919321601794</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1374417124332401</v>
+        <v>0.1374416653184525</v>
       </c>
     </row>
     <row r="22">
@@ -1803,10 +1803,10 @@
         <v>0.06888492201306051</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2081701541087022</v>
+        <v>0.2081702706352115</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.06506480656829616</v>
+        <v>0.06506484080968722</v>
       </c>
     </row>
     <row r="24">
@@ -1856,13 +1856,13 @@
         <v>0.05010382232501498</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.0499485502554029</v>
+        <v>0.04994844259306275</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.343173627774777</v>
+        <v>0.3431735396775757</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.103343443792179</v>
+        <v>0.1033434196698393</v>
       </c>
     </row>
     <row r="25">
@@ -1915,10 +1915,10 @@
         <v>0.06456690147598731</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.06570287206729386</v>
+        <v>0.06570278988904077</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02143808175415995</v>
+        <v>0.02143805549918731</v>
       </c>
     </row>
     <row r="26">
@@ -1971,10 +1971,10 @@
         <v>0.0004533878273946801</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.435837817441737</v>
+        <v>0.4358379360973801</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1281541947975784</v>
+        <v>0.128154225873943</v>
       </c>
     </row>
     <row r="27">
@@ -2027,10 +2027,10 @@
         <v>-0.1474368640589792</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.500661639853379</v>
+        <v>0.5006615352552777</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1448825263824935</v>
+        <v>0.1448824997825506</v>
       </c>
     </row>
     <row r="28">
@@ -2139,10 +2139,10 @@
         <v>0.006212588908945715</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.074448613572643</v>
+        <v>1.074448451359923</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2753642150205216</v>
+        <v>0.2753641817779042</v>
       </c>
     </row>
     <row r="30">
@@ -2195,10 +2195,10 @@
         <v>-0.06792370091179456</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4108129486747381</v>
+        <v>0.4108128229461934</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.121561636587131</v>
+        <v>0.1215616032700952</v>
       </c>
     </row>
     <row r="31">
@@ -2410,19 +2410,19 @@
         <v>-0.1428135898652946</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1369685681169452</v>
+        <v>-0.1369684721360162</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.08465373366541651</v>
+        <v>-0.08465384163525524</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.08481199010149587</v>
+        <v>-0.08481188216896285</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4943025766506834</v>
+        <v>0.4943030082692816</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.143263087778047</v>
+        <v>0.1432631978524883</v>
       </c>
     </row>
   </sheetData>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1369685681169452</v>
+        <v>-0.1369684721360162</v>
       </c>
     </row>
     <row r="46">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.08481199010149587</v>
+        <v>-0.08481188216896285</v>
       </c>
     </row>
     <row r="65">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2115636496948003</v>
+        <v>0.2115637409371509</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1729036379504256</v>
+        <v>0.1729035459467481</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.359113130059071</v>
+        <v>2.359113480748983</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.06570287206729386</v>
+        <v>0.06570278988904077</v>
       </c>
     </row>
     <row r="75">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.096818936315644</v>
+        <v>1.096818699691968</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1751889256560402</v>
+        <v>0.1751891587178109</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.074448613572643</v>
+        <v>1.074448451359923</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2081701541087022</v>
+        <v>0.2081702706352115</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.009552111810016</v>
+        <v>1.009552245393886</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8765180183736909</v>
+        <v>0.8765181305377678</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3022413990830206</v>
+        <v>0.3022415456414491</v>
       </c>
     </row>
     <row r="81">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7581638478441828</v>
+        <v>0.7581639646637217</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.343173627774777</v>
+        <v>0.3431735396775757</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,14 +489,14 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>221.39</v>
+        <v>224.86</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.002972319986663252</v>
+        <v>0.01567370355603059</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.01499374977554113</v>
+        <v>0.009336573491569577</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.03511312107436493</v>
+        <v>0.03194128916393457</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.0421295276096163</v>
+        <v>0.06186251626056194</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.05465648797266798</v>
+        <v>-0.004515690855373067</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5955534152989539</v>
+        <v>0.5123402626404436</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7355988004056864</v>
+        <v>0.7728454491722569</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8223239158885782</v>
+        <v>0.8156014012352288</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.357746338714539</v>
+        <v>2.410374659443898</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4974395338607549</v>
+        <v>0.5052224862771546</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>64.53</v>
+        <v>65.27</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.0004650973534399139</v>
+        <v>0.01146750159256071</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.008438773037441338</v>
+        <v>0.02416439842918039</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.1156638763668756</v>
+        <v>0.09311669140587209</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.08399126663074763</v>
+        <v>0.1075852079595829</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.09647157051656619</v>
+        <v>-0.03774148782075115</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.6313448386664984</v>
+        <v>0.4995431294397643</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6097525232330041</v>
+        <v>0.6500522882019224</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7520702072957179</v>
+        <v>0.750186115602185</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.831369177845073</v>
+        <v>2.8753054099937</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5647729636722747</v>
+        <v>0.5707315900168117</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>57.95</v>
+        <v>58.35</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.005378233458945614</v>
+        <v>0.0069024625697236</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.001550657325434579</v>
+        <v>0.004821745837237046</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.06427915428758313</v>
+        <v>0.04720023682341146</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.06019028402326487</v>
+        <v>0.07696563575963933</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.0417041101973652</v>
+        <v>0.06594805781809776</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5824935554351334</v>
+        <v>0.494765278170973</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4337444448135737</v>
+        <v>0.4568820645831817</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4711595496238392</v>
+        <v>0.4721807243781531</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.726561079565085</v>
+        <v>1.745381065360848</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3970278920802612</v>
+        <v>0.4002348356678871</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>88.73</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.001462944547884981</v>
+        <v>0.01791948921149666</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01607891930955074</v>
+        <v>-0.002099242480629537</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.04013413010048617</v>
+        <v>-0.02829475352088973</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.02301251205586308</v>
+        <v>-0.03976183245635034</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1492035281577626</v>
+        <v>0.1775750102802862</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.02839488247490651</v>
+        <v>0.08820807177394108</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4370285954631488</v>
+        <v>0.4710960093814747</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4647340353381937</v>
+        <v>0.4912223763539227</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5294918557650767</v>
+        <v>0.5568994661977285</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1521677714490668</v>
+        <v>0.1590091286206394</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>24.62</v>
+        <v>24.99</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01191947868626086</v>
+        <v>0.01502838827264186</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.006857606696878515</v>
+        <v>0.01338199212278934</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.03750532297368925</v>
+        <v>0.04038298479886038</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.002851389179156394</v>
+        <v>0.05132516995623448</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2340852079048172</v>
+        <v>0.2208109726127276</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4821376634325114</v>
+        <v>0.4579495566937486</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.05825446485924024</v>
+        <v>0.08522767699138312</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.04932812526801289</v>
+        <v>0.06472833247978182</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4696583412406776</v>
+        <v>0.4917449374209693</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1369432683546266</v>
+        <v>0.1426104478951329</v>
       </c>
     </row>
     <row r="7">
@@ -872,12 +872,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>57.04</v>
+        <v>29.23</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.008172446873987882</v>
+        <v>-0.02077054711256499</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.02682271285204152</v>
+        <v>-0.02534178841887669</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.06140675723839495</v>
+        <v>-0.02011399205512243</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.07278545946692105</v>
+        <v>-0.006120377630386864</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2211518311608913</v>
+        <v>0.05485386170999207</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3180479656575941</v>
+        <v>0.2268906701892381</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.07814633484393241</v>
+        <v>0.1578430109630988</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1729035459467481</v>
+        <v>0.2706923025004506</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3530289810930396</v>
+        <v>0.5045071092052744</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1060354145157052</v>
+        <v>0.1458596188213153</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="F8" s="5" t="n">
-        <v>29.85</v>
+        <v>55.43</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.007646261396931253</v>
+        <v>-0.02822581669898416</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.01049422668702205</v>
+        <v>-0.02463490200195417</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.01911913446358127</v>
+        <v>0.01186567251484782</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.0111788590307853</v>
+        <v>0.06452853140088544</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.08387797346222969</v>
+        <v>0.1632738411366372</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.3090223441374398</v>
+        <v>0.2501328798984246</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1803262875005383</v>
+        <v>0.05571387334913958</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3132565596967947</v>
+        <v>0.1236872077614355</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5364193803290569</v>
+        <v>0.3148386330842943</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.153904655561796</v>
+        <v>0.09552969044481019</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.83</v>
+        <v>14.97</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.001731275571796753</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.001039524809807069</v>
+        <v>-0.01707152219450048</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.0006932567590716143</v>
+        <v>-0.01707152219450048</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.04851483004516077</v>
+        <v>0.01148649149345071</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.007573126304038835</v>
+        <v>-0.01577907761447994</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.235514632274501</v>
+        <v>0.1965082368078443</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1914241584779632</v>
+        <v>0.2779512865010123</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3780539193590973</v>
+        <v>0.266232300622969</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.009552245393886</v>
+        <v>0.8765182427018583</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2619237107936334</v>
+        <v>0.2334387747929565</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>14.97</v>
+        <v>28.31</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0006684644957444252</v>
+        <v>-0.01803678318209401</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.02220771673867816</v>
+        <v>-0.0237931218640558</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.007952278618002739</v>
+        <v>-0.03477669486590262</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01012149630859827</v>
+        <v>-0.07362565573692215</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.02981205632203854</v>
+        <v>-0.01633082729289914</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2384055562476268</v>
+        <v>0.1449651394337794</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2694173218412927</v>
+        <v>0.1741247080725403</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2652297525499963</v>
+        <v>0.3293322705309683</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.8765181305377678</v>
+        <v>0.9733061249017507</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2334387502177373</v>
+        <v>0.2542905626533405</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>61.37</v>
+        <v>60.53</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01808001708984375</v>
+        <v>-0.01368747217219635</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.06519424972605647</v>
+        <v>-0.06704683505349451</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.05088160445237566</v>
+        <v>-0.09263978998635947</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.113918610467648</v>
+        <v>-0.07474777631482277</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1792851239857223</v>
+        <v>0.1647103590057977</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.05670751568678689</v>
+        <v>-0.06687192739613268</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.06367718193046068</v>
+        <v>0.06114194710974208</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2115637409371509</v>
+        <v>0.1836017692738379</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>2.359113480748983</v>
+        <v>2.313135708457982</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.4976427390802709</v>
+        <v>0.490778343314652</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>34.35</v>
+        <v>44.79</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.01378131873957067</v>
+        <v>0.01472590699743748</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.003481367633661581</v>
+        <v>-0.00753379447243363</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.004973615196825154</v>
+        <v>-0.005329732850889446</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.02248152900537792</v>
+        <v>-0.003559507112267379</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.01434720292373293</v>
+        <v>0.08502912403163232</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1690048981997525</v>
+        <v>0.2825695018304974</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1358202404564801</v>
+        <v>0.03398672043682116</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.3468486167896776</v>
+        <v>0.0179963122502842</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.7379649878448646</v>
+        <v>0.3214180848141299</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2023022902075839</v>
+        <v>0.09735399418606105</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>44.14</v>
+        <v>33.92</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.006527141875656506</v>
+        <v>-0.0125182044913259</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01495206344809297</v>
+        <v>-0.02724407204012791</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.01604996011830151</v>
+        <v>-0.02247846042779356</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.04376084195062924</v>
+        <v>-0.03909351552241414</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.0901456547264794</v>
+        <v>-0.0188024741572741</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2834477351893188</v>
+        <v>0.103448292978698</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.007896339346866732</v>
+        <v>0.1248675656997471</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.009968994022164779</v>
+        <v>0.2682053272210221</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3022415456414491</v>
+        <v>0.7162087867282581</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09201980670730192</v>
+        <v>0.1972643206045384</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>66.78</v>
+        <v>66.73</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.000598636870847602</v>
+        <v>-0.0007486586294874753</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.01707394201390855</v>
+        <v>-0.02270057776909706</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.04024149149286349</v>
+        <v>-0.03107302605348949</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.03858336223005909</v>
+        <v>-0.03902648313930235</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.0007164970735891174</v>
+        <v>0.006983137152548613</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.03023562685151071</v>
+        <v>0.007606323619082866</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1475689414163481</v>
+        <v>0.1498184551144492</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1346462564011093</v>
+        <v>0.1336102413856679</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7496393225430431</v>
+        <v>0.7483294399657308</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2049883374485861</v>
+        <v>0.2046875540689819</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>90.42</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.01449593276353878</v>
+        <v>-0.002986027964321902</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02089875838727406</v>
+        <v>-0.01561476606883916</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.02385835204579057</v>
+        <v>-0.02740318101871886</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.04881127192106649</v>
+        <v>-0.04653623885628322</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.0118440012333263</v>
+        <v>-0.01607920234752569</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.03386991669916184</v>
+        <v>0.03489089151861147</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.09025612559748208</v>
+        <v>0.09209466358783946</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1169305471037394</v>
+        <v>0.1104017067053986</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1751891587178109</v>
+        <v>0.1716798948435792</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.05528376985610883</v>
+        <v>0.05423231884661828</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16.15</v>
+        <v>16.16</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01162793955222363</v>
+        <v>0.0006192092333154875</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.0223971446114285</v>
+        <v>-0.01882206914793394</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.04775940505114529</v>
+        <v>-0.04716976888241509</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.09116492951611732</v>
+        <v>-0.0755148586608797</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.006765105092444879</v>
+        <v>-0.02533172968797359</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.133504672606312</v>
+        <v>0.1059087352167407</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.01677893693251442</v>
+        <v>0.02696467511741929</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.06529832249739687</v>
+        <v>0.07927405727143655</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8483113348529188</v>
+        <v>0.8494560281558461</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2272273977004544</v>
+        <v>0.2274806936054963</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>35.44</v>
+        <v>113.05</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.006169411711848038</v>
+        <v>0.008834602130402658</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01336301689044384</v>
+        <v>0.005693438028631315</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.04008666347879741</v>
+        <v>-0.01318081825258088</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.06736845719186879</v>
+        <v>-0.03094462966765765</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.05769747270478154</v>
+        <v>-0.09006757086620099</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1203021676470917</v>
+        <v>0.06124890796792726</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.05815392441037681</v>
+        <v>0.0992330430223205</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1301461039849694</v>
+        <v>0.169065491759407</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.096818699691968</v>
+        <v>0.4315802307947292</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2799321862860662</v>
+        <v>0.1270380126504891</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>108.34</v>
+        <v>35.47</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.01140615057733896</v>
+        <v>0.0008465743554382232</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.00932703243204247</v>
+        <v>-0.01772360506316273</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.0397944289665717</v>
+        <v>-0.04109219758831528</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.05873155713160483</v>
+        <v>-0.04829619573255439</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.08727886164031606</v>
+        <v>-0.07533887757208646</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.2163466566643109</v>
+        <v>0.07793326127208955</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.04929778535487284</v>
+        <v>0.06777895842537007</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.07037429414462748</v>
+        <v>0.1440619563528258</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.009042581501153668</v>
+        <v>1.098594049455126</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.003005153837665642</v>
+        <v>0.2802933184921583</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>112.06</v>
+        <v>50.71</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.01103168323124892</v>
+        <v>0.004755257736571705</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01286116215333621</v>
+        <v>-0.005491323490432132</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.01485716432005491</v>
+        <v>-0.0003942530641464215</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.07503098516547224</v>
+        <v>0.002768427733701673</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.09299882808056792</v>
+        <v>-0.05918371708903647</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.09967089072730628</v>
+        <v>0.07927226352083983</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.08361725429902234</v>
+        <v>0.08749184789455611</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1498648033254177</v>
+        <v>0.08408868255303759</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4190436827610273</v>
+        <v>0.7665244874588504</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1237384859216197</v>
+        <v>0.2088522430172191</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>50.47</v>
+        <v>91.44</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.004732752279678509</v>
+        <v>0.01206423891193942</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.01598751569871726</v>
+        <v>-0.0002186381288713513</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.008190168521067243</v>
+        <v>-0.04020147304097654</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.0184752427474012</v>
+        <v>-0.05663878929624211</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.07292427454357298</v>
+        <v>-0.02108983131859388</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1249439139647659</v>
+        <v>0.08845875667548309</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.07191388656859599</v>
+        <v>0.03215509956902629</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.08856507933321311</v>
+        <v>0.01590667361499376</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7581639646637217</v>
+        <v>0.4893456613475176</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2069421604550128</v>
+        <v>0.1419975395034101</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>90.34999999999999</v>
+        <v>108.43</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.01386164848710747</v>
+        <v>0.0008307547565762352</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.0181482094095593</v>
+        <v>-0.005046825424995016</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.05560781641732171</v>
+        <v>-0.02918794936852742</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.07909491476867558</v>
+        <v>-0.06879081044558699</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.008667993425695242</v>
+        <v>-0.1132646271866501</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.07661580032239312</v>
+        <v>0.1785869598388672</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.01133762428695229</v>
+        <v>0.05671961465944175</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.001989535183695157</v>
+        <v>0.07263087053510953</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.4715919321601794</v>
+        <v>0.009880848425323663</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1374416653184525</v>
+        <v>0.003282827393119803</v>
       </c>
     </row>
     <row r="22">
@@ -1726,28 +1726,28 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>66.45</v>
+        <v>67.12</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01174897294208588</v>
+        <v>0.0100828567209974</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.01817380838338334</v>
+        <v>-0.004302045687179623</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.00075294309057794</v>
+        <v>0.009778870376738524</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.05610801835259482</v>
+        <v>-0.0191436146829107</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.1188172162676773</v>
+        <v>-0.09845526530720994</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.0783836108419369</v>
+        <v>0.03118768663241855</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.07681085616742789</v>
+        <v>0.09852707729625743</v>
       </c>
       <c r="N22" s="6" t="inlineStr"/>
       <c r="O22" s="6" t="inlineStr"/>
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>95.56999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.008404208151863379</v>
+        <v>-0.003871536546651955</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.03474398916458021</v>
+        <v>-0.02688341851770915</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02915484229381571</v>
+        <v>-0.04360060204307425</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.08413990328398835</v>
+        <v>-0.06648368489419587</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.04276839743278205</v>
+        <v>-0.04503967683021282</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.0204249539011585</v>
+        <v>-0.05865572424691845</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.06478768722323736</v>
+        <v>0.06921532633590721</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.06888492201306051</v>
+        <v>0.07550739457694244</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2081702706352115</v>
+        <v>0.2034925631271458</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.06506484080968722</v>
+        <v>0.0636885156563749</v>
       </c>
     </row>
     <row r="24">
@@ -1832,37 +1832,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>39.06</v>
+        <v>38.86</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01163965281235946</v>
+        <v>-0.005120347053449215</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02154300689130062</v>
+        <v>-0.02361805640020431</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03340753474928682</v>
+        <v>-0.04120400244863476</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.0714213358766892</v>
+        <v>-0.06792765404688073</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.06180782139489882</v>
+        <v>-0.06967631190237833</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.03947464595705807</v>
+        <v>0.01544036304560059</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.05010382232501498</v>
+        <v>0.05356654919825066</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.04994844259306275</v>
+        <v>0.0445724492898294</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3431735396775757</v>
+        <v>0.3362961126475299</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1033434196698393</v>
+        <v>0.1014570533442207</v>
       </c>
     </row>
     <row r="25">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.18</v>
+        <v>13.14</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.006033176645940386</v>
+        <v>-0.003034898401126696</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.01641785967294096</v>
+        <v>-0.00755282700333193</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.009022547657005053</v>
+        <v>-0.01128665304445642</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.06058442223615079</v>
+        <v>-0.05194800369332064</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0866250847930784</v>
+        <v>-0.09316766384539654</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.03393238073581661</v>
+        <v>-0.04918583155125544</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1135833535781323</v>
+        <v>0.1166907646796613</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.06456690147598731</v>
+        <v>0.07909554298560306</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.06570278988904077</v>
+        <v>0.06246849019593026</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02143805549918731</v>
+        <v>0.02040368815196847</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.57</v>
+        <v>16.61</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.004804800332669057</v>
+        <v>0.002414056503563966</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.008378180569652338</v>
+        <v>-0.001202558714628155</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.0006038785751414366</v>
+        <v>-0.006578870067002418</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05798751841475147</v>
+        <v>-0.037659305325072</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.03774678539192411</v>
+        <v>-0.03430233293123763</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.03714076826798496</v>
+        <v>0.01173864071375919</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.01926307782516445</v>
+        <v>-0.01140944602913707</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.0004533878273946801</v>
+        <v>0.004887336474318715</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4358379360973801</v>
+        <v>0.4393040110629953</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.128154225873943</v>
+        <v>0.1290612745983679</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>164.26</v>
+        <v>164.58</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.009109065130644134</v>
+        <v>0.001948175666141472</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.03177129138558799</v>
+        <v>-0.02146382399637103</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.03733229908978464</v>
+        <v>-0.03922942849377942</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.1203813340744013</v>
+        <v>-0.09759843499946785</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.03314666854262405</v>
+        <v>0.007344821351320752</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.06753056609566443</v>
+        <v>0.0574948997479876</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.1348566687393248</v>
+        <v>-0.1245892370864127</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1474368640589792</v>
+        <v>-0.1278328472738053</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5006615352552777</v>
+        <v>0.5035851923432535</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1448824997825506</v>
+        <v>0.1456255215223217</v>
       </c>
     </row>
     <row r="28">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.11</v>
+        <v>16.21</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.00983404074434191</v>
+        <v>0.006207229691651328</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.006168937678527109</v>
+        <v>-0.01037851556800629</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.0277609591396879</v>
+        <v>-0.0175758130622633</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.1099447364186505</v>
+        <v>-0.07052760389444712</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.01003139830719513</v>
+        <v>-0.006740233603463097</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1218663645900984</v>
+        <v>0.1042233479216916</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1793173051912436</v>
+        <v>-0.1657231688177265</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1742695837336306</v>
+        <v>-0.1687179956680689</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1733431280018516</v>
+        <v>0.1806263383044795</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05473092064827267</v>
+        <v>0.05690873979921696</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>25.3</v>
+        <v>25.46</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.009397089657928959</v>
+        <v>0.006324104831502808</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02692310626690209</v>
+        <v>-0.01546796273928885</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.0302798356039482</v>
+        <v>-0.01812576996419513</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.1047417186074951</v>
+        <v>-0.06842300931041567</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.1464237598501302</v>
+        <v>-0.1453508458537097</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.01700187882372828</v>
+        <v>-0.04077132828413299</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.02668969437605895</v>
+        <v>-0.0129622368012704</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.006212588908945715</v>
+        <v>0.01336460697269248</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.074448451359923</v>
+        <v>1.087567317595326</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2753641817779042</v>
+        <v>0.2780470130773751</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>60.39</v>
+        <v>60.47</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.001983125685231846</v>
+        <v>0.001324752970081944</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01596870717439702</v>
+        <v>-0.01014894304036928</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.007233312973231265</v>
+        <v>-0.01626809793625317</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.06372093969537307</v>
+        <v>-0.04000635641553152</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.08776431761977632</v>
+        <v>-0.08930723145939401</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.03542521474727578</v>
+        <v>-0.006321939232857177</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.08923003637125138</v>
+        <v>-0.08050283032898731</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.06792370091179456</v>
+        <v>-0.0727059987699139</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4108128229461934</v>
+        <v>0.4126818014236211</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1215616032700952</v>
+        <v>0.1220566487517707</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>15.17</v>
+        <v>15.22</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.00849673940001916</v>
+        <v>0.003295991462320291</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.01607500108589832</v>
+        <v>0.02010725128691693</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.0187580828678825</v>
+        <v>-0.009114543800629371</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.1149357866689457</v>
+        <v>-0.075895512959259</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.08449002077939538</v>
+        <v>-0.08478646812347734</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.02740343511605681</v>
+        <v>0.001228375833066897</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.1067553025056834</v>
+        <v>-0.095737400586413</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1212458666746806</v>
+        <v>-0.1086996149710376</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2454799873564217</v>
+        <v>0.2495850787612395</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.07591736723846476</v>
+        <v>0.07709814239766044</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>50.64</v>
+        <v>50.94</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.01401871518977371</v>
+        <v>0.005924155621571225</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.03726234108993298</v>
+        <v>-0.01925298472160086</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.04217892164343251</v>
+        <v>-0.04499440418097689</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.07218765681983697</v>
+        <v>-0.06066754459337531</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.06877531454591457</v>
+        <v>-0.05736495626016236</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.01272600720194661</v>
+        <v>-0.0453445119560214</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.1158618972704618</v>
+        <v>-0.1020426127157633</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1249970256427495</v>
+        <v>-0.1261569560016438</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1551193212495849</v>
+        <v>0.1619625289781135</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.04924187792160084</v>
+        <v>0.05130978768502148</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>110.01</v>
+        <v>110.69</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.009989206109749738</v>
+        <v>0.006181258903474207</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01274340989909661</v>
+        <v>0.0002710896286293174</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.01061246766135837</v>
+        <v>-0.005301908198801941</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.06612903831678718</v>
+        <v>-0.03487662320038354</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1599083260787568</v>
+        <v>-0.1395366684810992</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.02149281471405839</v>
+        <v>-0.0523072525502577</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.061773901478403</v>
+        <v>-0.0470300793537306</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.09787518881816093</v>
+        <v>-0.08913401131773757</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3348206917128302</v>
+        <v>0.3430715639980215</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1010515266426513</v>
+        <v>0.1033154964866188</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>118.41</v>
+        <v>119.1</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.007460179102110498</v>
+        <v>0.005827166545663287</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.008457498930849794</v>
+        <v>0.006762429431327099</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.03629851863575972</v>
+        <v>-0.038508146982281</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.06469190292830751</v>
+        <v>-0.05752950949158364</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1428135898652946</v>
+        <v>-0.122761396247222</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1369684721360162</v>
+        <v>-0.1412531309074114</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.08465384163525524</v>
+        <v>-0.07314736046632031</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.08481188216896285</v>
+        <v>-0.09071960169998372</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4943030082692816</v>
+        <v>0.5030101266344409</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1432631978524883</v>
+        <v>0.1454794497724095</v>
       </c>
     </row>
   </sheetData>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.08399126663074763</v>
+        <v>0.1075852079595829</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1203813340744013</v>
+        <v>-0.09759843499946785</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.07278545946692105</v>
+        <v>0.07696563575963933</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1149357866689457</v>
+        <v>-0.075895512959259</v>
       </c>
     </row>
     <row r="19">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.06019028402326487</v>
+        <v>0.06452853140088544</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.113918610467648</v>
+        <v>-0.0755148586608797</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.0421295276096163</v>
+        <v>0.06186251626056194</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1099447364186505</v>
+        <v>-0.07474777631482277</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.0111788590307853</v>
+        <v>0.05132516995623448</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.1047417186074951</v>
+        <v>-0.07362565573692215</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01012149630859827</v>
+        <v>0.01148649149345071</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="K22" s="11" t="n">
-        <v>-0.09116492951611732</v>
+        <v>-0.07052760389444712</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.002851389179156394</v>
+        <v>0.002768427733701673</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.08413990328398835</v>
+        <v>-0.06879081044558699</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.0184752427474012</v>
+        <v>-0.003559507112267379</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.07909491476867558</v>
+        <v>-0.06842300931041567</v>
       </c>
     </row>
     <row r="25">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.02248152900537792</v>
+        <v>-0.006120377630386864</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07503098516547224</v>
+        <v>-0.06792765404688073</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.02301251205586308</v>
+        <v>-0.0191436146829107</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07218765681983697</v>
+        <v>-0.06648368489419587</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2340852079048172</v>
+        <v>0.2208109726127276</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3561,21 +3561,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1599083260787568</v>
+        <v>-0.1453508458537097</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2211518311608913</v>
+        <v>0.1775750102802862</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3606,21 +3606,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1464237598501302</v>
+        <v>-0.1395366684810992</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1792851239857223</v>
+        <v>0.1647103590057977</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1428135898652946</v>
+        <v>-0.122761396247222</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1492035281577626</v>
+        <v>0.1632738411366372</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1188172162676773</v>
+        <v>-0.1132646271866501</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.0901456547264794</v>
+        <v>0.08502912403163232</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.09647157051656619</v>
+        <v>-0.09845526530720994</v>
       </c>
     </row>
     <row r="36">
@@ -3764,21 +3764,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.08387797346222969</v>
+        <v>0.06594805781809776</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.09299882808056792</v>
+        <v>-0.09316766384539654</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.0417041101973652</v>
+        <v>0.05485386170999207</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.08776431761977632</v>
+        <v>-0.09006757086620099</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.03314666854262405</v>
+        <v>0.007344821351320752</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.08727886164031606</v>
+        <v>-0.08930723145939401</v>
       </c>
     </row>
     <row r="39">
@@ -3899,21 +3899,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.01003139830719513</v>
+        <v>0.006983137152548613</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.0866250847930784</v>
+        <v>-0.08478646812347734</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0007164970735891174</v>
+        <v>-0.004515690855373067</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.08449002077939538</v>
+        <v>-0.07533887757208646</v>
       </c>
     </row>
     <row r="41"/>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.6313448386664984</v>
+        <v>0.5123402626404436</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1369684721360162</v>
+        <v>-0.1412531309074114</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5955534152989539</v>
+        <v>0.4995431294397643</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,12 +4117,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.03393238073581661</v>
+        <v>-0.06687192739613268</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5824935554351334</v>
+        <v>0.494765278170973</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.02149281471405839</v>
+        <v>-0.05865572424691845</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4821376634325114</v>
+        <v>0.4579495566937486</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0204249539011585</v>
+        <v>-0.0523072525502577</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3180479656575941</v>
+        <v>0.2825695018304974</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,21 +4252,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01272600720194661</v>
+        <v>-0.04918583155125544</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E50" s="11" t="n">
-        <v>0.3090223441374398</v>
+        <v>0.2501328798984246</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.01700187882372828</v>
+        <v>-0.0453445119560214</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2834477351893188</v>
+        <v>0.2268906701892381</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.02740343511605681</v>
+        <v>-0.04077132828413299</v>
       </c>
     </row>
     <row r="52">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2384055562476268</v>
+        <v>0.1965082368078443</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.02839488247490651</v>
+        <v>-0.006321939232857177</v>
       </c>
     </row>
     <row r="53">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.235514632274501</v>
+        <v>0.1785869598388672</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.03023562685151071</v>
+        <v>0.001228375833066897</v>
       </c>
     </row>
     <row r="54">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2163466566643109</v>
+        <v>0.1449651394337794</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.03386991669916184</v>
+        <v>0.007606323619082866</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8223239158885782</v>
+        <v>0.8156014012352288</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1742695837336306</v>
+        <v>-0.1687179956680689</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7520702072957179</v>
+        <v>0.750186115602185</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1474368640589792</v>
+        <v>-0.1278328472738053</v>
       </c>
     </row>
     <row r="61">
@@ -4651,21 +4651,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.4711595496238392</v>
+        <v>0.4912223763539227</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1249970256427495</v>
+        <v>-0.1261569560016438</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4647340353381937</v>
+        <v>0.4721807243781531</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1212458666746806</v>
+        <v>-0.1086996149710376</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.3780539193590973</v>
+        <v>0.3293322705309683</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4763,21 +4763,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.09787518881816093</v>
+        <v>-0.09071960169998372</v>
       </c>
     </row>
     <row r="64">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.3468486167896776</v>
+        <v>0.2706923025004506</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4808,21 +4808,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.08481188216896285</v>
+        <v>-0.08913401131773757</v>
       </c>
     </row>
     <row r="65">
@@ -4831,21 +4831,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E65" s="11" t="n">
-        <v>0.3132565596967947</v>
+        <v>0.2682053272210221</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06792370091179456</v>
+        <v>-0.0727059987699139</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.2652297525499963</v>
+        <v>0.266232300622969</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.0004533878273946801</v>
+        <v>0.004887336474318715</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2115637409371509</v>
+        <v>0.1836017692738379</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.001989535183695157</v>
+        <v>0.01336460697269248</v>
       </c>
     </row>
     <row r="68">
@@ -4966,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1729035459467481</v>
+        <v>0.169065491759407</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.006212588908945715</v>
+        <v>0.01590667361499376</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.831369177845073</v>
+        <v>2.8753054099937</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.009042581501153668</v>
+        <v>0.009880848425323663</v>
       </c>
     </row>
     <row r="74">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.359113480748983</v>
+        <v>2.410374659443898</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.06570278988904077</v>
+        <v>0.06246849019593026</v>
       </c>
     </row>
     <row r="75">
@@ -5162,21 +5162,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.357746338714539</v>
+        <v>2.313135708457982</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1551193212495849</v>
+        <v>0.1619625289781135</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.726561079565085</v>
+        <v>1.745381065360848</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5229,21 +5229,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1733431280018516</v>
+        <v>0.1716798948435792</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.096818699691968</v>
+        <v>1.098594049455126</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5274,21 +5274,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1751891587178109</v>
+        <v>0.1806263383044795</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.074448451359923</v>
+        <v>1.087567317595326</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2081702706352115</v>
+        <v>0.2034925631271458</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.009552245393886</v>
+        <v>0.9733061249017507</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2454799873564217</v>
+        <v>0.2495850787612395</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8765181305377678</v>
+        <v>0.8765182427018583</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5409,21 +5409,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3022415456414491</v>
+        <v>0.3148386330842943</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8483113348529188</v>
+        <v>0.8494560281558461</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3348206917128302</v>
+        <v>0.3214180848141299</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7581639646637217</v>
+        <v>0.7665244874588504</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3431735396775757</v>
+        <v>0.3362961126475299</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -742,13 +742,13 @@
         <v>0.4568820645831817</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4721807243781531</v>
+        <v>0.4721808660689115</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.745381065360848</v>
+        <v>1.745381311734659</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4002348356678871</v>
+        <v>0.4002348775541404</v>
       </c>
     </row>
     <row r="5">
@@ -798,13 +798,13 @@
         <v>0.4710960093814747</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4912223763539227</v>
+        <v>0.4912224702745538</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5568994661977285</v>
+        <v>0.556899568573531</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1590091286206394</v>
+        <v>0.1590091540246532</v>
       </c>
     </row>
     <row r="6">
@@ -910,7 +910,7 @@
         <v>0.1578430109630988</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2706923025004506</v>
+        <v>0.2706921971389284</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>0.5045071092052744</v>
@@ -969,10 +969,10 @@
         <v>0.1236872077614355</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3148386330842943</v>
+        <v>0.3148385141081007</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.09552969044481019</v>
+        <v>0.09552965740096897</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.266232300622969</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.8765182427018583</v>
+        <v>0.8765180183736909</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2334387747929565</v>
+        <v>0.2334387256425201</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.3293322705309683</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9733061249017507</v>
+        <v>0.9733062560761798</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2542905626533405</v>
+        <v>0.2542905904460961</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         <v>0.0179963122502842</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3214180848141299</v>
+        <v>0.321418233530764</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.09735399418606105</v>
+        <v>0.09735403535264009</v>
       </c>
     </row>
     <row r="13">
@@ -1302,13 +1302,13 @@
         <v>0.1498184551144492</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1336102413856679</v>
+        <v>0.1336103148482994</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7483294399657308</v>
+        <v>0.7483297894402814</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2046875540689819</v>
+        <v>0.204687634337533</v>
       </c>
     </row>
     <row r="15">
@@ -1417,10 +1417,10 @@
         <v>0.07927405727143655</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8494560281558461</v>
+        <v>0.8494558262975014</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2274806936054963</v>
+        <v>0.2274806489478192</v>
       </c>
     </row>
     <row r="17">
@@ -1529,10 +1529,10 @@
         <v>0.1440619563528258</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>1.098594049455126</v>
+        <v>1.098593812631131</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2802933184921583</v>
+        <v>0.280293270332266</v>
       </c>
     </row>
     <row r="19">
@@ -1641,10 +1641,10 @@
         <v>0.01590667361499376</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4893456613475176</v>
+        <v>0.4893457538844046</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1419975395034101</v>
+        <v>0.1419975631551604</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>0.07263087053510953</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.009880848425323663</v>
+        <v>0.009880920185073805</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.003282827393119803</v>
+        <v>0.003282851156755973</v>
       </c>
     </row>
     <row r="22">
@@ -1803,10 +1803,10 @@
         <v>0.07550739457694244</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2034925631271458</v>
+        <v>0.2034926792024963</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.0636885156563749</v>
+        <v>0.06368854985351557</v>
       </c>
     </row>
     <row r="24">
@@ -1915,10 +1915,10 @@
         <v>0.07909554298560306</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.06246849019593026</v>
+        <v>0.06246857212478085</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02040368815196847</v>
+        <v>0.02040371438035393</v>
       </c>
     </row>
     <row r="26">
@@ -1971,10 +1971,10 @@
         <v>0.004887336474318715</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4393040110629953</v>
+        <v>0.4393041300050797</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1290612745983679</v>
+        <v>0.129061305699719</v>
       </c>
     </row>
     <row r="27">
@@ -2139,10 +2139,10 @@
         <v>0.01336460697269248</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.087567317595326</v>
+        <v>1.087567480833871</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2780470130773751</v>
+        <v>0.2780470463899183</v>
       </c>
     </row>
     <row r="30">
@@ -2195,10 +2195,10 @@
         <v>-0.0727059987699139</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4126818014236211</v>
+        <v>0.412681927318725</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1220566487517707</v>
+        <v>0.1220566820835123</v>
       </c>
     </row>
     <row r="31">
@@ -2307,10 +2307,10 @@
         <v>-0.1261569560016438</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1619625289781135</v>
+        <v>0.1619624278701512</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.05130978768502148</v>
+        <v>0.05130975719184283</v>
       </c>
     </row>
     <row r="33">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.4912223763539227</v>
+        <v>0.4912224702745538</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4721807243781531</v>
+        <v>0.4721808660689115</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.2706923025004506</v>
+        <v>0.2706921971389284</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.009880848425323663</v>
+        <v>0.009880920185073805</v>
       </c>
     </row>
     <row r="74">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.06246849019593026</v>
+        <v>0.06246857212478085</v>
       </c>
     </row>
     <row r="75">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1619625289781135</v>
+        <v>0.1619624278701512</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.745381065360848</v>
+        <v>1.745381311734659</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.098594049455126</v>
+        <v>1.098593812631131</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.087567317595326</v>
+        <v>1.087567480833871</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2034925631271458</v>
+        <v>0.2034926792024963</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9733061249017507</v>
+        <v>0.9733062560761798</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8765182427018583</v>
+        <v>0.8765180183736909</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3148386330842943</v>
+        <v>0.3148385141081007</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8494560281558461</v>
+        <v>0.8494558262975014</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3214180848141299</v>
+        <v>0.321418233530764</v>
       </c>
     </row>
     <row r="82">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -630,7 +630,7 @@
         <v>0.7728454491722569</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8156014012352288</v>
+        <v>0.8156015130808307</v>
       </c>
       <c r="O2" s="6" t="n">
         <v>2.410374659443898</v>
@@ -745,10 +745,10 @@
         <v>0.4721808660689115</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.745381311734659</v>
+        <v>1.745381065360848</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4002348775541404</v>
+        <v>0.4002348356678871</v>
       </c>
     </row>
     <row r="5">
@@ -969,10 +969,10 @@
         <v>0.1236872077614355</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3148385141081007</v>
+        <v>0.3148386330842943</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.09552965740096897</v>
+        <v>0.09552969044481019</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.266232300622969</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.8765180183736909</v>
+        <v>0.8765182427018583</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2334387256425201</v>
+        <v>0.2334387747929565</v>
       </c>
     </row>
     <row r="10">
@@ -1137,10 +1137,10 @@
         <v>0.1836017692738379</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>2.313135708457982</v>
+        <v>2.313136054347908</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.490778343314652</v>
+        <v>0.4907783951935203</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.0179963122502842</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.321418233530764</v>
+        <v>0.3214180848141299</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.09735403535264009</v>
+        <v>0.09735399418606105</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.2682053272210221</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.7162087867282581</v>
+        <v>0.7162086211076164</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1972643206045384</v>
+        <v>0.1972642820910249</v>
       </c>
     </row>
     <row r="14">
@@ -1302,7 +1302,7 @@
         <v>0.1498184551144492</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1336103148482994</v>
+        <v>0.1336102413856679</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>0.7483297894402814</v>
@@ -1361,10 +1361,10 @@
         <v>0.1104017067053986</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1716798948435792</v>
+        <v>0.1716797786606699</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.05423231884661828</v>
+        <v>0.05423228400098545</v>
       </c>
     </row>
     <row r="16">
@@ -1417,10 +1417,10 @@
         <v>0.07927405727143655</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8494558262975014</v>
+        <v>0.8494556244392009</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2274806489478192</v>
+        <v>0.2274806042901487</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.169065491759407</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.4315802307947292</v>
+        <v>0.4315803691038822</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1270380126504891</v>
+        <v>0.1270380489459675</v>
       </c>
     </row>
     <row r="18">
@@ -1529,10 +1529,10 @@
         <v>0.1440619563528258</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>1.098593812631131</v>
+        <v>1.098594049455126</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.280293270332266</v>
+        <v>0.2802933184921583</v>
       </c>
     </row>
     <row r="19">
@@ -1641,10 +1641,10 @@
         <v>0.01590667361499376</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4893457538844046</v>
+        <v>0.4893455688106421</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1419975631551604</v>
+        <v>0.1419975158516618</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>0.07263087053510953</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.009880920185073805</v>
+        <v>0.009880776665583735</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.003282851156755973</v>
+        <v>0.003282803629485853</v>
       </c>
     </row>
     <row r="22">
@@ -1803,10 +1803,10 @@
         <v>0.07550739457694244</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2034926792024963</v>
+        <v>0.2034927952778689</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.06368854985351557</v>
+        <v>0.06368858405066047</v>
       </c>
     </row>
     <row r="24">
@@ -1859,10 +1859,10 @@
         <v>0.0445724492898294</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3362961126475299</v>
+        <v>0.3362960250014166</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1014570533442207</v>
+        <v>0.1014570292631229</v>
       </c>
     </row>
     <row r="25">
@@ -2027,10 +2027,10 @@
         <v>-0.1278328472738053</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5035851923432535</v>
+        <v>0.5035850875413765</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1456255215223217</v>
+        <v>0.1456254949051163</v>
       </c>
     </row>
     <row r="28">
@@ -2251,10 +2251,10 @@
         <v>-0.1086996149710376</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2495850787612395</v>
+        <v>0.2495849809211019</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.07709814239766044</v>
+        <v>0.07709811428608027</v>
       </c>
     </row>
     <row r="32">
@@ -2304,7 +2304,7 @@
         <v>-0.1020426127157633</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1261569560016438</v>
+        <v>-0.1261570131847823</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>0.1619624278701512</v>
@@ -2410,7 +2410,7 @@
         <v>-0.122761396247222</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1412531309074114</v>
+        <v>-0.1412530364276703</v>
       </c>
       <c r="M34" s="6" t="n">
         <v>-0.07314736046632031</v>
@@ -2419,10 +2419,10 @@
         <v>-0.09071960169998372</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5030101266344409</v>
+        <v>0.5030105607681525</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1454794497724095</v>
+        <v>0.1454795600602441</v>
       </c>
     </row>
   </sheetData>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1412531309074114</v>
+        <v>-0.1412530364276703</v>
       </c>
     </row>
     <row r="46">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8156014012352288</v>
+        <v>0.8156015130808307</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1261569560016438</v>
+        <v>-0.1261570131847823</v>
       </c>
     </row>
     <row r="62">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.009880920185073805</v>
+        <v>0.009880776665583735</v>
       </c>
     </row>
     <row r="74">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.313135708457982</v>
+        <v>2.313136054347908</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.745381311734659</v>
+        <v>1.745381065360848</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1716798948435792</v>
+        <v>0.1716797786606699</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.098593812631131</v>
+        <v>1.098594049455126</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2034926792024963</v>
+        <v>0.2034927952778689</v>
       </c>
     </row>
     <row r="79">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2495850787612395</v>
+        <v>0.2495849809211019</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8765180183736909</v>
+        <v>0.8765182427018583</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3148385141081007</v>
+        <v>0.3148386330842943</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8494558262975014</v>
+        <v>0.8494556244392009</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.321418233530764</v>
+        <v>0.3214180848141299</v>
       </c>
     </row>
     <row r="82">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3362961126475299</v>
+        <v>0.3362960250014166</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>224.86</v>
+        <v>226.42</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.01567370355603059</v>
+        <v>0.006937639217109881</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.009336573491569577</v>
+        <v>0.002080111648821159</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.03194128916393457</v>
+        <v>0.02605700841850633</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.06186251626056194</v>
+        <v>0.05907668871062977</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.004515690855373067</v>
+        <v>0.05527591697102219</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5123402626404436</v>
+        <v>0.515085961318938</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7728454491722569</v>
+        <v>0.7427209876247423</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8156015130808307</v>
+        <v>0.8302339377083365</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.410374659443898</v>
+        <v>2.423538326959187</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5052224862771546</v>
+        <v>0.5071566637258926</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>65.27</v>
+        <v>66.58</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01146750159256071</v>
+        <v>0.0200705569995987</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.02416439842918039</v>
+        <v>0.03417217569887243</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.09311669140587209</v>
+        <v>0.08436482372060716</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1075852079595829</v>
+        <v>0.1210641945663911</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.03774148782075115</v>
+        <v>0.0343327480219815</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4995431294397643</v>
+        <v>0.5254719064758544</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6500522882019224</v>
+        <v>0.6223866526193755</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.750186115602185</v>
+        <v>0.7581633717962097</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.8753054099937</v>
+        <v>2.925537458770556</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5707315900168117</v>
+        <v>0.5774891298694234</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>58.35</v>
+        <v>58.86</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.0069024625697236</v>
+        <v>0.008740396736371059</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.004821745837237046</v>
+        <v>0.006842311531700895</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.04720023682341146</v>
+        <v>0.05069618224528782</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.07696563575963933</v>
+        <v>0.08537711796418557</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.06594805781809776</v>
+        <v>0.1003925736283262</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.494765278170973</v>
+        <v>0.5003987340473564</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4568820645831817</v>
+        <v>0.4538246741524081</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4721808660689115</v>
+        <v>0.4726055479882969</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.745381065360848</v>
+        <v>1.741151165470987</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4002348356678871</v>
+        <v>0.3995153365664166</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>90.31999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.01791948921149666</v>
+        <v>0.003210816170363229</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.002099242480629537</v>
+        <v>0.008009803377371449</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.02829475352088973</v>
+        <v>-0.02254580805496198</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.03976183245635034</v>
+        <v>-0.04035159534505117</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1775750102802862</v>
+        <v>0.1755318948869795</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.08820807177394108</v>
+        <v>0.08324125754278122</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4710960093814747</v>
+        <v>0.4450683885016133</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4912224702745538</v>
+        <v>0.5131469586456223</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.556899568573531</v>
+        <v>0.5989630546133098</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1590091540246532</v>
+        <v>0.1693543701223044</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>24.99</v>
+        <v>25.05</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01502838827264186</v>
+        <v>0.002400939035290595</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.01338199212278934</v>
+        <v>0.02119847272153286</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.04038298479886038</v>
+        <v>0.05562577835177751</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.05132516995623448</v>
+        <v>0.0774193220241095</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2208109726127276</v>
+        <v>0.2213553855443435</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4579495566937486</v>
+        <v>0.4483393751505309</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.08522767699138312</v>
+        <v>0.120703649659951</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.06472833247978182</v>
+        <v>0.0621251230163824</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4917449374209693</v>
+        <v>0.4852030020668696</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1426104478951329</v>
+        <v>0.1409377228771833</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.23</v>
+        <v>15.16</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.02077054711256499</v>
+        <v>0.0126920225113003</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.02534178841887669</v>
+        <v>-0.01044385447776242</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.02011399205512243</v>
+        <v>0.0006600811309331878</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.006120377630386864</v>
+        <v>0.02156332153193508</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.05485386170999207</v>
+        <v>0.01066665649414067</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2268906701892381</v>
+        <v>0.1947738267434951</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1578430109630988</v>
+        <v>0.28338623046875</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2706921971389284</v>
+        <v>0.2792623476479155</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5045071092052744</v>
+        <v>0.9096593329808276</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1458596188213153</v>
+        <v>0.240657675091156</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>55.43</v>
+        <v>55.82</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.02822581669898416</v>
+        <v>0.007035890086618313</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.02463490200195417</v>
+        <v>-0.01759943691254706</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.01186567251484782</v>
+        <v>0.02422017788668285</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.06452853140088544</v>
+        <v>0.05819904634737849</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1632738411366372</v>
+        <v>0.1518778528559614</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2501328798984246</v>
+        <v>0.2591762166968004</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.05571387334913958</v>
+        <v>0.06597262162027295</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.1236872077614355</v>
+        <v>0.1270419381247045</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3148386330842943</v>
+        <v>0.3378749964685401</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.09552969044481019</v>
+        <v>0.1018906868349236</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>14.97</v>
+        <v>29.36</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>0.004447522071541199</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.01707152219450048</v>
+        <v>-0.02002665195113618</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.01707152219450048</v>
+        <v>-0.005083009737948618</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.01148649149345071</v>
+        <v>-0.01509556738184248</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.01577907761447994</v>
+        <v>0.04150408138092843</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1965082368078443</v>
+        <v>0.2314293563311778</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2779512865010123</v>
+        <v>0.1675097997247386</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.266232300622969</v>
+        <v>0.2726760722681703</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.8765182427018583</v>
+        <v>0.5209299223533213</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2334387747929565</v>
+        <v>0.1500138428965871</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>28.31</v>
+        <v>28.24</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.01803678318209401</v>
+        <v>-0.00247261378116348</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.0237931218640558</v>
+        <v>-0.02351315018609512</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.03477669486590262</v>
+        <v>-0.02452507679136928</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.07362565573692215</v>
+        <v>-0.08608413851943697</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.01633082729289914</v>
+        <v>-0.04368441874472173</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1449651394337794</v>
+        <v>0.1447995561801336</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1741247080725403</v>
+        <v>0.1791986297431309</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3293322705309683</v>
+        <v>0.3237108946592626</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9733062560761798</v>
+        <v>1.01889960585766</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2542905904460961</v>
+        <v>0.2638772826106397</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>60.53</v>
+        <v>61.07</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01368747217219635</v>
+        <v>0.008921211406203389</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.06704683505349451</v>
+        <v>-0.06204885390348225</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.09263978998635947</v>
+        <v>-0.08823534437009828</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.07474777631482277</v>
+        <v>-0.09122020136607045</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1647103590057977</v>
+        <v>0.1315545361039847</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.06687192739613268</v>
+        <v>-0.05069345820660898</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.06114194710974208</v>
+        <v>0.07391518804158581</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1836017692738379</v>
+        <v>0.2002112366090676</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>2.313136054347908</v>
+        <v>2.453653763159947</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.4907783951935203</v>
+        <v>0.511563044320289</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>44.79</v>
+        <v>44.62</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01472590699743748</v>
+        <v>-0.003795534274785961</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.00753379447243363</v>
+        <v>-0.00512819509612783</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.005329732850889446</v>
+        <v>0.002021112846509521</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.003559507112267379</v>
+        <v>-0.009984485599877413</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.08502912403163232</v>
+        <v>0.06263389255272833</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2825695018304974</v>
+        <v>0.2630711610648664</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.03398672043682116</v>
+        <v>0.04900037101518517</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.0179963122502842</v>
+        <v>0.007212801540880331</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3214180848141299</v>
+        <v>0.3133897231710356</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.09735399418606105</v>
+        <v>0.09512712970314419</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>33.92</v>
+        <v>33.86</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.0125182044913259</v>
+        <v>-0.00176879604459057</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.02724407204012791</v>
+        <v>-0.03257141113281248</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.02247846042779356</v>
+        <v>-0.01541142159648912</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.03909351552241414</v>
+        <v>-0.04727068829201386</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.0188024741572741</v>
+        <v>-0.04941039793119606</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.103448292978698</v>
+        <v>0.1071181786387287</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1248675656997471</v>
+        <v>0.122514731573969</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2682053272210221</v>
+        <v>0.2695637186839939</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.7162086211076164</v>
+        <v>0.7305312707270215</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1972642820910249</v>
+        <v>0.2005856564235504</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>66.73</v>
+        <v>67.08</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.0007486586294874753</v>
+        <v>0.005244994103311917</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.02270057776909706</v>
+        <v>-0.0146886012500641</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.03107302605348949</v>
+        <v>-0.01771853958487113</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.03902648313930235</v>
+        <v>-0.04376335891727201</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.006983137152548613</v>
+        <v>0.0206443344744367</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.007606323619082866</v>
+        <v>-0.009751441959199414</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1498184551144492</v>
+        <v>0.1542846910250835</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1336102413856679</v>
+        <v>0.1335908104508179</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7483297894402814</v>
+        <v>0.7992000267660448</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.204687634337533</v>
+        <v>0.2162601650486309</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>90.15000000000001</v>
+        <v>51.47</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.002986027964321902</v>
+        <v>0.01498722441237788</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01561476606883916</v>
+        <v>0.003705195903455527</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.02740318101871886</v>
+        <v>0.01338846806297056</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.04653623885628322</v>
+        <v>0.01518738552616594</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.01607920234752569</v>
+        <v>-0.0305142009272682</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.03489089151861147</v>
+        <v>0.1016927258757372</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.09209466358783946</v>
+        <v>0.09521770173438626</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1104017067053986</v>
+        <v>0.1066144821794131</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1716797786606699</v>
+        <v>0.8089758373779559</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.05423228400098545</v>
+        <v>0.2184590051426256</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16.16</v>
+        <v>114.56</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.0006192092333154875</v>
+        <v>0.01335687276491826</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01882206914793394</v>
+        <v>0.01326729199001275</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.04716976888241509</v>
+        <v>0.005264991917702133</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.0755148586608797</v>
+        <v>-0.02302579335193855</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.02533172968797359</v>
+        <v>-0.08131515347075058</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1059087352167407</v>
+        <v>0.07645974289604762</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.02696467511741929</v>
+        <v>0.1031200245901687</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.07927405727143655</v>
+        <v>0.1761834185924078</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8494556244392009</v>
+        <v>0.4686769756475537</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2274806042901487</v>
+        <v>0.1366901470644648</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>113.05</v>
+        <v>35.76</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.008834602130402658</v>
+        <v>0.008175841298274644</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.005693438028631315</v>
+        <v>-0.02054231811776497</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.01318081825258088</v>
+        <v>-0.03115690952676975</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.03094462966765765</v>
+        <v>-0.06043097658351271</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.09006757086620099</v>
+        <v>-0.05993697526604103</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.06124890796792726</v>
+        <v>0.08481194605905973</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0992330430223205</v>
+        <v>0.06553064096978467</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.169065491759407</v>
+        <v>0.1557924419582044</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.4315803691038822</v>
+        <v>1.164781716409724</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1270380489459675</v>
+        <v>0.2936139902302406</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>35.47</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.0008465743554382232</v>
+        <v>-0.001774860337228512</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.01772360506316273</v>
+        <v>-0.02163519700517658</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.04109219758831528</v>
+        <v>-0.02259152642499263</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.04829619573255439</v>
+        <v>-0.05253743226783947</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.07533887757208646</v>
+        <v>-0.03902277471171101</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.07793326127208955</v>
+        <v>0.02965395829712425</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.06777895842537007</v>
+        <v>0.08963256490472671</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1440619563528258</v>
+        <v>0.1113524319896448</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>1.098594049455126</v>
+        <v>0.1810465915453696</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2802933184921583</v>
+        <v>0.05703412991839363</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>50.71</v>
+        <v>16.22</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.004755257736571705</v>
+        <v>0.003712838274066543</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.005491323490432132</v>
+        <v>-0.02347990864937211</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.0003942530641464215</v>
+        <v>-0.04193744707755442</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.002768427733701673</v>
+        <v>-0.08257924019344487</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.05918371708903647</v>
+        <v>-0.03221962459145922</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.07927226352083983</v>
+        <v>0.1062848765016531</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.08749184789455611</v>
+        <v>0.02500124298991357</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.08408868255303759</v>
+        <v>0.08463616267187324</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7665244874588504</v>
+        <v>0.8856135108622962</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2088522430172191</v>
+        <v>0.2354283424850685</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>91.44</v>
+        <v>109.98</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01206423891193942</v>
+        <v>0.01429496493032678</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.0002186381288713513</v>
+        <v>-0.003533563286610586</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.04020147304097654</v>
+        <v>-0.011060118133845</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.05663878929624211</v>
+        <v>-0.06072246309103535</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.02108983131859388</v>
+        <v>-0.1043973890572367</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.08845875667548309</v>
+        <v>0.1827078813148748</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.03215509956902629</v>
+        <v>0.06343072233739511</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01590667361499376</v>
+        <v>0.07959025101169703</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4893455688106421</v>
+        <v>0.01739379112587058</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1419975158516618</v>
+        <v>0.005764635497955473</v>
       </c>
     </row>
     <row r="21">
@@ -1656,52 +1656,46 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>108.43</v>
+        <v>67.7</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0008307547565762352</v>
+        <v>0.008641152829656162</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.005046825424995016</v>
+        <v>-0.003532609428017808</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.02918794936852742</v>
+        <v>0.011202390353801</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.06879081044558699</v>
+        <v>-0.01239979672756308</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.1132646271866501</v>
+        <v>-0.08723205312700266</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1785869598388672</v>
+        <v>0.04798759361214167</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.05671961465944175</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0.07263087053510953</v>
-      </c>
-      <c r="O21" s="6" t="n">
-        <v>0.009880776665583735</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0.003282803629485853</v>
-      </c>
+        <v>0.08268028578079956</v>
+      </c>
+      <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr"/>
+      <c r="P21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1712,46 +1706,52 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>67.12</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.0100828567209974</v>
+        <v>-0.002515347230890308</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.004302045687179623</v>
+        <v>-0.007724098113750077</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.009778870376738524</v>
+        <v>-0.03766617156365726</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.0191436146829107</v>
+        <v>-0.06575845897322863</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.09845526530720994</v>
+        <v>-0.05216672656490384</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.03118768663241855</v>
+        <v>0.07728989310343359</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.09852707729625743</v>
-      </c>
-      <c r="N22" s="6" t="inlineStr"/>
-      <c r="O22" s="6" t="inlineStr"/>
-      <c r="P22" s="6" t="inlineStr"/>
+        <v>0.03876357432811628</v>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>0.0131363660901247</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>0.4975198700379082</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>0.144082996722577</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>95.2</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.003871536546651955</v>
+        <v>0.0111345086341188</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.02688341851770915</v>
+        <v>-0.01825600061004029</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.04360060204307425</v>
+        <v>-0.02135012668859304</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.06648368489419587</v>
+        <v>-0.07317541333967226</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.04503967683021282</v>
+        <v>-0.05040939599386429</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.05865572424691845</v>
+        <v>-0.0483568852035644</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.06921532633590721</v>
+        <v>0.0639672725895879</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.07550739457694244</v>
+        <v>0.07660212624165164</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2034927952778689</v>
+        <v>0.2416576283859846</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.06368858405066047</v>
+        <v>0.07481558138360267</v>
       </c>
     </row>
     <row r="24">
@@ -1832,37 +1832,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>38.86</v>
+        <v>39.04</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.005120347053449215</v>
+        <v>0.004632020132491421</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02361805640020431</v>
+        <v>-0.01588094989908895</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.04120400244863476</v>
+        <v>-0.02957988168654191</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.06792765404688073</v>
+        <v>-0.05539821066477468</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.06967631190237833</v>
+        <v>-0.07577111249082802</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.01544036304560059</v>
+        <v>0.006295923961993521</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.05356654919825066</v>
+        <v>0.05900669804195391</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.0445724492898294</v>
+        <v>0.05542612946692738</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3362960250014166</v>
+        <v>0.3644602446257914</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1014570292631229</v>
+        <v>0.109141517483526</v>
       </c>
     </row>
     <row r="25">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.14</v>
+        <v>13.26</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.003034898401126696</v>
+        <v>0.009132411143357499</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.00755282700333193</v>
+        <v>-0.005251289964355643</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.01128665304445642</v>
+        <v>0.006833724530487473</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.05194800369332064</v>
+        <v>-0.05285712650844032</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.09316766384539654</v>
+        <v>-0.09673024841786215</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.04918583155125544</v>
+        <v>-0.04050260564405195</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1166907646796613</v>
+        <v>0.1129536734563683</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.07909554298560306</v>
+        <v>0.07355271590163293</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.06246857212478085</v>
+        <v>0.09005337092459409</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02040371438035393</v>
+        <v>0.02915926332640906</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.61</v>
+        <v>16.63</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.002414056503563966</v>
+        <v>0.001204006603261476</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.001202558714628155</v>
+        <v>-0.005382784466743784</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.006578870067002418</v>
+        <v>-0.003595049213364399</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.037659305325072</v>
+        <v>-0.0365006407740962</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.03430233293123763</v>
+        <v>-0.04425290084165601</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.01173864071375919</v>
+        <v>0.01527611163938469</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.01140944602913707</v>
+        <v>-0.01352209551409789</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.004887336474318715</v>
+        <v>0.003068369734008591</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4393041300050797</v>
+        <v>0.4402167929643213</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.129061305699719</v>
+        <v>0.1292999012553295</v>
       </c>
     </row>
     <row r="27">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>164.58</v>
+        <v>164.36</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.001948175666141472</v>
+        <v>-0.001336743336100787</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02146382399637103</v>
+        <v>-0.02561057773895636</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.03922942849377942</v>
+        <v>-0.04812647041591445</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.09759843499946785</v>
+        <v>-0.09478441383293168</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.007344821351320752</v>
+        <v>-0.01486451559562785</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0574948997479876</v>
+        <v>0.05321538047862329</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.1245892370864127</v>
+        <v>-0.1348236181049424</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1278328472738053</v>
+        <v>-0.1330902245563741</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5035850875413765</v>
+        <v>0.5129828757512243</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1456254949051163</v>
+        <v>0.1480073560150224</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.21</v>
+        <v>61.11</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.006207229691651328</v>
+        <v>0.01058375023530389</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01037851556800629</v>
+        <v>-0.002448542528426967</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.0175758130622633</v>
+        <v>-0.001470590710227482</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.07052760389444712</v>
+        <v>-0.03535908315269476</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.006740233603463097</v>
+        <v>-0.07619048827316532</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1042233479216916</v>
+        <v>0.01884999889017758</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.1657231688177265</v>
+        <v>-0.06888518268243449</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1687179956680689</v>
+        <v>-0.05840496365192371</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1806263383044795</v>
+        <v>0.4279111918002083</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05690873979921696</v>
+        <v>0.1260743493125038</v>
       </c>
     </row>
     <row r="29">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>25.46</v>
+        <v>16.28</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.006324104831502808</v>
+        <v>0.004318421105890424</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01546796273928885</v>
+        <v>-0.007317008211950138</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.01812576996419513</v>
+        <v>-0.004281326800674168</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.06842300931041567</v>
+        <v>-0.08384916897777495</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.1453508458537097</v>
+        <v>-0.02163453823363004</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.04077132828413299</v>
+        <v>0.1044776756743817</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.0129622368012704</v>
+        <v>-0.1511991435030218</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.01336460697269248</v>
+        <v>-0.1727642055796149</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.087567480833871</v>
+        <v>0.1874544596169012</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2780470463899183</v>
+        <v>0.05894235897637423</v>
       </c>
     </row>
     <row r="30">
@@ -2154,51 +2154,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
+          <t>Leisure</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="F30" s="5" t="n">
-        <v>60.47</v>
+        <v>15.38</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.001324752970081944</v>
+        <v>0.0105124733643216</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01014894304036928</v>
+        <v>0.0185430282051382</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.01626809793625317</v>
+        <v>0.004572154990572619</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.04000635641553152</v>
+        <v>-0.07125600178479918</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.08930723145939401</v>
+        <v>-0.08288612435184839</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.006321939232857177</v>
+        <v>0.01238495703244147</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.08050283032898731</v>
+        <v>-0.08879661208670797</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.0727059987699139</v>
+        <v>-0.1073239943992079</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.412681927318725</v>
+        <v>0.271300398233765</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1220566820835123</v>
+        <v>0.08330162434275756</v>
       </c>
     </row>
     <row r="31">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>15.22</v>
+        <v>50.95</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.003295991462320291</v>
+        <v>0.0001963513250906601</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.02010725128691693</v>
+        <v>-0.02859866497961772</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.009114543800629371</v>
+        <v>-0.02804268327648884</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.075895512959259</v>
+        <v>-0.06427915428758302</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.08478646812347734</v>
+        <v>-0.05121042757783134</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.001228375833066897</v>
+        <v>-0.03353353364218326</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.095737400586413</v>
+        <v>-0.1002197066038026</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1086996149710376</v>
+        <v>-0.1221629610214015</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2495849809211019</v>
+        <v>0.1720864611672952</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.07709811428608027</v>
+        <v>0.05435424230425423</v>
       </c>
     </row>
     <row r="32">
@@ -2266,51 +2266,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>50.94</v>
+        <v>25.4</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.005924155621571225</v>
+        <v>-0.002356616971717629</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01925298472160086</v>
+        <v>-0.02532616503982121</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.04499440418097689</v>
+        <v>-0.02157162887872877</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.06066754459337531</v>
+        <v>-0.06307639075332039</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.05736495626016236</v>
+        <v>-0.1608853903398054</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.0453445119560214</v>
+        <v>-0.03138811326627078</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.1020426127157633</v>
+        <v>-0.04874938711554</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.1261570131847823</v>
+        <v>0.01058299711522515</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1619624278701512</v>
+        <v>1.102618445340808</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.05130975719184283</v>
+        <v>0.2811111862359537</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>110.69</v>
+        <v>111.41</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.006181258903474207</v>
+        <v>0.006504663518137166</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.0002710896286293174</v>
+        <v>-0.006775381289489402</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.005301908198801941</v>
+        <v>0.0008984467317321165</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.03487662320038354</v>
+        <v>-0.03138578583130791</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1395366684810992</v>
+        <v>-0.1313060143305312</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.0523072525502577</v>
+        <v>-0.0358632061335622</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.0470300793537306</v>
+        <v>-0.05820816348511293</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.08913401131773757</v>
+        <v>-0.08328021329208446</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3430715639980215</v>
+        <v>0.3692675695265564</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1033154964866188</v>
+        <v>0.1104425823559563</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>119.1</v>
+        <v>119.11</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.005827166545663287</v>
+        <v>8.398099377515678e-05</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.006762429431327099</v>
+        <v>0.002609406991838981</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.038508146982281</v>
+        <v>-0.02568506658199132</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.05752950949158364</v>
+        <v>-0.05990526062120738</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.122761396247222</v>
+        <v>-0.1371861920928559</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1412530364276703</v>
+        <v>-0.1450433223343996</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.07314736046632031</v>
+        <v>-0.08903197481963554</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09071960169998372</v>
+        <v>-0.09209509073765187</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5030105607681525</v>
+        <v>0.574990158824765</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1454795600602441</v>
+        <v>0.1634809624305233</v>
       </c>
     </row>
   </sheetData>
@@ -2629,17 +2629,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1075852079595829</v>
+        <v>0.1210641945663911</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.09759843499946785</v>
+        <v>-0.09478441383293168</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.07696563575963933</v>
+        <v>0.08537711796418557</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.075895512959259</v>
+        <v>-0.09122020136607045</v>
       </c>
     </row>
     <row r="19">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.06452853140088544</v>
+        <v>0.0774193220241095</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.0755148586608797</v>
+        <v>-0.08608413851943697</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.06186251626056194</v>
+        <v>0.05907668871062977</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.07474777631482277</v>
+        <v>-0.08384916897777495</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.05132516995623448</v>
+        <v>0.05819904634737849</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.07362565573692215</v>
+        <v>-0.08257924019344487</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.01148649149345071</v>
+        <v>0.02156332153193508</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.07052760389444712</v>
+        <v>-0.07317541333967226</v>
       </c>
     </row>
     <row r="23">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.002768427733701673</v>
+        <v>0.01518738552616594</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.06879081044558699</v>
+        <v>-0.07125600178479918</v>
       </c>
     </row>
     <row r="24">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.003559507112267379</v>
+        <v>-0.009984485599877413</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06842300931041567</v>
+        <v>-0.06575845897322863</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.006120377630386864</v>
+        <v>-0.01239979672756308</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06792765404688073</v>
+        <v>-0.06427915428758302</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.0191436146829107</v>
+        <v>-0.01509556738184248</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06648368489419587</v>
+        <v>-0.06307639075332039</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2208109726127276</v>
+        <v>0.2213553855443435</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1453508458537097</v>
+        <v>-0.1608853903398054</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.1775750102802862</v>
+        <v>0.1755318948869795</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3606,21 +3606,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1395366684810992</v>
+        <v>-0.1371861920928559</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1647103590057977</v>
+        <v>0.1518778528559614</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.122761396247222</v>
+        <v>-0.1313060143305312</v>
       </c>
     </row>
     <row r="34">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1632738411366372</v>
+        <v>0.1315545361039847</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1132646271866501</v>
+        <v>-0.1043973890572367</v>
       </c>
     </row>
     <row r="35">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.08502912403163232</v>
+        <v>0.1003925736283262</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.09845526530720994</v>
+        <v>-0.09673024841786215</v>
       </c>
     </row>
     <row r="36">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.06594805781809776</v>
+        <v>0.06263389255272833</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.09316766384539654</v>
+        <v>-0.08723205312700266</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.05485386170999207</v>
+        <v>0.05527591697102219</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.09006757086620099</v>
+        <v>-0.08288612435184839</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.007344821351320752</v>
+        <v>0.04150408138092843</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.08930723145939401</v>
+        <v>-0.08131515347075058</v>
       </c>
     </row>
     <row r="39">
@@ -3899,21 +3899,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.006983137152548613</v>
+        <v>0.0343327480219815</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.08478646812347734</v>
+        <v>-0.07619048827316532</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>-0.004515690855373067</v>
+        <v>0.0206443344744367</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.07533887757208646</v>
+        <v>-0.07577111249082802</v>
       </c>
     </row>
     <row r="41"/>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5123402626404436</v>
+        <v>0.5254719064758544</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1412530364276703</v>
+        <v>-0.1450433223343996</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4995431294397643</v>
+        <v>0.515085961318938</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.06687192739613268</v>
+        <v>-0.05069345820660898</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.494765278170973</v>
+        <v>0.5003987340473564</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.05865572424691845</v>
+        <v>-0.0483568852035644</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4579495566937486</v>
+        <v>0.4483393751505309</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0523072525502577</v>
+        <v>-0.04050260564405195</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2825695018304974</v>
+        <v>0.2630711610648664</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,21 +4252,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.04918583155125544</v>
+        <v>-0.0358632061335622</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2501328798984246</v>
+        <v>0.2591762166968004</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.0453445119560214</v>
+        <v>-0.03353353364218326</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2268906701892381</v>
+        <v>0.2314293563311778</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.04077132828413299</v>
+        <v>-0.03138811326627078</v>
       </c>
     </row>
     <row r="52">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1965082368078443</v>
+        <v>0.1947738267434951</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.006321939232857177</v>
+        <v>-0.009751441959199414</v>
       </c>
     </row>
     <row r="53">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1785869598388672</v>
+        <v>0.1827078813148748</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.001228375833066897</v>
+        <v>0.006295923961993521</v>
       </c>
     </row>
     <row r="54">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1449651394337794</v>
+        <v>0.1447995561801336</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.007606323619082866</v>
+        <v>0.01238495703244147</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8156015130808307</v>
+        <v>0.8302339377083365</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1687179956680689</v>
+        <v>-0.1727642055796149</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.750186115602185</v>
+        <v>0.7581633717962097</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1278328472738053</v>
+        <v>-0.1330902245563741</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.4912224702745538</v>
+        <v>0.5131469586456223</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1261570131847823</v>
+        <v>-0.1221629610214015</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4721808660689115</v>
+        <v>0.4726055479882969</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1086996149710376</v>
+        <v>-0.1073239943992079</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.3293322705309683</v>
+        <v>0.3237108946592626</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.09071960169998372</v>
+        <v>-0.09209509073765187</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.2706921971389284</v>
+        <v>0.2792623476479155</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.08913401131773757</v>
+        <v>-0.08328021329208446</v>
       </c>
     </row>
     <row r="65">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.2682053272210221</v>
+        <v>0.2726760722681703</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.0727059987699139</v>
+        <v>-0.05840496365192371</v>
       </c>
     </row>
     <row r="66">
@@ -4876,21 +4876,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.266232300622969</v>
+        <v>0.2695637186839939</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.004887336474318715</v>
+        <v>0.003068369734008591</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.1836017692738379</v>
+        <v>0.2002112366090676</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.01336460697269248</v>
+        <v>0.007212801540880331</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.169065491759407</v>
+        <v>0.1761834185924078</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01590667361499376</v>
+        <v>0.01058299711522515</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.8753054099937</v>
+        <v>2.925537458770556</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.009880776665583735</v>
+        <v>0.01739379112587058</v>
       </c>
     </row>
     <row r="74">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.410374659443898</v>
+        <v>2.453653763159947</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.06246857212478085</v>
+        <v>0.09005337092459409</v>
       </c>
     </row>
     <row r="75">
@@ -5162,21 +5162,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.313136054347908</v>
+        <v>2.423538326959187</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1619624278701512</v>
+        <v>0.1720864611672952</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.745381065360848</v>
+        <v>1.741151165470987</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1716797786606699</v>
+        <v>0.1810465915453696</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.098594049455126</v>
+        <v>1.164781716409724</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1806263383044795</v>
+        <v>0.1874544596169012</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.087567480833871</v>
+        <v>1.102618445340808</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2034927952778689</v>
+        <v>0.2416576283859846</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9733062560761798</v>
+        <v>1.01889960585766</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2495849809211019</v>
+        <v>0.271300398233765</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.8765182427018583</v>
+        <v>0.9096593329808276</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5409,21 +5409,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3148386330842943</v>
+        <v>0.3133897231710356</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8494556244392009</v>
+        <v>0.8856135108622962</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3214180848141299</v>
+        <v>0.3378749964685401</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7665244874588504</v>
+        <v>0.8089758373779559</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3362960250014166</v>
+        <v>0.3644602446257914</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -630,13 +630,13 @@
         <v>0.7427209876247423</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8302339377083365</v>
+        <v>0.8302338248357513</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.423538326959187</v>
+        <v>2.423537932024181</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5071566637258926</v>
+        <v>0.5071566057713348</v>
       </c>
     </row>
     <row r="3">
@@ -798,13 +798,13 @@
         <v>0.4450683885016133</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5131469586456223</v>
+        <v>0.5131470550387764</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5989630546133098</v>
+        <v>0.5989629469765108</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1693543701223044</v>
+        <v>0.1693543438833065</v>
       </c>
     </row>
     <row r="6">
@@ -857,10 +857,10 @@
         <v>0.0621251230163824</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4852030020668696</v>
+        <v>0.4852031700223005</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1409377228771833</v>
+        <v>0.1409377658851492</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.2792623476479155</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.9096593329808276</v>
+        <v>0.9096595623910371</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.240657675091156</v>
+        <v>0.2406577247718364</v>
       </c>
     </row>
     <row r="8">
@@ -966,13 +966,13 @@
         <v>0.06597262162027295</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.1270419381247045</v>
+        <v>0.1270420249308426</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3378749964685401</v>
+        <v>0.3378751187896358</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1018906868349236</v>
+        <v>0.1018907204166539</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.2726760722681703</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.5209299223533213</v>
+        <v>0.5209297720763659</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1500138428965871</v>
+        <v>0.1500138050205084</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.3237108946592626</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.01889960585766</v>
+        <v>1.018899468211274</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2638772826106397</v>
+        <v>0.2638772538873779</v>
       </c>
     </row>
     <row r="11">
@@ -1134,13 +1134,13 @@
         <v>0.07391518804158581</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2002112366090676</v>
+        <v>0.2002113265893952</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>2.453653763159947</v>
+        <v>2.45365339063127</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.511563044320289</v>
+        <v>0.511562989971992</v>
       </c>
     </row>
     <row r="12">
@@ -1296,19 +1296,19 @@
         <v>0.0206443344744367</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-0.009751441959199414</v>
+        <v>-0.009751330430793681</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>0.1542846910250835</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1335908104508179</v>
+        <v>0.1335907373740017</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7992000267660448</v>
+        <v>0.7991996585897552</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2162601650486309</v>
+        <v>0.21626008208617</v>
       </c>
     </row>
     <row r="15">
@@ -1414,13 +1414,13 @@
         <v>0.1031200245901687</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1761834185924078</v>
+        <v>0.1761833264611186</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.4686769756475537</v>
+        <v>0.4686768319962378</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1366901470644648</v>
+        <v>0.1366901100045705</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.1557924419582044</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.164781716409724</v>
+        <v>1.164781466455337</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2936139902302406</v>
+        <v>0.2936139404416171</v>
       </c>
     </row>
     <row r="18">
@@ -1529,10 +1529,10 @@
         <v>0.1113524319896448</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1810465915453696</v>
+        <v>0.181046709803208</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.05703412991839363</v>
+        <v>0.05703416519856197</v>
       </c>
     </row>
     <row r="19">
@@ -1585,10 +1585,10 @@
         <v>0.08463616267187324</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.8856135108622962</v>
+        <v>0.8856137199144596</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2354283424850685</v>
+        <v>0.2354283881411121</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.07959025101169703</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01739379112587058</v>
+        <v>0.01739386293084655</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.005764635497955473</v>
+        <v>0.005764659159361862</v>
       </c>
     </row>
     <row r="21">
@@ -1859,10 +1859,10 @@
         <v>0.05542612946692738</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3644602446257914</v>
+        <v>0.3644605175005582</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.109141517483526</v>
+        <v>0.1091415914216061</v>
       </c>
     </row>
     <row r="25">
@@ -2027,10 +2027,10 @@
         <v>-0.1330902245563741</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5129828757512243</v>
+        <v>0.5129829820093119</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1480073560150224</v>
+        <v>0.1480073828902027</v>
       </c>
     </row>
     <row r="28">
@@ -2083,10 +2083,10 @@
         <v>-0.05840496365192371</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.4279111918002083</v>
+        <v>0.4279113190772943</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1260743493125038</v>
+        <v>0.126074382770107</v>
       </c>
     </row>
     <row r="29">
@@ -2195,10 +2195,10 @@
         <v>-0.1073239943992079</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.271300398233765</v>
+        <v>0.2713004984504765</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08330162434275756</v>
+        <v>0.08330165280834123</v>
       </c>
     </row>
     <row r="31">
@@ -2363,10 +2363,10 @@
         <v>-0.08328021329208446</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3692675695265564</v>
+        <v>0.3692676979199183</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1104425823559563</v>
+        <v>0.1104426170639163</v>
       </c>
     </row>
     <row r="34">
@@ -2416,13 +2416,13 @@
         <v>-0.08903197481963554</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09209509073765187</v>
+        <v>-0.09209487954312068</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.574990158824765</v>
+        <v>0.5749899999344259</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1634809624305233</v>
+        <v>0.1634809233052226</v>
       </c>
     </row>
   </sheetData>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.009751441959199414</v>
+        <v>-0.009751330430793681</v>
       </c>
     </row>
     <row r="53">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8302339377083365</v>
+        <v>0.8302338248357513</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5131469586456223</v>
+        <v>0.5131470550387764</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.09209509073765187</v>
+        <v>-0.09209487954312068</v>
       </c>
     </row>
     <row r="64">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2002112366090676</v>
+        <v>0.2002113265893952</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1761834185924078</v>
+        <v>0.1761833264611186</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.01739379112587058</v>
+        <v>0.01739386293084655</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.453653763159947</v>
+        <v>2.45365339063127</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.423538326959187</v>
+        <v>2.423537932024181</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1810465915453696</v>
+        <v>0.181046709803208</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.164781716409724</v>
+        <v>1.164781466455337</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.01889960585766</v>
+        <v>1.018899468211274</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.271300398233765</v>
+        <v>0.2713004984504765</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9096593329808276</v>
+        <v>0.9096595623910371</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8856135108622962</v>
+        <v>0.8856137199144596</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3378749964685401</v>
+        <v>0.3378751187896358</v>
       </c>
     </row>
     <row r="82">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3644602446257914</v>
+        <v>0.3644605175005582</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,16 +489,16 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>226.42</v>
+        <v>227.1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.006937639217109881</v>
+        <v>0.003003303330401552</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.002080111648821159</v>
+        <v>0.0238492791269449</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.02605700841850633</v>
+        <v>0.003180498300085377</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.05907668871062977</v>
+        <v>0.03481271828998667</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.05527591697102219</v>
+        <v>0.05844523064695384</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.515085961318938</v>
+        <v>0.5196362240324119</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7427209876247423</v>
+        <v>0.7359175636545927</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8302338248357513</v>
+        <v>0.8305651524257818</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.423537932024181</v>
+        <v>2.457804184801877</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5071566057713348</v>
+        <v>0.5121683079023518</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>66.58</v>
+        <v>67.16</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.0200705569995987</v>
+        <v>0.008711351984135307</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.03417217569887243</v>
+        <v>0.05200506738073529</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.08436482372060716</v>
+        <v>0.05663943063303867</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1210641945663911</v>
+        <v>0.09470261340656894</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.0343327480219815</v>
+        <v>0.04334318465871889</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.5254719064758544</v>
+        <v>0.5387608291950756</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6223866526193755</v>
+        <v>0.6296177816283781</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7581633717962097</v>
+        <v>0.7738881959040229</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.925537458770556</v>
+        <v>3.02637259697903</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5774891298694234</v>
+        <v>0.5908820701982471</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>58.86</v>
+        <v>59.37</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.008740396736371059</v>
+        <v>0.008664599324579525</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.006842311531700895</v>
+        <v>0.02556572046709982</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.05069618224528782</v>
+        <v>0.02876451002853586</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.08537711796418557</v>
+        <v>0.07030823193358859</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1003925736283262</v>
+        <v>0.1099270343785586</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5003987340473564</v>
+        <v>0.513399087904983</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4538246741524081</v>
+        <v>0.4553017680944813</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4726055479882969</v>
+        <v>0.4846927293934644</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.741151165470987</v>
+        <v>1.79669503316063</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3995153365664166</v>
+        <v>0.4089049783541014</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>90.61</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.003210816170363229</v>
+        <v>0.0087186945172264</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.008009803377371449</v>
+        <v>0.01679833292338806</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.02254580805496198</v>
+        <v>0.009610104477113746</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.04035159534505117</v>
+        <v>-0.01952370382955992</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1755318948869795</v>
+        <v>0.1857809983737553</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.08324125754278122</v>
+        <v>0.09268570715575275</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4450683885016133</v>
+        <v>0.4377714315443593</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5131470550387764</v>
+        <v>0.5169070191501584</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5989629469765108</v>
+        <v>0.6882678865431449</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1693543438833065</v>
+        <v>0.1907313458742415</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>25.05</v>
+        <v>25.36</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.002400939035290595</v>
+        <v>0.01237530469990511</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.02119847272153286</v>
+        <v>0.04362145706055753</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.05562577835177751</v>
+        <v>0.03764321015508609</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.0774193220241095</v>
+        <v>0.07412113319610558</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2213553855443435</v>
+        <v>0.2364700305873249</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4483393751505309</v>
+        <v>0.4662630162268888</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.120703649659951</v>
+        <v>0.1244713689490167</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.0621251230163824</v>
+        <v>0.08049265341540646</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4852031700223005</v>
+        <v>0.5242213037420387</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1409377658851492</v>
+        <v>0.1508428109650286</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>15.16</v>
+        <v>57.7</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.0126920225113003</v>
+        <v>0.03367970401994747</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.01044385447776242</v>
+        <v>0.005226467405672341</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.0006600811309331878</v>
+        <v>0.0477574193333874</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.02156332153193508</v>
+        <v>0.09967599429314911</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.01066665649414067</v>
+        <v>0.1906727580072827</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1947738267434951</v>
+        <v>0.3015848989841057</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.28338623046875</v>
+        <v>0.08206612934794921</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2792623476479155</v>
+        <v>0.14825854731188</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.9096595623910371</v>
+        <v>0.4052516880578529</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2406577247718364</v>
+        <v>0.1200860074411023</v>
       </c>
     </row>
     <row r="8">
@@ -928,12 +928,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>55.82</v>
+        <v>29.89</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.007035890086618313</v>
+        <v>0.01805172916481523</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.01759943691254706</v>
+        <v>-0.008294625250916954</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.02422017788668285</v>
+        <v>0.005381764207053052</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.05819904634737849</v>
+        <v>0.007075440778753439</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1518778528559614</v>
+        <v>0.06030503098206674</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2591762166968004</v>
+        <v>0.2536587855572709</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.06597262162027295</v>
+        <v>0.1957633676293506</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.1270420249308426</v>
+        <v>0.2804719820702506</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3378751187896358</v>
+        <v>0.5566399157022783</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1018907204166539</v>
+        <v>0.1589447189572291</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>29.36</v>
+        <v>15.12</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.004447522071541199</v>
+        <v>-0.002638519937706696</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.02002665195113618</v>
+        <v>0.003984028172019816</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.005083009737948618</v>
+        <v>-0.02072536939902392</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.01509556738184248</v>
+        <v>0.009345817596857708</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.04150408138092843</v>
+        <v>0.007999992370605558</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2314293563311778</v>
+        <v>0.1916213921805823</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1675097997247386</v>
+        <v>0.2725766716000897</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2726760722681703</v>
+        <v>0.2718652225345324</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.5209297720763659</v>
+        <v>0.9273174580511778</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1500138050205084</v>
+        <v>0.2444699620733914</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>28.24</v>
+        <v>28.54</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.00247261378116348</v>
+        <v>0.01062327007226105</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.02351315018609512</v>
+        <v>-0.01484288602067485</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.02452507679136928</v>
+        <v>-0.02126196622527721</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.08608413851943697</v>
+        <v>-0.06732024314580876</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.04368441874472173</v>
+        <v>-0.03352522005073555</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1447995561801336</v>
+        <v>0.1569610710440399</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1791986297431309</v>
+        <v>0.2215798136017191</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3237108946592626</v>
+        <v>0.3249434539389564</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.018899468211274</v>
+        <v>1.019107138435502</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2638772538873779</v>
+        <v>0.2639205878386848</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>61.07</v>
+        <v>45.38</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.008921211406203389</v>
+        <v>0.01703276903683171</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.06204885390348225</v>
+        <v>0.01977530490146595</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.08823534437009828</v>
+        <v>0.002429878710829447</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.09122020136607045</v>
+        <v>0.003316416701238944</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1315545361039847</v>
+        <v>0.08073349021528831</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.05069345820660898</v>
+        <v>0.2845847604283671</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.07391518804158581</v>
+        <v>0.04738969083057087</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2002113265893952</v>
+        <v>0.02301102866910476</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>2.45365339063127</v>
+        <v>0.3416655557638264</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.511562989971992</v>
+        <v>0.1029303563469517</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>44.62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.003795534274785961</v>
+        <v>-0.001146220651285668</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.00512819509612783</v>
+        <v>-0.01597034443718515</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.002021112846509521</v>
+        <v>-0.07631739620921685</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.009984485599877413</v>
+        <v>-0.1107871522327823</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.06263389255272833</v>
+        <v>0.1302575249266464</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2630711610648664</v>
+        <v>-0.05178157296921315</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.04900037101518517</v>
+        <v>0.04437084933556723</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.007212801540880331</v>
+        <v>0.1947998345145132</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3133897231710356</v>
+        <v>2.435440253501147</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.09512712970314419</v>
+        <v>0.5089011864019342</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>33.86</v>
+        <v>33.83</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.00176879604459057</v>
+        <v>-0.0008859651138843905</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.03257141113281248</v>
+        <v>-0.03315232328571127</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.01541142159648912</v>
+        <v>-0.03065901570321705</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.04727068829201386</v>
+        <v>-0.04137146632462307</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.04941039793119606</v>
+        <v>-0.05025258715625025</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1071181786387287</v>
+        <v>0.1061373105555077</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.122514731573969</v>
+        <v>0.1384572389427405</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2695637186839939</v>
+        <v>0.2471505091039774</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.7305312707270215</v>
+        <v>0.7229260553765549</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2005856564235504</v>
+        <v>0.1988243243133418</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>67.08</v>
+        <v>67.37</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.005244994103311917</v>
+        <v>0.004323209713943177</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.0146886012500641</v>
+        <v>0.002529848304469118</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.01771853958487113</v>
+        <v>-0.02305679174883624</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.04376335891727201</v>
+        <v>-0.03894430509220193</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.0206443344744367</v>
+        <v>0.02505679397571758</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-0.009751330430793681</v>
+        <v>-0.005470389773859163</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1542846910250835</v>
+        <v>0.1518686171367687</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1335907373740017</v>
+        <v>0.1265534757599829</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7991996585897552</v>
+        <v>0.8011908437150466</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.21626008208617</v>
+        <v>0.2167085974607244</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>51.47</v>
+        <v>51.75</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.01498722441237788</v>
+        <v>0.005440038326329999</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.003705195903455527</v>
+        <v>0.02171763950607319</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.01338846806297056</v>
+        <v>0.008968591855364805</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.01518738552616594</v>
+        <v>0.00661350230688651</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.0305142009272682</v>
+        <v>-0.02524016102347992</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1016927258757372</v>
+        <v>0.1076859765283402</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.09521770173438626</v>
+        <v>0.08928595230474801</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1066144821794131</v>
+        <v>0.1140471861339971</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8089758373779559</v>
+        <v>0.8332666092738401</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2184590051426256</v>
+        <v>0.2238885621971691</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>114.56</v>
+        <v>90.37</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01335687276491826</v>
+        <v>0.004222745769899561</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01326729199001275</v>
+        <v>-0.02122819284742417</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.005264991917702133</v>
+        <v>-0.01579173331585104</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.02302579335193855</v>
+        <v>-0.0417770640865921</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.08131515347075058</v>
+        <v>-0.0349648121986551</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.07645974289604762</v>
+        <v>0.03400192519398382</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1031200245901687</v>
+        <v>0.1001800137631905</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1761833264611186</v>
+        <v>0.1120298296830771</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.4686768319962378</v>
+        <v>0.2194228232539699</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1366901100045705</v>
+        <v>0.06836119796423956</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>35.76</v>
+        <v>111.82</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.008175841298274644</v>
+        <v>0.01673028079403704</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.02054231811776497</v>
+        <v>0.01765564697760214</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.03115690952676975</v>
+        <v>0.006752498442970101</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.06043097658351271</v>
+        <v>-0.04181660137988097</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.05993697526604103</v>
+        <v>-0.08941370589629172</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.08481194605905973</v>
+        <v>0.2024949162665932</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06553064096978467</v>
+        <v>0.06495237804594489</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1557924419582044</v>
+        <v>0.08674651554929613</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.164781466455337</v>
+        <v>0.03636985505147594</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2936139404416171</v>
+        <v>0.01197921052095485</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>89.98999999999999</v>
+        <v>16.36</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.001774860337228512</v>
+        <v>0.00863139968703952</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02163519700517658</v>
+        <v>-0.00304687614414767</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.02259152642499263</v>
+        <v>-0.03821279305020919</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.05253743226783947</v>
+        <v>-0.08347337474933325</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.03902277471171101</v>
+        <v>-0.02386632536203492</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.02965395829712425</v>
+        <v>0.115833663438466</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.08963256490472671</v>
+        <v>0.01303270909048826</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1113524319896448</v>
+        <v>0.08584913823360729</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.181046709803208</v>
+        <v>0.9094211944178268</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.05703416519856197</v>
+        <v>0.2406061020675132</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="F19" s="5" t="n">
-        <v>16.22</v>
+        <v>35.71</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.003712838274066543</v>
+        <v>-0.001398189021458607</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.02347990864937211</v>
+        <v>-0.008055580986870647</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.04193744707755442</v>
+        <v>-0.03355890806125528</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.08257924019344487</v>
+        <v>-0.07463076073406283</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.03221962459145922</v>
+        <v>-0.06125136106670326</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1062848765016531</v>
+        <v>0.08329517390573282</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.02500124298991357</v>
+        <v>0.04217698889428845</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.08463616267187324</v>
+        <v>0.1450751184901662</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.8856137199144596</v>
+        <v>1.163935191713342</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2354283881411121</v>
+        <v>0.2934453482906572</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>109.98</v>
+        <v>113.57</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01429496493032678</v>
+        <v>-0.008641741313438644</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.003533563286610586</v>
+        <v>0.00754079546589792</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.011060118133845</v>
+        <v>-0.002897294351481672</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.06072246309103535</v>
+        <v>-0.04474724301569322</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.1043973890572367</v>
+        <v>-0.08925419026303238</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1827078813148748</v>
+        <v>0.06715725626360936</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.06343072233739511</v>
+        <v>0.08145669922306653</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.07959025101169703</v>
+        <v>0.1578238381624713</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01739386293084655</v>
+        <v>0.4688321391590173</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.005764659159361862</v>
+        <v>0.136730175522453</v>
       </c>
     </row>
     <row r="21">
@@ -1670,28 +1670,28 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>67.7</v>
+        <v>67.55</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.008641152829656162</v>
+        <v>-0.002215567256214968</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.003532609428017808</v>
+        <v>0.005956835693067708</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.011202390353801</v>
+        <v>0.001482670245224194</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.01239979672756308</v>
+        <v>-0.032234955610698</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.08723205312700266</v>
+        <v>-0.08925435190261699</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.04798759361214167</v>
+        <v>0.04566570661481517</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.08268028578079956</v>
+        <v>0.06646673332851116</v>
       </c>
       <c r="N21" s="6" t="inlineStr"/>
       <c r="O21" s="6" t="inlineStr"/>
@@ -1720,37 +1720,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>91.20999999999999</v>
+        <v>91.72</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.002515347230890308</v>
+        <v>0.005591515638084132</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.007724098113750077</v>
+        <v>-0.0001090388734812375</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.03766617156365726</v>
+        <v>-0.02311213316702354</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.06575845897322863</v>
+        <v>-0.06159194571967463</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.05216672656490384</v>
+        <v>-0.04686690199419508</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.07728989310343359</v>
+        <v>0.0833135763874715</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03876357432811628</v>
+        <v>0.02984010993025876</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.0131363660901247</v>
+        <v>0.008955777042695123</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.4975198700379082</v>
+        <v>0.4894853833875612</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.144082996722577</v>
+        <v>0.1420332503171367</v>
       </c>
     </row>
     <row r="23">
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>96.26000000000001</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0111345086341188</v>
+        <v>0.01018071582994717</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01825600061004029</v>
+        <v>0.003094650451908265</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02135012668859304</v>
+        <v>-0.0078563846105284</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.07317541333967226</v>
+        <v>-0.05601401953987073</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.05040939599386429</v>
+        <v>-0.04074188389969002</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.0483568852035644</v>
+        <v>-0.03866847708029619</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0639672725895879</v>
+        <v>0.05823591658782412</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.07660212624165164</v>
+        <v>0.08605992116559968</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2416576283859846</v>
+        <v>0.2710849693643718</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.07481558138360267</v>
+        <v>0.08324043040624307</v>
       </c>
     </row>
     <row r="24">
@@ -1818,51 +1818,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>39.04</v>
+        <v>13.34</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.004632020132491421</v>
+        <v>0.006033176645940497</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01588094989908895</v>
+        <v>0.003762241601082073</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.02957988168654191</v>
+        <v>0.01754389793545874</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.05539821066477468</v>
+        <v>-0.04097769238511273</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.07577111249082802</v>
+        <v>-0.09128066244763233</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.006295923961993521</v>
+        <v>-0.03471378837258299</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.05900669804195391</v>
+        <v>0.1087001390234121</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.05542612946692738</v>
+        <v>0.08002964907539667</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3644605175005582</v>
+        <v>0.1050774454611099</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1091415914216061</v>
+        <v>0.03386596459717461</v>
       </c>
     </row>
     <row r="25">
@@ -1874,51 +1874,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.26</v>
+        <v>38.89</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.009132411143357499</v>
+        <v>-0.003842252109662381</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.005251289964355643</v>
+        <v>-0.01643908727436705</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.006833724530487473</v>
+        <v>-0.0418822556429842</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.05285712650844032</v>
+        <v>-0.06311729794808607</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.09673024841786215</v>
+        <v>-0.07932223288367102</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.04050260564405195</v>
+        <v>0.002429481325205929</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1129536734563683</v>
+        <v>0.05243185137338879</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.07355271590163293</v>
+        <v>0.04619177463095925</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.09005337092459409</v>
+        <v>0.3612810338214534</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.02915926332640906</v>
+        <v>0.1082794093216581</v>
       </c>
     </row>
     <row r="26">
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16.63</v>
+        <v>16.67</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.001204006603261476</v>
+        <v>0.002405346815754106</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.005382784466743784</v>
+        <v>-0.0005995340946566285</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.003595049213364399</v>
+        <v>-0.009506824012918691</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.0365006407740962</v>
+        <v>-0.04415140104267656</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.04425290084165601</v>
+        <v>-0.04195399760002916</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.01527611163938469</v>
+        <v>0.01771820280162761</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>-0.01352209551409789</v>
+        <v>-0.02577886640359361</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.003068369734008591</v>
+        <v>0.01208285898540895</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4402167929643213</v>
+        <v>0.4738800530300495</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1292999012553295</v>
+        <v>0.1380308812607272</v>
       </c>
     </row>
     <row r="27">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>164.36</v>
+        <v>16.71</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.001336743336100787</v>
+        <v>0.02641267688519666</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02561057773895636</v>
+        <v>0.02704355343143372</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.04812647041591445</v>
+        <v>0.009057948270998706</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.09478441383293168</v>
+        <v>-0.05752963813303158</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.01486451559562785</v>
+        <v>0.004206712583641359</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.05321538047862329</v>
+        <v>0.1336498876488823</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.1348236181049424</v>
+        <v>-0.1465781843930759</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1330902245563741</v>
+        <v>-0.1564866463928628</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5129829820093119</v>
+        <v>0.2323007793052116</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1480073828902027</v>
+        <v>0.07210891587815871</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>61.11</v>
+        <v>166.25</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01058375023530389</v>
+        <v>0.01149914445503719</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.002448542528426967</v>
+        <v>0.001264795966989141</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.001470590710227482</v>
+        <v>-0.04929373453353669</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.03535908315269476</v>
+        <v>-0.1021279071511439</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.07619048827316532</v>
+        <v>-0.003536300352678823</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.01884999889017758</v>
+        <v>0.06532645628101386</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.06888518268243449</v>
+        <v>-0.1552237315438573</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.05840496365192371</v>
+        <v>-0.1307052217079231</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.4279113190772943</v>
+        <v>0.5349914356084269</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.126074382770107</v>
+        <v>0.153547065959674</v>
       </c>
     </row>
     <row r="29">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16.28</v>
+        <v>61.42</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.004318421105890424</v>
+        <v>0.005072779504132985</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.007317008211950138</v>
+        <v>0.01587825172030488</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.004281326800674168</v>
+        <v>-0.009195087822033154</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.08384916897777495</v>
+        <v>-0.03866021668961417</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.02163453823363004</v>
+        <v>-0.07150420631635424</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1044776756743817</v>
+        <v>0.02401840028233382</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>-0.1511991435030218</v>
+        <v>-0.0788510550752749</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.1727642055796149</v>
+        <v>-0.04880620508219158</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.1874544596169012</v>
+        <v>0.4598841332726684</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.05894235897637423</v>
+        <v>0.1344171830426102</v>
       </c>
     </row>
     <row r="30">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>15.38</v>
+        <v>51.28</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.0105124733643216</v>
+        <v>0.006476899144571835</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.0185430282051382</v>
+        <v>-0.001946327106645773</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.004572154990572619</v>
+        <v>-0.02878788787361908</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.07125600178479918</v>
+        <v>-0.07319723328627648</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.08288612435184839</v>
+        <v>-0.04506521320783141</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.01238495703244147</v>
+        <v>-0.02727382781297283</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.08879661208670797</v>
+        <v>-0.1068953601988241</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.1073239943992079</v>
+        <v>-0.1146079883995169</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2713004984504765</v>
+        <v>0.2044831676028627</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08330165280834123</v>
+        <v>0.06398027916403581</v>
       </c>
     </row>
     <row r="31">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>50.95</v>
+        <v>15.34</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.0001963513250906601</v>
+        <v>-0.002600777734420801</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02859866497961772</v>
+        <v>0.0172413945754144</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02804268327648884</v>
+        <v>-0.003896069313546469</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.06427915428758302</v>
+        <v>-0.05947267597279748</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.05121042757783134</v>
+        <v>-0.08527133369956241</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.03353353364218326</v>
+        <v>0.00975196877752893</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.1002197066038026</v>
+        <v>-0.09573603056421931</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.1221629610214015</v>
+        <v>-0.1087667468223978</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1720864611672952</v>
+        <v>0.2960116745468677</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.05435424230425423</v>
+        <v>0.09027562946407164</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>25.4</v>
+        <v>25.29</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.002356616971717629</v>
+        <v>-0.004330657663580539</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02532616503982121</v>
+        <v>-0.007846169375702816</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02157162887872877</v>
+        <v>-0.03546904737535506</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.06307639075332039</v>
+        <v>-0.07969427449745736</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.1608853903398054</v>
+        <v>-0.1645193084547527</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.03138811326627078</v>
+        <v>-0.03558283975658938</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.04874938711554</v>
+        <v>-0.06954619475326063</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01058299711522515</v>
+        <v>0.005814943165939779</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1.102618445340808</v>
+        <v>1.127020694636979</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.2811111862359537</v>
+        <v>0.2860481779860782</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>111.41</v>
+        <v>111.44</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.006504663518137166</v>
+        <v>0.0002692646828004186</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.006775381289489402</v>
+        <v>0.001437847446662088</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.0008984467317321165</v>
+        <v>-0.003309141626567036</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.03138578583130791</v>
+        <v>-0.05028118357439548</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1313060143305312</v>
+        <v>-0.1310721057200293</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.0358632061335622</v>
+        <v>-0.03560359814558556</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.05820816348511293</v>
+        <v>-0.06086683464337295</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.08328021329208446</v>
+        <v>-0.08473527393719515</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3692676979199183</v>
+        <v>0.3904876538191551</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1104426170639163</v>
+        <v>0.1161495256788054</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>119.11</v>
+        <v>119.51</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>8.398099377515678e-05</v>
+        <v>0.003358253075553597</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.002609406991838981</v>
+        <v>0.01339779383503781</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02568506658199132</v>
+        <v>-0.01896238355262359</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.05990526062120738</v>
+        <v>-0.0687290545389041</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1371861920928559</v>
+        <v>-0.1342886449688216</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1450433223343996</v>
+        <v>-0.1421720674879779</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.08903197481963554</v>
+        <v>-0.07608054542833598</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.09209487954312068</v>
+        <v>-0.0986927708950841</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5749899999344259</v>
+        <v>0.5779556848366849</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1634809233052226</v>
+        <v>0.1642107383753171</v>
       </c>
     </row>
   </sheetData>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3028,21 +3028,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1210641945663911</v>
+        <v>0.09967599429314911</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3050,21 +3050,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.09478441383293168</v>
+        <v>-0.1107871522327823</v>
       </c>
     </row>
     <row r="18">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.08537711796418557</v>
+        <v>0.09470261340656894</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3095,21 +3095,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.09122020136607045</v>
+        <v>-0.1021279071511439</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0774193220241095</v>
+        <v>0.07412113319610558</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3140,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.08608413851943697</v>
+        <v>-0.08347337474933325</v>
       </c>
     </row>
     <row r="20">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.05907668871062977</v>
+        <v>0.07030823193358859</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.08384916897777495</v>
+        <v>-0.07969427449745736</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.05819904634737849</v>
+        <v>0.03481271828998667</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08257924019344487</v>
+        <v>-0.07463076073406283</v>
       </c>
     </row>
     <row r="22">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.02156332153193508</v>
+        <v>0.009345817596857708</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.07317541333967226</v>
+        <v>-0.07319723328627648</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.01518738552616594</v>
+        <v>0.007075440778753439</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.07125600178479918</v>
+        <v>-0.0687290545389041</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.009984485599877413</v>
+        <v>0.00661350230688651</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.06575845897322863</v>
+        <v>-0.06732024314580876</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-0.01239979672756308</v>
+        <v>0.003316416701238944</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06427915428758302</v>
+        <v>-0.06311729794808607</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-0.01509556738184248</v>
+        <v>-0.01952370382955992</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06307639075332039</v>
+        <v>-0.06159194571967463</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2213553855443435</v>
+        <v>0.2364700305873249</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1608853903398054</v>
+        <v>-0.1645193084547527</v>
       </c>
     </row>
     <row r="32">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.1755318948869795</v>
+        <v>0.1906727580072827</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1371861920928559</v>
+        <v>-0.1342886449688216</v>
       </c>
     </row>
     <row r="33">
@@ -3629,21 +3629,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1518778528559614</v>
+        <v>0.1857809983737553</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1313060143305312</v>
+        <v>-0.1310721057200293</v>
       </c>
     </row>
     <row r="34">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1315545361039847</v>
+        <v>0.1302575249266464</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1043973890572367</v>
+        <v>-0.09128066244763233</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1003925736283262</v>
+        <v>0.1099270343785586</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.09673024841786215</v>
+        <v>-0.08941370589629172</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.06263389255272833</v>
+        <v>0.08073349021528831</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08723205312700266</v>
+        <v>-0.08925435190261699</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.05527591697102219</v>
+        <v>0.06030503098206674</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.08288612435184839</v>
+        <v>-0.08925419026303238</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.04150408138092843</v>
+        <v>0.05844523064695384</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.08131515347075058</v>
+        <v>-0.08527133369956241</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.0343327480219815</v>
+        <v>0.04334318465871889</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.07619048827316532</v>
+        <v>-0.07932223288367102</v>
       </c>
     </row>
     <row r="40">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0206443344744367</v>
+        <v>0.02505679397571758</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.07577111249082802</v>
+        <v>-0.07150420631635424</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5254719064758544</v>
+        <v>0.5387608291950756</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1450433223343996</v>
+        <v>-0.1421720674879779</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.515085961318938</v>
+        <v>0.5196362240324119</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.05069345820660898</v>
+        <v>-0.05178157296921315</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5003987340473564</v>
+        <v>0.513399087904983</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.0483568852035644</v>
+        <v>-0.03866847708029619</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4483393751505309</v>
+        <v>0.4662630162268888</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.04050260564405195</v>
+        <v>-0.03560359814558556</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2630711610648664</v>
+        <v>0.3015848989841057</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4252,21 +4252,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0358632061335622</v>
+        <v>-0.03558283975658938</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2591762166968004</v>
+        <v>0.2845847604283671</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.03353353364218326</v>
+        <v>-0.03471378837258299</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2314293563311778</v>
+        <v>0.2536587855572709</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.03138811326627078</v>
+        <v>-0.02727382781297283</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1947738267434951</v>
+        <v>0.2024949162665932</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.009751330430793681</v>
+        <v>-0.005470389773859163</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1827078813148748</v>
+        <v>0.1916213921805823</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.006295923961993521</v>
+        <v>0.002429481325205929</v>
       </c>
     </row>
     <row r="54">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1447995561801336</v>
+        <v>0.1569610710440399</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.01238495703244147</v>
+        <v>0.00975196877752893</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8302338248357513</v>
+        <v>0.8305651524257818</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1727642055796149</v>
+        <v>-0.1564866463928628</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7581633717962097</v>
+        <v>0.7738881959040229</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1330902245563741</v>
+        <v>-0.1307052217079231</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5131470550387764</v>
+        <v>0.5169070191501584</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1221629610214015</v>
+        <v>-0.1146079883995169</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.4726055479882969</v>
+        <v>0.4846927293934644</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1073239943992079</v>
+        <v>-0.1087667468223978</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.3237108946592626</v>
+        <v>0.3249434539389564</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.09209487954312068</v>
+        <v>-0.0986927708950841</v>
       </c>
     </row>
     <row r="64">
@@ -4786,21 +4786,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.2792623476479155</v>
+        <v>0.2804719820702506</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.08328021329208446</v>
+        <v>-0.08473527393719515</v>
       </c>
     </row>
     <row r="65">
@@ -4831,21 +4831,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.2726760722681703</v>
+        <v>0.2718652225345324</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.05840496365192371</v>
+        <v>-0.04880620508219158</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.2695637186839939</v>
+        <v>0.2471505091039774</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4898,21 +4898,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.003068369734008591</v>
+        <v>0.005814943165939779</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2002113265893952</v>
+        <v>0.1947998345145132</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.007212801540880331</v>
+        <v>0.008955777042695123</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1761833264611186</v>
+        <v>0.1578238381624713</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01058299711522515</v>
+        <v>0.01208285898540895</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.925537458770556</v>
+        <v>3.02637259697903</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.01739386293084655</v>
+        <v>0.03636985505147594</v>
       </c>
     </row>
     <row r="74">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.45365339063127</v>
+        <v>2.457804184801877</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09005337092459409</v>
+        <v>0.1050774454611099</v>
       </c>
     </row>
     <row r="75">
@@ -5162,21 +5162,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.423537932024181</v>
+        <v>2.435440253501147</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1720864611672952</v>
+        <v>0.2044831676028627</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.741151165470987</v>
+        <v>1.79669503316063</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.181046709803208</v>
+        <v>0.2194228232539699</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.164781466455337</v>
+        <v>1.163935191713342</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1874544596169012</v>
+        <v>0.2323007793052116</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.102618445340808</v>
+        <v>1.127020694636979</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2416576283859846</v>
+        <v>0.2710849693643718</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.018899468211274</v>
+        <v>1.019107138435502</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2713004984504765</v>
+        <v>0.2960116745468677</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9096595623910371</v>
+        <v>0.9273174580511778</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3133897231710356</v>
+        <v>0.3416655557638264</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8856137199144596</v>
+        <v>0.9094211944178268</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5454,21 +5454,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3378751187896358</v>
+        <v>0.3612810338214534</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8089758373779559</v>
+        <v>0.8332666092738401</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,21 +5499,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3644605175005582</v>
+        <v>0.3904876538191551</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,15 +490,15 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>227.1</v>
+        <v>227.29</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.003003303330401552</v>
+        <v>0.0008365793813787104</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.0238492791269449</v>
+        <v>0.02359824437000158</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.003180498300085377</v>
+        <v>0.001056992870069662</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.03481271828998667</v>
+        <v>0.03567842127369647</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.05844523064695384</v>
+        <v>0.02065647669089632</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5196362240324119</v>
+        <v>0.5027880268296256</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7359175636545927</v>
+        <v>0.7066402186691654</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8305651524257818</v>
+        <v>0.8118366365666507</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.457804184801877</v>
+        <v>2.416209711571021</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5121683079023518</v>
+        <v>0.5060804611450886</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>67.16</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.008711351984135307</v>
+        <v>0.005211412373977486</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.05200506738073529</v>
+        <v>0.04666669978651883</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.05663943063303867</v>
+        <v>0.04117837676032643</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.09470261340656894</v>
+        <v>0.1004075601519014</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.04334318465871889</v>
+        <v>0.02567612350717074</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.5387608291950756</v>
+        <v>0.531373204281774</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6296177816283781</v>
+        <v>0.5890799623017213</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7738881959040229</v>
+        <v>0.7620160411350163</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>3.02637259697903</v>
+        <v>2.952824331880731</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5908820701982471</v>
+        <v>0.581135797634408</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>59.37</v>
+        <v>59.55</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.008664599324579525</v>
+        <v>0.003031839454507912</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02556572046709982</v>
+        <v>0.03313670832125526</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.02876451002853586</v>
+        <v>0.02144082360819977</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.07030823193358859</v>
+        <v>0.07355323465964947</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1099270343785586</v>
+        <v>0.0964831105002788</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.513399087904983</v>
+        <v>0.506847655601838</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4553017680944813</v>
+        <v>0.4318905007942015</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4846927293934644</v>
+        <v>0.4791500968275544</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.79669503316063</v>
+        <v>1.748504167958915</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4089049783541014</v>
+        <v>0.4007655962129955</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>91.40000000000001</v>
+        <v>91.75</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.0087186945172264</v>
+        <v>0.003829304904573672</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.01679833292338806</v>
+        <v>0.0325230629056712</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.009610104477113746</v>
+        <v>0.02410987554863686</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.01952370382955992</v>
+        <v>-0.01576916113981619</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1857809983737553</v>
+        <v>0.1909397573943676</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.09268570715575275</v>
+        <v>0.09179306052161196</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4377714315443593</v>
+        <v>0.4716763164232527</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5169070191501584</v>
+        <v>0.5126298748732201</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6882678865431449</v>
+        <v>0.6836196379656434</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1907313458742415</v>
+        <v>0.1896375418405567</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>25.36</v>
+        <v>25.51</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01237530469990511</v>
+        <v>0.005914811313886492</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.04362145706055753</v>
+        <v>0.04849980718767055</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.03764321015508609</v>
+        <v>0.04079967322161138</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.07412113319610558</v>
+        <v>0.08047435702721839</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2364700305873249</v>
+        <v>0.2335589870613881</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4662630162268888</v>
+        <v>0.4764940953315844</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1244713689490167</v>
+        <v>0.1108915838497373</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.08049265341540646</v>
+        <v>0.07163811534258979</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.5242213037420387</v>
+        <v>0.4928568917145837</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1508428109650286</v>
+        <v>0.1428942799376407</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>57.7</v>
+        <v>15.37</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.03367970401994747</v>
+        <v>0.01653439165953774</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.005226467405672341</v>
+        <v>0.0274064068426898</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.0477574193333874</v>
+        <v>-0.004533659114418276</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.09967599429314911</v>
+        <v>0.02603473666492051</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1906727580072827</v>
+        <v>0.01519151499476457</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3015848989841057</v>
+        <v>0.2075767689828516</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.08206612934794921</v>
+        <v>0.2946905087596348</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.14825854731188</v>
+        <v>0.3021295989801827</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4052516880578529</v>
+        <v>0.9399198988959332</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1200860074411023</v>
+        <v>0.2471765390207448</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>29.89</v>
+        <v>29.09</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01805172916481523</v>
+        <v>-0.02676477930399701</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.008294625250916954</v>
+        <v>-0.03291222651692716</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.005381764207053052</v>
+        <v>-0.03323363226749587</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.007075440778753439</v>
+        <v>-0.01987871113616546</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.06030503098206674</v>
+        <v>0.0407870969062738</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2536587855572709</v>
+        <v>0.2228374456483524</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1957633676293506</v>
+        <v>0.1438483066602307</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.2804719820702506</v>
+        <v>0.2470859358346182</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5566399157022783</v>
+        <v>0.4961749851820039</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1589447189572291</v>
+        <v>0.1437404034416254</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>15.12</v>
+        <v>55.65</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.002638519937706696</v>
+        <v>-0.03552858249487678</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.003984028172019816</v>
+        <v>-0.03234214658215118</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.02072536939902392</v>
+        <v>-0.003224078439410971</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.009345817596857708</v>
+        <v>0.06060606501226928</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.007999992370605558</v>
+        <v>0.1545643287347764</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1916213921805823</v>
+        <v>0.2573186730902191</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2725766716000897</v>
+        <v>0.01751464354658294</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2718652225345324</v>
+        <v>0.1100294956520469</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.9273174580511778</v>
+        <v>0.3454337994507524</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2444699620733914</v>
+        <v>0.1039619660008066</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>28.54</v>
+        <v>27.79</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01062327007226105</v>
+        <v>-0.0262789059544829</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.01484288602067485</v>
+        <v>-0.03774232260782118</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.02126196622527721</v>
+        <v>-0.06682336216367368</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.06732024314580876</v>
+        <v>-0.09183004676183004</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.03352522005073555</v>
+        <v>-0.0541183897432681</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1569610710440399</v>
+        <v>0.1309562029336315</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2215798136017191</v>
+        <v>0.1745251081762869</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3249434539389564</v>
+        <v>0.2923788664576383</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.019107138435502</v>
+        <v>0.9533384238236018</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2639205878386848</v>
+        <v>0.2500455287573873</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>45.38</v>
+        <v>45.29</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01703276903683171</v>
+        <v>-0.001983255849923871</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01977530490146595</v>
+        <v>0.01935630439893066</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.002429878710829447</v>
+        <v>0.008461390991011841</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.003316416701238944</v>
+        <v>0.001326583548491689</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.08073349021528831</v>
+        <v>0.07475086785721907</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2845847604283671</v>
+        <v>0.274577768340041</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.04738969083057087</v>
+        <v>0.02510795254828113</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.02301102866910476</v>
+        <v>0.01674814495413401</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3416655557638264</v>
+        <v>0.3198661246313603</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1029303563469517</v>
+        <v>0.09692422435903492</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>61</v>
+        <v>61.59</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.001146220651285668</v>
+        <v>0.009672133648981784</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.01597034443718515</v>
+        <v>-0.01455999755859372</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.07631739620921685</v>
+        <v>-0.09916633496600358</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.1107871522327823</v>
+        <v>-0.1021865667267862</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1302575249266464</v>
+        <v>0.1373960926511391</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-0.05178157296921315</v>
+        <v>-0.03896617421674797</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.04437084933556723</v>
+        <v>0.01758350523156982</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1947998345145132</v>
+        <v>0.1835570850103896</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>2.435440253501147</v>
+        <v>2.395015406464775</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.5089011864019342</v>
+        <v>0.5029594028522286</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>33.83</v>
+        <v>33.8</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.0008859651138843905</v>
+        <v>-0.0008868635048845386</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.03315232328571127</v>
+        <v>-0.02957228078798957</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.03065901570321705</v>
+        <v>-0.03840689132899267</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.04137146632462307</v>
+        <v>-0.04222163898588072</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.05025258715625025</v>
+        <v>-0.0394998421112025</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1061373105555077</v>
+        <v>0.111538377101509</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1384572389427405</v>
+        <v>0.1118951134095201</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2471505091039774</v>
+        <v>0.2451736430307643</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.7229260553765549</v>
+        <v>0.6895066004552275</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1988243243133418</v>
+        <v>0.1910224953423494</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>67.37</v>
+        <v>67.91</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.004323209713943177</v>
+        <v>0.00801545040095375</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.002529848304469118</v>
+        <v>0.01631254074024757</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.02305679174883624</v>
+        <v>-0.01020254980345492</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.03894430509220193</v>
+        <v>-0.03124101083711439</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.02505679397571758</v>
+        <v>0.04126600426936489</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-0.005470389773859163</v>
+        <v>0.009092729149675849</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1518686171367687</v>
+        <v>0.1481679889820453</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1265534757599829</v>
+        <v>0.1468397003845689</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8011908437150466</v>
+        <v>0.8232822809105453</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2167085974607244</v>
+        <v>0.2216626709524201</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>51.75</v>
+        <v>91.27</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.005440038326329999</v>
+        <v>0.009958989367391702</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.02171763950607319</v>
+        <v>-0.005231644217259857</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.008968591855364805</v>
+        <v>-0.01595690950871798</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.00661350230688651</v>
+        <v>-0.03223413205623959</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.02524016102347992</v>
+        <v>-0.01116170268164718</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1076859765283402</v>
+        <v>0.03536888801109961</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.08928595230474801</v>
+        <v>0.1081926717746482</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1140471861339971</v>
+        <v>0.1360482135807766</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8332666092738401</v>
+        <v>0.2308393289418125</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2238885621971691</v>
+        <v>0.07168492475618127</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>90.37</v>
+        <v>52.16</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.004222745769899561</v>
+        <v>0.00792270236545134</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02122819284742417</v>
+        <v>0.02859398124863</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.01579173331585104</v>
+        <v>0.01360281335781588</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.0417770640865921</v>
+        <v>0.01458860148270857</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.0349648121986551</v>
+        <v>-0.03603771467277361</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.03400192519398382</v>
+        <v>0.1145791701639667</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1001800137631905</v>
+        <v>0.09314941585545133</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1120298296830771</v>
+        <v>0.1085647364616957</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2194228232539699</v>
+        <v>0.824473027058005</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.06836119796423956</v>
+        <v>0.2219285602177072</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>111.82</v>
+        <v>112.05</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.01673028079403704</v>
+        <v>0.002056907150431941</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.01765564697760214</v>
+        <v>0.02244736559970706</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.006752498442970101</v>
+        <v>0.01182955764185434</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.04181660137988097</v>
+        <v>-0.0398457070958339</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.08941370589629172</v>
+        <v>-0.07861193578334702</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2024949162665932</v>
+        <v>0.1976272549770466</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06495237804594489</v>
+        <v>0.05300252979557718</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.08674651554929613</v>
+        <v>0.09098130850146657</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.03636985505147594</v>
+        <v>0.02685842647105297</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.01197921052095485</v>
+        <v>0.008873831023735512</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>16.36</v>
+        <v>16.38</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.00863139968703952</v>
+        <v>0.001222405236487978</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.00304687614414767</v>
+        <v>0.0024479196943199</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.03821279305020919</v>
+        <v>-0.01562501432804009</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.08347337474933325</v>
+        <v>-0.08235300780324628</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.02386632536203492</v>
+        <v>-0.03533571246437761</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.115833663438466</v>
+        <v>0.1067843573140947</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.01303270909048826</v>
+        <v>0.009344369730753366</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.08584913823360729</v>
+        <v>0.08785170987427215</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.9094211944178268</v>
+        <v>0.8985969062762222</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2406061020675132</v>
+        <v>0.2382573740191605</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>35.71</v>
+        <v>35.65</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.001398189021458607</v>
+        <v>-0.001680133299690745</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.008055580986870647</v>
+        <v>-0.00028037918048196</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.03355890806125528</v>
+        <v>-0.01925713831158871</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.07463076073406283</v>
+        <v>-0.07618550440746308</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.06125136106670326</v>
+        <v>-0.07354464786963333</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.08329517390573282</v>
+        <v>0.06973366642914991</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.04217698889428845</v>
+        <v>0.03130201101725905</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1450751184901662</v>
+        <v>0.1375036210980387</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>1.163935191713342</v>
+        <v>1.15161963157556</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2934453482906572</v>
+        <v>0.2909868920947509</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>113.57</v>
+        <v>113.4</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.008641741313438644</v>
+        <v>-0.001496858055843209</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.00754079546589792</v>
+        <v>0.0007943162053163366</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.002897294351481672</v>
+        <v>-0.008394535496231481</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.04474724301569322</v>
+        <v>-0.04617712080035163</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.08925419026303238</v>
+        <v>-0.08703001077427019</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.06715725626360936</v>
+        <v>0.06026783246279299</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.08145669922306653</v>
+        <v>0.05676886166153761</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1578238381624713</v>
+        <v>0.1398543437627997</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4688321391590173</v>
+        <v>0.4563835441088229</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.136730175522453</v>
+        <v>0.1335097350461132</v>
       </c>
     </row>
     <row r="21">
@@ -1656,46 +1656,52 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>67.55</v>
+        <v>92.2</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.002215567256214968</v>
+        <v>0.005233272145124257</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.005956835693067708</v>
+        <v>0.006330432048385681</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.001482670245224194</v>
+        <v>-0.002919912067660735</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.032234955610698</v>
+        <v>-0.05668100098844919</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.08925435190261699</v>
+        <v>-0.03787962864919991</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.04566570661481517</v>
+        <v>0.08345756429378071</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.06646673332851116</v>
-      </c>
-      <c r="N21" s="6" t="inlineStr"/>
-      <c r="O21" s="6" t="inlineStr"/>
-      <c r="P21" s="6" t="inlineStr"/>
+        <v>0.04362371044680047</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>0.0164781005121486</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>0.4884703585044621</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0.1417737746634484</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1706,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>91.72</v>
+        <v>98.03</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.005591515638084132</v>
+        <v>0.008124238306073561</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.0001090388734812375</v>
+        <v>0.0171197507045</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.02311213316702354</v>
+        <v>-0.01901332452793458</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.06159194571967463</v>
+        <v>-0.04834485247702014</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.04686690199419508</v>
+        <v>-0.02680437295399796</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.0833135763874715</v>
+        <v>-0.02908948548041979</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.02984010993025876</v>
+        <v>0.047701658907356</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.008955777042695123</v>
+        <v>0.09488333077982447</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.4894853833875612</v>
+        <v>0.2691599474911621</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1420332503171367</v>
+        <v>0.08269330855128487</v>
       </c>
     </row>
     <row r="23">
@@ -1762,52 +1768,46 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>97.23999999999999</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.01018071582994717</v>
+        <v>0.009326383789135528</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.003094650451908265</v>
+        <v>0.01397981069706056</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.0078563846105284</v>
+        <v>0.00783442375968213</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.05601401953987073</v>
+        <v>-0.02320920738901366</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.04074188389969002</v>
+        <v>-0.09214378574627924</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.03866847708029619</v>
+        <v>0.04715097014353486</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.05823591658782412</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0.08605992116559968</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>0.2710849693643718</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>0.08324043040624307</v>
-      </c>
+        <v>0.06398249620732899</v>
+      </c>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1832,37 +1832,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>13.34</v>
+        <v>13.48</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.006033176645940497</v>
+        <v>0.01049470675015529</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.003762241601082073</v>
+        <v>0.01659119981576684</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.01754389793545874</v>
+        <v>0.007473798724970226</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.04097769238511273</v>
+        <v>-0.03091303449983729</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.09128066244763233</v>
+        <v>-0.07098557342509992</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>-0.03471378837258299</v>
+        <v>-0.02249915197945807</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1087001390234121</v>
+        <v>0.09880803911080127</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.08002964907539667</v>
+        <v>0.09222215001599143</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1050774454611099</v>
+        <v>0.1081385773357393</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.03386596459717461</v>
+        <v>0.03481970840654158</v>
       </c>
     </row>
     <row r="25">
@@ -1888,37 +1888,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>38.89</v>
+        <v>39.3</v>
       </c>
       <c r="G25" s="6" t="n">
-  